--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -2903,7 +2903,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="55" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2942,6 +2941,7 @@
     <xf numFmtId="2" fontId="7" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4249,8 +4249,8 @@
         <v>21</v>
       </c>
       <c r="B4" s="271"/>
-      <c r="C4" s="59">
-        <v>25823.91</v>
+      <c r="C4" s="394">
+        <v>27000</v>
       </c>
       <c r="D4" s="421">
         <v>17814</v>
@@ -4339,10 +4339,10 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="438" t="s">
+      <c r="K7" s="458" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="439">
+      <c r="L7" s="438">
         <v>13800</v>
       </c>
       <c r="M7" s="248"/>
@@ -4360,7 +4360,7 @@
       <c r="I8" s="291"/>
       <c r="J8" s="297"/>
       <c r="K8" s="271"/>
-      <c r="L8" s="440">
+      <c r="L8" s="439">
         <v>130000</v>
       </c>
       <c r="M8" s="248"/>
@@ -4380,7 +4380,7 @@
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
       <c r="K9" s="271"/>
-      <c r="L9" s="441">
+      <c r="L9" s="440">
         <f>SUM(L2:L8)</f>
         <v>749855.02</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="H10" s="292"/>
       <c r="I10" s="292"/>
       <c r="J10" s="293"/>
-      <c r="K10" s="442">
+      <c r="K10" s="441">
         <v>69853</v>
       </c>
       <c r="L10" s="271"/>
@@ -4430,7 +4430,7 @@
         <v>255458</v>
       </c>
       <c r="J11" s="271"/>
-      <c r="K11" s="443">
+      <c r="K11" s="442">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
@@ -4440,10 +4440,10 @@
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="273"/>
       <c r="B12" s="412"/>
-      <c r="C12" s="453"/>
+      <c r="C12" s="452"/>
       <c r="D12" s="422"/>
       <c r="E12" s="292"/>
-      <c r="F12" s="456">
+      <c r="F12" s="455">
         <v>4022.77</v>
       </c>
       <c r="G12" s="394"/>
@@ -4461,9 +4461,9 @@
       <c r="A13" s="270"/>
       <c r="B13" s="308"/>
       <c r="C13" s="273"/>
-      <c r="D13" s="452"/>
+      <c r="D13" s="451"/>
       <c r="E13" s="277"/>
-      <c r="F13" s="458">
+      <c r="F13" s="457">
         <f>SUM(F11:F12)</f>
         <v>301589.77</v>
       </c>
@@ -4481,10 +4481,10 @@
     <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="454"/>
+      <c r="C14" s="453"/>
       <c r="D14" s="305"/>
       <c r="E14" s="331"/>
-      <c r="F14" s="457"/>
+      <c r="F14" s="456"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
       <c r="I14" s="428">
@@ -4505,13 +4505,13 @@
       <c r="F15" s="358"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="455">
+      <c r="I15" s="454">
         <f>SUM(I11:I14)</f>
         <v>372360</v>
       </c>
       <c r="J15" s="401"/>
-      <c r="K15" s="444"/>
-      <c r="L15" s="445"/>
+      <c r="K15" s="443"/>
+      <c r="L15" s="444"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
@@ -4526,7 +4526,7 @@
       <c r="H16" s="400"/>
       <c r="I16" s="429"/>
       <c r="J16" s="282"/>
-      <c r="K16" s="446"/>
+      <c r="K16" s="445"/>
       <c r="L16" s="271"/>
       <c r="M16" s="248"/>
       <c r="N16" s="51"/>
@@ -4542,7 +4542,7 @@
       <c r="H17" s="397"/>
       <c r="I17" s="111"/>
       <c r="J17" s="430"/>
-      <c r="K17" s="444"/>
+      <c r="K17" s="443"/>
       <c r="L17" s="271"/>
       <c r="M17" s="248"/>
       <c r="N17" s="51"/>
@@ -4558,7 +4558,7 @@
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="446"/>
+      <c r="K18" s="445"/>
       <c r="L18" s="271"/>
       <c r="M18" s="248"/>
       <c r="N18" s="51"/>
@@ -4574,7 +4574,7 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="444"/>
+      <c r="K19" s="443"/>
       <c r="L19" s="271"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
@@ -4590,7 +4590,7 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="444"/>
+      <c r="K20" s="443"/>
       <c r="L20" s="271"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
@@ -4601,7 +4601,7 @@
       <c r="C21" s="402" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="451" t="s">
+      <c r="D21" s="450" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="447"/>
+      <c r="K22" s="446"/>
       <c r="L22" s="271"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
@@ -4656,8 +4656,8 @@
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="448"/>
-      <c r="L23" s="445"/>
+      <c r="K23" s="447"/>
+      <c r="L23" s="444"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4672,8 +4672,8 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="448"/>
-      <c r="L24" s="445"/>
+      <c r="K24" s="447"/>
+      <c r="L24" s="444"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4688,8 +4688,8 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="448"/>
-      <c r="L25" s="445"/>
+      <c r="K25" s="447"/>
+      <c r="L25" s="444"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4704,8 +4704,8 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="448"/>
-      <c r="L26" s="445"/>
+      <c r="K26" s="447"/>
+      <c r="L26" s="444"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
@@ -4720,8 +4720,8 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="448"/>
-      <c r="L27" s="445"/>
+      <c r="K27" s="447"/>
+      <c r="L27" s="444"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
@@ -4736,8 +4736,8 @@
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="449"/>
-      <c r="L28" s="450"/>
+      <c r="K28" s="448"/>
+      <c r="L28" s="449"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -93,6 +93,30 @@
           </rPr>
           <t xml:space="preserve">
 Cel Lais Movistar deuda</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Edgardo Omar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+2 Patentes Vencidas</t>
         </r>
       </text>
     </comment>
@@ -893,7 +917,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="57" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1329,6 +1353,12 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="40">
     <fill>
@@ -1566,7 +1596,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -2128,17 +2158,6 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -2150,7 +2169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="459">
+  <cellXfs count="460">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2889,7 +2908,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2909,7 +2928,6 @@
     <xf numFmtId="2" fontId="55" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="45" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2942,6 +2960,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4339,7 +4359,7 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="458" t="s">
+      <c r="K7" s="457" t="s">
         <v>186</v>
       </c>
       <c r="L7" s="438">
@@ -4366,7 +4386,7 @@
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="291"/>
       <c r="B9" s="411"/>
       <c r="C9" s="417">
@@ -4379,8 +4399,8 @@
       <c r="H9" s="292"/>
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
-      <c r="K9" s="271"/>
-      <c r="L9" s="440">
+      <c r="K9" s="288"/>
+      <c r="L9" s="459">
         <f>SUM(L2:L8)</f>
         <v>749855.02</v>
       </c>
@@ -4398,10 +4418,10 @@
       <c r="H10" s="292"/>
       <c r="I10" s="292"/>
       <c r="J10" s="293"/>
-      <c r="K10" s="441">
+      <c r="K10" s="440">
         <v>69853</v>
       </c>
-      <c r="L10" s="271"/>
+      <c r="L10" s="458"/>
       <c r="M10" s="51"/>
       <c r="N10" s="51"/>
     </row>
@@ -4430,7 +4450,7 @@
         <v>255458</v>
       </c>
       <c r="J11" s="271"/>
-      <c r="K11" s="442">
+      <c r="K11" s="441">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
@@ -4440,10 +4460,10 @@
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="273"/>
       <c r="B12" s="412"/>
-      <c r="C12" s="452"/>
+      <c r="C12" s="451"/>
       <c r="D12" s="422"/>
       <c r="E12" s="292"/>
-      <c r="F12" s="455">
+      <c r="F12" s="454">
         <v>4022.77</v>
       </c>
       <c r="G12" s="394"/>
@@ -4461,9 +4481,9 @@
       <c r="A13" s="270"/>
       <c r="B13" s="308"/>
       <c r="C13" s="273"/>
-      <c r="D13" s="451"/>
+      <c r="D13" s="450"/>
       <c r="E13" s="277"/>
-      <c r="F13" s="457">
+      <c r="F13" s="456">
         <f>SUM(F11:F12)</f>
         <v>301589.77</v>
       </c>
@@ -4481,10 +4501,10 @@
     <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="453"/>
+      <c r="C14" s="452"/>
       <c r="D14" s="305"/>
       <c r="E14" s="331"/>
-      <c r="F14" s="456"/>
+      <c r="F14" s="455"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
       <c r="I14" s="428">
@@ -4505,13 +4525,13 @@
       <c r="F15" s="358"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="454">
+      <c r="I15" s="453">
         <f>SUM(I11:I14)</f>
         <v>372360</v>
       </c>
       <c r="J15" s="401"/>
-      <c r="K15" s="443"/>
-      <c r="L15" s="444"/>
+      <c r="K15" s="442"/>
+      <c r="L15" s="443"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
@@ -4526,7 +4546,7 @@
       <c r="H16" s="400"/>
       <c r="I16" s="429"/>
       <c r="J16" s="282"/>
-      <c r="K16" s="445"/>
+      <c r="K16" s="444"/>
       <c r="L16" s="271"/>
       <c r="M16" s="248"/>
       <c r="N16" s="51"/>
@@ -4542,7 +4562,7 @@
       <c r="H17" s="397"/>
       <c r="I17" s="111"/>
       <c r="J17" s="430"/>
-      <c r="K17" s="443"/>
+      <c r="K17" s="442"/>
       <c r="L17" s="271"/>
       <c r="M17" s="248"/>
       <c r="N17" s="51"/>
@@ -4558,7 +4578,7 @@
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="445"/>
+      <c r="K18" s="444"/>
       <c r="L18" s="271"/>
       <c r="M18" s="248"/>
       <c r="N18" s="51"/>
@@ -4574,7 +4594,7 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="443"/>
+      <c r="K19" s="442"/>
       <c r="L19" s="271"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
@@ -4590,7 +4610,7 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="443"/>
+      <c r="K20" s="442"/>
       <c r="L20" s="271"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
@@ -4601,7 +4621,7 @@
       <c r="C21" s="402" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="450" t="s">
+      <c r="D21" s="449" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4631,16 +4651,20 @@
       <c r="A22" s="291"/>
       <c r="B22" s="309"/>
       <c r="C22" s="310"/>
-      <c r="D22" s="409"/>
+      <c r="D22" s="409">
+        <v>7500</v>
+      </c>
       <c r="E22" s="284"/>
       <c r="F22" s="284"/>
-      <c r="G22" s="284"/>
+      <c r="G22" s="394">
+        <v>33000</v>
+      </c>
       <c r="H22" s="284">
         <v>59159</v>
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="446"/>
+      <c r="K22" s="445"/>
       <c r="L22" s="271"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
@@ -4656,8 +4680,8 @@
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="447"/>
-      <c r="L23" s="444"/>
+      <c r="K23" s="446"/>
+      <c r="L23" s="443"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4672,8 +4696,8 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="447"/>
-      <c r="L24" s="444"/>
+      <c r="K24" s="446"/>
+      <c r="L24" s="443"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4688,8 +4712,8 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="447"/>
-      <c r="L25" s="444"/>
+      <c r="K25" s="446"/>
+      <c r="L25" s="443"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4704,8 +4728,8 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="447"/>
-      <c r="L26" s="444"/>
+      <c r="K26" s="446"/>
+      <c r="L26" s="443"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
@@ -4720,8 +4744,8 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="447"/>
-      <c r="L27" s="444"/>
+      <c r="K27" s="446"/>
+      <c r="L27" s="443"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
@@ -4736,8 +4760,8 @@
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="448"/>
-      <c r="L28" s="449"/>
+      <c r="K28" s="447"/>
+      <c r="L28" s="448"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -72,30 +72,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Edgardo Omar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Cel Lais Movistar deuda</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="K4" authorId="0">
       <text>
         <r>
@@ -117,6 +93,30 @@
           </rPr>
           <t xml:space="preserve">
 2 Patentes Vencidas</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Edgardo Omar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Cel Lais Movistar deuda</t>
         </r>
       </text>
     </comment>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="210">
   <si>
     <t>Servicios</t>
   </si>
@@ -911,13 +911,25 @@
   </si>
   <si>
     <t>Gasto mens prest</t>
+  </si>
+  <si>
+    <t>Faltan seguros</t>
+  </si>
+  <si>
+    <t>Falta  Youtube</t>
+  </si>
+  <si>
+    <t>Faltan Intereses</t>
+  </si>
+  <si>
+    <t>Relacionar conpagos realizados</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1358,6 +1370,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -2169,7 +2188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="460">
+  <cellXfs count="463">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2867,12 +2886,6 @@
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2887,7 +2900,6 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2922,16 +2934,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="55" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="55" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2962,6 +2968,26 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="55" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4238,7 +4264,7 @@
       <c r="I2" s="270"/>
       <c r="J2" s="395"/>
       <c r="K2" s="331"/>
-      <c r="L2" s="423">
+      <c r="L2" s="420">
         <v>102247</v>
       </c>
       <c r="M2" s="112">
@@ -4258,7 +4284,7 @@
       <c r="I3" s="198"/>
       <c r="J3" s="288"/>
       <c r="K3" s="331"/>
-      <c r="L3" s="424">
+      <c r="L3" s="421">
         <v>67275.839999999997</v>
       </c>
       <c r="M3" s="101"/>
@@ -4269,28 +4295,28 @@
         <v>21</v>
       </c>
       <c r="B4" s="271"/>
-      <c r="C4" s="394">
+      <c r="C4" s="150">
         <v>27000</v>
       </c>
-      <c r="D4" s="421">
-        <v>17814</v>
-      </c>
-      <c r="E4" s="289">
+      <c r="D4" s="458">
+        <v>17825</v>
+      </c>
+      <c r="E4" s="150">
         <v>9444.76</v>
       </c>
-      <c r="F4" s="289">
-        <v>20000</v>
+      <c r="F4" s="459">
+        <v>23800</v>
       </c>
       <c r="G4" s="271"/>
       <c r="H4" s="271"/>
-      <c r="I4" s="58">
+      <c r="I4" s="394">
         <v>21158.21</v>
       </c>
       <c r="J4" s="178">
         <v>5581</v>
       </c>
       <c r="K4" s="331"/>
-      <c r="L4" s="423">
+      <c r="L4" s="420">
         <v>236679.18</v>
       </c>
       <c r="M4" s="101"/>
@@ -4302,13 +4328,15 @@
       <c r="C5" s="289"/>
       <c r="D5" s="289"/>
       <c r="E5" s="289"/>
-      <c r="F5" s="290"/>
+      <c r="F5" s="289">
+        <v>20000</v>
+      </c>
       <c r="G5" s="271"/>
       <c r="H5" s="271"/>
       <c r="I5" s="289"/>
       <c r="J5" s="271"/>
       <c r="K5" s="288"/>
-      <c r="L5" s="424">
+      <c r="L5" s="421">
         <v>130000</v>
       </c>
       <c r="M5" s="101"/>
@@ -4326,7 +4354,7 @@
       <c r="I6" s="271"/>
       <c r="J6" s="271"/>
       <c r="K6" s="288"/>
-      <c r="L6" s="423">
+      <c r="L6" s="420">
         <v>69853</v>
       </c>
       <c r="M6" s="101"/>
@@ -4359,10 +4387,10 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="457" t="s">
+      <c r="K7" s="452" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="438">
+      <c r="L7" s="462">
         <v>13800</v>
       </c>
       <c r="M7" s="248"/>
@@ -4380,19 +4408,21 @@
       <c r="I8" s="291"/>
       <c r="J8" s="297"/>
       <c r="K8" s="271"/>
-      <c r="L8" s="439">
+      <c r="L8" s="435">
         <v>130000</v>
       </c>
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="291"/>
-      <c r="B9" s="411"/>
-      <c r="C9" s="417">
+      <c r="B9" s="455">
+        <v>1</v>
+      </c>
+      <c r="C9" s="415">
         <v>150000</v>
       </c>
-      <c r="D9" s="416"/>
+      <c r="D9" s="414"/>
       <c r="E9" s="292"/>
       <c r="F9" s="292"/>
       <c r="G9" s="289"/>
@@ -4400,44 +4430,50 @@
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
       <c r="K9" s="288"/>
-      <c r="L9" s="459">
+      <c r="L9" s="454">
         <f>SUM(L2:L8)</f>
         <v>749855.02</v>
       </c>
       <c r="M9" s="248"/>
       <c r="N9" s="51"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="291"/>
-      <c r="B10" s="411"/>
-      <c r="C10" s="418"/>
-      <c r="D10" s="413"/>
+      <c r="B10" s="455">
+        <v>2</v>
+      </c>
+      <c r="C10" s="416" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="411"/>
       <c r="E10" s="295"/>
       <c r="F10" s="292"/>
       <c r="G10" s="292"/>
       <c r="H10" s="292"/>
       <c r="I10" s="292"/>
       <c r="J10" s="293"/>
-      <c r="K10" s="440">
+      <c r="K10" s="436">
         <v>69853</v>
       </c>
-      <c r="L10" s="458"/>
+      <c r="L10" s="453"/>
       <c r="M10" s="51"/>
       <c r="N10" s="51"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="291" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="288"/>
+      <c r="B11" s="455">
+        <v>3</v>
+      </c>
       <c r="C11" s="198"/>
-      <c r="D11" s="414">
-        <v>91000</v>
+      <c r="D11" s="412">
+        <v>192750</v>
       </c>
       <c r="E11" s="375">
-        <v>5307</v>
-      </c>
-      <c r="F11" s="425">
+        <v>592</v>
+      </c>
+      <c r="F11" s="422">
         <v>297567</v>
       </c>
       <c r="G11" s="150">
@@ -4446,29 +4482,33 @@
       <c r="H11" s="292">
         <v>1000000</v>
       </c>
-      <c r="I11" s="425">
+      <c r="I11" s="422">
         <v>255458</v>
       </c>
       <c r="J11" s="271"/>
-      <c r="K11" s="441">
+      <c r="K11" s="461">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
       <c r="M11" s="51"/>
       <c r="N11" s="51"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="273"/>
-      <c r="B12" s="412"/>
-      <c r="C12" s="451"/>
-      <c r="D12" s="422"/>
+      <c r="B12" s="456">
+        <v>4</v>
+      </c>
+      <c r="C12" s="446"/>
+      <c r="D12" s="419" t="s">
+        <v>206</v>
+      </c>
       <c r="E12" s="292"/>
-      <c r="F12" s="454">
+      <c r="F12" s="449">
         <v>4022.77</v>
       </c>
       <c r="G12" s="394"/>
       <c r="H12" s="304"/>
-      <c r="I12" s="426">
+      <c r="I12" s="423">
         <v>90764</v>
       </c>
       <c r="J12" s="288"/>
@@ -4477,19 +4517,23 @@
       <c r="M12" s="248"/>
       <c r="N12" s="51"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="270"/>
-      <c r="B13" s="308"/>
+      <c r="B13" s="457">
+        <v>5</v>
+      </c>
       <c r="C13" s="273"/>
-      <c r="D13" s="450"/>
+      <c r="D13" s="445" t="s">
+        <v>207</v>
+      </c>
       <c r="E13" s="277"/>
-      <c r="F13" s="456">
+      <c r="F13" s="451">
         <f>SUM(F11:F12)</f>
         <v>301589.77</v>
       </c>
       <c r="G13" s="305"/>
       <c r="H13" s="328"/>
-      <c r="I13" s="427">
+      <c r="I13" s="424">
         <v>-20000</v>
       </c>
       <c r="J13" s="306"/>
@@ -4501,13 +4545,15 @@
     <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="452"/>
-      <c r="D14" s="305"/>
+      <c r="C14" s="447"/>
+      <c r="D14" s="460" t="s">
+        <v>208</v>
+      </c>
       <c r="E14" s="331"/>
-      <c r="F14" s="455"/>
+      <c r="F14" s="450"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
-      <c r="I14" s="428">
+      <c r="I14" s="425">
         <v>46138</v>
       </c>
       <c r="J14" s="330"/>
@@ -4519,34 +4565,34 @@
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="270"/>
       <c r="B15" s="308"/>
-      <c r="C15" s="419"/>
+      <c r="C15" s="417"/>
       <c r="D15" s="305"/>
       <c r="E15" s="398"/>
       <c r="F15" s="358"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="453">
+      <c r="I15" s="448">
         <f>SUM(I11:I14)</f>
         <v>372360</v>
       </c>
       <c r="J15" s="401"/>
-      <c r="K15" s="442"/>
-      <c r="L15" s="443"/>
+      <c r="K15" s="437"/>
+      <c r="L15" s="438"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="271"/>
       <c r="B16" s="288"/>
-      <c r="C16" s="420"/>
+      <c r="C16" s="418"/>
       <c r="D16" s="305"/>
       <c r="E16" s="398"/>
       <c r="F16" s="358"/>
       <c r="G16" s="394"/>
       <c r="H16" s="400"/>
-      <c r="I16" s="429"/>
+      <c r="I16" s="426"/>
       <c r="J16" s="282"/>
-      <c r="K16" s="444"/>
+      <c r="K16" s="439"/>
       <c r="L16" s="271"/>
       <c r="M16" s="248"/>
       <c r="N16" s="51"/>
@@ -4561,8 +4607,8 @@
       <c r="G17" s="304"/>
       <c r="H17" s="397"/>
       <c r="I17" s="111"/>
-      <c r="J17" s="430"/>
-      <c r="K17" s="442"/>
+      <c r="J17" s="427"/>
+      <c r="K17" s="437"/>
       <c r="L17" s="271"/>
       <c r="M17" s="248"/>
       <c r="N17" s="51"/>
@@ -4573,12 +4619,12 @@
       <c r="C18" s="404"/>
       <c r="D18" s="304"/>
       <c r="E18" s="282"/>
-      <c r="F18" s="415"/>
+      <c r="F18" s="413"/>
       <c r="G18" s="304"/>
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="444"/>
+      <c r="K18" s="439"/>
       <c r="L18" s="271"/>
       <c r="M18" s="248"/>
       <c r="N18" s="51"/>
@@ -4594,7 +4640,7 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="442"/>
+      <c r="K19" s="437"/>
       <c r="L19" s="271"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
@@ -4610,7 +4656,7 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="442"/>
+      <c r="K20" s="437"/>
       <c r="L20" s="271"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
@@ -4621,7 +4667,7 @@
       <c r="C21" s="402" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="449" t="s">
+      <c r="D21" s="444" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4664,7 +4710,7 @@
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="445"/>
+      <c r="K22" s="440"/>
       <c r="L22" s="271"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
@@ -4680,8 +4726,8 @@
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="446"/>
-      <c r="L23" s="443"/>
+      <c r="K23" s="441"/>
+      <c r="L23" s="438"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4696,8 +4742,8 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="446"/>
-      <c r="L24" s="443"/>
+      <c r="K24" s="441"/>
+      <c r="L24" s="438"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4712,8 +4758,8 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="446"/>
-      <c r="L25" s="443"/>
+      <c r="K25" s="441"/>
+      <c r="L25" s="438"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4728,8 +4774,8 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="446"/>
-      <c r="L26" s="443"/>
+      <c r="K26" s="441"/>
+      <c r="L26" s="438"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
@@ -4744,39 +4790,39 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="446"/>
-      <c r="L27" s="443"/>
+      <c r="K27" s="441"/>
+      <c r="L27" s="438"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="277"/>
       <c r="B28" s="273"/>
-      <c r="C28" s="431"/>
+      <c r="C28" s="428"/>
       <c r="D28" s="350"/>
       <c r="E28" s="315"/>
-      <c r="F28" s="432"/>
+      <c r="F28" s="429"/>
       <c r="G28" s="379"/>
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="447"/>
-      <c r="L28" s="448"/>
+      <c r="K28" s="442"/>
+      <c r="L28" s="443"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="433"/>
+      <c r="A29" s="430"/>
       <c r="B29" s="271"/>
-      <c r="C29" s="434"/>
-      <c r="D29" s="435"/>
-      <c r="E29" s="436"/>
-      <c r="F29" s="436"/>
-      <c r="G29" s="437"/>
+      <c r="C29" s="431"/>
+      <c r="D29" s="432"/>
+      <c r="E29" s="433"/>
+      <c r="F29" s="433"/>
+      <c r="G29" s="434"/>
       <c r="H29" s="198"/>
-      <c r="I29" s="435"/>
-      <c r="J29" s="435"/>
-      <c r="K29" s="435"/>
+      <c r="I29" s="432"/>
+      <c r="J29" s="432"/>
+      <c r="K29" s="432"/>
       <c r="L29" s="271"/>
       <c r="M29" s="248"/>
       <c r="N29" s="51"/>

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -120,31 +120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Edgardo Omar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ref tarjeta</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L6" authorId="0">
+    <comment ref="M6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -168,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0">
+    <comment ref="M7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -293,7 +269,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="209">
   <si>
     <t>Servicios</t>
   </si>
@@ -920,9 +896,6 @@
   </si>
   <si>
     <t>Faltan Intereses</t>
-  </si>
-  <si>
-    <t>Relacionar conpagos realizados</t>
   </si>
 </sst>
 </file>
@@ -2188,7 +2161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="463">
+  <cellXfs count="469">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2934,10 +2907,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="55" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2962,12 +2931,8 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="46" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2988,6 +2953,20 @@
     <xf numFmtId="2" fontId="55" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="55" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="55" fillId="35" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="55" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="51" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4298,13 +4277,13 @@
       <c r="C4" s="150">
         <v>27000</v>
       </c>
-      <c r="D4" s="458">
+      <c r="D4" s="454">
         <v>17825</v>
       </c>
       <c r="E4" s="150">
         <v>9444.76</v>
       </c>
-      <c r="F4" s="459">
+      <c r="F4" s="455">
         <v>23800</v>
       </c>
       <c r="G4" s="271"/>
@@ -4322,7 +4301,7 @@
       <c r="M4" s="101"/>
       <c r="N4" s="50"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="291"/>
       <c r="B5" s="302"/>
       <c r="C5" s="289"/>
@@ -4336,13 +4315,13 @@
       <c r="I5" s="289"/>
       <c r="J5" s="271"/>
       <c r="K5" s="288"/>
-      <c r="L5" s="421">
+      <c r="L5" s="464">
         <v>130000</v>
       </c>
       <c r="M5" s="101"/>
       <c r="N5" s="50"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="271"/>
       <c r="B6" s="271"/>
       <c r="C6" s="271"/>
@@ -4354,13 +4333,16 @@
       <c r="I6" s="271"/>
       <c r="J6" s="271"/>
       <c r="K6" s="288"/>
-      <c r="L6" s="420">
+      <c r="L6" s="465">
+        <f>SUM(L2:L5)</f>
+        <v>536202.02</v>
+      </c>
+      <c r="M6" s="462">
         <v>69853</v>
       </c>
-      <c r="M6" s="101"/>
       <c r="N6" s="50"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="291"/>
       <c r="B7" s="357"/>
       <c r="C7" s="262" t="s">
@@ -4387,16 +4369,16 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="452" t="s">
+      <c r="K7" s="449" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="462">
+      <c r="L7" s="450"/>
+      <c r="M7" s="458">
         <v>13800</v>
       </c>
-      <c r="M7" s="248"/>
       <c r="N7" s="51"/>
     </row>
-    <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="300"/>
       <c r="B8" s="294"/>
       <c r="C8" s="290"/>
@@ -4408,19 +4390,17 @@
       <c r="I8" s="291"/>
       <c r="J8" s="297"/>
       <c r="K8" s="271"/>
-      <c r="L8" s="435">
-        <v>130000</v>
-      </c>
+      <c r="L8" s="463"/>
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
-    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="291"/>
-      <c r="B9" s="455">
+      <c r="B9" s="451">
         <v>1</v>
       </c>
       <c r="C9" s="415">
-        <v>150000</v>
+        <v>136200</v>
       </c>
       <c r="D9" s="414"/>
       <c r="E9" s="292"/>
@@ -4430,20 +4410,17 @@
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
       <c r="K9" s="288"/>
-      <c r="L9" s="454">
-        <f>SUM(L2:L8)</f>
-        <v>749855.02</v>
-      </c>
+      <c r="L9" s="461"/>
       <c r="M9" s="248"/>
       <c r="N9" s="51"/>
     </row>
     <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="291"/>
-      <c r="B10" s="455">
+      <c r="B10" s="451">
         <v>2</v>
       </c>
-      <c r="C10" s="416" t="s">
-        <v>209</v>
+      <c r="C10" s="416">
+        <v>50000</v>
       </c>
       <c r="D10" s="411"/>
       <c r="E10" s="295"/>
@@ -4451,11 +4428,13 @@
       <c r="G10" s="292"/>
       <c r="H10" s="292"/>
       <c r="I10" s="292"/>
-      <c r="J10" s="293"/>
-      <c r="K10" s="436">
+      <c r="J10" s="293">
+        <v>55747</v>
+      </c>
+      <c r="K10" s="459">
         <v>69853</v>
       </c>
-      <c r="L10" s="453"/>
+      <c r="L10" s="450"/>
       <c r="M10" s="51"/>
       <c r="N10" s="51"/>
     </row>
@@ -4463,7 +4442,7 @@
       <c r="A11" s="291" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="455">
+      <c r="B11" s="451">
         <v>3</v>
       </c>
       <c r="C11" s="198"/>
@@ -4483,10 +4462,10 @@
         <v>1000000</v>
       </c>
       <c r="I11" s="422">
-        <v>255458</v>
+        <v>342328</v>
       </c>
       <c r="J11" s="271"/>
-      <c r="K11" s="461">
+      <c r="K11" s="457">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
@@ -4495,22 +4474,20 @@
     </row>
     <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="273"/>
-      <c r="B12" s="456">
+      <c r="B12" s="452">
         <v>4</v>
       </c>
-      <c r="C12" s="446"/>
+      <c r="C12" s="444"/>
       <c r="D12" s="419" t="s">
         <v>206</v>
       </c>
       <c r="E12" s="292"/>
-      <c r="F12" s="449">
+      <c r="F12" s="447">
         <v>4022.77</v>
       </c>
       <c r="G12" s="394"/>
       <c r="H12" s="304"/>
-      <c r="I12" s="423">
-        <v>90764</v>
-      </c>
+      <c r="I12" s="423"/>
       <c r="J12" s="288"/>
       <c r="K12" s="271"/>
       <c r="L12" s="271"/>
@@ -4519,23 +4496,21 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="270"/>
-      <c r="B13" s="457">
+      <c r="B13" s="453">
         <v>5</v>
       </c>
       <c r="C13" s="273"/>
-      <c r="D13" s="445" t="s">
+      <c r="D13" s="443" t="s">
         <v>207</v>
       </c>
       <c r="E13" s="277"/>
-      <c r="F13" s="451">
+      <c r="F13" s="446">
         <f>SUM(F11:F12)</f>
         <v>301589.77</v>
       </c>
       <c r="G13" s="305"/>
       <c r="H13" s="328"/>
-      <c r="I13" s="424">
-        <v>-20000</v>
-      </c>
+      <c r="I13" s="424"/>
       <c r="J13" s="306"/>
       <c r="K13" s="271"/>
       <c r="L13" s="271"/>
@@ -4545,17 +4520,15 @@
     <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="447"/>
-      <c r="D14" s="460" t="s">
+      <c r="C14" s="445"/>
+      <c r="D14" s="456" t="s">
         <v>208</v>
       </c>
       <c r="E14" s="331"/>
-      <c r="F14" s="450"/>
+      <c r="F14" s="448"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
-      <c r="I14" s="425">
-        <v>46138</v>
-      </c>
+      <c r="I14" s="425"/>
       <c r="J14" s="330"/>
       <c r="K14" s="271"/>
       <c r="L14" s="271"/>
@@ -4571,17 +4544,14 @@
       <c r="F15" s="358"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="448">
-        <f>SUM(I11:I14)</f>
-        <v>372360</v>
-      </c>
+      <c r="I15" s="446"/>
       <c r="J15" s="401"/>
-      <c r="K15" s="437"/>
-      <c r="L15" s="438"/>
+      <c r="K15" s="435"/>
+      <c r="L15" s="441"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="271"/>
       <c r="B16" s="288"/>
       <c r="C16" s="418"/>
@@ -4592,12 +4562,12 @@
       <c r="H16" s="400"/>
       <c r="I16" s="426"/>
       <c r="J16" s="282"/>
-      <c r="K16" s="439"/>
-      <c r="L16" s="271"/>
-      <c r="M16" s="248"/>
+      <c r="K16" s="437"/>
+      <c r="L16" s="468"/>
+      <c r="M16" s="466"/>
       <c r="N16" s="51"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="271"/>
       <c r="B17" s="288"/>
       <c r="C17" s="271"/>
@@ -4606,12 +4576,12 @@
       <c r="F17" s="358"/>
       <c r="G17" s="304"/>
       <c r="H17" s="397"/>
-      <c r="I17" s="111"/>
+      <c r="I17" s="460"/>
       <c r="J17" s="427"/>
-      <c r="K17" s="437"/>
-      <c r="L17" s="271"/>
-      <c r="M17" s="248"/>
-      <c r="N17" s="51"/>
+      <c r="K17" s="435"/>
+      <c r="L17" s="467"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="248"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="403"/>
@@ -4624,9 +4594,9 @@
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="439"/>
+      <c r="K18" s="437"/>
       <c r="L18" s="271"/>
-      <c r="M18" s="248"/>
+      <c r="M18" s="388"/>
       <c r="N18" s="51"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -4640,7 +4610,7 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="437"/>
+      <c r="K19" s="435"/>
       <c r="L19" s="271"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
@@ -4656,7 +4626,7 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="437"/>
+      <c r="K20" s="435"/>
       <c r="L20" s="271"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
@@ -4667,7 +4637,7 @@
       <c r="C21" s="402" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="444" t="s">
+      <c r="D21" s="442" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4710,7 +4680,7 @@
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="440"/>
+      <c r="K22" s="438"/>
       <c r="L22" s="271"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
@@ -4726,8 +4696,8 @@
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="441"/>
-      <c r="L23" s="438"/>
+      <c r="K23" s="439"/>
+      <c r="L23" s="436"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4742,8 +4712,8 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="441"/>
-      <c r="L24" s="438"/>
+      <c r="K24" s="439"/>
+      <c r="L24" s="436"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4758,8 +4728,8 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="441"/>
-      <c r="L25" s="438"/>
+      <c r="K25" s="439"/>
+      <c r="L25" s="436"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4774,8 +4744,8 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="441"/>
-      <c r="L26" s="438"/>
+      <c r="K26" s="439"/>
+      <c r="L26" s="436"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
@@ -4790,8 +4760,8 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="441"/>
-      <c r="L27" s="438"/>
+      <c r="K27" s="439"/>
+      <c r="L27" s="436"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
@@ -4806,8 +4776,8 @@
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="442"/>
-      <c r="L28" s="443"/>
+      <c r="K28" s="440"/>
+      <c r="L28" s="441"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -902,7 +902,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="57" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1243,14 +1243,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1310,14 +1302,6 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2161,7 +2145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="469">
+  <cellXfs count="471">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2610,7 +2594,7 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2676,10 +2660,10 @@
     <xf numFmtId="0" fontId="38" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2698,10 +2682,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="26" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="26" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="26" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="26" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2715,9 +2699,9 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="26" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2730,7 +2714,7 @@
     <xf numFmtId="0" fontId="38" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2740,8 +2724,8 @@
     <xf numFmtId="0" fontId="12" fillId="26" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="52" fillId="26" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="51" fillId="26" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2749,7 +2733,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2765,13 +2749,13 @@
     <xf numFmtId="0" fontId="7" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="38" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2846,16 +2830,15 @@
     <xf numFmtId="0" fontId="7" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="43" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2867,17 +2850,13 @@
     <xf numFmtId="0" fontId="17" fillId="35" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="55" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="55" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="53" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2894,14 +2873,14 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2920,8 +2899,7 @@
     <xf numFmtId="0" fontId="17" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2933,13 +2911,13 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2950,23 +2928,31 @@
     <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="55" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="55" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="55" fillId="35" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="53" fillId="35" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="55" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="53" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="51" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="50" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4222,7 +4208,7 @@
       <c r="J1" s="355" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="410" t="s">
+      <c r="K1" s="409" t="s">
         <v>204</v>
       </c>
       <c r="L1" s="360" t="s">
@@ -4243,7 +4229,7 @@
       <c r="I2" s="270"/>
       <c r="J2" s="395"/>
       <c r="K2" s="331"/>
-      <c r="L2" s="420">
+      <c r="L2" s="417">
         <v>102247</v>
       </c>
       <c r="M2" s="112">
@@ -4263,7 +4249,7 @@
       <c r="I3" s="198"/>
       <c r="J3" s="288"/>
       <c r="K3" s="331"/>
-      <c r="L3" s="421">
+      <c r="L3" s="418">
         <v>67275.839999999997</v>
       </c>
       <c r="M3" s="101"/>
@@ -4277,25 +4263,25 @@
       <c r="C4" s="150">
         <v>27000</v>
       </c>
-      <c r="D4" s="454">
+      <c r="D4" s="450">
         <v>17825</v>
       </c>
       <c r="E4" s="150">
         <v>9444.76</v>
       </c>
-      <c r="F4" s="455">
+      <c r="F4" s="451">
         <v>23800</v>
       </c>
       <c r="G4" s="271"/>
       <c r="H4" s="271"/>
-      <c r="I4" s="394">
-        <v>21158.21</v>
+      <c r="I4" s="150">
+        <v>22138.21</v>
       </c>
       <c r="J4" s="178">
         <v>5581</v>
       </c>
       <c r="K4" s="331"/>
-      <c r="L4" s="420">
+      <c r="L4" s="417">
         <v>236679.18</v>
       </c>
       <c r="M4" s="101"/>
@@ -4315,7 +4301,7 @@
       <c r="I5" s="289"/>
       <c r="J5" s="271"/>
       <c r="K5" s="288"/>
-      <c r="L5" s="464">
+      <c r="L5" s="460">
         <v>130000</v>
       </c>
       <c r="M5" s="101"/>
@@ -4333,11 +4319,11 @@
       <c r="I6" s="271"/>
       <c r="J6" s="271"/>
       <c r="K6" s="288"/>
-      <c r="L6" s="465">
+      <c r="L6" s="461">
         <f>SUM(L2:L5)</f>
         <v>536202.02</v>
       </c>
-      <c r="M6" s="462">
+      <c r="M6" s="458">
         <v>69853</v>
       </c>
       <c r="N6" s="50"/>
@@ -4369,11 +4355,11 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="449" t="s">
+      <c r="K7" s="445" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="450"/>
-      <c r="M7" s="458">
+      <c r="L7" s="446"/>
+      <c r="M7" s="454">
         <v>13800</v>
       </c>
       <c r="N7" s="51"/>
@@ -4390,19 +4376,19 @@
       <c r="I8" s="291"/>
       <c r="J8" s="297"/>
       <c r="K8" s="271"/>
-      <c r="L8" s="463"/>
+      <c r="L8" s="459"/>
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="291"/>
-      <c r="B9" s="451">
+      <c r="B9" s="447">
         <v>1</v>
       </c>
-      <c r="C9" s="415">
+      <c r="C9" s="466">
         <v>136200</v>
       </c>
-      <c r="D9" s="414"/>
+      <c r="D9" s="413"/>
       <c r="E9" s="292"/>
       <c r="F9" s="292"/>
       <c r="G9" s="289"/>
@@ -4410,19 +4396,19 @@
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
       <c r="K9" s="288"/>
-      <c r="L9" s="461"/>
+      <c r="L9" s="457"/>
       <c r="M9" s="248"/>
       <c r="N9" s="51"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="291"/>
-      <c r="B10" s="451">
+      <c r="B10" s="447">
         <v>2</v>
       </c>
-      <c r="C10" s="416">
+      <c r="C10" s="467">
         <v>50000</v>
       </c>
-      <c r="D10" s="411"/>
+      <c r="D10" s="410"/>
       <c r="E10" s="295"/>
       <c r="F10" s="292"/>
       <c r="G10" s="292"/>
@@ -4431,29 +4417,31 @@
       <c r="J10" s="293">
         <v>55747</v>
       </c>
-      <c r="K10" s="459">
+      <c r="K10" s="455">
         <v>69853</v>
       </c>
-      <c r="L10" s="450"/>
-      <c r="M10" s="51"/>
+      <c r="L10" s="446"/>
+      <c r="M10" s="461"/>
       <c r="N10" s="51"/>
     </row>
-    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="291" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="451">
+      <c r="B11" s="447">
         <v>3</v>
       </c>
-      <c r="C11" s="198"/>
-      <c r="D11" s="412">
-        <v>192750</v>
+      <c r="C11" s="466">
+        <v>200000</v>
+      </c>
+      <c r="D11" s="411">
+        <v>92750</v>
       </c>
       <c r="E11" s="375">
         <v>592</v>
       </c>
-      <c r="F11" s="422">
-        <v>297567</v>
+      <c r="F11" s="419">
+        <v>271590</v>
       </c>
       <c r="G11" s="150">
         <v>406202.02</v>
@@ -4461,11 +4449,11 @@
       <c r="H11" s="292">
         <v>1000000</v>
       </c>
-      <c r="I11" s="422">
-        <v>342328</v>
+      <c r="I11" s="419">
+        <v>242328</v>
       </c>
       <c r="J11" s="271"/>
-      <c r="K11" s="457">
+      <c r="K11" s="453">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
@@ -4474,43 +4462,40 @@
     </row>
     <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="273"/>
-      <c r="B12" s="452">
+      <c r="B12" s="448">
         <v>4</v>
       </c>
-      <c r="C12" s="444"/>
-      <c r="D12" s="419" t="s">
+      <c r="C12" s="470">
+        <v>151000</v>
+      </c>
+      <c r="D12" s="416" t="s">
         <v>206</v>
       </c>
       <c r="E12" s="292"/>
-      <c r="F12" s="447">
-        <v>4022.77</v>
-      </c>
+      <c r="F12" s="443"/>
       <c r="G12" s="394"/>
       <c r="H12" s="304"/>
-      <c r="I12" s="423"/>
+      <c r="I12" s="420"/>
       <c r="J12" s="288"/>
       <c r="K12" s="271"/>
       <c r="L12" s="271"/>
-      <c r="M12" s="248"/>
+      <c r="M12" s="461"/>
       <c r="N12" s="51"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="270"/>
-      <c r="B13" s="453">
+      <c r="B13" s="449">
         <v>5</v>
       </c>
       <c r="C13" s="273"/>
-      <c r="D13" s="443" t="s">
+      <c r="D13" s="440" t="s">
         <v>207</v>
       </c>
       <c r="E13" s="277"/>
-      <c r="F13" s="446">
-        <f>SUM(F11:F12)</f>
-        <v>301589.77</v>
-      </c>
+      <c r="F13" s="442"/>
       <c r="G13" s="305"/>
       <c r="H13" s="328"/>
-      <c r="I13" s="424"/>
+      <c r="I13" s="421"/>
       <c r="J13" s="306"/>
       <c r="K13" s="271"/>
       <c r="L13" s="271"/>
@@ -4520,51 +4505,51 @@
     <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="445"/>
-      <c r="D14" s="456" t="s">
+      <c r="C14" s="441"/>
+      <c r="D14" s="452" t="s">
         <v>208</v>
       </c>
       <c r="E14" s="331"/>
-      <c r="F14" s="448"/>
+      <c r="F14" s="444"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
-      <c r="I14" s="425"/>
+      <c r="I14" s="422"/>
       <c r="J14" s="330"/>
       <c r="K14" s="271"/>
       <c r="L14" s="271"/>
-      <c r="M14" s="248"/>
+      <c r="M14" s="469"/>
       <c r="N14" s="51"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="270"/>
       <c r="B15" s="308"/>
-      <c r="C15" s="417"/>
+      <c r="C15" s="414"/>
       <c r="D15" s="305"/>
       <c r="E15" s="398"/>
-      <c r="F15" s="358"/>
+      <c r="F15" s="468"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="446"/>
+      <c r="I15" s="442"/>
       <c r="J15" s="401"/>
-      <c r="K15" s="435"/>
-      <c r="L15" s="441"/>
+      <c r="K15" s="432"/>
+      <c r="L15" s="438"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="271"/>
       <c r="B16" s="288"/>
-      <c r="C16" s="418"/>
+      <c r="C16" s="415"/>
       <c r="D16" s="305"/>
       <c r="E16" s="398"/>
       <c r="F16" s="358"/>
       <c r="G16" s="394"/>
       <c r="H16" s="400"/>
-      <c r="I16" s="426"/>
+      <c r="I16" s="423"/>
       <c r="J16" s="282"/>
-      <c r="K16" s="437"/>
-      <c r="L16" s="468"/>
-      <c r="M16" s="466"/>
+      <c r="K16" s="434"/>
+      <c r="L16" s="464"/>
+      <c r="M16" s="462"/>
       <c r="N16" s="51"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4576,10 +4561,10 @@
       <c r="F17" s="358"/>
       <c r="G17" s="304"/>
       <c r="H17" s="397"/>
-      <c r="I17" s="460"/>
-      <c r="J17" s="427"/>
-      <c r="K17" s="435"/>
-      <c r="L17" s="467"/>
+      <c r="I17" s="456"/>
+      <c r="J17" s="424"/>
+      <c r="K17" s="432"/>
+      <c r="L17" s="463"/>
       <c r="M17" s="100"/>
       <c r="N17" s="248"/>
     </row>
@@ -4589,12 +4574,12 @@
       <c r="C18" s="404"/>
       <c r="D18" s="304"/>
       <c r="E18" s="282"/>
-      <c r="F18" s="413"/>
+      <c r="F18" s="412"/>
       <c r="G18" s="304"/>
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="437"/>
+      <c r="K18" s="434"/>
       <c r="L18" s="271"/>
       <c r="M18" s="388"/>
       <c r="N18" s="51"/>
@@ -4610,7 +4595,7 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="435"/>
+      <c r="K19" s="432"/>
       <c r="L19" s="271"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
@@ -4626,7 +4611,7 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="435"/>
+      <c r="K20" s="432"/>
       <c r="L20" s="271"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
@@ -4637,7 +4622,7 @@
       <c r="C21" s="402" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="442" t="s">
+      <c r="D21" s="439" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4667,7 +4652,7 @@
       <c r="A22" s="291"/>
       <c r="B22" s="309"/>
       <c r="C22" s="310"/>
-      <c r="D22" s="409">
+      <c r="D22" s="465">
         <v>7500</v>
       </c>
       <c r="E22" s="284"/>
@@ -4680,7 +4665,7 @@
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="438"/>
+      <c r="K22" s="435"/>
       <c r="L22" s="271"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
@@ -4689,15 +4674,17 @@
       <c r="A23" s="304"/>
       <c r="B23" s="309"/>
       <c r="C23" s="310"/>
-      <c r="D23" s="277"/>
+      <c r="D23" s="451">
+        <v>7500</v>
+      </c>
       <c r="E23" s="287"/>
       <c r="F23" s="284"/>
       <c r="G23" s="284"/>
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="439"/>
-      <c r="L23" s="436"/>
+      <c r="K23" s="436"/>
+      <c r="L23" s="433"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4712,8 +4699,8 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="439"/>
-      <c r="L24" s="436"/>
+      <c r="K24" s="436"/>
+      <c r="L24" s="433"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4728,8 +4715,8 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="439"/>
-      <c r="L25" s="436"/>
+      <c r="K25" s="436"/>
+      <c r="L25" s="433"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4744,8 +4731,8 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="439"/>
-      <c r="L26" s="436"/>
+      <c r="K26" s="436"/>
+      <c r="L26" s="433"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
@@ -4760,39 +4747,39 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="439"/>
-      <c r="L27" s="436"/>
+      <c r="K27" s="436"/>
+      <c r="L27" s="433"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="277"/>
       <c r="B28" s="273"/>
-      <c r="C28" s="428"/>
+      <c r="C28" s="425"/>
       <c r="D28" s="350"/>
       <c r="E28" s="315"/>
-      <c r="F28" s="429"/>
+      <c r="F28" s="426"/>
       <c r="G28" s="379"/>
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="440"/>
-      <c r="L28" s="441"/>
+      <c r="K28" s="437"/>
+      <c r="L28" s="438"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="430"/>
+      <c r="A29" s="427"/>
       <c r="B29" s="271"/>
-      <c r="C29" s="431"/>
-      <c r="D29" s="432"/>
-      <c r="E29" s="433"/>
-      <c r="F29" s="433"/>
-      <c r="G29" s="434"/>
+      <c r="C29" s="428"/>
+      <c r="D29" s="429"/>
+      <c r="E29" s="430"/>
+      <c r="F29" s="430"/>
+      <c r="G29" s="431"/>
       <c r="H29" s="198"/>
-      <c r="I29" s="432"/>
-      <c r="J29" s="432"/>
-      <c r="K29" s="432"/>
+      <c r="I29" s="429"/>
+      <c r="J29" s="429"/>
+      <c r="K29" s="429"/>
       <c r="L29" s="271"/>
       <c r="M29" s="248"/>
       <c r="N29" s="51"/>

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -48,30 +48,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Edgardo Omar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-contando tarjetas financiadas 130000</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="K4" authorId="0">
       <text>
         <r>
@@ -92,7 +68,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-2 Patentes Vencidas</t>
+1 Patentes Vencidas</t>
         </r>
       </text>
     </comment>
@@ -117,54 +93,6 @@
           </rPr>
           <t xml:space="preserve">
 Cel Lais Movistar deuda</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Edgardo Omar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-vto 15/4</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Edgardo Omar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Abonado 15/4</t>
         </r>
       </text>
     </comment>
@@ -202,7 +130,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-vto 15/4</t>
+vto 15/5</t>
         </r>
       </text>
     </comment>
@@ -226,7 +154,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Abonado 15/4</t>
+Abonado 15/5</t>
         </r>
       </text>
     </comment>
@@ -269,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="206">
   <si>
     <t>Servicios</t>
   </si>
@@ -835,9 +763,6 @@
     <t>Gastos  2026</t>
   </si>
   <si>
-    <t>Ser e Impuestos</t>
-  </si>
-  <si>
     <t>Gast Financieros</t>
   </si>
   <si>
@@ -889,20 +814,14 @@
     <t>Gasto mens prest</t>
   </si>
   <si>
-    <t>Faltan seguros</t>
-  </si>
-  <si>
-    <t>Falta  Youtube</t>
-  </si>
-  <si>
-    <t>Faltan Intereses</t>
+    <t>Serv e Impuestos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="57" x14ac:knownFonts="1">
+  <fonts count="60" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1331,6 +1250,30 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2145,7 +2088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="471">
+  <cellXfs count="476">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2886,13 +2829,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2901,9 +2837,6 @@
     </xf>
     <xf numFmtId="0" fontId="50" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2925,16 +2858,8 @@
     <xf numFmtId="0" fontId="17" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="53" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="53" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="53" fillId="35" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2943,7 +2868,6 @@
     </xf>
     <xf numFmtId="2" fontId="50" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2952,7 +2876,33 @@
     </xf>
     <xf numFmtId="2" fontId="29" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="58" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4209,10 +4159,10 @@
         <v>30</v>
       </c>
       <c r="K1" s="409" t="s">
+        <v>203</v>
+      </c>
+      <c r="L1" s="360" t="s">
         <v>204</v>
-      </c>
-      <c r="L1" s="360" t="s">
-        <v>205</v>
       </c>
       <c r="M1" s="101"/>
       <c r="N1" s="50"/>
@@ -4232,9 +4182,7 @@
       <c r="L2" s="417">
         <v>102247</v>
       </c>
-      <c r="M2" s="112">
-        <v>150000</v>
-      </c>
+      <c r="M2" s="112"/>
       <c r="N2" s="50"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -4263,13 +4211,13 @@
       <c r="C4" s="150">
         <v>27000</v>
       </c>
-      <c r="D4" s="450">
+      <c r="D4" s="442">
         <v>17825</v>
       </c>
       <c r="E4" s="150">
         <v>9444.76</v>
       </c>
-      <c r="F4" s="451">
+      <c r="F4" s="443">
         <v>23800</v>
       </c>
       <c r="G4" s="271"/>
@@ -4301,7 +4249,7 @@
       <c r="I5" s="289"/>
       <c r="J5" s="271"/>
       <c r="K5" s="288"/>
-      <c r="L5" s="460">
+      <c r="L5" s="448">
         <v>130000</v>
       </c>
       <c r="M5" s="101"/>
@@ -4319,26 +4267,23 @@
       <c r="I6" s="271"/>
       <c r="J6" s="271"/>
       <c r="K6" s="288"/>
-      <c r="L6" s="461">
+      <c r="L6" s="449">
         <f>SUM(L2:L5)</f>
         <v>536202.02</v>
       </c>
-      <c r="M6" s="458">
-        <v>69853</v>
-      </c>
-      <c r="N6" s="50"/>
+      <c r="M6" s="50"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="291"/>
       <c r="B7" s="357"/>
       <c r="C7" s="262" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D7" s="263" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E7" s="263" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F7" s="264" t="s">
         <v>50</v>
@@ -4355,14 +4300,11 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="445" t="s">
+      <c r="K7" s="437" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="446"/>
-      <c r="M7" s="454">
-        <v>13800</v>
-      </c>
-      <c r="N7" s="51"/>
+      <c r="L7" s="438"/>
+      <c r="M7" s="51"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="300"/>
@@ -4376,16 +4318,16 @@
       <c r="I8" s="291"/>
       <c r="J8" s="297"/>
       <c r="K8" s="271"/>
-      <c r="L8" s="459"/>
+      <c r="L8" s="447"/>
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="291"/>
-      <c r="B9" s="447">
+      <c r="B9" s="439">
         <v>1</v>
       </c>
-      <c r="C9" s="466">
+      <c r="C9" s="453">
         <v>136200</v>
       </c>
       <c r="D9" s="413"/>
@@ -4396,16 +4338,16 @@
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
       <c r="K9" s="288"/>
-      <c r="L9" s="457"/>
+      <c r="L9" s="446"/>
       <c r="M9" s="248"/>
       <c r="N9" s="51"/>
     </row>
     <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="291"/>
-      <c r="B10" s="447">
+      <c r="B10" s="439">
         <v>2</v>
       </c>
-      <c r="C10" s="467">
+      <c r="C10" s="454">
         <v>50000</v>
       </c>
       <c r="D10" s="410"/>
@@ -4414,28 +4356,26 @@
       <c r="G10" s="292"/>
       <c r="H10" s="292"/>
       <c r="I10" s="292"/>
-      <c r="J10" s="293">
-        <v>55747</v>
-      </c>
-      <c r="K10" s="455">
+      <c r="J10" s="459"/>
+      <c r="K10" s="460">
         <v>69853</v>
       </c>
-      <c r="L10" s="446"/>
-      <c r="M10" s="461"/>
+      <c r="L10" s="438"/>
+      <c r="M10" s="449"/>
       <c r="N10" s="51"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="291" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="447">
+        <v>195</v>
+      </c>
+      <c r="B11" s="439">
         <v>3</v>
       </c>
-      <c r="C11" s="466">
+      <c r="C11" s="453">
         <v>200000</v>
       </c>
       <c r="D11" s="411">
-        <v>92750</v>
+        <v>290000</v>
       </c>
       <c r="E11" s="375">
         <v>592</v>
@@ -4452,8 +4392,10 @@
       <c r="I11" s="419">
         <v>242328</v>
       </c>
-      <c r="J11" s="271"/>
-      <c r="K11" s="453">
+      <c r="J11" s="293">
+        <v>55747</v>
+      </c>
+      <c r="K11" s="461">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
@@ -4462,37 +4404,38 @@
     </row>
     <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="273"/>
-      <c r="B12" s="448">
+      <c r="B12" s="440">
         <v>4</v>
       </c>
-      <c r="C12" s="470">
+      <c r="C12" s="457">
         <v>151000</v>
       </c>
-      <c r="D12" s="416" t="s">
-        <v>206</v>
-      </c>
+      <c r="D12" s="416"/>
       <c r="E12" s="292"/>
-      <c r="F12" s="443"/>
+      <c r="F12" s="468">
+        <v>-50000</v>
+      </c>
       <c r="G12" s="394"/>
       <c r="H12" s="304"/>
       <c r="I12" s="420"/>
       <c r="J12" s="288"/>
       <c r="K12" s="271"/>
       <c r="L12" s="271"/>
-      <c r="M12" s="461"/>
+      <c r="M12" s="449"/>
       <c r="N12" s="51"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="270"/>
-      <c r="B13" s="449">
+      <c r="B13" s="441">
         <v>5</v>
       </c>
-      <c r="C13" s="273"/>
-      <c r="D13" s="440" t="s">
-        <v>207</v>
-      </c>
+      <c r="C13" s="458">
+        <f>SUM(C9:C12)</f>
+        <v>537200</v>
+      </c>
+      <c r="D13" s="433"/>
       <c r="E13" s="277"/>
-      <c r="F13" s="442"/>
+      <c r="F13" s="435"/>
       <c r="G13" s="305"/>
       <c r="H13" s="328"/>
       <c r="I13" s="421"/>
@@ -4505,19 +4448,21 @@
     <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="441"/>
-      <c r="D14" s="452" t="s">
-        <v>208</v>
-      </c>
+      <c r="C14" s="434"/>
+      <c r="D14" s="444"/>
       <c r="E14" s="331"/>
-      <c r="F14" s="444"/>
+      <c r="F14" s="436"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
       <c r="I14" s="422"/>
       <c r="J14" s="330"/>
-      <c r="K14" s="271"/>
-      <c r="L14" s="271"/>
-      <c r="M14" s="469"/>
+      <c r="K14" s="469">
+        <v>57525.78</v>
+      </c>
+      <c r="L14" s="198">
+        <v>-85000</v>
+      </c>
+      <c r="M14" s="456"/>
       <c r="N14" s="51"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4526,13 +4471,17 @@
       <c r="C15" s="414"/>
       <c r="D15" s="305"/>
       <c r="E15" s="398"/>
-      <c r="F15" s="468"/>
+      <c r="F15" s="455"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="442"/>
+      <c r="I15" s="435"/>
       <c r="J15" s="401"/>
-      <c r="K15" s="432"/>
-      <c r="L15" s="438"/>
+      <c r="K15" s="470">
+        <v>18603</v>
+      </c>
+      <c r="L15" s="462">
+        <v>85797.5</v>
+      </c>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
@@ -4547,9 +4496,13 @@
       <c r="H16" s="400"/>
       <c r="I16" s="423"/>
       <c r="J16" s="282"/>
-      <c r="K16" s="434"/>
-      <c r="L16" s="464"/>
-      <c r="M16" s="462"/>
+      <c r="K16" s="471">
+        <v>39900</v>
+      </c>
+      <c r="L16" s="451">
+        <v>-100000</v>
+      </c>
+      <c r="M16" s="450"/>
       <c r="N16" s="51"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4561,10 +4514,14 @@
       <c r="F17" s="358"/>
       <c r="G17" s="304"/>
       <c r="H17" s="397"/>
-      <c r="I17" s="456"/>
+      <c r="I17" s="445"/>
       <c r="J17" s="424"/>
-      <c r="K17" s="432"/>
-      <c r="L17" s="463"/>
+      <c r="K17" s="470">
+        <v>1700</v>
+      </c>
+      <c r="L17" s="463">
+        <v>-18000</v>
+      </c>
       <c r="M17" s="100"/>
       <c r="N17" s="248"/>
     </row>
@@ -4579,8 +4536,12 @@
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="434"/>
-      <c r="L18" s="271"/>
+      <c r="K18" s="471">
+        <v>4008</v>
+      </c>
+      <c r="L18" s="198">
+        <v>18283.599999999999</v>
+      </c>
       <c r="M18" s="388"/>
       <c r="N18" s="51"/>
     </row>
@@ -4595,8 +4556,12 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="432"/>
-      <c r="L19" s="271"/>
+      <c r="K19" s="470">
+        <v>1700</v>
+      </c>
+      <c r="L19" s="198">
+        <v>-30000</v>
+      </c>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
     </row>
@@ -4611,8 +4576,12 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="432"/>
-      <c r="L20" s="271"/>
+      <c r="K20" s="470">
+        <v>32998.89</v>
+      </c>
+      <c r="L20" s="198">
+        <v>-46685</v>
+      </c>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
     </row>
@@ -4622,11 +4591,11 @@
       <c r="C21" s="402" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="439" t="s">
+      <c r="D21" s="432" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F21" s="276" t="s">
         <v>179</v>
@@ -4643,8 +4612,12 @@
       <c r="J21" s="298" t="s">
         <v>172</v>
       </c>
-      <c r="K21" s="288"/>
-      <c r="L21" s="291"/>
+      <c r="K21" s="472">
+        <v>19500</v>
+      </c>
+      <c r="L21" s="403">
+        <v>-1200</v>
+      </c>
       <c r="M21" s="248"/>
       <c r="N21" s="51"/>
     </row>
@@ -4652,7 +4625,7 @@
       <c r="A22" s="291"/>
       <c r="B22" s="309"/>
       <c r="C22" s="310"/>
-      <c r="D22" s="465">
+      <c r="D22" s="452">
         <v>7500</v>
       </c>
       <c r="E22" s="284"/>
@@ -4665,8 +4638,12 @@
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="435"/>
-      <c r="L22" s="271"/>
+      <c r="K22" s="473">
+        <v>12693.5</v>
+      </c>
+      <c r="L22" s="403">
+        <v>47854.3</v>
+      </c>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
     </row>
@@ -4674,7 +4651,7 @@
       <c r="A23" s="304"/>
       <c r="B23" s="309"/>
       <c r="C23" s="310"/>
-      <c r="D23" s="451">
+      <c r="D23" s="443">
         <v>7500</v>
       </c>
       <c r="E23" s="287"/>
@@ -4683,8 +4660,12 @@
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="436"/>
-      <c r="L23" s="433"/>
+      <c r="K23" s="470">
+        <v>8800</v>
+      </c>
+      <c r="L23" s="464">
+        <v>-20000</v>
+      </c>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4699,8 +4680,12 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="436"/>
-      <c r="L24" s="433"/>
+      <c r="K24" s="470">
+        <v>4418.01</v>
+      </c>
+      <c r="L24" s="464">
+        <v>46137.5</v>
+      </c>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4715,8 +4700,12 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="436"/>
-      <c r="L25" s="433"/>
+      <c r="K25" s="470">
+        <v>12592.5</v>
+      </c>
+      <c r="L25" s="464">
+        <v>52724.2</v>
+      </c>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4731,12 +4720,16 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="436"/>
-      <c r="L26" s="433"/>
+      <c r="K26" s="470">
+        <v>55000</v>
+      </c>
+      <c r="L26" s="465">
+        <v>24871.200000000001</v>
+      </c>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="377"/>
       <c r="B27" s="378"/>
       <c r="C27" s="310"/>
@@ -4747,12 +4740,16 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="436"/>
-      <c r="L27" s="433"/>
+      <c r="K27" s="470">
+        <v>5690</v>
+      </c>
+      <c r="L27" s="462">
+        <v>13169.2</v>
+      </c>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="277"/>
       <c r="B28" s="273"/>
       <c r="C28" s="425"/>
@@ -4763,8 +4760,13 @@
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="437"/>
-      <c r="L28" s="438"/>
+      <c r="K28" s="474">
+        <v>3703.9</v>
+      </c>
+      <c r="L28" s="467">
+        <f>SUM(L14:L27)</f>
+        <v>-12047.499999999978</v>
+      </c>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>
@@ -4779,8 +4781,10 @@
       <c r="H29" s="198"/>
       <c r="I29" s="429"/>
       <c r="J29" s="429"/>
-      <c r="K29" s="429"/>
-      <c r="L29" s="271"/>
+      <c r="K29" s="475">
+        <v>55385.24</v>
+      </c>
+      <c r="L29" s="466"/>
       <c r="M29" s="248"/>
       <c r="N29" s="51"/>
     </row>
@@ -4795,7 +4799,9 @@
       <c r="H30" s="271"/>
       <c r="I30" s="271"/>
       <c r="J30" s="271"/>
-      <c r="K30" s="271"/>
+      <c r="K30" s="469">
+        <v>67064.66</v>
+      </c>
       <c r="L30" s="271"/>
       <c r="M30" s="248"/>
       <c r="N30" s="51"/>
@@ -4811,7 +4817,9 @@
       <c r="H31" s="271"/>
       <c r="I31" s="271"/>
       <c r="J31" s="271"/>
-      <c r="K31" s="271"/>
+      <c r="K31" s="469">
+        <v>2864.16</v>
+      </c>
       <c r="L31" s="271"/>
       <c r="M31" s="248"/>
       <c r="N31" s="51"/>
@@ -4827,7 +4835,9 @@
       <c r="H32" s="271"/>
       <c r="I32" s="271"/>
       <c r="J32" s="271"/>
-      <c r="K32" s="271"/>
+      <c r="K32" s="271">
+        <v>7729.12</v>
+      </c>
       <c r="L32" s="271"/>
       <c r="M32" s="248"/>
       <c r="N32" s="51"/>
@@ -4843,7 +4853,9 @@
       <c r="H33" s="271"/>
       <c r="I33" s="271"/>
       <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
+      <c r="K33" s="271">
+        <v>5822.42</v>
+      </c>
       <c r="L33" s="271"/>
       <c r="M33" s="248"/>
       <c r="N33" s="51"/>
@@ -4859,7 +4871,9 @@
       <c r="H34" s="271"/>
       <c r="I34" s="271"/>
       <c r="J34" s="271"/>
-      <c r="K34" s="271"/>
+      <c r="K34" s="271">
+        <v>10760.39</v>
+      </c>
       <c r="L34" s="271"/>
       <c r="M34" s="248"/>
       <c r="N34" s="51"/>
@@ -4875,7 +4889,9 @@
       <c r="H35" s="271"/>
       <c r="I35" s="271"/>
       <c r="J35" s="271"/>
-      <c r="K35" s="271"/>
+      <c r="K35" s="271">
+        <v>47658</v>
+      </c>
       <c r="L35" s="271"/>
       <c r="M35" s="248"/>
       <c r="N35" s="51"/>
@@ -4891,7 +4907,10 @@
       <c r="H36" s="271"/>
       <c r="I36" s="271"/>
       <c r="J36" s="271"/>
-      <c r="K36" s="271"/>
+      <c r="K36" s="271">
+        <f>SUM(K14:K35)</f>
+        <v>476117.56999999995</v>
+      </c>
       <c r="L36" s="271"/>
       <c r="M36" s="248"/>
       <c r="N36" s="51"/>
@@ -4907,7 +4926,9 @@
       <c r="H37" s="271"/>
       <c r="I37" s="271"/>
       <c r="J37" s="271"/>
-      <c r="K37" s="271"/>
+      <c r="K37" s="271">
+        <v>-11999.87</v>
+      </c>
       <c r="L37" s="271"/>
       <c r="M37" s="248"/>
       <c r="N37" s="51"/>
@@ -4923,7 +4944,10 @@
       <c r="H38" s="270"/>
       <c r="I38" s="312"/>
       <c r="J38" s="284"/>
-      <c r="K38" s="359"/>
+      <c r="K38" s="359">
+        <f>SUM(K36:K37)</f>
+        <v>464117.69999999995</v>
+      </c>
       <c r="L38" s="364"/>
       <c r="M38" s="248"/>
       <c r="N38" s="51"/>
@@ -4954,7 +4978,9 @@
       <c r="G40" s="284"/>
       <c r="H40" s="270"/>
       <c r="I40" s="312"/>
-      <c r="J40" s="284"/>
+      <c r="J40" s="284">
+        <v>480632.66</v>
+      </c>
       <c r="K40" s="359"/>
       <c r="L40" s="364"/>
       <c r="M40" s="248"/>
@@ -4970,8 +4996,12 @@
       <c r="G41" s="284"/>
       <c r="H41" s="284"/>
       <c r="I41" s="312"/>
-      <c r="J41" s="284"/>
-      <c r="K41" s="359"/>
+      <c r="J41" s="284">
+        <v>464117.7</v>
+      </c>
+      <c r="K41" s="359">
+        <v>100000</v>
+      </c>
       <c r="L41" s="364"/>
       <c r="M41" s="248"/>
       <c r="N41" s="51"/>
@@ -4986,8 +5016,12 @@
       <c r="G42" s="284"/>
       <c r="H42" s="284"/>
       <c r="I42" s="284"/>
-      <c r="J42" s="284"/>
-      <c r="K42" s="359"/>
+      <c r="J42" s="284">
+        <v>-655633</v>
+      </c>
+      <c r="K42" s="359">
+        <v>40000</v>
+      </c>
       <c r="L42" s="364"/>
       <c r="M42" s="248"/>
       <c r="N42" s="51"/>
@@ -5002,8 +5036,13 @@
       <c r="G43" s="315"/>
       <c r="H43" s="284"/>
       <c r="I43" s="284"/>
-      <c r="J43" s="270"/>
-      <c r="K43" s="359"/>
+      <c r="J43" s="270">
+        <f>SUM(J40:J42)</f>
+        <v>289117.36</v>
+      </c>
+      <c r="K43" s="359">
+        <v>515633</v>
+      </c>
       <c r="L43" s="364"/>
       <c r="M43" s="248"/>
       <c r="N43" s="51"/>
@@ -5021,7 +5060,10 @@
       <c r="H44" s="315"/>
       <c r="I44" s="315"/>
       <c r="J44" s="284"/>
-      <c r="K44" s="359"/>
+      <c r="K44" s="359">
+        <f>SUM(K41:K43)</f>
+        <v>655633</v>
+      </c>
       <c r="L44" s="364"/>
       <c r="M44" s="248"/>
       <c r="N44" s="51"/>
@@ -5029,7 +5071,7 @@
     <row r="45" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="306"/>
       <c r="B45" s="316" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C45" s="317" t="s">
         <v>24</v>
@@ -5085,7 +5127,7 @@
       <c r="D47" s="270"/>
       <c r="E47" s="284"/>
       <c r="F47" s="349" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="G47" s="329"/>
       <c r="H47" s="327"/>
@@ -5107,7 +5149,7 @@
       <c r="D48" s="270"/>
       <c r="E48" s="304"/>
       <c r="F48" s="343" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G48" s="329"/>
       <c r="H48" s="330"/>
@@ -5129,7 +5171,7 @@
       <c r="D49" s="270"/>
       <c r="E49" s="304"/>
       <c r="F49" s="343" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G49" s="329"/>
       <c r="H49" s="330"/>
@@ -5301,10 +5343,10 @@
         <v>3801.42</v>
       </c>
       <c r="E58" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F58" s="382" t="s">
         <v>197</v>
-      </c>
-      <c r="F58" s="382" t="s">
-        <v>198</v>
       </c>
       <c r="G58" s="98"/>
       <c r="H58" s="98"/>
@@ -5325,13 +5367,13 @@
         <v>6644.52</v>
       </c>
       <c r="E59" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F59" s="383" t="s">
         <v>197</v>
       </c>
-      <c r="F59" s="383" t="s">
+      <c r="G59" s="98" t="s">
         <v>198</v>
-      </c>
-      <c r="G59" s="98" t="s">
-        <v>199</v>
       </c>
       <c r="H59" s="98"/>
       <c r="I59" s="384"/>
@@ -5351,22 +5393,22 @@
         <v>10760.39</v>
       </c>
       <c r="E60" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F60" s="383" t="s">
         <v>197</v>
       </c>
-      <c r="F60" s="383" t="s">
+      <c r="G60" s="98" t="s">
         <v>198</v>
       </c>
-      <c r="G60" s="98" t="s">
+      <c r="H60" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="H60" s="98" t="s">
+      <c r="I60" s="385" t="s">
         <v>200</v>
       </c>
-      <c r="I60" s="385" t="s">
+      <c r="J60" s="51" t="s">
         <v>201</v>
-      </c>
-      <c r="J60" s="51" t="s">
-        <v>202</v>
       </c>
       <c r="K60" s="51"/>
       <c r="L60" s="248"/>
@@ -5381,22 +5423,22 @@
         <v>19601</v>
       </c>
       <c r="E61" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F61" s="383" t="s">
         <v>197</v>
       </c>
-      <c r="F61" s="383" t="s">
+      <c r="G61" s="98" t="s">
         <v>198</v>
       </c>
-      <c r="G61" s="98" t="s">
+      <c r="H61" s="98" t="s">
         <v>199</v>
       </c>
-      <c r="H61" s="98" t="s">
+      <c r="I61" s="385" t="s">
         <v>200</v>
       </c>
-      <c r="I61" s="385" t="s">
+      <c r="J61" s="51" t="s">
         <v>201</v>
-      </c>
-      <c r="J61" s="51" t="s">
-        <v>202</v>
       </c>
       <c r="K61" s="51"/>
       <c r="L61" s="248"/>
@@ -5414,14 +5456,14 @@
         <v>5822.42</v>
       </c>
       <c r="E62" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F62" s="383" t="s">
         <v>197</v>
-      </c>
-      <c r="F62" s="383" t="s">
-        <v>198</v>
       </c>
       <c r="G62" s="386"/>
       <c r="H62" s="98" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I62" s="99"/>
       <c r="J62" s="51"/>
@@ -5438,10 +5480,10 @@
         <v>15744.77</v>
       </c>
       <c r="E63" s="386" t="s">
+        <v>196</v>
+      </c>
+      <c r="F63" s="387" t="s">
         <v>197</v>
-      </c>
-      <c r="F63" s="387" t="s">
-        <v>198</v>
       </c>
       <c r="G63" s="393">
         <v>36183.39</v>
@@ -5466,7 +5508,7 @@
         <v>62374.52</v>
       </c>
       <c r="F64" s="393" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G64" s="253"/>
       <c r="H64" s="393">

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="205">
   <si>
     <t>Servicios</t>
   </si>
@@ -782,9 +782,6 @@
   </si>
   <si>
     <t>Comp deb/efec</t>
-  </si>
-  <si>
-    <t>MARZO</t>
   </si>
   <si>
     <t>Feb</t>
@@ -2765,7 +2762,6 @@
     <xf numFmtId="0" fontId="17" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2814,7 +2810,6 @@
     <xf numFmtId="2" fontId="7" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2836,14 +2831,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2860,15 +2851,10 @@
     </xf>
     <xf numFmtId="2" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="53" fillId="35" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="53" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="50" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2886,13 +2872,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="58" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2903,6 +2887,19 @@
     <xf numFmtId="0" fontId="58" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="58" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="58" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="50" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="53" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4158,11 +4155,11 @@
       <c r="J1" s="355" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="409" t="s">
+      <c r="K1" s="408" t="s">
+        <v>202</v>
+      </c>
+      <c r="L1" s="360" t="s">
         <v>203</v>
-      </c>
-      <c r="L1" s="360" t="s">
-        <v>204</v>
       </c>
       <c r="M1" s="101"/>
       <c r="N1" s="50"/>
@@ -4170,16 +4167,16 @@
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="291"/>
       <c r="B2" s="302"/>
-      <c r="C2" s="407"/>
-      <c r="D2" s="403"/>
+      <c r="C2" s="406"/>
+      <c r="D2" s="402"/>
       <c r="E2" s="289"/>
-      <c r="F2" s="408"/>
+      <c r="F2" s="407"/>
       <c r="G2" s="198"/>
       <c r="H2" s="271"/>
       <c r="I2" s="270"/>
       <c r="J2" s="395"/>
       <c r="K2" s="331"/>
-      <c r="L2" s="417">
+      <c r="L2" s="416">
         <v>102247</v>
       </c>
       <c r="M2" s="112"/>
@@ -4197,27 +4194,27 @@
       <c r="I3" s="198"/>
       <c r="J3" s="288"/>
       <c r="K3" s="331"/>
-      <c r="L3" s="418">
+      <c r="L3" s="417">
         <v>67275.839999999997</v>
       </c>
       <c r="M3" s="101"/>
       <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="406" t="s">
-        <v>21</v>
+      <c r="A4" s="405" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="271"/>
       <c r="C4" s="150">
         <v>27000</v>
       </c>
-      <c r="D4" s="442">
+      <c r="D4" s="438">
         <v>17825</v>
       </c>
       <c r="E4" s="150">
         <v>9444.76</v>
       </c>
-      <c r="F4" s="443">
+      <c r="F4" s="439">
         <v>23800</v>
       </c>
       <c r="G4" s="271"/>
@@ -4229,7 +4226,7 @@
         <v>5581</v>
       </c>
       <c r="K4" s="331"/>
-      <c r="L4" s="417">
+      <c r="L4" s="416">
         <v>236679.18</v>
       </c>
       <c r="M4" s="101"/>
@@ -4249,13 +4246,13 @@
       <c r="I5" s="289"/>
       <c r="J5" s="271"/>
       <c r="K5" s="288"/>
-      <c r="L5" s="448">
+      <c r="L5" s="443">
         <v>130000</v>
       </c>
       <c r="M5" s="101"/>
       <c r="N5" s="50"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="271"/>
       <c r="B6" s="271"/>
       <c r="C6" s="271"/>
@@ -4267,7 +4264,7 @@
       <c r="I6" s="271"/>
       <c r="J6" s="271"/>
       <c r="K6" s="288"/>
-      <c r="L6" s="449">
+      <c r="L6" s="474">
         <f>SUM(L2:L5)</f>
         <v>536202.02</v>
       </c>
@@ -4300,11 +4297,11 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="437" t="s">
+      <c r="K7" s="434" t="s">
         <v>186</v>
       </c>
-      <c r="L7" s="438"/>
-      <c r="M7" s="51"/>
+      <c r="L7" s="271"/>
+      <c r="M7" s="248"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="300"/>
@@ -4317,20 +4314,20 @@
       <c r="H8" s="291"/>
       <c r="I8" s="291"/>
       <c r="J8" s="297"/>
-      <c r="K8" s="271"/>
-      <c r="L8" s="447"/>
+      <c r="K8" s="288"/>
+      <c r="L8" s="475"/>
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="291"/>
-      <c r="B9" s="439">
+      <c r="B9" s="435">
         <v>1</v>
       </c>
-      <c r="C9" s="453">
+      <c r="C9" s="446">
         <v>136200</v>
       </c>
-      <c r="D9" s="413"/>
+      <c r="D9" s="412"/>
       <c r="E9" s="292"/>
       <c r="F9" s="292"/>
       <c r="G9" s="289"/>
@@ -4338,171 +4335,155 @@
       <c r="I9" s="292"/>
       <c r="J9" s="293"/>
       <c r="K9" s="288"/>
-      <c r="L9" s="446"/>
+      <c r="L9" s="442"/>
       <c r="M9" s="248"/>
       <c r="N9" s="51"/>
     </row>
     <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="291"/>
-      <c r="B10" s="439">
+      <c r="B10" s="435">
         <v>2</v>
       </c>
-      <c r="C10" s="454">
+      <c r="C10" s="447">
         <v>50000</v>
       </c>
-      <c r="D10" s="410"/>
+      <c r="D10" s="409"/>
       <c r="E10" s="295"/>
       <c r="F10" s="292"/>
       <c r="G10" s="292"/>
       <c r="H10" s="292"/>
       <c r="I10" s="292"/>
-      <c r="J10" s="459"/>
-      <c r="K10" s="460">
+      <c r="J10" s="452"/>
+      <c r="K10" s="453">
         <v>69853</v>
       </c>
-      <c r="L10" s="438"/>
-      <c r="M10" s="449"/>
+      <c r="L10" s="271"/>
+      <c r="M10" s="472"/>
       <c r="N10" s="51"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="291" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="439">
+      <c r="A11" s="291"/>
+      <c r="B11" s="435">
         <v>3</v>
       </c>
-      <c r="C11" s="453">
+      <c r="C11" s="446">
         <v>200000</v>
       </c>
-      <c r="D11" s="411">
+      <c r="D11" s="410">
         <v>290000</v>
       </c>
       <c r="E11" s="375">
         <v>592</v>
       </c>
-      <c r="F11" s="419">
-        <v>271590</v>
+      <c r="F11" s="418">
+        <v>303674</v>
       </c>
       <c r="G11" s="150">
         <v>406202.02</v>
       </c>
-      <c r="H11" s="292">
-        <v>1000000</v>
-      </c>
-      <c r="I11" s="419">
-        <v>242328</v>
+      <c r="H11" s="295">
+        <v>0</v>
+      </c>
+      <c r="I11" s="418">
+        <v>266991</v>
       </c>
       <c r="J11" s="293">
         <v>55747</v>
       </c>
-      <c r="K11" s="461">
+      <c r="K11" s="454">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
-      <c r="M11" s="51"/>
+      <c r="M11" s="248"/>
       <c r="N11" s="51"/>
     </row>
     <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="273"/>
-      <c r="B12" s="440">
+      <c r="B12" s="436">
         <v>4</v>
       </c>
-      <c r="C12" s="457">
+      <c r="C12" s="450">
         <v>151000</v>
       </c>
-      <c r="D12" s="416"/>
+      <c r="D12" s="415"/>
       <c r="E12" s="292"/>
-      <c r="F12" s="468">
-        <v>-50000</v>
-      </c>
+      <c r="F12" s="459"/>
       <c r="G12" s="394"/>
       <c r="H12" s="304"/>
-      <c r="I12" s="420"/>
+      <c r="I12" s="419"/>
       <c r="J12" s="288"/>
-      <c r="K12" s="271"/>
+      <c r="K12" s="288"/>
       <c r="L12" s="271"/>
-      <c r="M12" s="449"/>
+      <c r="M12" s="472"/>
       <c r="N12" s="51"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="270"/>
-      <c r="B13" s="441">
+      <c r="B13" s="437">
         <v>5</v>
       </c>
-      <c r="C13" s="458">
+      <c r="C13" s="451">
         <f>SUM(C9:C12)</f>
         <v>537200</v>
       </c>
-      <c r="D13" s="433"/>
+      <c r="D13" s="431"/>
       <c r="E13" s="277"/>
-      <c r="F13" s="435"/>
+      <c r="F13" s="418"/>
       <c r="G13" s="305"/>
       <c r="H13" s="328"/>
-      <c r="I13" s="421"/>
+      <c r="I13" s="420"/>
       <c r="J13" s="306"/>
-      <c r="K13" s="271"/>
-      <c r="L13" s="271"/>
+      <c r="K13" s="288"/>
+      <c r="L13" s="469"/>
       <c r="M13" s="248"/>
       <c r="N13" s="51"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="270"/>
       <c r="B14" s="308"/>
-      <c r="C14" s="434"/>
-      <c r="D14" s="444"/>
+      <c r="C14" s="432"/>
+      <c r="D14" s="440"/>
       <c r="E14" s="331"/>
-      <c r="F14" s="436"/>
+      <c r="F14" s="433"/>
       <c r="G14" s="304"/>
       <c r="H14" s="328"/>
-      <c r="I14" s="422"/>
+      <c r="I14" s="421"/>
       <c r="J14" s="330"/>
-      <c r="K14" s="469">
-        <v>57525.78</v>
-      </c>
-      <c r="L14" s="198">
-        <v>-85000</v>
-      </c>
-      <c r="M14" s="456"/>
+      <c r="K14" s="406"/>
+      <c r="L14" s="470"/>
+      <c r="M14" s="449"/>
       <c r="N14" s="51"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="270"/>
       <c r="B15" s="308"/>
-      <c r="C15" s="414"/>
+      <c r="C15" s="413"/>
       <c r="D15" s="305"/>
       <c r="E15" s="398"/>
-      <c r="F15" s="455"/>
+      <c r="F15" s="448"/>
       <c r="G15" s="304"/>
       <c r="H15" s="399"/>
-      <c r="I15" s="435"/>
-      <c r="J15" s="401"/>
-      <c r="K15" s="470">
-        <v>18603</v>
-      </c>
-      <c r="L15" s="462">
-        <v>85797.5</v>
-      </c>
+      <c r="I15" s="418"/>
+      <c r="J15" s="400"/>
+      <c r="K15" s="461"/>
+      <c r="L15" s="470"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="271"/>
       <c r="B16" s="288"/>
-      <c r="C16" s="415"/>
+      <c r="C16" s="414"/>
       <c r="D16" s="305"/>
       <c r="E16" s="398"/>
       <c r="F16" s="358"/>
       <c r="G16" s="394"/>
-      <c r="H16" s="400"/>
-      <c r="I16" s="423"/>
-      <c r="J16" s="282"/>
-      <c r="K16" s="471">
-        <v>39900</v>
-      </c>
-      <c r="L16" s="451">
-        <v>-100000</v>
-      </c>
-      <c r="M16" s="450"/>
+      <c r="H16" s="467"/>
+      <c r="I16" s="442"/>
+      <c r="J16" s="368"/>
+      <c r="K16" s="462"/>
+      <c r="L16" s="470"/>
+      <c r="M16" s="444"/>
       <c r="N16" s="51"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4513,35 +4494,27 @@
       <c r="E17" s="308"/>
       <c r="F17" s="358"/>
       <c r="G17" s="304"/>
-      <c r="H17" s="397"/>
-      <c r="I17" s="445"/>
-      <c r="J17" s="424"/>
-      <c r="K17" s="470">
-        <v>1700</v>
-      </c>
-      <c r="L17" s="463">
-        <v>-18000</v>
-      </c>
-      <c r="M17" s="100"/>
+      <c r="H17" s="468"/>
+      <c r="I17" s="441"/>
+      <c r="J17" s="422"/>
+      <c r="K17" s="461"/>
+      <c r="L17" s="470"/>
+      <c r="M17" s="473"/>
       <c r="N17" s="248"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="403"/>
-      <c r="B18" s="405"/>
-      <c r="C18" s="404"/>
+      <c r="A18" s="402"/>
+      <c r="B18" s="404"/>
+      <c r="C18" s="403"/>
       <c r="D18" s="304"/>
       <c r="E18" s="282"/>
-      <c r="F18" s="412"/>
+      <c r="F18" s="411"/>
       <c r="G18" s="304"/>
       <c r="H18" s="397"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="471">
-        <v>4008</v>
-      </c>
-      <c r="L18" s="198">
-        <v>18283.599999999999</v>
-      </c>
+      <c r="K18" s="462"/>
+      <c r="L18" s="470"/>
       <c r="M18" s="388"/>
       <c r="N18" s="51"/>
     </row>
@@ -4556,12 +4529,8 @@
       <c r="H19" s="371"/>
       <c r="I19" s="370"/>
       <c r="J19" s="370"/>
-      <c r="K19" s="470">
-        <v>1700</v>
-      </c>
-      <c r="L19" s="198">
-        <v>-30000</v>
-      </c>
+      <c r="K19" s="461"/>
+      <c r="L19" s="470"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
     </row>
@@ -4576,22 +4545,18 @@
       <c r="H20" s="282"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="470">
-        <v>32998.89</v>
-      </c>
-      <c r="L20" s="198">
-        <v>-46685</v>
-      </c>
+      <c r="K20" s="461"/>
+      <c r="L20" s="470"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="307"/>
       <c r="B21" s="303"/>
-      <c r="C21" s="402" t="s">
+      <c r="C21" s="401" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="432" t="s">
+      <c r="D21" s="430" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4612,12 +4577,8 @@
       <c r="J21" s="298" t="s">
         <v>172</v>
       </c>
-      <c r="K21" s="472">
-        <v>19500</v>
-      </c>
-      <c r="L21" s="403">
-        <v>-1200</v>
-      </c>
+      <c r="K21" s="463"/>
+      <c r="L21" s="471"/>
       <c r="M21" s="248"/>
       <c r="N21" s="51"/>
     </row>
@@ -4625,7 +4586,7 @@
       <c r="A22" s="291"/>
       <c r="B22" s="309"/>
       <c r="C22" s="310"/>
-      <c r="D22" s="452">
+      <c r="D22" s="445">
         <v>7500</v>
       </c>
       <c r="E22" s="284"/>
@@ -4633,17 +4594,13 @@
       <c r="G22" s="394">
         <v>33000</v>
       </c>
-      <c r="H22" s="284">
+      <c r="H22" s="394">
         <v>59159</v>
       </c>
       <c r="I22" s="284"/>
       <c r="J22" s="284"/>
-      <c r="K22" s="473">
-        <v>12693.5</v>
-      </c>
-      <c r="L22" s="403">
-        <v>47854.3</v>
-      </c>
+      <c r="K22" s="464"/>
+      <c r="L22" s="471"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
     </row>
@@ -4651,7 +4608,7 @@
       <c r="A23" s="304"/>
       <c r="B23" s="309"/>
       <c r="C23" s="310"/>
-      <c r="D23" s="443">
+      <c r="D23" s="439">
         <v>7500</v>
       </c>
       <c r="E23" s="287"/>
@@ -4660,12 +4617,8 @@
       <c r="H23" s="284"/>
       <c r="I23" s="284"/>
       <c r="J23" s="284"/>
-      <c r="K23" s="470">
-        <v>8800</v>
-      </c>
-      <c r="L23" s="464">
-        <v>-20000</v>
-      </c>
+      <c r="K23" s="461"/>
+      <c r="L23" s="471"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
@@ -4680,12 +4633,8 @@
       <c r="H24" s="284"/>
       <c r="I24" s="284"/>
       <c r="J24" s="284"/>
-      <c r="K24" s="470">
-        <v>4418.01</v>
-      </c>
-      <c r="L24" s="464">
-        <v>46137.5</v>
-      </c>
+      <c r="K24" s="461"/>
+      <c r="L24" s="471"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
@@ -4700,12 +4649,8 @@
       <c r="H25" s="284"/>
       <c r="I25" s="284"/>
       <c r="J25" s="284"/>
-      <c r="K25" s="470">
-        <v>12592.5</v>
-      </c>
-      <c r="L25" s="464">
-        <v>52724.2</v>
-      </c>
+      <c r="K25" s="461"/>
+      <c r="L25" s="456"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
@@ -4720,16 +4665,12 @@
       <c r="H26" s="284"/>
       <c r="I26" s="284"/>
       <c r="J26" s="284"/>
-      <c r="K26" s="470">
-        <v>55000</v>
-      </c>
-      <c r="L26" s="465">
-        <v>24871.200000000001</v>
-      </c>
+      <c r="K26" s="461"/>
+      <c r="L26" s="457"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="377"/>
       <c r="B27" s="378"/>
       <c r="C27" s="310"/>
@@ -4740,51 +4681,40 @@
       <c r="H27" s="284"/>
       <c r="I27" s="284"/>
       <c r="J27" s="284"/>
-      <c r="K27" s="470">
-        <v>5690</v>
-      </c>
-      <c r="L27" s="462">
-        <v>13169.2</v>
-      </c>
+      <c r="K27" s="461"/>
+      <c r="L27" s="455"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="277"/>
       <c r="B28" s="273"/>
-      <c r="C28" s="425"/>
+      <c r="C28" s="423"/>
       <c r="D28" s="350"/>
       <c r="E28" s="315"/>
-      <c r="F28" s="426"/>
+      <c r="F28" s="424"/>
       <c r="G28" s="379"/>
       <c r="H28" s="315"/>
       <c r="I28" s="315"/>
       <c r="J28" s="315"/>
-      <c r="K28" s="474">
-        <v>3703.9</v>
-      </c>
-      <c r="L28" s="467">
-        <f>SUM(L14:L27)</f>
-        <v>-12047.499999999978</v>
-      </c>
+      <c r="K28" s="465"/>
+      <c r="L28" s="446"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="427"/>
+      <c r="A29" s="425"/>
       <c r="B29" s="271"/>
-      <c r="C29" s="428"/>
-      <c r="D29" s="429"/>
-      <c r="E29" s="430"/>
-      <c r="F29" s="430"/>
-      <c r="G29" s="431"/>
+      <c r="C29" s="426"/>
+      <c r="D29" s="427"/>
+      <c r="E29" s="428"/>
+      <c r="F29" s="428"/>
+      <c r="G29" s="429"/>
       <c r="H29" s="198"/>
-      <c r="I29" s="429"/>
-      <c r="J29" s="429"/>
-      <c r="K29" s="475">
-        <v>55385.24</v>
-      </c>
-      <c r="L29" s="466"/>
+      <c r="I29" s="427"/>
+      <c r="J29" s="427"/>
+      <c r="K29" s="466"/>
+      <c r="L29" s="458"/>
       <c r="M29" s="248"/>
       <c r="N29" s="51"/>
     </row>
@@ -4799,9 +4729,7 @@
       <c r="H30" s="271"/>
       <c r="I30" s="271"/>
       <c r="J30" s="271"/>
-      <c r="K30" s="469">
-        <v>67064.66</v>
-      </c>
+      <c r="K30" s="460"/>
       <c r="L30" s="271"/>
       <c r="M30" s="248"/>
       <c r="N30" s="51"/>
@@ -4817,9 +4745,7 @@
       <c r="H31" s="271"/>
       <c r="I31" s="271"/>
       <c r="J31" s="271"/>
-      <c r="K31" s="469">
-        <v>2864.16</v>
-      </c>
+      <c r="K31" s="460"/>
       <c r="L31" s="271"/>
       <c r="M31" s="248"/>
       <c r="N31" s="51"/>
@@ -4835,9 +4761,7 @@
       <c r="H32" s="271"/>
       <c r="I32" s="271"/>
       <c r="J32" s="271"/>
-      <c r="K32" s="271">
-        <v>7729.12</v>
-      </c>
+      <c r="K32" s="271"/>
       <c r="L32" s="271"/>
       <c r="M32" s="248"/>
       <c r="N32" s="51"/>
@@ -4853,9 +4777,7 @@
       <c r="H33" s="271"/>
       <c r="I33" s="271"/>
       <c r="J33" s="271"/>
-      <c r="K33" s="271">
-        <v>5822.42</v>
-      </c>
+      <c r="K33" s="271"/>
       <c r="L33" s="271"/>
       <c r="M33" s="248"/>
       <c r="N33" s="51"/>
@@ -4871,9 +4793,7 @@
       <c r="H34" s="271"/>
       <c r="I34" s="271"/>
       <c r="J34" s="271"/>
-      <c r="K34" s="271">
-        <v>10760.39</v>
-      </c>
+      <c r="K34" s="271"/>
       <c r="L34" s="271"/>
       <c r="M34" s="248"/>
       <c r="N34" s="51"/>
@@ -4889,9 +4809,7 @@
       <c r="H35" s="271"/>
       <c r="I35" s="271"/>
       <c r="J35" s="271"/>
-      <c r="K35" s="271">
-        <v>47658</v>
-      </c>
+      <c r="K35" s="271"/>
       <c r="L35" s="271"/>
       <c r="M35" s="248"/>
       <c r="N35" s="51"/>
@@ -4907,10 +4825,7 @@
       <c r="H36" s="271"/>
       <c r="I36" s="271"/>
       <c r="J36" s="271"/>
-      <c r="K36" s="271">
-        <f>SUM(K14:K35)</f>
-        <v>476117.56999999995</v>
-      </c>
+      <c r="K36" s="271"/>
       <c r="L36" s="271"/>
       <c r="M36" s="248"/>
       <c r="N36" s="51"/>
@@ -4926,9 +4841,7 @@
       <c r="H37" s="271"/>
       <c r="I37" s="271"/>
       <c r="J37" s="271"/>
-      <c r="K37" s="271">
-        <v>-11999.87</v>
-      </c>
+      <c r="K37" s="271"/>
       <c r="L37" s="271"/>
       <c r="M37" s="248"/>
       <c r="N37" s="51"/>
@@ -4944,10 +4857,7 @@
       <c r="H38" s="270"/>
       <c r="I38" s="312"/>
       <c r="J38" s="284"/>
-      <c r="K38" s="359">
-        <f>SUM(K36:K37)</f>
-        <v>464117.69999999995</v>
-      </c>
+      <c r="K38" s="359"/>
       <c r="L38" s="364"/>
       <c r="M38" s="248"/>
       <c r="N38" s="51"/>
@@ -4978,9 +4888,7 @@
       <c r="G40" s="284"/>
       <c r="H40" s="270"/>
       <c r="I40" s="312"/>
-      <c r="J40" s="284">
-        <v>480632.66</v>
-      </c>
+      <c r="J40" s="284"/>
       <c r="K40" s="359"/>
       <c r="L40" s="364"/>
       <c r="M40" s="248"/>
@@ -4996,12 +4904,8 @@
       <c r="G41" s="284"/>
       <c r="H41" s="284"/>
       <c r="I41" s="312"/>
-      <c r="J41" s="284">
-        <v>464117.7</v>
-      </c>
-      <c r="K41" s="359">
-        <v>100000</v>
-      </c>
+      <c r="J41" s="284"/>
+      <c r="K41" s="359"/>
       <c r="L41" s="364"/>
       <c r="M41" s="248"/>
       <c r="N41" s="51"/>
@@ -5016,12 +4920,8 @@
       <c r="G42" s="284"/>
       <c r="H42" s="284"/>
       <c r="I42" s="284"/>
-      <c r="J42" s="284">
-        <v>-655633</v>
-      </c>
-      <c r="K42" s="359">
-        <v>40000</v>
-      </c>
+      <c r="J42" s="284"/>
+      <c r="K42" s="359"/>
       <c r="L42" s="364"/>
       <c r="M42" s="248"/>
       <c r="N42" s="51"/>
@@ -5036,13 +4936,8 @@
       <c r="G43" s="315"/>
       <c r="H43" s="284"/>
       <c r="I43" s="284"/>
-      <c r="J43" s="270">
-        <f>SUM(J40:J42)</f>
-        <v>289117.36</v>
-      </c>
-      <c r="K43" s="359">
-        <v>515633</v>
-      </c>
+      <c r="J43" s="270"/>
+      <c r="K43" s="359"/>
       <c r="L43" s="364"/>
       <c r="M43" s="248"/>
       <c r="N43" s="51"/>
@@ -5060,10 +4955,7 @@
       <c r="H44" s="315"/>
       <c r="I44" s="315"/>
       <c r="J44" s="284"/>
-      <c r="K44" s="359">
-        <f>SUM(K41:K43)</f>
-        <v>655633</v>
-      </c>
+      <c r="K44" s="359"/>
       <c r="L44" s="364"/>
       <c r="M44" s="248"/>
       <c r="N44" s="51"/>
@@ -5127,7 +5019,7 @@
       <c r="D47" s="270"/>
       <c r="E47" s="284"/>
       <c r="F47" s="349" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G47" s="329"/>
       <c r="H47" s="327"/>
@@ -5343,10 +5235,10 @@
         <v>3801.42</v>
       </c>
       <c r="E58" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="382" t="s">
         <v>196</v>
-      </c>
-      <c r="F58" s="382" t="s">
-        <v>197</v>
       </c>
       <c r="G58" s="98"/>
       <c r="H58" s="98"/>
@@ -5367,13 +5259,13 @@
         <v>6644.52</v>
       </c>
       <c r="E59" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="F59" s="383" t="s">
         <v>196</v>
       </c>
-      <c r="F59" s="383" t="s">
+      <c r="G59" s="98" t="s">
         <v>197</v>
-      </c>
-      <c r="G59" s="98" t="s">
-        <v>198</v>
       </c>
       <c r="H59" s="98"/>
       <c r="I59" s="384"/>
@@ -5393,22 +5285,22 @@
         <v>10760.39</v>
       </c>
       <c r="E60" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" s="383" t="s">
         <v>196</v>
       </c>
-      <c r="F60" s="383" t="s">
+      <c r="G60" s="98" t="s">
         <v>197</v>
       </c>
-      <c r="G60" s="98" t="s">
+      <c r="H60" s="98" t="s">
         <v>198</v>
       </c>
-      <c r="H60" s="98" t="s">
+      <c r="I60" s="385" t="s">
         <v>199</v>
       </c>
-      <c r="I60" s="385" t="s">
+      <c r="J60" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="J60" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="K60" s="51"/>
       <c r="L60" s="248"/>
@@ -5423,22 +5315,22 @@
         <v>19601</v>
       </c>
       <c r="E61" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="F61" s="383" t="s">
         <v>196</v>
       </c>
-      <c r="F61" s="383" t="s">
+      <c r="G61" s="98" t="s">
         <v>197</v>
       </c>
-      <c r="G61" s="98" t="s">
+      <c r="H61" s="98" t="s">
         <v>198</v>
       </c>
-      <c r="H61" s="98" t="s">
+      <c r="I61" s="385" t="s">
         <v>199</v>
       </c>
-      <c r="I61" s="385" t="s">
+      <c r="J61" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="J61" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="K61" s="51"/>
       <c r="L61" s="248"/>
@@ -5456,14 +5348,14 @@
         <v>5822.42</v>
       </c>
       <c r="E62" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="F62" s="383" t="s">
         <v>196</v>
-      </c>
-      <c r="F62" s="383" t="s">
-        <v>197</v>
       </c>
       <c r="G62" s="386"/>
       <c r="H62" s="98" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I62" s="99"/>
       <c r="J62" s="51"/>
@@ -5480,10 +5372,10 @@
         <v>15744.77</v>
       </c>
       <c r="E63" s="386" t="s">
+        <v>195</v>
+      </c>
+      <c r="F63" s="387" t="s">
         <v>196</v>
-      </c>
-      <c r="F63" s="387" t="s">
-        <v>197</v>
       </c>
       <c r="G63" s="393">
         <v>36183.39</v>
@@ -5508,7 +5400,7 @@
         <v>62374.52</v>
       </c>
       <c r="F64" s="393" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G64" s="253"/>
       <c r="H64" s="393">

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -134,6 +134,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="E11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Edgardo Omar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Saldo a favor hasta 07/26
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K11" authorId="0">
       <text>
         <r>
@@ -197,7 +222,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="208">
   <si>
     <t>Servicios</t>
   </si>
@@ -784,27 +809,6 @@
     <t>Comp deb/efec</t>
   </si>
   <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Abr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jun </t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>62,374,52</t>
-  </si>
-  <si>
     <t>Patente</t>
   </si>
   <si>
@@ -812,13 +816,43 @@
   </si>
   <si>
     <t>Serv e Impuestos</t>
+  </si>
+  <si>
+    <t>CHAMPION</t>
+  </si>
+  <si>
+    <t>AGUINALDO</t>
+  </si>
+  <si>
+    <t>Prerstamos</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Cuota</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Vto</t>
+  </si>
+  <si>
+    <t>Frances</t>
+  </si>
+  <si>
+    <t>MercadoPago</t>
+  </si>
+  <si>
+    <t>Carrefour</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="60" x14ac:knownFonts="1">
+  <fonts count="62" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1253,15 +1287,6 @@
     </font>
     <font>
       <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="3" tint="0.39997558519241921"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
@@ -1271,6 +1296,30 @@
     <font>
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1512,7 +1561,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -2081,11 +2130,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="476">
+  <cellXfs count="498">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2535,13 +2666,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="12" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2667,12 +2796,6 @@
     <xf numFmtId="17" fontId="51" fillId="26" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="52" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2684,14 +2807,11 @@
     <xf numFmtId="0" fontId="30" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="38" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="47" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2709,56 +2829,17 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="29" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2785,7 +2866,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2812,18 +2892,11 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2831,9 +2904,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2844,8 +2914,6 @@
     <xf numFmtId="0" fontId="56" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2855,38 +2923,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="29" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="58" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="58" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="28" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2900,6 +2953,114 @@
     <xf numFmtId="2" fontId="53" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="29" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="29" fillId="6" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="29" fillId="6" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="29" fillId="6" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="35" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3652,60 +3813,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>847725</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="1 Flecha a la derecha con muesca"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10334625" y="11630025"/>
-          <a:ext cx="666750" cy="257175"/>
-        </a:xfrm>
-        <a:prstGeom prst="notchedRightArrow">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4129,11 +4236,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="299" t="s">
+      <c r="A1" s="297" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="301"/>
-      <c r="C1" s="376" t="s">
+      <c r="B1" s="299"/>
+      <c r="C1" s="368" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="267" t="s">
@@ -4149,104 +4256,104 @@
         <v>55</v>
       </c>
       <c r="H1" s="274"/>
-      <c r="I1" s="354" t="s">
+      <c r="I1" s="350" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="355" t="s">
+      <c r="J1" s="351" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="408" t="s">
-        <v>202</v>
-      </c>
-      <c r="L1" s="360" t="s">
-        <v>203</v>
+      <c r="K1" s="384" t="s">
+        <v>195</v>
+      </c>
+      <c r="L1" s="355" t="s">
+        <v>196</v>
       </c>
       <c r="M1" s="101"/>
       <c r="N1" s="50"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="291"/>
-      <c r="B2" s="302"/>
-      <c r="C2" s="406"/>
-      <c r="D2" s="402"/>
-      <c r="E2" s="289"/>
-      <c r="F2" s="407"/>
+      <c r="A2" s="289"/>
+      <c r="B2" s="300"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="378"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="383"/>
       <c r="G2" s="198"/>
       <c r="H2" s="271"/>
       <c r="I2" s="270"/>
-      <c r="J2" s="395"/>
-      <c r="K2" s="331"/>
-      <c r="L2" s="416">
+      <c r="J2" s="373"/>
+      <c r="K2" s="329"/>
+      <c r="L2" s="391">
         <v>102247</v>
       </c>
       <c r="M2" s="112"/>
       <c r="N2" s="50"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="291"/>
-      <c r="B3" s="302"/>
-      <c r="C3" s="289"/>
+      <c r="A3" s="289"/>
+      <c r="B3" s="300"/>
+      <c r="C3" s="287"/>
       <c r="D3" s="198"/>
       <c r="E3" s="198"/>
-      <c r="F3" s="290"/>
+      <c r="F3" s="288"/>
       <c r="G3" s="271"/>
       <c r="H3" s="271"/>
       <c r="I3" s="198"/>
-      <c r="J3" s="288"/>
-      <c r="K3" s="331"/>
-      <c r="L3" s="417">
+      <c r="J3" s="286"/>
+      <c r="K3" s="329"/>
+      <c r="L3" s="392">
         <v>67275.839999999997</v>
       </c>
       <c r="M3" s="101"/>
       <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="405" t="s">
+      <c r="A4" s="381" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="271"/>
       <c r="C4" s="150">
-        <v>27000</v>
-      </c>
-      <c r="D4" s="438">
-        <v>17825</v>
-      </c>
-      <c r="E4" s="150">
-        <v>9444.76</v>
-      </c>
-      <c r="F4" s="439">
-        <v>23800</v>
-      </c>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
+        <v>13361.72</v>
+      </c>
+      <c r="D4" s="372" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="457">
+        <v>9588</v>
+      </c>
+      <c r="F4" s="456">
+        <v>23947.99</v>
+      </c>
+      <c r="G4" s="302"/>
+      <c r="H4" s="302"/>
       <c r="I4" s="150">
-        <v>22138.21</v>
+        <v>12165</v>
       </c>
       <c r="J4" s="178">
         <v>5581</v>
       </c>
-      <c r="K4" s="331"/>
-      <c r="L4" s="416">
+      <c r="K4" s="329"/>
+      <c r="L4" s="391">
         <v>236679.18</v>
       </c>
       <c r="M4" s="101"/>
       <c r="N4" s="50"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="291"/>
-      <c r="B5" s="302"/>
-      <c r="C5" s="289"/>
-      <c r="D5" s="289"/>
-      <c r="E5" s="289"/>
-      <c r="F5" s="289">
+      <c r="A5" s="289"/>
+      <c r="B5" s="300"/>
+      <c r="C5" s="287"/>
+      <c r="D5" s="287"/>
+      <c r="E5" s="287"/>
+      <c r="F5" s="287">
         <v>20000</v>
       </c>
       <c r="G5" s="271"/>
       <c r="H5" s="271"/>
-      <c r="I5" s="289"/>
+      <c r="I5" s="287"/>
       <c r="J5" s="271"/>
-      <c r="K5" s="288"/>
-      <c r="L5" s="443">
+      <c r="K5" s="286"/>
+      <c r="L5" s="412">
         <v>130000</v>
       </c>
       <c r="M5" s="101"/>
@@ -4263,16 +4370,16 @@
       <c r="H6" s="271"/>
       <c r="I6" s="271"/>
       <c r="J6" s="271"/>
-      <c r="K6" s="288"/>
-      <c r="L6" s="474">
+      <c r="K6" s="286"/>
+      <c r="L6" s="436">
         <f>SUM(L2:L5)</f>
         <v>536202.02</v>
       </c>
       <c r="M6" s="50"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="291"/>
-      <c r="B7" s="357"/>
+      <c r="A7" s="289"/>
+      <c r="B7" s="353"/>
       <c r="C7" s="262" t="s">
         <v>193</v>
       </c>
@@ -4297,100 +4404,98 @@
       <c r="J7" s="278" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="434" t="s">
+      <c r="K7" s="405" t="s">
         <v>186</v>
       </c>
       <c r="L7" s="271"/>
       <c r="M7" s="248"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="300"/>
-      <c r="B8" s="294"/>
-      <c r="C8" s="290"/>
-      <c r="D8" s="295"/>
-      <c r="E8" s="291"/>
-      <c r="F8" s="291"/>
-      <c r="G8" s="296"/>
-      <c r="H8" s="291"/>
-      <c r="I8" s="291"/>
-      <c r="J8" s="297"/>
-      <c r="K8" s="288"/>
-      <c r="L8" s="475"/>
+      <c r="A8" s="298"/>
+      <c r="B8" s="292"/>
+      <c r="C8" s="288"/>
+      <c r="D8" s="293"/>
+      <c r="E8" s="289"/>
+      <c r="F8" s="289"/>
+      <c r="G8" s="294"/>
+      <c r="H8" s="289"/>
+      <c r="I8" s="289"/>
+      <c r="J8" s="295"/>
+      <c r="K8" s="286"/>
+      <c r="L8" s="437"/>
       <c r="M8" s="248"/>
       <c r="N8" s="51"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="291"/>
-      <c r="B9" s="435">
+      <c r="A9" s="289"/>
+      <c r="B9" s="406">
         <v>1</v>
       </c>
-      <c r="C9" s="446">
-        <v>136200</v>
-      </c>
-      <c r="D9" s="412"/>
-      <c r="E9" s="292"/>
-      <c r="F9" s="292"/>
-      <c r="G9" s="289"/>
-      <c r="H9" s="292"/>
-      <c r="I9" s="292"/>
-      <c r="J9" s="293"/>
-      <c r="K9" s="288"/>
-      <c r="L9" s="442"/>
+      <c r="C9" s="479">
+        <v>107000</v>
+      </c>
+      <c r="D9" s="387"/>
+      <c r="E9" s="290"/>
+      <c r="F9" s="290"/>
+      <c r="G9" s="287"/>
+      <c r="H9" s="290"/>
+      <c r="I9" s="290"/>
+      <c r="J9" s="291"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="411"/>
       <c r="M9" s="248"/>
       <c r="N9" s="51"/>
     </row>
     <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="291"/>
-      <c r="B10" s="435">
+      <c r="A10" s="289"/>
+      <c r="B10" s="406">
         <v>2</v>
       </c>
-      <c r="C10" s="447">
-        <v>50000</v>
-      </c>
-      <c r="D10" s="409"/>
-      <c r="E10" s="295"/>
-      <c r="F10" s="292"/>
-      <c r="G10" s="292"/>
-      <c r="H10" s="292"/>
-      <c r="I10" s="292"/>
-      <c r="J10" s="452"/>
-      <c r="K10" s="453">
+      <c r="C10" s="287">
+        <v>107000</v>
+      </c>
+      <c r="D10" s="385"/>
+      <c r="E10" s="293"/>
+      <c r="F10" s="290"/>
+      <c r="G10" s="290"/>
+      <c r="H10" s="290"/>
+      <c r="I10" s="290"/>
+      <c r="J10" s="416"/>
+      <c r="K10" s="417">
         <v>69853</v>
       </c>
       <c r="L10" s="271"/>
-      <c r="M10" s="472"/>
+      <c r="M10" s="434"/>
       <c r="N10" s="51"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="291"/>
-      <c r="B11" s="435">
+      <c r="A11" s="289"/>
+      <c r="B11" s="406">
         <v>3</v>
       </c>
-      <c r="C11" s="446">
-        <v>200000</v>
-      </c>
-      <c r="D11" s="410">
-        <v>290000</v>
-      </c>
-      <c r="E11" s="375">
-        <v>592</v>
-      </c>
-      <c r="F11" s="418">
-        <v>303674</v>
-      </c>
-      <c r="G11" s="150">
-        <v>406202.02</v>
-      </c>
-      <c r="H11" s="295">
+      <c r="C11" s="287">
+        <v>107000</v>
+      </c>
+      <c r="D11" s="386">
+        <v>257883</v>
+      </c>
+      <c r="E11" s="460">
+        <v>500</v>
+      </c>
+      <c r="F11" s="393">
+        <v>440000</v>
+      </c>
+      <c r="G11" s="287"/>
+      <c r="H11" s="293">
         <v>0</v>
       </c>
-      <c r="I11" s="418">
-        <v>266991</v>
-      </c>
-      <c r="J11" s="293">
+      <c r="I11" s="393">
+        <v>92416</v>
+      </c>
+      <c r="J11" s="291">
         <v>55747</v>
       </c>
-      <c r="K11" s="454">
+      <c r="K11" s="458">
         <v>13800</v>
       </c>
       <c r="L11" s="271"/>
@@ -4399,164 +4504,172 @@
     </row>
     <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="273"/>
-      <c r="B12" s="436">
+      <c r="B12" s="407">
         <v>4</v>
       </c>
-      <c r="C12" s="450">
-        <v>151000</v>
-      </c>
-      <c r="D12" s="415"/>
-      <c r="E12" s="292"/>
-      <c r="F12" s="459"/>
-      <c r="G12" s="394"/>
-      <c r="H12" s="304"/>
-      <c r="I12" s="419"/>
-      <c r="J12" s="288"/>
-      <c r="K12" s="288"/>
+      <c r="C12" s="287">
+        <v>107000</v>
+      </c>
+      <c r="D12" s="390"/>
+      <c r="E12" s="290"/>
+      <c r="F12" s="455"/>
+      <c r="G12" s="372"/>
+      <c r="H12" s="302"/>
+      <c r="I12" s="394"/>
+      <c r="J12" s="286"/>
+      <c r="K12" s="286"/>
       <c r="L12" s="271"/>
-      <c r="M12" s="472"/>
+      <c r="M12" s="434"/>
       <c r="N12" s="51"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="270"/>
-      <c r="B13" s="437">
+      <c r="B13" s="408">
         <v>5</v>
       </c>
-      <c r="C13" s="451">
-        <f>SUM(C9:C12)</f>
-        <v>537200</v>
-      </c>
-      <c r="D13" s="431"/>
+      <c r="C13" s="287">
+        <v>107000</v>
+      </c>
+      <c r="D13" s="403"/>
       <c r="E13" s="277"/>
-      <c r="F13" s="418"/>
-      <c r="G13" s="305"/>
-      <c r="H13" s="328"/>
-      <c r="I13" s="420"/>
-      <c r="J13" s="306"/>
-      <c r="K13" s="288"/>
-      <c r="L13" s="469"/>
+      <c r="F13" s="393"/>
+      <c r="G13" s="303"/>
+      <c r="H13" s="326"/>
+      <c r="I13" s="395"/>
+      <c r="J13" s="304"/>
+      <c r="K13" s="286"/>
+      <c r="L13" s="431"/>
       <c r="M13" s="248"/>
       <c r="N13" s="51"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="270"/>
-      <c r="B14" s="308"/>
-      <c r="C14" s="432"/>
-      <c r="D14" s="440"/>
-      <c r="E14" s="331"/>
-      <c r="F14" s="433"/>
-      <c r="G14" s="304"/>
-      <c r="H14" s="328"/>
-      <c r="I14" s="421"/>
-      <c r="J14" s="330"/>
-      <c r="K14" s="406"/>
-      <c r="L14" s="470"/>
-      <c r="M14" s="449"/>
+      <c r="B14" s="306"/>
+      <c r="C14" s="404">
+        <f>SUM(C9:C13)</f>
+        <v>535000</v>
+      </c>
+      <c r="D14" s="409"/>
+      <c r="E14" s="439"/>
+      <c r="F14" s="440"/>
+      <c r="G14" s="369"/>
+      <c r="H14" s="326"/>
+      <c r="I14" s="396"/>
+      <c r="J14" s="328"/>
+      <c r="K14" s="382"/>
+      <c r="L14" s="432"/>
+      <c r="M14" s="415"/>
       <c r="N14" s="51"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="270"/>
-      <c r="B15" s="308"/>
-      <c r="C15" s="413"/>
-      <c r="D15" s="305"/>
-      <c r="E15" s="398"/>
-      <c r="F15" s="448"/>
-      <c r="G15" s="304"/>
-      <c r="H15" s="399"/>
-      <c r="I15" s="418"/>
-      <c r="J15" s="400"/>
-      <c r="K15" s="461"/>
-      <c r="L15" s="470"/>
+      <c r="B15" s="306"/>
+      <c r="C15" s="388"/>
+      <c r="D15" s="326"/>
+      <c r="E15" s="442" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="443">
+        <v>5000000</v>
+      </c>
+      <c r="G15" s="444" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="375"/>
+      <c r="I15" s="393"/>
+      <c r="J15" s="376"/>
+      <c r="K15" s="423"/>
+      <c r="L15" s="432"/>
       <c r="M15" s="248"/>
       <c r="N15" s="51"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="271"/>
-      <c r="B16" s="288"/>
-      <c r="C16" s="414"/>
-      <c r="D16" s="305"/>
-      <c r="E16" s="398"/>
-      <c r="F16" s="358"/>
-      <c r="G16" s="394"/>
-      <c r="H16" s="467"/>
-      <c r="I16" s="442"/>
-      <c r="J16" s="368"/>
-      <c r="K16" s="462"/>
-      <c r="L16" s="470"/>
-      <c r="M16" s="444"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="389"/>
+      <c r="D16" s="326"/>
+      <c r="E16" s="445"/>
+      <c r="F16" s="446"/>
+      <c r="G16" s="447"/>
+      <c r="H16" s="429"/>
+      <c r="I16" s="411"/>
+      <c r="J16" s="361"/>
+      <c r="K16" s="424"/>
+      <c r="L16" s="432"/>
+      <c r="M16" s="413"/>
       <c r="N16" s="51"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="271"/>
-      <c r="B17" s="288"/>
+      <c r="B17" s="286"/>
       <c r="C17" s="271"/>
-      <c r="D17" s="305"/>
-      <c r="E17" s="308"/>
-      <c r="F17" s="358"/>
-      <c r="G17" s="304"/>
-      <c r="H17" s="468"/>
-      <c r="I17" s="441"/>
-      <c r="J17" s="422"/>
-      <c r="K17" s="461"/>
-      <c r="L17" s="470"/>
-      <c r="M17" s="473"/>
+      <c r="D17" s="326"/>
+      <c r="E17" s="448"/>
+      <c r="F17" s="446"/>
+      <c r="G17" s="449"/>
+      <c r="H17" s="430"/>
+      <c r="I17" s="410"/>
+      <c r="J17" s="397"/>
+      <c r="K17" s="423"/>
+      <c r="L17" s="432"/>
+      <c r="M17" s="435"/>
       <c r="N17" s="248"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="402"/>
-      <c r="B18" s="404"/>
-      <c r="C18" s="403"/>
-      <c r="D18" s="304"/>
-      <c r="E18" s="282"/>
-      <c r="F18" s="411"/>
-      <c r="G18" s="304"/>
-      <c r="H18" s="397"/>
+      <c r="A18" s="378"/>
+      <c r="B18" s="380"/>
+      <c r="C18" s="379"/>
+      <c r="D18" s="329"/>
+      <c r="E18" s="450"/>
+      <c r="F18" s="451"/>
+      <c r="G18" s="449"/>
+      <c r="H18" s="374"/>
       <c r="I18" s="111"/>
       <c r="J18" s="111"/>
-      <c r="K18" s="462"/>
-      <c r="L18" s="470"/>
-      <c r="M18" s="388"/>
+      <c r="K18" s="424"/>
+      <c r="L18" s="432"/>
+      <c r="M18" s="371"/>
       <c r="N18" s="51"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="307"/>
-      <c r="B19" s="308"/>
-      <c r="C19" s="367"/>
-      <c r="D19" s="366"/>
-      <c r="E19" s="368"/>
-      <c r="F19" s="358"/>
-      <c r="G19" s="304"/>
-      <c r="H19" s="371"/>
-      <c r="I19" s="370"/>
-      <c r="J19" s="370"/>
-      <c r="K19" s="461"/>
-      <c r="L19" s="470"/>
+    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="305"/>
+      <c r="B19" s="306"/>
+      <c r="C19" s="360"/>
+      <c r="D19" s="438"/>
+      <c r="E19" s="452"/>
+      <c r="F19" s="453"/>
+      <c r="G19" s="454"/>
+      <c r="H19" s="364"/>
+      <c r="I19" s="363"/>
+      <c r="J19" s="363"/>
+      <c r="K19" s="423"/>
+      <c r="L19" s="432"/>
       <c r="M19" s="248"/>
       <c r="N19" s="51"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="306"/>
-      <c r="B20" s="308"/>
-      <c r="C20" s="353"/>
-      <c r="D20" s="370"/>
-      <c r="E20" s="281"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="338"/>
-      <c r="H20" s="282"/>
+      <c r="A20" s="304"/>
+      <c r="B20" s="306"/>
+      <c r="C20" s="349"/>
+      <c r="D20" s="363"/>
+      <c r="E20" s="441"/>
+      <c r="F20" s="363"/>
+      <c r="G20" s="336"/>
+      <c r="H20" s="281"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="461"/>
-      <c r="L20" s="470"/>
+      <c r="K20" s="423"/>
+      <c r="L20" s="432"/>
       <c r="M20" s="248"/>
       <c r="N20" s="51"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="307"/>
-      <c r="B21" s="303"/>
-      <c r="C21" s="401" t="s">
+      <c r="A21" s="305"/>
+      <c r="B21" s="301"/>
+      <c r="C21" s="377" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="430" t="s">
+      <c r="D21" s="402" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="272" t="s">
@@ -4568,153 +4681,149 @@
       <c r="G21" s="266" t="s">
         <v>58</v>
       </c>
-      <c r="H21" s="356" t="s">
+      <c r="H21" s="352" t="s">
         <v>80</v>
       </c>
       <c r="I21" s="269" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="298" t="s">
+      <c r="J21" s="296" t="s">
         <v>172</v>
       </c>
-      <c r="K21" s="463"/>
-      <c r="L21" s="471"/>
+      <c r="K21" s="425"/>
+      <c r="L21" s="433"/>
       <c r="M21" s="248"/>
       <c r="N21" s="51"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="291"/>
-      <c r="B22" s="309"/>
-      <c r="C22" s="310"/>
-      <c r="D22" s="445">
-        <v>7500</v>
-      </c>
-      <c r="E22" s="284"/>
-      <c r="F22" s="284"/>
-      <c r="G22" s="394">
-        <v>33000</v>
-      </c>
-      <c r="H22" s="394">
+      <c r="A22" s="289"/>
+      <c r="B22" s="307"/>
+      <c r="C22" s="308"/>
+      <c r="D22" s="388">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="283"/>
+      <c r="F22" s="283"/>
+      <c r="G22" s="372"/>
+      <c r="H22" s="372">
         <v>59159</v>
       </c>
-      <c r="I22" s="284"/>
-      <c r="J22" s="284"/>
-      <c r="K22" s="464"/>
-      <c r="L22" s="471"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="283"/>
+      <c r="K22" s="426"/>
+      <c r="L22" s="433"/>
       <c r="M22" s="248"/>
       <c r="N22" s="51"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="304"/>
-      <c r="B23" s="309"/>
-      <c r="C23" s="310"/>
-      <c r="D23" s="439">
-        <v>7500</v>
-      </c>
-      <c r="E23" s="287"/>
-      <c r="F23" s="284"/>
-      <c r="G23" s="284"/>
-      <c r="H23" s="284"/>
-      <c r="I23" s="284"/>
-      <c r="J23" s="284"/>
-      <c r="K23" s="461"/>
-      <c r="L23" s="471"/>
+      <c r="A23" s="302"/>
+      <c r="B23" s="307"/>
+      <c r="C23" s="308"/>
+      <c r="D23" s="383"/>
+      <c r="E23" s="285"/>
+      <c r="F23" s="283"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="283"/>
+      <c r="I23" s="283"/>
+      <c r="J23" s="461"/>
+      <c r="K23" s="423"/>
+      <c r="L23" s="433"/>
       <c r="M23" s="248"/>
       <c r="N23" s="51"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="304"/>
-      <c r="B24" s="309"/>
-      <c r="C24" s="310"/>
-      <c r="D24" s="310"/>
-      <c r="E24" s="284"/>
-      <c r="F24" s="284"/>
-      <c r="G24" s="284"/>
-      <c r="H24" s="284"/>
-      <c r="I24" s="284"/>
-      <c r="J24" s="284"/>
-      <c r="K24" s="461"/>
-      <c r="L24" s="471"/>
+      <c r="A24" s="302"/>
+      <c r="B24" s="307"/>
+      <c r="C24" s="308"/>
+      <c r="D24" s="308"/>
+      <c r="E24" s="354"/>
+      <c r="F24" s="271"/>
+      <c r="G24" s="271"/>
+      <c r="H24" s="271"/>
+      <c r="I24" s="271"/>
+      <c r="J24" s="271"/>
+      <c r="K24" s="423"/>
+      <c r="L24" s="433"/>
       <c r="M24" s="248"/>
       <c r="N24" s="51"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="304"/>
-      <c r="B25" s="311"/>
-      <c r="C25" s="310"/>
-      <c r="D25" s="310"/>
-      <c r="E25" s="284"/>
-      <c r="F25" s="284"/>
-      <c r="G25" s="284"/>
-      <c r="H25" s="284"/>
-      <c r="I25" s="284"/>
-      <c r="J25" s="284"/>
-      <c r="K25" s="461"/>
-      <c r="L25" s="456"/>
+      <c r="A25" s="302"/>
+      <c r="B25" s="309"/>
+      <c r="C25" s="308"/>
+      <c r="D25" s="308"/>
+      <c r="E25" s="354"/>
+      <c r="F25" s="271"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="271"/>
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="423"/>
+      <c r="L25" s="419"/>
       <c r="M25" s="248"/>
       <c r="N25" s="51"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="304"/>
-      <c r="B26" s="311"/>
-      <c r="C26" s="310"/>
-      <c r="D26" s="310"/>
-      <c r="E26" s="284"/>
-      <c r="F26" s="285"/>
-      <c r="G26" s="284"/>
-      <c r="H26" s="284"/>
-      <c r="I26" s="284"/>
-      <c r="J26" s="284"/>
-      <c r="K26" s="461"/>
-      <c r="L26" s="457"/>
+      <c r="A26" s="302"/>
+      <c r="B26" s="309"/>
+      <c r="C26" s="308"/>
+      <c r="D26" s="308"/>
+      <c r="E26" s="354"/>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="423"/>
+      <c r="L26" s="420"/>
       <c r="M26" s="248"/>
       <c r="N26" s="51"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="377"/>
-      <c r="B27" s="378"/>
-      <c r="C27" s="310"/>
-      <c r="D27" s="284"/>
-      <c r="E27" s="284"/>
-      <c r="F27" s="284"/>
-      <c r="G27" s="284"/>
-      <c r="H27" s="284"/>
-      <c r="I27" s="284"/>
-      <c r="J27" s="284"/>
-      <c r="K27" s="461"/>
-      <c r="L27" s="455"/>
+      <c r="A27" s="369"/>
+      <c r="B27" s="370"/>
+      <c r="C27" s="308"/>
+      <c r="D27" s="283"/>
+      <c r="E27" s="277"/>
+      <c r="F27" s="271"/>
+      <c r="G27" s="271"/>
+      <c r="H27" s="271"/>
+      <c r="I27" s="271"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="423"/>
+      <c r="L27" s="418"/>
       <c r="M27" s="248"/>
       <c r="N27" s="51"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="277"/>
       <c r="B28" s="273"/>
-      <c r="C28" s="423"/>
-      <c r="D28" s="350"/>
-      <c r="E28" s="315"/>
-      <c r="F28" s="424"/>
-      <c r="G28" s="379"/>
-      <c r="H28" s="315"/>
-      <c r="I28" s="315"/>
-      <c r="J28" s="315"/>
-      <c r="K28" s="465"/>
-      <c r="L28" s="446"/>
+      <c r="C28" s="398"/>
+      <c r="D28" s="348"/>
+      <c r="E28" s="480"/>
+      <c r="F28" s="271"/>
+      <c r="G28" s="271"/>
+      <c r="H28" s="271"/>
+      <c r="I28" s="271"/>
+      <c r="J28" s="271"/>
+      <c r="K28" s="427"/>
+      <c r="L28" s="414"/>
       <c r="M28" s="248"/>
       <c r="N28" s="51"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="425"/>
+      <c r="A29" s="399"/>
       <c r="B29" s="271"/>
-      <c r="C29" s="426"/>
-      <c r="D29" s="427"/>
-      <c r="E29" s="428"/>
-      <c r="F29" s="428"/>
-      <c r="G29" s="429"/>
-      <c r="H29" s="198"/>
-      <c r="I29" s="427"/>
-      <c r="J29" s="427"/>
-      <c r="K29" s="466"/>
-      <c r="L29" s="458"/>
+      <c r="C29" s="400"/>
+      <c r="D29" s="401"/>
+      <c r="E29" s="481"/>
+      <c r="F29" s="271"/>
+      <c r="G29" s="271"/>
+      <c r="H29" s="271"/>
+      <c r="I29" s="271"/>
+      <c r="J29" s="271"/>
+      <c r="K29" s="428"/>
+      <c r="L29" s="421"/>
       <c r="M29" s="248"/>
       <c r="N29" s="51"/>
     </row>
@@ -4723,13 +4832,13 @@
       <c r="B30" s="271"/>
       <c r="C30" s="271"/>
       <c r="D30" s="271"/>
-      <c r="E30" s="271"/>
+      <c r="E30" s="286"/>
       <c r="F30" s="271"/>
       <c r="G30" s="271"/>
       <c r="H30" s="271"/>
       <c r="I30" s="271"/>
       <c r="J30" s="271"/>
-      <c r="K30" s="460"/>
+      <c r="K30" s="422"/>
       <c r="L30" s="271"/>
       <c r="M30" s="248"/>
       <c r="N30" s="51"/>
@@ -4738,14 +4847,16 @@
       <c r="A31" s="271"/>
       <c r="B31" s="271"/>
       <c r="C31" s="271"/>
-      <c r="D31" s="271"/>
-      <c r="E31" s="271"/>
-      <c r="F31" s="271"/>
-      <c r="G31" s="271"/>
-      <c r="H31" s="271"/>
+      <c r="D31" s="283"/>
+      <c r="E31" s="354" t="s">
+        <v>200</v>
+      </c>
+      <c r="F31" s="401"/>
+      <c r="G31" s="401"/>
+      <c r="H31" s="459"/>
       <c r="I31" s="271"/>
       <c r="J31" s="271"/>
-      <c r="K31" s="460"/>
+      <c r="K31" s="422"/>
       <c r="L31" s="271"/>
       <c r="M31" s="248"/>
       <c r="N31" s="51"/>
@@ -4754,11 +4865,11 @@
       <c r="A32" s="271"/>
       <c r="B32" s="271"/>
       <c r="C32" s="271"/>
-      <c r="D32" s="271"/>
-      <c r="E32" s="271"/>
-      <c r="F32" s="271"/>
-      <c r="G32" s="271"/>
-      <c r="H32" s="271"/>
+      <c r="D32" s="283"/>
+      <c r="E32" s="354"/>
+      <c r="F32" s="401"/>
+      <c r="G32" s="459"/>
+      <c r="H32" s="459"/>
       <c r="I32" s="271"/>
       <c r="J32" s="271"/>
       <c r="K32" s="271"/>
@@ -4770,11 +4881,19 @@
       <c r="A33" s="271"/>
       <c r="B33" s="271"/>
       <c r="C33" s="271"/>
-      <c r="D33" s="271"/>
-      <c r="E33" s="271"/>
-      <c r="F33" s="271"/>
-      <c r="G33" s="271"/>
-      <c r="H33" s="271"/>
+      <c r="D33" s="470"/>
+      <c r="E33" s="471" t="s">
+        <v>201</v>
+      </c>
+      <c r="F33" s="459" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="459" t="s">
+        <v>203</v>
+      </c>
+      <c r="H33" s="459" t="s">
+        <v>204</v>
+      </c>
       <c r="I33" s="271"/>
       <c r="J33" s="271"/>
       <c r="K33" s="271"/>
@@ -4786,13 +4905,23 @@
       <c r="A34" s="271"/>
       <c r="B34" s="271"/>
       <c r="C34" s="271"/>
-      <c r="D34" s="271"/>
-      <c r="E34" s="271"/>
-      <c r="F34" s="271"/>
-      <c r="G34" s="271"/>
-      <c r="H34" s="271"/>
-      <c r="I34" s="271"/>
-      <c r="J34" s="271"/>
+      <c r="D34" s="461" t="s">
+        <v>205</v>
+      </c>
+      <c r="E34" s="464">
+        <v>466976.92</v>
+      </c>
+      <c r="F34" s="482">
+        <v>100649</v>
+      </c>
+      <c r="G34" s="459">
+        <v>5</v>
+      </c>
+      <c r="H34" s="483">
+        <v>20</v>
+      </c>
+      <c r="I34" s="279"/>
+      <c r="J34" s="279"/>
       <c r="K34" s="271"/>
       <c r="L34" s="271"/>
       <c r="M34" s="248"/>
@@ -4802,12 +4931,22 @@
       <c r="A35" s="271"/>
       <c r="B35" s="271"/>
       <c r="C35" s="271"/>
-      <c r="D35" s="271"/>
-      <c r="E35" s="271"/>
-      <c r="F35" s="271"/>
-      <c r="G35" s="271"/>
-      <c r="H35" s="271"/>
-      <c r="I35" s="271"/>
+      <c r="D35" s="461" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" s="468">
+        <v>815680.37</v>
+      </c>
+      <c r="F35" s="465">
+        <v>67064.67</v>
+      </c>
+      <c r="G35" s="462">
+        <v>31</v>
+      </c>
+      <c r="H35" s="462">
+        <v>7</v>
+      </c>
+      <c r="I35" s="279"/>
       <c r="J35" s="271"/>
       <c r="K35" s="271"/>
       <c r="L35" s="271"/>
@@ -4818,12 +4957,22 @@
       <c r="A36" s="271"/>
       <c r="B36" s="271"/>
       <c r="C36" s="271"/>
-      <c r="D36" s="271"/>
-      <c r="E36" s="271"/>
-      <c r="F36" s="271"/>
-      <c r="G36" s="271"/>
-      <c r="H36" s="271"/>
-      <c r="I36" s="271"/>
+      <c r="D36" s="461" t="s">
+        <v>205</v>
+      </c>
+      <c r="E36" s="469">
+        <v>3073505.09</v>
+      </c>
+      <c r="F36" s="469">
+        <v>235697.3</v>
+      </c>
+      <c r="G36" s="459">
+        <v>25</v>
+      </c>
+      <c r="H36" s="459">
+        <v>20</v>
+      </c>
+      <c r="I36" s="279"/>
       <c r="J36" s="271"/>
       <c r="K36" s="271"/>
       <c r="L36" s="271"/>
@@ -4834,13 +4983,23 @@
       <c r="A37" s="271"/>
       <c r="B37" s="271"/>
       <c r="C37" s="271"/>
-      <c r="D37" s="271"/>
-      <c r="E37" s="271"/>
-      <c r="F37" s="271"/>
-      <c r="G37" s="271"/>
-      <c r="H37" s="271"/>
-      <c r="I37" s="271"/>
-      <c r="J37" s="271"/>
+      <c r="D37" s="289" t="s">
+        <v>206</v>
+      </c>
+      <c r="E37" s="466">
+        <v>698529.91</v>
+      </c>
+      <c r="F37" s="466">
+        <v>69852.990000000005</v>
+      </c>
+      <c r="G37" s="279">
+        <v>9</v>
+      </c>
+      <c r="H37" s="279">
+        <v>15</v>
+      </c>
+      <c r="I37" s="279"/>
+      <c r="J37" s="279"/>
       <c r="K37" s="271"/>
       <c r="L37" s="271"/>
       <c r="M37" s="248"/>
@@ -4848,1242 +5007,1150 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="270"/>
-      <c r="B38" s="304"/>
-      <c r="C38" s="310"/>
-      <c r="D38" s="312"/>
-      <c r="E38" s="284"/>
-      <c r="F38" s="359"/>
-      <c r="G38" s="380"/>
-      <c r="H38" s="270"/>
-      <c r="I38" s="312"/>
-      <c r="J38" s="284"/>
-      <c r="K38" s="359"/>
-      <c r="L38" s="364"/>
+      <c r="B38" s="302"/>
+      <c r="C38" s="308"/>
+      <c r="D38" s="289" t="s">
+        <v>206</v>
+      </c>
+      <c r="E38" s="466">
+        <v>98848.21</v>
+      </c>
+      <c r="F38" s="277">
+        <v>13835</v>
+      </c>
+      <c r="G38" s="279">
+        <v>7</v>
+      </c>
+      <c r="H38" s="279">
+        <v>15</v>
+      </c>
+      <c r="I38" s="463"/>
+      <c r="J38" s="461"/>
+      <c r="K38" s="354"/>
+      <c r="L38" s="496"/>
       <c r="M38" s="248"/>
       <c r="N38" s="51"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="306"/>
-      <c r="B39" s="304"/>
-      <c r="C39" s="313"/>
-      <c r="D39" s="312"/>
-      <c r="E39" s="284"/>
-      <c r="F39" s="359"/>
-      <c r="G39" s="381"/>
-      <c r="H39" s="270"/>
-      <c r="I39" s="312"/>
-      <c r="J39" s="284"/>
-      <c r="K39" s="359"/>
-      <c r="L39" s="364"/>
+    <row r="39" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="304"/>
+      <c r="B39" s="302"/>
+      <c r="C39" s="311"/>
+      <c r="D39" s="472" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" s="478">
+        <v>746515</v>
+      </c>
+      <c r="F39" s="475">
+        <v>131515</v>
+      </c>
+      <c r="G39" s="279">
+        <v>11</v>
+      </c>
+      <c r="H39" s="473">
+        <v>5</v>
+      </c>
+      <c r="I39" s="310"/>
+      <c r="J39" s="283"/>
+      <c r="K39" s="354"/>
+      <c r="L39" s="496"/>
       <c r="M39" s="248"/>
       <c r="N39" s="51"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="306"/>
-      <c r="B40" s="304"/>
-      <c r="C40" s="310"/>
-      <c r="D40" s="312"/>
-      <c r="E40" s="284"/>
-      <c r="F40" s="359"/>
-      <c r="G40" s="284"/>
-      <c r="H40" s="270"/>
-      <c r="I40" s="312"/>
-      <c r="J40" s="284"/>
-      <c r="K40" s="359"/>
-      <c r="L40" s="364"/>
+    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="304"/>
+      <c r="B40" s="302"/>
+      <c r="C40" s="308"/>
+      <c r="D40" s="477"/>
+      <c r="E40" s="476">
+        <f>SUM(E34:E39)</f>
+        <v>5900055.5</v>
+      </c>
+      <c r="F40" s="476">
+        <f>SUM(F34:F39)</f>
+        <v>618613.96</v>
+      </c>
+      <c r="G40" s="474"/>
+      <c r="H40" s="279"/>
+      <c r="I40" s="310"/>
+      <c r="J40" s="283"/>
+      <c r="K40" s="354"/>
+      <c r="L40" s="496"/>
       <c r="M40" s="248"/>
       <c r="N40" s="51"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="314"/>
-      <c r="B41" s="304"/>
-      <c r="C41" s="310"/>
-      <c r="D41" s="312"/>
-      <c r="E41" s="284"/>
-      <c r="F41" s="359"/>
-      <c r="G41" s="284"/>
-      <c r="H41" s="284"/>
-      <c r="I41" s="312"/>
-      <c r="J41" s="284"/>
-      <c r="K41" s="359"/>
-      <c r="L41" s="364"/>
+      <c r="A41" s="312"/>
+      <c r="B41" s="302"/>
+      <c r="C41" s="308"/>
+      <c r="D41" s="310"/>
+      <c r="E41" s="283"/>
+      <c r="F41" s="471"/>
+      <c r="G41" s="464"/>
+      <c r="H41" s="283"/>
+      <c r="I41" s="310"/>
+      <c r="J41" s="283"/>
+      <c r="K41" s="354"/>
+      <c r="L41" s="496"/>
       <c r="M41" s="248"/>
       <c r="N41" s="51"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="306"/>
-      <c r="B42" s="304"/>
-      <c r="C42" s="310"/>
-      <c r="D42" s="312"/>
-      <c r="E42" s="284"/>
-      <c r="F42" s="284"/>
-      <c r="G42" s="284"/>
-      <c r="H42" s="284"/>
-      <c r="I42" s="284"/>
-      <c r="J42" s="284"/>
-      <c r="K42" s="359"/>
-      <c r="L42" s="364"/>
+      <c r="A42" s="304"/>
+      <c r="B42" s="302"/>
+      <c r="C42" s="308"/>
+      <c r="D42" s="310"/>
+      <c r="E42" s="283"/>
+      <c r="F42" s="461"/>
+      <c r="G42" s="464"/>
+      <c r="H42" s="283"/>
+      <c r="I42" s="283"/>
+      <c r="J42" s="283"/>
+      <c r="K42" s="354"/>
+      <c r="L42" s="496"/>
       <c r="M42" s="248"/>
       <c r="N42" s="51"/>
     </row>
     <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="306"/>
-      <c r="B43" s="304"/>
-      <c r="C43" s="310"/>
-      <c r="D43" s="312"/>
-      <c r="E43" s="284"/>
-      <c r="F43" s="284"/>
-      <c r="G43" s="315"/>
-      <c r="H43" s="284"/>
-      <c r="I43" s="284"/>
+      <c r="A43" s="304"/>
+      <c r="B43" s="302"/>
+      <c r="C43" s="308"/>
+      <c r="D43" s="310"/>
+      <c r="E43" s="283"/>
+      <c r="F43" s="461"/>
+      <c r="G43" s="465"/>
+      <c r="H43" s="283"/>
+      <c r="I43" s="283"/>
       <c r="J43" s="270"/>
-      <c r="K43" s="359"/>
-      <c r="L43" s="364"/>
+      <c r="K43" s="354"/>
+      <c r="L43" s="496"/>
       <c r="M43" s="248"/>
       <c r="N43" s="51"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="306"/>
-      <c r="B44" s="304"/>
-      <c r="C44" s="310"/>
-      <c r="D44" s="315"/>
-      <c r="E44" s="350"/>
-      <c r="F44" s="315"/>
-      <c r="G44" s="318" t="s">
+      <c r="A44" s="304"/>
+      <c r="B44" s="302"/>
+      <c r="C44" s="308"/>
+      <c r="D44" s="313"/>
+      <c r="E44" s="348"/>
+      <c r="F44" s="462"/>
+      <c r="G44" s="467" t="s">
         <v>24</v>
       </c>
-      <c r="H44" s="315"/>
-      <c r="I44" s="315"/>
-      <c r="J44" s="284"/>
-      <c r="K44" s="359"/>
-      <c r="L44" s="364"/>
+      <c r="H44" s="313"/>
+      <c r="I44" s="313"/>
+      <c r="J44" s="283"/>
+      <c r="K44" s="354"/>
+      <c r="L44" s="496"/>
       <c r="M44" s="248"/>
       <c r="N44" s="51"/>
     </row>
     <row r="45" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="306"/>
-      <c r="B45" s="316" t="s">
+      <c r="A45" s="304"/>
+      <c r="B45" s="314" t="s">
         <v>190</v>
       </c>
-      <c r="C45" s="317" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="339"/>
-      <c r="E45" s="284"/>
-      <c r="F45" s="347" t="s">
+      <c r="C45" s="315"/>
+      <c r="D45" s="337"/>
+      <c r="E45" s="283"/>
+      <c r="F45" s="345" t="s">
         <v>185</v>
       </c>
-      <c r="G45" s="322" t="s">
+      <c r="G45" s="320" t="s">
         <v>178</v>
       </c>
-      <c r="H45" s="318" t="s">
+      <c r="H45" s="316" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="319" t="s">
+      <c r="I45" s="317" t="s">
         <v>21</v>
       </c>
-      <c r="J45" s="312"/>
-      <c r="K45" s="359"/>
-      <c r="L45" s="364"/>
+      <c r="J45" s="310"/>
+      <c r="K45" s="354"/>
+      <c r="L45" s="496"/>
       <c r="M45" s="248"/>
       <c r="N45" s="51"/>
     </row>
     <row r="46" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="310"/>
-      <c r="B46" s="320"/>
-      <c r="C46" s="321"/>
+      <c r="A46" s="308"/>
+      <c r="B46" s="318"/>
+      <c r="C46" s="319"/>
       <c r="D46" s="273"/>
-      <c r="E46" s="284"/>
-      <c r="F46" s="348"/>
-      <c r="G46" s="326"/>
-      <c r="H46" s="323" t="s">
+      <c r="E46" s="283"/>
+      <c r="F46" s="346"/>
+      <c r="G46" s="324"/>
+      <c r="H46" s="321" t="s">
         <v>178</v>
       </c>
-      <c r="I46" s="324" t="s">
+      <c r="I46" s="322" t="s">
         <v>178</v>
       </c>
-      <c r="J46" s="312"/>
-      <c r="K46" s="359"/>
-      <c r="L46" s="364"/>
+      <c r="J46" s="310"/>
+      <c r="K46" s="354"/>
+      <c r="L46" s="496"/>
       <c r="M46" s="248"/>
       <c r="N46" s="51"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="310"/>
-      <c r="B47" s="325" t="s">
+      <c r="A47" s="308"/>
+      <c r="B47" s="323" t="s">
         <v>174</v>
       </c>
-      <c r="C47" s="273">
-        <v>419230</v>
-      </c>
+      <c r="C47" s="273"/>
       <c r="D47" s="270"/>
-      <c r="E47" s="284"/>
-      <c r="F47" s="349" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="329"/>
-      <c r="H47" s="327"/>
-      <c r="I47" s="283"/>
-      <c r="J47" s="284"/>
-      <c r="K47" s="359"/>
-      <c r="L47" s="364"/>
+      <c r="E47" s="283"/>
+      <c r="F47" s="347" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="327"/>
+      <c r="H47" s="325"/>
+      <c r="I47" s="282"/>
+      <c r="J47" s="283"/>
+      <c r="K47" s="354"/>
+      <c r="L47" s="496"/>
       <c r="M47" s="248"/>
       <c r="N47" s="51"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="311"/>
-      <c r="B48" s="325" t="s">
+      <c r="A48" s="309"/>
+      <c r="B48" s="323" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="366">
-        <v>400000</v>
-      </c>
+      <c r="C48" s="359"/>
       <c r="D48" s="270"/>
-      <c r="E48" s="304"/>
-      <c r="F48" s="343" t="s">
+      <c r="E48" s="302"/>
+      <c r="F48" s="341" t="s">
         <v>188</v>
       </c>
-      <c r="G48" s="329"/>
-      <c r="H48" s="330"/>
-      <c r="I48" s="304"/>
-      <c r="J48" s="304"/>
-      <c r="K48" s="331"/>
-      <c r="L48" s="364"/>
-      <c r="M48" s="286"/>
+      <c r="G48" s="327"/>
+      <c r="H48" s="328"/>
+      <c r="I48" s="302"/>
+      <c r="J48" s="302"/>
+      <c r="K48" s="329"/>
+      <c r="L48" s="496"/>
+      <c r="M48" s="284"/>
       <c r="N48" s="51"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="311"/>
-      <c r="B49" s="325" t="s">
+      <c r="A49" s="309"/>
+      <c r="B49" s="323" t="s">
         <v>175</v>
       </c>
-      <c r="C49" s="366">
-        <v>300000</v>
-      </c>
+      <c r="C49" s="359"/>
       <c r="D49" s="270"/>
-      <c r="E49" s="304"/>
-      <c r="F49" s="343" t="s">
+      <c r="E49" s="302"/>
+      <c r="F49" s="341" t="s">
         <v>189</v>
       </c>
-      <c r="G49" s="329"/>
-      <c r="H49" s="330"/>
-      <c r="I49" s="304"/>
-      <c r="J49" s="304"/>
-      <c r="K49" s="362"/>
-      <c r="L49" s="364"/>
-      <c r="M49" s="286"/>
+      <c r="G49" s="327"/>
+      <c r="H49" s="328"/>
+      <c r="I49" s="302"/>
+      <c r="J49" s="302"/>
+      <c r="K49" s="357"/>
+      <c r="L49" s="496"/>
+      <c r="M49" s="284"/>
       <c r="N49" s="51"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="311"/>
-      <c r="B50" s="325" t="s">
+      <c r="A50" s="309"/>
+      <c r="B50" s="323" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="366">
-        <v>300000</v>
-      </c>
+      <c r="C50" s="359"/>
       <c r="D50" s="270"/>
-      <c r="E50" s="304"/>
-      <c r="F50" s="343" t="s">
+      <c r="E50" s="302"/>
+      <c r="F50" s="341" t="s">
         <v>179</v>
       </c>
-      <c r="G50" s="329"/>
-      <c r="H50" s="330"/>
-      <c r="I50" s="304"/>
-      <c r="J50" s="304"/>
-      <c r="K50" s="362"/>
-      <c r="L50" s="364"/>
-      <c r="M50" s="286"/>
+      <c r="G50" s="327"/>
+      <c r="H50" s="328"/>
+      <c r="I50" s="302"/>
+      <c r="J50" s="302"/>
+      <c r="K50" s="357"/>
+      <c r="L50" s="496"/>
+      <c r="M50" s="284"/>
       <c r="N50" s="51"/>
     </row>
     <row r="51" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="311"/>
-      <c r="B51" s="346" t="s">
+      <c r="A51" s="309"/>
+      <c r="B51" s="344" t="s">
         <v>177</v>
       </c>
-      <c r="C51" s="369">
-        <v>500000</v>
-      </c>
-      <c r="D51" s="306"/>
-      <c r="E51" s="304"/>
-      <c r="F51" s="343" t="s">
+      <c r="C51" s="362"/>
+      <c r="D51" s="304"/>
+      <c r="E51" s="302"/>
+      <c r="F51" s="341" t="s">
         <v>181</v>
       </c>
-      <c r="G51" s="333"/>
-      <c r="H51" s="330"/>
-      <c r="I51" s="304"/>
-      <c r="J51" s="304"/>
-      <c r="K51" s="362"/>
-      <c r="L51" s="364"/>
-      <c r="M51" s="286"/>
+      <c r="G51" s="331"/>
+      <c r="H51" s="328"/>
+      <c r="I51" s="302"/>
+      <c r="J51" s="302"/>
+      <c r="K51" s="357"/>
+      <c r="L51" s="496"/>
+      <c r="M51" s="284"/>
       <c r="N51" s="51"/>
     </row>
     <row r="52" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="340"/>
-      <c r="B52" s="332" t="s">
+      <c r="A52" s="338"/>
+      <c r="B52" s="330" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="374">
-        <f>SUM(C47:C51)</f>
-        <v>1919230</v>
-      </c>
-      <c r="D52" s="372"/>
-      <c r="E52" s="304"/>
-      <c r="F52" s="343" t="s">
+      <c r="C52" s="367"/>
+      <c r="D52" s="365"/>
+      <c r="E52" s="302"/>
+      <c r="F52" s="341" t="s">
         <v>182</v>
       </c>
-      <c r="G52" s="335"/>
-      <c r="H52" s="334"/>
-      <c r="I52" s="304"/>
-      <c r="J52" s="304"/>
-      <c r="K52" s="340"/>
-      <c r="L52" s="364"/>
-      <c r="M52" s="286"/>
+      <c r="G52" s="333"/>
+      <c r="H52" s="332"/>
+      <c r="I52" s="302"/>
+      <c r="J52" s="302"/>
+      <c r="K52" s="338"/>
+      <c r="L52" s="496"/>
+      <c r="M52" s="284"/>
       <c r="N52" s="51"/>
     </row>
     <row r="53" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="340"/>
-      <c r="B53" s="321"/>
-      <c r="C53" s="373"/>
-      <c r="D53" s="304"/>
-      <c r="E53" s="304"/>
-      <c r="F53" s="344" t="s">
+      <c r="A53" s="338"/>
+      <c r="B53" s="319"/>
+      <c r="C53" s="366"/>
+      <c r="D53" s="302"/>
+      <c r="E53" s="302"/>
+      <c r="F53" s="342" t="s">
         <v>180</v>
       </c>
-      <c r="G53" s="321"/>
-      <c r="H53" s="336"/>
-      <c r="I53" s="305"/>
-      <c r="J53" s="304"/>
-      <c r="K53" s="362"/>
-      <c r="L53" s="364"/>
-      <c r="M53" s="286"/>
+      <c r="G53" s="319"/>
+      <c r="H53" s="334"/>
+      <c r="I53" s="303"/>
+      <c r="J53" s="302"/>
+      <c r="K53" s="357"/>
+      <c r="L53" s="496"/>
+      <c r="M53" s="284"/>
       <c r="N53" s="51"/>
     </row>
     <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="341"/>
-      <c r="B54" s="304"/>
-      <c r="C54" s="304"/>
-      <c r="D54" s="304"/>
-      <c r="E54" s="304"/>
-      <c r="F54" s="305"/>
-      <c r="G54" s="337" t="s">
+      <c r="A54" s="339"/>
+      <c r="B54" s="302"/>
+      <c r="C54" s="302"/>
+      <c r="D54" s="302"/>
+      <c r="E54" s="302"/>
+      <c r="F54" s="303"/>
+      <c r="G54" s="335" t="s">
         <v>178</v>
       </c>
-      <c r="H54" s="321"/>
-      <c r="I54" s="304"/>
-      <c r="J54" s="304"/>
-      <c r="K54" s="363"/>
-      <c r="L54" s="364"/>
-      <c r="M54" s="286"/>
+      <c r="H54" s="319"/>
+      <c r="I54" s="302"/>
+      <c r="J54" s="302"/>
+      <c r="K54" s="358"/>
+      <c r="L54" s="496"/>
+      <c r="M54" s="284"/>
       <c r="N54" s="51"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="342"/>
-      <c r="B55" s="304"/>
-      <c r="C55" s="304"/>
-      <c r="D55" s="304"/>
-      <c r="E55" s="304"/>
-      <c r="F55" s="345"/>
-      <c r="G55" s="304"/>
-      <c r="H55" s="337" t="s">
+      <c r="A55" s="340"/>
+      <c r="B55" s="302"/>
+      <c r="C55" s="302"/>
+      <c r="D55" s="302"/>
+      <c r="E55" s="302"/>
+      <c r="F55" s="343"/>
+      <c r="G55" s="302"/>
+      <c r="H55" s="335" t="s">
         <v>178</v>
       </c>
       <c r="I55" s="270"/>
-      <c r="J55" s="304"/>
-      <c r="K55" s="361"/>
-      <c r="L55" s="364"/>
-      <c r="M55" s="286"/>
+      <c r="J55" s="302"/>
+      <c r="K55" s="356"/>
+      <c r="L55" s="496"/>
+      <c r="M55" s="284"/>
       <c r="N55" s="51"/>
     </row>
     <row r="56" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="342"/>
-      <c r="B56" s="304"/>
-      <c r="C56" s="304"/>
-      <c r="D56" s="304"/>
-      <c r="E56" s="304"/>
-      <c r="F56" s="305"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="304"/>
+      <c r="A56" s="340"/>
+      <c r="B56" s="302"/>
+      <c r="C56" s="302"/>
+      <c r="D56" s="302"/>
+      <c r="E56" s="302"/>
+      <c r="F56" s="303"/>
+      <c r="G56" s="271"/>
+      <c r="H56" s="302"/>
       <c r="I56" s="270"/>
-      <c r="J56" s="304"/>
-      <c r="K56" s="331"/>
-      <c r="L56" s="365"/>
-      <c r="M56" s="286"/>
+      <c r="J56" s="302"/>
+      <c r="K56" s="329"/>
+      <c r="L56" s="497"/>
+      <c r="M56" s="284"/>
       <c r="N56" s="51"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="342"/>
-      <c r="B57" s="51"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="248"/>
-      <c r="G57" s="98"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="89"/>
-      <c r="J57" s="51"/>
-      <c r="K57" s="51"/>
-      <c r="L57" s="253"/>
+      <c r="A57" s="484"/>
+      <c r="B57" s="271"/>
+      <c r="C57" s="271"/>
+      <c r="D57" s="271"/>
+      <c r="E57" s="271"/>
+      <c r="F57" s="485"/>
+      <c r="G57" s="279"/>
+      <c r="H57" s="271"/>
+      <c r="I57" s="198"/>
+      <c r="J57" s="271"/>
+      <c r="K57" s="271"/>
+      <c r="L57" s="486"/>
       <c r="M57" s="87"/>
       <c r="N57" s="51"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="342"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51">
-        <v>3801.42</v>
-      </c>
-      <c r="E58" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="F58" s="382" t="s">
-        <v>196</v>
-      </c>
-      <c r="G58" s="98"/>
-      <c r="H58" s="98"/>
-      <c r="I58" s="89"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="51"/>
-      <c r="L58" s="51"/>
+      <c r="A58" s="484"/>
+      <c r="B58" s="271"/>
+      <c r="C58" s="271"/>
+      <c r="D58" s="271"/>
+      <c r="E58" s="279"/>
+      <c r="F58" s="487"/>
+      <c r="G58" s="279"/>
+      <c r="H58" s="279"/>
+      <c r="I58" s="198"/>
+      <c r="J58" s="271"/>
+      <c r="K58" s="271"/>
+      <c r="L58" s="271"/>
       <c r="M58" s="87"/>
       <c r="N58" s="51"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="342"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51">
-        <v>10760.39</v>
-      </c>
-      <c r="D59" s="51">
-        <v>6644.52</v>
-      </c>
-      <c r="E59" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="F59" s="383" t="s">
-        <v>196</v>
-      </c>
-      <c r="G59" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="H59" s="98"/>
-      <c r="I59" s="384"/>
-      <c r="J59" s="120"/>
-      <c r="K59" s="120"/>
-      <c r="L59" s="51"/>
+      <c r="A59" s="484"/>
+      <c r="B59" s="271"/>
+      <c r="C59" s="271"/>
+      <c r="D59" s="271"/>
+      <c r="E59" s="279"/>
+      <c r="F59" s="279"/>
+      <c r="G59" s="279"/>
+      <c r="H59" s="279"/>
+      <c r="I59" s="289"/>
+      <c r="J59" s="271"/>
+      <c r="K59" s="271"/>
+      <c r="L59" s="271"/>
       <c r="M59" s="87"/>
       <c r="N59" s="51"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="342"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="51">
-        <v>19601</v>
-      </c>
-      <c r="D60" s="51">
-        <v>10760.39</v>
-      </c>
-      <c r="E60" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="F60" s="383" t="s">
-        <v>196</v>
-      </c>
-      <c r="G60" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="H60" s="98" t="s">
-        <v>198</v>
-      </c>
-      <c r="I60" s="385" t="s">
-        <v>199</v>
-      </c>
-      <c r="J60" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="K60" s="51"/>
-      <c r="L60" s="248"/>
+      <c r="A60" s="484"/>
+      <c r="B60" s="271"/>
+      <c r="C60" s="271"/>
+      <c r="D60" s="271"/>
+      <c r="E60" s="279"/>
+      <c r="F60" s="279"/>
+      <c r="G60" s="279"/>
+      <c r="H60" s="279"/>
+      <c r="I60" s="294"/>
+      <c r="J60" s="271"/>
+      <c r="K60" s="271"/>
+      <c r="L60" s="271"/>
       <c r="M60" s="87"/>
       <c r="N60" s="51"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="342"/>
-      <c r="B61" s="51"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="51">
-        <v>19601</v>
-      </c>
-      <c r="E61" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="F61" s="383" t="s">
-        <v>196</v>
-      </c>
-      <c r="G61" s="98" t="s">
-        <v>197</v>
-      </c>
-      <c r="H61" s="98" t="s">
-        <v>198</v>
-      </c>
-      <c r="I61" s="385" t="s">
-        <v>199</v>
-      </c>
-      <c r="J61" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="K61" s="51"/>
-      <c r="L61" s="248"/>
+      <c r="A61" s="484"/>
+      <c r="B61" s="271"/>
+      <c r="C61" s="271"/>
+      <c r="D61" s="271"/>
+      <c r="E61" s="279"/>
+      <c r="F61" s="279"/>
+      <c r="G61" s="279"/>
+      <c r="H61" s="279"/>
+      <c r="I61" s="294"/>
+      <c r="J61" s="271"/>
+      <c r="K61" s="271"/>
+      <c r="L61" s="271"/>
       <c r="M61" s="87"/>
       <c r="N61" s="51"/>
     </row>
-    <row r="62" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="328"/>
-      <c r="B62" s="190"/>
-      <c r="C62" s="51">
-        <f>SUM(C59:C61)</f>
-        <v>30361.39</v>
-      </c>
-      <c r="D62" s="51">
-        <v>5822.42</v>
-      </c>
-      <c r="E62" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="F62" s="383" t="s">
-        <v>196</v>
-      </c>
-      <c r="G62" s="386"/>
-      <c r="H62" s="98" t="s">
-        <v>198</v>
-      </c>
-      <c r="I62" s="99"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="248"/>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="489"/>
+      <c r="B62" s="490"/>
+      <c r="C62" s="271"/>
+      <c r="D62" s="271"/>
+      <c r="E62" s="279"/>
+      <c r="F62" s="279"/>
+      <c r="G62" s="279"/>
+      <c r="H62" s="279"/>
+      <c r="I62" s="289"/>
+      <c r="J62" s="271"/>
+      <c r="K62" s="271"/>
+      <c r="L62" s="271"/>
       <c r="M62" s="87"/>
       <c r="N62" s="51"/>
     </row>
-    <row r="63" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="331"/>
-      <c r="B63" s="190"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="120">
-        <v>15744.77</v>
-      </c>
-      <c r="E63" s="386" t="s">
-        <v>195</v>
-      </c>
-      <c r="F63" s="387" t="s">
-        <v>196</v>
-      </c>
-      <c r="G63" s="393">
-        <v>36183.39</v>
-      </c>
-      <c r="H63" s="384"/>
-      <c r="I63" s="390"/>
-      <c r="J63" s="253"/>
-      <c r="K63" s="391"/>
-      <c r="L63" s="51"/>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="286"/>
+      <c r="B63" s="490"/>
+      <c r="C63" s="271"/>
+      <c r="D63" s="271"/>
+      <c r="E63" s="279"/>
+      <c r="F63" s="279"/>
+      <c r="G63" s="495"/>
+      <c r="H63" s="289"/>
+      <c r="I63" s="279"/>
+      <c r="J63" s="271"/>
+      <c r="K63" s="271"/>
+      <c r="L63" s="271"/>
       <c r="M63" s="87"/>
       <c r="N63" s="51"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="331"/>
-      <c r="B64" s="190"/>
-      <c r="C64" s="87"/>
-      <c r="D64" s="392">
-        <f>SUM(D58:D63)</f>
-        <v>62374.520000000004</v>
-      </c>
-      <c r="E64" s="392">
-        <v>62374.52</v>
-      </c>
-      <c r="F64" s="393" t="s">
-        <v>201</v>
-      </c>
-      <c r="G64" s="253"/>
-      <c r="H64" s="393">
-        <v>36183.39</v>
-      </c>
-      <c r="I64" s="393">
-        <v>30361.39</v>
-      </c>
-      <c r="J64" s="393">
-        <v>30361.39</v>
-      </c>
-      <c r="K64" s="392">
-        <v>19601</v>
-      </c>
-      <c r="L64" s="248"/>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="286"/>
+      <c r="B64" s="490"/>
+      <c r="C64" s="271"/>
+      <c r="D64" s="271"/>
+      <c r="E64" s="271"/>
+      <c r="F64" s="495"/>
+      <c r="G64" s="271"/>
+      <c r="H64" s="495"/>
+      <c r="I64" s="495"/>
+      <c r="J64" s="495"/>
+      <c r="K64" s="271"/>
+      <c r="L64" s="271"/>
       <c r="M64" s="87"/>
       <c r="N64" s="51"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="331"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="253"/>
-      <c r="E65" s="253"/>
-      <c r="F65" s="388"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="389"/>
-      <c r="I65" s="253"/>
-      <c r="J65" s="51"/>
-      <c r="K65" s="253"/>
-      <c r="L65" s="51"/>
+      <c r="A65" s="286"/>
+      <c r="B65" s="271"/>
+      <c r="C65" s="271"/>
+      <c r="D65" s="271"/>
+      <c r="E65" s="271"/>
+      <c r="F65" s="271"/>
+      <c r="G65" s="271"/>
+      <c r="H65" s="198"/>
+      <c r="I65" s="271"/>
+      <c r="J65" s="271"/>
+      <c r="K65" s="271"/>
+      <c r="L65" s="271"/>
       <c r="M65" s="87"/>
       <c r="N65" s="51"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="331"/>
-      <c r="B66" s="51"/>
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="248"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="89"/>
-      <c r="I66" s="51"/>
-      <c r="J66" s="51"/>
-      <c r="K66" s="51"/>
-      <c r="L66" s="51"/>
+      <c r="A66" s="286"/>
+      <c r="B66" s="271"/>
+      <c r="C66" s="271"/>
+      <c r="D66" s="271"/>
+      <c r="E66" s="271"/>
+      <c r="F66" s="271"/>
+      <c r="G66" s="271"/>
+      <c r="H66" s="198"/>
+      <c r="I66" s="271"/>
+      <c r="J66" s="271"/>
+      <c r="K66" s="271"/>
+      <c r="L66" s="271"/>
       <c r="M66" s="87"/>
       <c r="N66" s="51"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="331"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="248"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="118"/>
-      <c r="I67" s="51"/>
-      <c r="J67" s="51"/>
-      <c r="K67" s="51"/>
-      <c r="L67" s="51"/>
+      <c r="A67" s="286"/>
+      <c r="B67" s="271"/>
+      <c r="C67" s="271"/>
+      <c r="D67" s="271"/>
+      <c r="E67" s="271"/>
+      <c r="F67" s="271"/>
+      <c r="G67" s="271"/>
+      <c r="H67" s="378"/>
+      <c r="I67" s="271"/>
+      <c r="J67" s="271"/>
+      <c r="K67" s="271"/>
+      <c r="L67" s="271"/>
       <c r="M67" s="87"/>
       <c r="N67" s="51"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="304"/>
-      <c r="B68" s="51"/>
-      <c r="C68" s="51"/>
-      <c r="D68" s="51"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="51"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="118"/>
-      <c r="I68" s="51"/>
-      <c r="J68" s="51"/>
-      <c r="K68" s="51"/>
-      <c r="L68" s="51"/>
+      <c r="A68" s="271"/>
+      <c r="B68" s="271"/>
+      <c r="C68" s="271"/>
+      <c r="D68" s="271"/>
+      <c r="E68" s="271"/>
+      <c r="F68" s="271"/>
+      <c r="G68" s="271"/>
+      <c r="H68" s="378"/>
+      <c r="I68" s="271"/>
+      <c r="J68" s="271"/>
+      <c r="K68" s="271"/>
+      <c r="L68" s="271"/>
       <c r="M68" s="87"/>
       <c r="N68" s="51"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="304"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="118"/>
-      <c r="I69" s="51"/>
-      <c r="J69" s="51"/>
-      <c r="K69" s="51"/>
-      <c r="L69" s="51"/>
+      <c r="A69" s="271"/>
+      <c r="B69" s="271"/>
+      <c r="C69" s="271"/>
+      <c r="D69" s="271"/>
+      <c r="E69" s="271"/>
+      <c r="F69" s="271"/>
+      <c r="G69" s="271"/>
+      <c r="H69" s="378"/>
+      <c r="I69" s="271"/>
+      <c r="J69" s="271"/>
+      <c r="K69" s="271"/>
+      <c r="L69" s="271"/>
       <c r="M69" s="87"/>
       <c r="N69" s="51"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="304"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="118"/>
-      <c r="I70" s="51"/>
-      <c r="J70" s="118"/>
-      <c r="K70" s="51"/>
-      <c r="L70" s="51"/>
+      <c r="A70" s="271"/>
+      <c r="B70" s="271"/>
+      <c r="C70" s="271"/>
+      <c r="D70" s="271"/>
+      <c r="E70" s="271"/>
+      <c r="F70" s="271"/>
+      <c r="G70" s="271"/>
+      <c r="H70" s="378"/>
+      <c r="I70" s="271"/>
+      <c r="J70" s="378"/>
+      <c r="K70" s="271"/>
+      <c r="L70" s="271"/>
       <c r="M70" s="87"/>
       <c r="N70" s="51"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="304"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="118"/>
-      <c r="I71" s="51"/>
-      <c r="J71" s="51"/>
-      <c r="K71" s="51"/>
-      <c r="L71" s="51"/>
+      <c r="A71" s="271"/>
+      <c r="B71" s="271"/>
+      <c r="C71" s="271"/>
+      <c r="D71" s="271"/>
+      <c r="E71" s="271"/>
+      <c r="F71" s="271"/>
+      <c r="G71" s="271"/>
+      <c r="H71" s="378"/>
+      <c r="I71" s="271"/>
+      <c r="J71" s="271"/>
+      <c r="K71" s="271"/>
+      <c r="L71" s="271"/>
       <c r="M71" s="87"/>
       <c r="N71" s="51"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="304"/>
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="118">
-        <v>320959</v>
-      </c>
-      <c r="I72" s="199">
-        <v>46092</v>
-      </c>
-      <c r="J72" s="51"/>
-      <c r="K72" s="51"/>
-      <c r="L72" s="51"/>
+      <c r="A72" s="271"/>
+      <c r="B72" s="271"/>
+      <c r="C72" s="271"/>
+      <c r="D72" s="271"/>
+      <c r="E72" s="271"/>
+      <c r="F72" s="271"/>
+      <c r="G72" s="271"/>
+      <c r="H72" s="378"/>
+      <c r="I72" s="491"/>
+      <c r="J72" s="271"/>
+      <c r="K72" s="271"/>
+      <c r="L72" s="271"/>
       <c r="M72" s="87"/>
       <c r="N72" s="51"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="304"/>
-      <c r="B73" s="51"/>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="51"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="89">
-        <v>310000</v>
-      </c>
-      <c r="I73" s="199">
-        <v>46093</v>
-      </c>
-      <c r="J73" s="51"/>
-      <c r="K73" s="51"/>
-      <c r="L73" s="51"/>
+      <c r="A73" s="271"/>
+      <c r="B73" s="271"/>
+      <c r="C73" s="271"/>
+      <c r="D73" s="271"/>
+      <c r="E73" s="271"/>
+      <c r="F73" s="271"/>
+      <c r="G73" s="271"/>
+      <c r="H73" s="198"/>
+      <c r="I73" s="491"/>
+      <c r="J73" s="271"/>
+      <c r="K73" s="271"/>
+      <c r="L73" s="271"/>
       <c r="M73" s="87"/>
       <c r="N73" s="51"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="304"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="89">
-        <v>436108.36</v>
-      </c>
-      <c r="I74" s="199">
-        <v>46095</v>
-      </c>
-      <c r="J74" s="51"/>
-      <c r="K74" s="51"/>
-      <c r="L74" s="51"/>
+      <c r="A74" s="271"/>
+      <c r="B74" s="271"/>
+      <c r="C74" s="271"/>
+      <c r="D74" s="271"/>
+      <c r="E74" s="271"/>
+      <c r="F74" s="271"/>
+      <c r="G74" s="271"/>
+      <c r="H74" s="198"/>
+      <c r="I74" s="491"/>
+      <c r="J74" s="271"/>
+      <c r="K74" s="271"/>
+      <c r="L74" s="271"/>
       <c r="M74" s="87"/>
       <c r="N74" s="51"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="304"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="118">
-        <v>432480</v>
-      </c>
-      <c r="I75" s="199">
-        <v>46095</v>
-      </c>
-      <c r="J75" s="51"/>
-      <c r="K75" s="51"/>
-      <c r="L75" s="51"/>
+      <c r="A75" s="271"/>
+      <c r="B75" s="271"/>
+      <c r="C75" s="271"/>
+      <c r="D75" s="271"/>
+      <c r="E75" s="271"/>
+      <c r="F75" s="271"/>
+      <c r="G75" s="271"/>
+      <c r="H75" s="378"/>
+      <c r="I75" s="491"/>
+      <c r="J75" s="271"/>
+      <c r="K75" s="271"/>
+      <c r="L75" s="271"/>
       <c r="M75" s="87"/>
       <c r="N75" s="51"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="304"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="120"/>
-      <c r="G76" s="396"/>
-      <c r="H76" s="351">
-        <v>545859</v>
-      </c>
-      <c r="I76" s="199">
-        <v>46106</v>
-      </c>
-      <c r="J76" s="51"/>
-      <c r="K76" s="51"/>
-      <c r="L76" s="51"/>
+      <c r="A76" s="271"/>
+      <c r="B76" s="271"/>
+      <c r="C76" s="271"/>
+      <c r="D76" s="271"/>
+      <c r="E76" s="271"/>
+      <c r="F76" s="488"/>
+      <c r="G76" s="492"/>
+      <c r="H76" s="493"/>
+      <c r="I76" s="491"/>
+      <c r="J76" s="271"/>
+      <c r="K76" s="271"/>
+      <c r="L76" s="271"/>
       <c r="M76" s="87"/>
       <c r="N76" s="51"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="304"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51"/>
-      <c r="D77" s="51"/>
-      <c r="E77" s="87"/>
-      <c r="F77" s="51"/>
-      <c r="G77" s="199"/>
-      <c r="H77" s="118">
-        <f>SUM(H72:H76)</f>
-        <v>2045406.3599999999</v>
-      </c>
-      <c r="I77" s="248"/>
-      <c r="J77" s="51"/>
-      <c r="K77" s="51"/>
-      <c r="L77" s="51"/>
+      <c r="A77" s="271"/>
+      <c r="B77" s="271"/>
+      <c r="C77" s="271"/>
+      <c r="D77" s="271"/>
+      <c r="E77" s="286"/>
+      <c r="F77" s="271"/>
+      <c r="G77" s="491"/>
+      <c r="H77" s="378"/>
+      <c r="I77" s="485"/>
+      <c r="J77" s="271"/>
+      <c r="K77" s="271"/>
+      <c r="L77" s="271"/>
       <c r="M77" s="87"/>
       <c r="N77" s="51"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="304"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="51"/>
-      <c r="D78" s="89"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="253"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="352"/>
-      <c r="I78" s="117"/>
-      <c r="J78" s="51"/>
-      <c r="K78" s="51"/>
-      <c r="L78" s="51"/>
+      <c r="A78" s="271"/>
+      <c r="B78" s="271"/>
+      <c r="C78" s="271"/>
+      <c r="D78" s="198"/>
+      <c r="E78" s="271"/>
+      <c r="F78" s="486"/>
+      <c r="G78" s="271"/>
+      <c r="H78" s="494"/>
+      <c r="I78" s="495"/>
+      <c r="J78" s="271"/>
+      <c r="K78" s="271"/>
+      <c r="L78" s="271"/>
       <c r="M78" s="87"/>
       <c r="N78" s="51"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="304"/>
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="89"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="117"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="51"/>
-      <c r="K79" s="51"/>
-      <c r="L79" s="51"/>
+      <c r="A79" s="271"/>
+      <c r="B79" s="271"/>
+      <c r="C79" s="271"/>
+      <c r="D79" s="198"/>
+      <c r="E79" s="271"/>
+      <c r="F79" s="271"/>
+      <c r="G79" s="271"/>
+      <c r="H79" s="495"/>
+      <c r="I79" s="271"/>
+      <c r="J79" s="271"/>
+      <c r="K79" s="271"/>
+      <c r="L79" s="271"/>
       <c r="M79" s="87"/>
       <c r="N79" s="51"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="304"/>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="89"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="51"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="117"/>
-      <c r="I80" s="51"/>
-      <c r="J80" s="51"/>
-      <c r="K80" s="51"/>
-      <c r="L80" s="51"/>
+      <c r="A80" s="271"/>
+      <c r="B80" s="271"/>
+      <c r="C80" s="271"/>
+      <c r="D80" s="198"/>
+      <c r="E80" s="271"/>
+      <c r="F80" s="271"/>
+      <c r="G80" s="271"/>
+      <c r="H80" s="495"/>
+      <c r="I80" s="271"/>
+      <c r="J80" s="271"/>
+      <c r="K80" s="271"/>
+      <c r="L80" s="271"/>
       <c r="M80" s="87"/>
       <c r="N80" s="51"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="304"/>
-      <c r="B81" s="51"/>
-      <c r="C81" s="51"/>
-      <c r="D81" s="89"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="51"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="117"/>
-      <c r="I81" s="51"/>
-      <c r="J81" s="51"/>
-      <c r="K81" s="51"/>
-      <c r="L81" s="51"/>
+      <c r="A81" s="271"/>
+      <c r="B81" s="271"/>
+      <c r="C81" s="271"/>
+      <c r="D81" s="198"/>
+      <c r="E81" s="271"/>
+      <c r="F81" s="271"/>
+      <c r="G81" s="271"/>
+      <c r="H81" s="495"/>
+      <c r="I81" s="271"/>
+      <c r="J81" s="271"/>
+      <c r="K81" s="271"/>
+      <c r="L81" s="271"/>
       <c r="M81" s="87"/>
       <c r="N81" s="51"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="304"/>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="51"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="117"/>
-      <c r="I82" s="51"/>
-      <c r="J82" s="51"/>
-      <c r="K82" s="51"/>
-      <c r="L82" s="51"/>
+      <c r="A82" s="271"/>
+      <c r="B82" s="271"/>
+      <c r="C82" s="271"/>
+      <c r="D82" s="271"/>
+      <c r="E82" s="271"/>
+      <c r="F82" s="271"/>
+      <c r="G82" s="271"/>
+      <c r="H82" s="495"/>
+      <c r="I82" s="271"/>
+      <c r="J82" s="271"/>
+      <c r="K82" s="271"/>
+      <c r="L82" s="271"/>
       <c r="M82" s="87"/>
       <c r="N82" s="51"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="304"/>
-      <c r="B83" s="51"/>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="51"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="117"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="51"/>
-      <c r="K83" s="51"/>
-      <c r="L83" s="51"/>
+      <c r="A83" s="271"/>
+      <c r="B83" s="271"/>
+      <c r="C83" s="271"/>
+      <c r="D83" s="271"/>
+      <c r="E83" s="271"/>
+      <c r="F83" s="271"/>
+      <c r="G83" s="271"/>
+      <c r="H83" s="495"/>
+      <c r="I83" s="271"/>
+      <c r="J83" s="271"/>
+      <c r="K83" s="271"/>
+      <c r="L83" s="271"/>
       <c r="M83" s="87"/>
       <c r="N83" s="51"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="304"/>
-      <c r="B84" s="51"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="117"/>
-      <c r="I84" s="51"/>
-      <c r="J84" s="51"/>
-      <c r="K84" s="51"/>
-      <c r="L84" s="51"/>
+      <c r="A84" s="271"/>
+      <c r="B84" s="271"/>
+      <c r="C84" s="271"/>
+      <c r="D84" s="271"/>
+      <c r="E84" s="271"/>
+      <c r="F84" s="271"/>
+      <c r="G84" s="271"/>
+      <c r="H84" s="495"/>
+      <c r="I84" s="271"/>
+      <c r="J84" s="271"/>
+      <c r="K84" s="271"/>
+      <c r="L84" s="271"/>
       <c r="M84" s="87"/>
       <c r="N84" s="51"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="304"/>
-      <c r="B85" s="51"/>
-      <c r="C85" s="51"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="117"/>
-      <c r="I85" s="51"/>
-      <c r="J85" s="51"/>
-      <c r="K85" s="51"/>
-      <c r="L85" s="51"/>
+      <c r="A85" s="271"/>
+      <c r="B85" s="271"/>
+      <c r="C85" s="271"/>
+      <c r="D85" s="271"/>
+      <c r="E85" s="271"/>
+      <c r="F85" s="271"/>
+      <c r="G85" s="271"/>
+      <c r="H85" s="495"/>
+      <c r="I85" s="271"/>
+      <c r="J85" s="271"/>
+      <c r="K85" s="271"/>
+      <c r="L85" s="271"/>
       <c r="M85" s="87"/>
       <c r="N85" s="51"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="304"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="117"/>
-      <c r="I86" s="51"/>
-      <c r="J86" s="51"/>
-      <c r="K86" s="51"/>
-      <c r="L86" s="51"/>
+      <c r="A86" s="271"/>
+      <c r="B86" s="271"/>
+      <c r="C86" s="271"/>
+      <c r="D86" s="271"/>
+      <c r="E86" s="271"/>
+      <c r="F86" s="271"/>
+      <c r="G86" s="271"/>
+      <c r="H86" s="495"/>
+      <c r="I86" s="271"/>
+      <c r="J86" s="271"/>
+      <c r="K86" s="271"/>
+      <c r="L86" s="271"/>
       <c r="M86" s="87"/>
       <c r="N86" s="51"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="304"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="117"/>
-      <c r="I87" s="51"/>
-      <c r="J87" s="51"/>
-      <c r="K87" s="51"/>
-      <c r="L87" s="51"/>
+      <c r="A87" s="271"/>
+      <c r="B87" s="271"/>
+      <c r="C87" s="271"/>
+      <c r="D87" s="271"/>
+      <c r="E87" s="271"/>
+      <c r="F87" s="271"/>
+      <c r="G87" s="271"/>
+      <c r="H87" s="495"/>
+      <c r="I87" s="271"/>
+      <c r="J87" s="271"/>
+      <c r="K87" s="271"/>
+      <c r="L87" s="271"/>
       <c r="M87" s="87"/>
       <c r="N87" s="51"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="304"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
-      <c r="J88" s="51"/>
-      <c r="K88" s="51"/>
-      <c r="L88" s="51"/>
+      <c r="A88" s="271"/>
+      <c r="B88" s="271"/>
+      <c r="C88" s="271"/>
+      <c r="D88" s="271"/>
+      <c r="E88" s="271"/>
+      <c r="F88" s="271"/>
+      <c r="G88" s="271"/>
+      <c r="H88" s="271"/>
+      <c r="I88" s="271"/>
+      <c r="J88" s="271"/>
+      <c r="K88" s="271"/>
+      <c r="L88" s="271"/>
       <c r="M88" s="51"/>
       <c r="N88" s="51"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="304"/>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="51"/>
-      <c r="G89" s="51"/>
-      <c r="H89" s="51"/>
-      <c r="I89" s="51"/>
-      <c r="J89" s="51"/>
-      <c r="K89" s="51"/>
-      <c r="L89" s="51"/>
+      <c r="A89" s="271"/>
+      <c r="B89" s="271"/>
+      <c r="C89" s="271"/>
+      <c r="D89" s="271"/>
+      <c r="E89" s="271"/>
+      <c r="F89" s="271"/>
+      <c r="G89" s="271"/>
+      <c r="H89" s="271"/>
+      <c r="I89" s="271"/>
+      <c r="J89" s="271"/>
+      <c r="K89" s="271"/>
+      <c r="L89" s="271"/>
       <c r="M89" s="51"/>
       <c r="N89" s="51"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="304"/>
-      <c r="B90" s="51"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="51"/>
-      <c r="G90" s="51"/>
-      <c r="H90" s="51"/>
-      <c r="I90" s="51"/>
-      <c r="J90" s="51"/>
-      <c r="K90" s="51"/>
-      <c r="L90" s="51"/>
+      <c r="A90" s="271"/>
+      <c r="B90" s="271"/>
+      <c r="C90" s="271"/>
+      <c r="D90" s="271"/>
+      <c r="E90" s="271"/>
+      <c r="F90" s="271"/>
+      <c r="G90" s="271"/>
+      <c r="H90" s="271"/>
+      <c r="I90" s="271"/>
+      <c r="J90" s="271"/>
+      <c r="K90" s="271"/>
+      <c r="L90" s="271"/>
       <c r="M90" s="51"/>
       <c r="N90" s="51"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="304"/>
-      <c r="B91" s="51"/>
-      <c r="C91" s="51"/>
-      <c r="D91" s="51"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="51"/>
-      <c r="G91" s="51"/>
-      <c r="H91" s="51"/>
-      <c r="I91" s="51"/>
-      <c r="J91" s="51"/>
-      <c r="K91" s="51"/>
-      <c r="L91" s="51"/>
+      <c r="A91" s="271"/>
+      <c r="B91" s="271"/>
+      <c r="C91" s="271"/>
+      <c r="D91" s="271"/>
+      <c r="E91" s="271"/>
+      <c r="F91" s="271"/>
+      <c r="G91" s="271"/>
+      <c r="H91" s="271"/>
+      <c r="I91" s="271"/>
+      <c r="J91" s="271"/>
+      <c r="K91" s="271"/>
+      <c r="L91" s="271"/>
       <c r="M91" s="51"/>
       <c r="N91" s="51"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="304"/>
-      <c r="B92" s="51"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="51"/>
-      <c r="G92" s="51"/>
-      <c r="H92" s="51"/>
-      <c r="I92" s="51"/>
-      <c r="J92" s="51"/>
-      <c r="K92" s="51"/>
-      <c r="L92" s="51"/>
+      <c r="A92" s="271"/>
+      <c r="B92" s="271"/>
+      <c r="C92" s="271"/>
+      <c r="D92" s="271"/>
+      <c r="E92" s="271"/>
+      <c r="F92" s="271"/>
+      <c r="G92" s="271"/>
+      <c r="H92" s="271"/>
+      <c r="I92" s="271"/>
+      <c r="J92" s="271"/>
+      <c r="K92" s="271"/>
+      <c r="L92" s="271"/>
       <c r="M92" s="51"/>
       <c r="N92" s="51"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="304"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="51"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="51"/>
-      <c r="I93" s="51"/>
-      <c r="J93" s="51"/>
-      <c r="K93" s="51"/>
-      <c r="L93" s="51"/>
+      <c r="A93" s="271"/>
+      <c r="B93" s="271"/>
+      <c r="C93" s="271"/>
+      <c r="D93" s="271"/>
+      <c r="E93" s="271"/>
+      <c r="F93" s="271"/>
+      <c r="G93" s="271"/>
+      <c r="H93" s="271"/>
+      <c r="I93" s="271"/>
+      <c r="J93" s="271"/>
+      <c r="K93" s="271"/>
+      <c r="L93" s="271"/>
       <c r="M93" s="51"/>
       <c r="N93" s="51"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="304"/>
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="51"/>
-      <c r="G94" s="51"/>
-      <c r="H94" s="51"/>
-      <c r="I94" s="51"/>
-      <c r="J94" s="51"/>
-      <c r="K94" s="51"/>
-      <c r="L94" s="51"/>
+      <c r="A94" s="271"/>
+      <c r="B94" s="271"/>
+      <c r="C94" s="271"/>
+      <c r="D94" s="271"/>
+      <c r="E94" s="271"/>
+      <c r="F94" s="271"/>
+      <c r="G94" s="271"/>
+      <c r="H94" s="271"/>
+      <c r="I94" s="271"/>
+      <c r="J94" s="271"/>
+      <c r="K94" s="271"/>
+      <c r="L94" s="271"/>
       <c r="M94" s="51"/>
       <c r="N94" s="51"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="304"/>
-      <c r="B95" s="51"/>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
-      <c r="E95" s="51"/>
-      <c r="F95" s="51"/>
-      <c r="G95" s="51"/>
-      <c r="H95" s="51"/>
-      <c r="I95" s="51"/>
-      <c r="J95" s="51"/>
-      <c r="K95" s="51"/>
-      <c r="L95" s="51"/>
+      <c r="A95" s="271"/>
+      <c r="B95" s="271"/>
+      <c r="C95" s="271"/>
+      <c r="D95" s="271"/>
+      <c r="E95" s="271"/>
+      <c r="F95" s="271"/>
+      <c r="G95" s="271"/>
+      <c r="H95" s="271"/>
+      <c r="I95" s="271"/>
+      <c r="J95" s="271"/>
+      <c r="K95" s="271"/>
+      <c r="L95" s="271"/>
       <c r="M95" s="51"/>
       <c r="N95" s="51"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="304"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="51"/>
-      <c r="E96" s="51"/>
-      <c r="F96" s="51"/>
-      <c r="G96" s="51"/>
-      <c r="H96" s="51"/>
-      <c r="I96" s="51"/>
-      <c r="J96" s="51"/>
-      <c r="K96" s="51"/>
-      <c r="L96" s="51"/>
+      <c r="A96" s="271"/>
+      <c r="B96" s="271"/>
+      <c r="C96" s="271"/>
+      <c r="D96" s="271"/>
+      <c r="E96" s="271"/>
+      <c r="F96" s="271"/>
+      <c r="G96" s="271"/>
+      <c r="H96" s="271"/>
+      <c r="I96" s="271"/>
+      <c r="J96" s="271"/>
+      <c r="K96" s="271"/>
+      <c r="L96" s="271"/>
       <c r="M96" s="51"/>
       <c r="N96" s="51"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="304"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="51"/>
-      <c r="J97" s="51"/>
-      <c r="K97" s="51"/>
-      <c r="L97" s="51"/>
+      <c r="A97" s="271"/>
+      <c r="B97" s="271"/>
+      <c r="C97" s="271"/>
+      <c r="D97" s="271"/>
+      <c r="E97" s="271"/>
+      <c r="F97" s="271"/>
+      <c r="G97" s="271"/>
+      <c r="H97" s="271"/>
+      <c r="I97" s="271"/>
+      <c r="J97" s="271"/>
+      <c r="K97" s="271"/>
+      <c r="L97" s="271"/>
       <c r="M97" s="51"/>
       <c r="N97" s="51"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="304"/>
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="51"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="51"/>
-      <c r="I98" s="51"/>
-      <c r="J98" s="51"/>
-      <c r="K98" s="51"/>
-      <c r="L98" s="51"/>
+      <c r="A98" s="271"/>
+      <c r="B98" s="271"/>
+      <c r="C98" s="271"/>
+      <c r="D98" s="271"/>
+      <c r="E98" s="271"/>
+      <c r="F98" s="271"/>
+      <c r="G98" s="271"/>
+      <c r="H98" s="271"/>
+      <c r="I98" s="271"/>
+      <c r="J98" s="271"/>
+      <c r="K98" s="271"/>
+      <c r="L98" s="271"/>
       <c r="M98" s="51"/>
       <c r="N98" s="51"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="304"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
-      <c r="J99" s="51"/>
-      <c r="K99" s="51"/>
-      <c r="L99" s="51"/>
+      <c r="A99" s="271"/>
+      <c r="B99" s="271"/>
+      <c r="C99" s="271"/>
+      <c r="D99" s="271"/>
+      <c r="E99" s="271"/>
+      <c r="F99" s="271"/>
+      <c r="G99" s="271"/>
+      <c r="H99" s="271"/>
+      <c r="I99" s="271"/>
+      <c r="J99" s="271"/>
+      <c r="K99" s="271"/>
+      <c r="L99" s="271"/>
       <c r="M99" s="51"/>
       <c r="N99" s="51"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="304"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
-      <c r="J100" s="51"/>
-      <c r="K100" s="51"/>
-      <c r="L100" s="51"/>
+      <c r="A100" s="271"/>
+      <c r="B100" s="271"/>
+      <c r="C100" s="271"/>
+      <c r="D100" s="271"/>
+      <c r="E100" s="271"/>
+      <c r="F100" s="271"/>
+      <c r="G100" s="271"/>
+      <c r="H100" s="271"/>
+      <c r="I100" s="271"/>
+      <c r="J100" s="271"/>
+      <c r="K100" s="271"/>
+      <c r="L100" s="271"/>
       <c r="M100" s="51"/>
       <c r="N100" s="51"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="304"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
-      <c r="J101" s="51"/>
-      <c r="K101" s="51"/>
-      <c r="L101" s="51"/>
+      <c r="A101" s="271"/>
+      <c r="B101" s="271"/>
+      <c r="C101" s="271"/>
+      <c r="D101" s="271"/>
+      <c r="E101" s="271"/>
+      <c r="F101" s="271"/>
+      <c r="G101" s="271"/>
+      <c r="H101" s="271"/>
+      <c r="I101" s="271"/>
+      <c r="J101" s="271"/>
+      <c r="K101" s="271"/>
+      <c r="L101" s="271"/>
       <c r="M101" s="51"/>
       <c r="N101" s="51"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="304"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
-      <c r="F102" s="51"/>
-      <c r="G102" s="51"/>
-      <c r="H102" s="51"/>
-      <c r="I102" s="51"/>
-      <c r="J102" s="51"/>
-      <c r="K102" s="51"/>
-      <c r="L102" s="51"/>
+      <c r="A102" s="271"/>
+      <c r="B102" s="271"/>
+      <c r="C102" s="271"/>
+      <c r="D102" s="271"/>
+      <c r="E102" s="271"/>
+      <c r="F102" s="271"/>
+      <c r="G102" s="271"/>
+      <c r="H102" s="271"/>
+      <c r="I102" s="271"/>
+      <c r="J102" s="271"/>
+      <c r="K102" s="271"/>
+      <c r="L102" s="271"/>
       <c r="M102" s="51"/>
       <c r="N102" s="51"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="304"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="51"/>
-      <c r="G103" s="51"/>
-      <c r="H103" s="51"/>
-      <c r="I103" s="51"/>
-      <c r="J103" s="51"/>
-      <c r="K103" s="51"/>
-      <c r="L103" s="51"/>
+      <c r="A103" s="271"/>
+      <c r="B103" s="271"/>
+      <c r="C103" s="271"/>
+      <c r="D103" s="271"/>
+      <c r="E103" s="271"/>
+      <c r="F103" s="271"/>
+      <c r="G103" s="271"/>
+      <c r="H103" s="271"/>
+      <c r="I103" s="271"/>
+      <c r="J103" s="271"/>
+      <c r="K103" s="271"/>
+      <c r="L103" s="271"/>
       <c r="M103" s="51"/>
       <c r="N103" s="51"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="304"/>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="51"/>
-      <c r="G104" s="51"/>
-      <c r="H104" s="51"/>
-      <c r="I104" s="51"/>
-      <c r="J104" s="51"/>
-      <c r="K104" s="51"/>
-      <c r="L104" s="51"/>
+      <c r="A104" s="271"/>
+      <c r="B104" s="271"/>
+      <c r="C104" s="271"/>
+      <c r="D104" s="271"/>
+      <c r="E104" s="271"/>
+      <c r="F104" s="271"/>
+      <c r="G104" s="271"/>
+      <c r="H104" s="271"/>
+      <c r="I104" s="271"/>
+      <c r="J104" s="271"/>
+      <c r="K104" s="271"/>
+      <c r="L104" s="271"/>
       <c r="M104" s="51"/>
       <c r="N104" s="51"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="304"/>
+      <c r="A105" s="302"/>
       <c r="B105" s="51"/>
       <c r="C105" s="51"/>
       <c r="D105" s="51"/>
@@ -6099,7 +6166,7 @@
       <c r="N105" s="51"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="304"/>
+      <c r="A106" s="302"/>
       <c r="B106" s="51"/>
       <c r="C106" s="51"/>
       <c r="D106" s="51"/>
@@ -6115,7 +6182,7 @@
       <c r="N106" s="51"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="304"/>
+      <c r="A107" s="302"/>
       <c r="B107" s="51"/>
       <c r="C107" s="51"/>
       <c r="D107" s="51"/>
@@ -6131,7 +6198,7 @@
       <c r="N107" s="51"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="304"/>
+      <c r="A108" s="302"/>
       <c r="B108" s="51"/>
       <c r="C108" s="51"/>
       <c r="D108" s="51"/>
@@ -6147,7 +6214,7 @@
       <c r="N108" s="51"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" s="304"/>
+      <c r="A109" s="302"/>
       <c r="B109" s="51"/>
       <c r="C109" s="51"/>
       <c r="D109" s="51"/>
@@ -6163,7 +6230,7 @@
       <c r="N109" s="51"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="304"/>
+      <c r="A110" s="302"/>
       <c r="B110" s="51"/>
       <c r="C110" s="51"/>
       <c r="D110" s="51"/>
@@ -6179,7 +6246,7 @@
       <c r="N110" s="51"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="304"/>
+      <c r="A111" s="302"/>
       <c r="B111" s="51"/>
       <c r="C111" s="51"/>
       <c r="D111" s="51"/>
@@ -6195,7 +6262,7 @@
       <c r="N111" s="51"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" s="304"/>
+      <c r="A112" s="302"/>
       <c r="B112" s="51"/>
       <c r="C112" s="51"/>
       <c r="D112" s="51"/>
@@ -6211,7 +6278,7 @@
       <c r="N112" s="51"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="304"/>
+      <c r="A113" s="302"/>
       <c r="B113" s="51"/>
       <c r="C113" s="51"/>
       <c r="D113" s="51"/>
@@ -6227,13 +6294,13 @@
       <c r="N113" s="51"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="304"/>
+      <c r="A114" s="302"/>
       <c r="B114" s="51"/>
       <c r="C114" s="51"/>
       <c r="D114" s="51"/>
       <c r="E114" s="51"/>
       <c r="F114" s="51"/>
-      <c r="G114" s="304"/>
+      <c r="G114" s="302"/>
       <c r="H114" s="51"/>
       <c r="I114" s="51"/>
       <c r="J114" s="51"/>
@@ -6243,179 +6310,179 @@
       <c r="N114" s="51"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="304"/>
-      <c r="B115" s="304"/>
-      <c r="C115" s="304"/>
-      <c r="D115" s="304"/>
-      <c r="E115" s="304"/>
-      <c r="F115" s="304"/>
-      <c r="G115" s="304"/>
-      <c r="H115" s="304"/>
-      <c r="I115" s="304"/>
-      <c r="J115" s="304"/>
-      <c r="K115" s="304"/>
-      <c r="L115" s="304"/>
-      <c r="M115" s="304"/>
+      <c r="A115" s="302"/>
+      <c r="B115" s="302"/>
+      <c r="C115" s="302"/>
+      <c r="D115" s="302"/>
+      <c r="E115" s="302"/>
+      <c r="F115" s="302"/>
+      <c r="G115" s="302"/>
+      <c r="H115" s="302"/>
+      <c r="I115" s="302"/>
+      <c r="J115" s="302"/>
+      <c r="K115" s="302"/>
+      <c r="L115" s="302"/>
+      <c r="M115" s="302"/>
       <c r="N115" s="51"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="304"/>
-      <c r="B116" s="304"/>
-      <c r="C116" s="304"/>
-      <c r="D116" s="304"/>
-      <c r="E116" s="304"/>
-      <c r="F116" s="304"/>
-      <c r="G116" s="304"/>
-      <c r="H116" s="304"/>
-      <c r="I116" s="304"/>
-      <c r="J116" s="304"/>
-      <c r="K116" s="304"/>
-      <c r="L116" s="304"/>
-      <c r="M116" s="304"/>
+      <c r="A116" s="302"/>
+      <c r="B116" s="302"/>
+      <c r="C116" s="302"/>
+      <c r="D116" s="302"/>
+      <c r="E116" s="302"/>
+      <c r="F116" s="302"/>
+      <c r="G116" s="302"/>
+      <c r="H116" s="302"/>
+      <c r="I116" s="302"/>
+      <c r="J116" s="302"/>
+      <c r="K116" s="302"/>
+      <c r="L116" s="302"/>
+      <c r="M116" s="302"/>
       <c r="N116" s="51"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="304"/>
-      <c r="B117" s="304"/>
-      <c r="C117" s="304"/>
-      <c r="D117" s="304"/>
-      <c r="E117" s="304"/>
-      <c r="F117" s="304"/>
-      <c r="G117" s="304"/>
-      <c r="H117" s="304"/>
-      <c r="I117" s="304"/>
-      <c r="J117" s="304"/>
-      <c r="K117" s="304"/>
-      <c r="L117" s="304"/>
-      <c r="M117" s="304"/>
+      <c r="A117" s="302"/>
+      <c r="B117" s="302"/>
+      <c r="C117" s="302"/>
+      <c r="D117" s="302"/>
+      <c r="E117" s="302"/>
+      <c r="F117" s="302"/>
+      <c r="G117" s="302"/>
+      <c r="H117" s="302"/>
+      <c r="I117" s="302"/>
+      <c r="J117" s="302"/>
+      <c r="K117" s="302"/>
+      <c r="L117" s="302"/>
+      <c r="M117" s="302"/>
       <c r="N117" s="51"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="304"/>
-      <c r="B118" s="304"/>
-      <c r="C118" s="304"/>
-      <c r="D118" s="304"/>
-      <c r="E118" s="304"/>
-      <c r="F118" s="304"/>
-      <c r="G118" s="304"/>
-      <c r="H118" s="304"/>
-      <c r="I118" s="304"/>
-      <c r="J118" s="304"/>
-      <c r="K118" s="304"/>
-      <c r="L118" s="304"/>
-      <c r="M118" s="304"/>
+      <c r="A118" s="302"/>
+      <c r="B118" s="302"/>
+      <c r="C118" s="302"/>
+      <c r="D118" s="302"/>
+      <c r="E118" s="302"/>
+      <c r="F118" s="302"/>
+      <c r="G118" s="302"/>
+      <c r="H118" s="302"/>
+      <c r="I118" s="302"/>
+      <c r="J118" s="302"/>
+      <c r="K118" s="302"/>
+      <c r="L118" s="302"/>
+      <c r="M118" s="302"/>
       <c r="N118" s="51"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="304"/>
-      <c r="B119" s="304"/>
-      <c r="C119" s="304"/>
-      <c r="D119" s="304"/>
-      <c r="E119" s="304"/>
-      <c r="F119" s="304"/>
-      <c r="G119" s="304"/>
-      <c r="H119" s="304"/>
-      <c r="I119" s="304"/>
-      <c r="J119" s="304"/>
-      <c r="K119" s="304"/>
-      <c r="L119" s="304"/>
-      <c r="M119" s="304"/>
+      <c r="A119" s="302"/>
+      <c r="B119" s="302"/>
+      <c r="C119" s="302"/>
+      <c r="D119" s="302"/>
+      <c r="E119" s="302"/>
+      <c r="F119" s="302"/>
+      <c r="G119" s="302"/>
+      <c r="H119" s="302"/>
+      <c r="I119" s="302"/>
+      <c r="J119" s="302"/>
+      <c r="K119" s="302"/>
+      <c r="L119" s="302"/>
+      <c r="M119" s="302"/>
       <c r="N119" s="51"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="304"/>
-      <c r="B120" s="304"/>
-      <c r="C120" s="304"/>
-      <c r="D120" s="304"/>
-      <c r="E120" s="304"/>
-      <c r="F120" s="304"/>
-      <c r="G120" s="304"/>
-      <c r="H120" s="304"/>
-      <c r="I120" s="304"/>
-      <c r="J120" s="304"/>
-      <c r="K120" s="304"/>
-      <c r="L120" s="304"/>
-      <c r="M120" s="304"/>
+      <c r="A120" s="302"/>
+      <c r="B120" s="302"/>
+      <c r="C120" s="302"/>
+      <c r="D120" s="302"/>
+      <c r="E120" s="302"/>
+      <c r="F120" s="302"/>
+      <c r="G120" s="302"/>
+      <c r="H120" s="302"/>
+      <c r="I120" s="302"/>
+      <c r="J120" s="302"/>
+      <c r="K120" s="302"/>
+      <c r="L120" s="302"/>
+      <c r="M120" s="302"/>
       <c r="N120" s="51"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="304"/>
-      <c r="B121" s="304"/>
-      <c r="C121" s="304"/>
-      <c r="D121" s="304"/>
-      <c r="E121" s="304"/>
-      <c r="F121" s="304"/>
-      <c r="G121" s="304"/>
-      <c r="H121" s="304"/>
-      <c r="I121" s="304"/>
-      <c r="J121" s="304"/>
-      <c r="K121" s="304"/>
-      <c r="L121" s="304"/>
-      <c r="M121" s="304"/>
+      <c r="A121" s="302"/>
+      <c r="B121" s="302"/>
+      <c r="C121" s="302"/>
+      <c r="D121" s="302"/>
+      <c r="E121" s="302"/>
+      <c r="F121" s="302"/>
+      <c r="G121" s="302"/>
+      <c r="H121" s="302"/>
+      <c r="I121" s="302"/>
+      <c r="J121" s="302"/>
+      <c r="K121" s="302"/>
+      <c r="L121" s="302"/>
+      <c r="M121" s="302"/>
       <c r="N121" s="51"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A122" s="304"/>
-      <c r="B122" s="304"/>
-      <c r="C122" s="304"/>
-      <c r="D122" s="304"/>
-      <c r="E122" s="304"/>
-      <c r="F122" s="304"/>
-      <c r="G122" s="304"/>
-      <c r="H122" s="304"/>
-      <c r="I122" s="304"/>
-      <c r="J122" s="304"/>
-      <c r="K122" s="304"/>
-      <c r="L122" s="304"/>
-      <c r="M122" s="304"/>
+      <c r="A122" s="302"/>
+      <c r="B122" s="302"/>
+      <c r="C122" s="302"/>
+      <c r="D122" s="302"/>
+      <c r="E122" s="302"/>
+      <c r="F122" s="302"/>
+      <c r="G122" s="302"/>
+      <c r="H122" s="302"/>
+      <c r="I122" s="302"/>
+      <c r="J122" s="302"/>
+      <c r="K122" s="302"/>
+      <c r="L122" s="302"/>
+      <c r="M122" s="302"/>
       <c r="N122" s="51"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A123" s="304"/>
-      <c r="B123" s="304"/>
-      <c r="C123" s="304"/>
-      <c r="D123" s="304"/>
-      <c r="E123" s="304"/>
-      <c r="F123" s="304"/>
-      <c r="G123" s="304"/>
-      <c r="H123" s="304"/>
-      <c r="I123" s="304"/>
-      <c r="J123" s="304"/>
-      <c r="K123" s="304"/>
-      <c r="L123" s="304"/>
-      <c r="M123" s="304"/>
+      <c r="A123" s="302"/>
+      <c r="B123" s="302"/>
+      <c r="C123" s="302"/>
+      <c r="D123" s="302"/>
+      <c r="E123" s="302"/>
+      <c r="F123" s="302"/>
+      <c r="G123" s="302"/>
+      <c r="H123" s="302"/>
+      <c r="I123" s="302"/>
+      <c r="J123" s="302"/>
+      <c r="K123" s="302"/>
+      <c r="L123" s="302"/>
+      <c r="M123" s="302"/>
       <c r="N123" s="51"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A124" s="304"/>
-      <c r="B124" s="304"/>
-      <c r="C124" s="304"/>
-      <c r="D124" s="304"/>
-      <c r="E124" s="304"/>
-      <c r="F124" s="304"/>
-      <c r="G124" s="304"/>
-      <c r="H124" s="304"/>
-      <c r="I124" s="304"/>
-      <c r="J124" s="304"/>
-      <c r="K124" s="304"/>
-      <c r="L124" s="304"/>
-      <c r="M124" s="304"/>
+      <c r="A124" s="302"/>
+      <c r="B124" s="302"/>
+      <c r="C124" s="302"/>
+      <c r="D124" s="302"/>
+      <c r="E124" s="302"/>
+      <c r="F124" s="302"/>
+      <c r="G124" s="302"/>
+      <c r="H124" s="302"/>
+      <c r="I124" s="302"/>
+      <c r="J124" s="302"/>
+      <c r="K124" s="302"/>
+      <c r="L124" s="302"/>
+      <c r="M124" s="302"/>
       <c r="N124" s="51"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A125" s="304"/>
-      <c r="B125" s="304"/>
-      <c r="C125" s="304"/>
-      <c r="D125" s="304"/>
-      <c r="E125" s="304"/>
-      <c r="F125" s="304"/>
+      <c r="A125" s="302"/>
+      <c r="B125" s="302"/>
+      <c r="C125" s="302"/>
+      <c r="D125" s="302"/>
+      <c r="E125" s="302"/>
+      <c r="F125" s="302"/>
       <c r="G125" s="50"/>
-      <c r="H125" s="304"/>
-      <c r="I125" s="304"/>
-      <c r="J125" s="304"/>
-      <c r="K125" s="304"/>
-      <c r="L125" s="304"/>
-      <c r="M125" s="304"/>
+      <c r="H125" s="302"/>
+      <c r="I125" s="302"/>
+      <c r="J125" s="302"/>
+      <c r="K125" s="302"/>
+      <c r="L125" s="302"/>
+      <c r="M125" s="302"/>
       <c r="N125" s="51"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -96,21 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Edgardo Omar:5 aportes nesesarios</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K10" authorId="0">
+    <comment ref="L10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -159,7 +145,55 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0">
+    <comment ref="L11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Edgardo Omar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Abonado 15/5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Edgardo Omar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+vto 15/5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -222,7 +256,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="209">
   <si>
     <t>Servicios</t>
   </si>
@@ -737,15 +771,9 @@
     <t>NOVIEMBRE</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuenta corriente </t>
-  </si>
-  <si>
     <t>Y P F</t>
   </si>
   <si>
-    <t xml:space="preserve"> Carrefour Omar</t>
-  </si>
-  <si>
     <t>Eliel</t>
   </si>
   <si>
@@ -812,18 +840,12 @@
     <t>Patente</t>
   </si>
   <si>
-    <t>Gasto mens prest</t>
-  </si>
-  <si>
     <t>Serv e Impuestos</t>
   </si>
   <si>
     <t>CHAMPION</t>
   </si>
   <si>
-    <t>AGUINALDO</t>
-  </si>
-  <si>
     <t>Prerstamos</t>
   </si>
   <si>
@@ -846,6 +868,21 @@
   </si>
   <si>
     <t>Carrefour</t>
+  </si>
+  <si>
+    <t>PrestamCArrefour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuent corriente </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Carref Omar</t>
+  </si>
+  <si>
+    <t>Vto Prestamos</t>
+  </si>
+  <si>
+    <t>Mantenimiento</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1598,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -2122,15 +2159,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2216,7 +2244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="498">
+  <cellXfs count="527">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2619,14 +2647,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2666,9 +2690,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2684,9 +2705,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2804,9 +2822,6 @@
     <xf numFmtId="0" fontId="7" fillId="22" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2816,14 +2831,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2834,16 +2845,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2881,16 +2886,6 @@
     <xf numFmtId="2" fontId="17" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2917,40 +2912,17 @@
     <xf numFmtId="0" fontId="17" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="53" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="58" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="57" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="28" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="35" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="50" fillId="35" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="53" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2961,13 +2933,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="29" fillId="26" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="29" fillId="6" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="29" fillId="6" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="29" fillId="6" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="29" fillId="6" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="29" fillId="6" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="29" fillId="6" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2975,23 +2945,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3061,6 +3020,134 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="57" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="53" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="32" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="53" fillId="26" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="9" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="43" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="50" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="53" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="53" fillId="28" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4216,7 +4303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N172"/>
+  <dimension ref="A1:Q172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -4227,1930 +4314,1986 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" customWidth="1"/>
     <col min="12" max="12" width="17.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="297" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="299"/>
-      <c r="C1" s="368" t="s">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="293" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="295"/>
+      <c r="C1" s="361" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="267" t="s">
+      <c r="D1" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="267" t="s">
+      <c r="E1" s="265" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="267" t="s">
-        <v>183</v>
-      </c>
-      <c r="G1" s="268" t="s">
+      <c r="F1" s="265" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="266" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="274"/>
-      <c r="I1" s="350" t="s">
+      <c r="H1" s="272"/>
+      <c r="I1" s="346" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="351" t="s">
+      <c r="J1" s="347" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="384" t="s">
-        <v>195</v>
-      </c>
-      <c r="L1" s="355" t="s">
-        <v>196</v>
-      </c>
-      <c r="M1" s="101"/>
-      <c r="N1" s="50"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="289"/>
-      <c r="B2" s="300"/>
-      <c r="C2" s="382"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="287"/>
-      <c r="F2" s="383"/>
+      <c r="K1" s="373" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1" s="350"/>
+      <c r="M1" s="448"/>
+      <c r="N1" s="269"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="286"/>
+      <c r="B2" s="296"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="284"/>
+      <c r="F2" s="372"/>
       <c r="G2" s="198"/>
-      <c r="H2" s="271"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="373"/>
-      <c r="K2" s="329"/>
-      <c r="L2" s="391">
-        <v>102247</v>
-      </c>
-      <c r="M2" s="112"/>
-      <c r="N2" s="50"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="289"/>
-      <c r="B3" s="300"/>
-      <c r="C3" s="287"/>
+      <c r="H2" s="269"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="365"/>
+      <c r="K2" s="325"/>
+      <c r="L2" s="380"/>
+      <c r="M2" s="513"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="286"/>
+      <c r="B3" s="296"/>
+      <c r="C3" s="284"/>
       <c r="D3" s="198"/>
       <c r="E3" s="198"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
+      <c r="F3" s="285"/>
+      <c r="G3" s="269"/>
+      <c r="H3" s="269"/>
       <c r="I3" s="198"/>
-      <c r="J3" s="286"/>
-      <c r="K3" s="329"/>
-      <c r="L3" s="392">
-        <v>67275.839999999997</v>
-      </c>
-      <c r="M3" s="101"/>
-      <c r="N3" s="50"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="381" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="271"/>
+      <c r="J3" s="283"/>
+      <c r="K3" s="325"/>
+      <c r="L3" s="381"/>
+      <c r="M3" s="448"/>
+      <c r="N3" s="269"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+    </row>
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="370" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="269"/>
       <c r="C4" s="150">
-        <v>13361.72</v>
-      </c>
-      <c r="D4" s="372" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="457">
-        <v>9588</v>
-      </c>
-      <c r="F4" s="456">
-        <v>23947.99</v>
-      </c>
-      <c r="G4" s="302"/>
-      <c r="H4" s="302"/>
-      <c r="I4" s="150">
+        <v>37728</v>
+      </c>
+      <c r="D4" s="150">
+        <v>24360</v>
+      </c>
+      <c r="E4" s="284">
+        <v>9568</v>
+      </c>
+      <c r="F4" s="150">
+        <v>25000</v>
+      </c>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="284">
         <v>12165</v>
       </c>
-      <c r="J4" s="178">
-        <v>5581</v>
-      </c>
-      <c r="K4" s="329"/>
-      <c r="L4" s="391">
-        <v>236679.18</v>
-      </c>
-      <c r="M4" s="101"/>
-      <c r="N4" s="50"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="289"/>
-      <c r="B5" s="300"/>
-      <c r="C5" s="287"/>
-      <c r="D5" s="287"/>
-      <c r="E5" s="287"/>
-      <c r="F5" s="287">
-        <v>20000</v>
-      </c>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="287"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="286"/>
-      <c r="L5" s="412">
-        <v>130000</v>
-      </c>
-      <c r="M5" s="101"/>
-      <c r="N5" s="50"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="271"/>
-      <c r="B6" s="271"/>
-      <c r="C6" s="271"/>
-      <c r="D6" s="271"/>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="286"/>
-      <c r="L6" s="436">
-        <f>SUM(L2:L5)</f>
-        <v>536202.02</v>
-      </c>
-      <c r="M6" s="50"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="289"/>
-      <c r="B7" s="353"/>
-      <c r="C7" s="262" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7" s="263" t="s">
+      <c r="J4" s="461"/>
+      <c r="K4" s="325"/>
+      <c r="L4" s="380"/>
+      <c r="M4" s="448"/>
+      <c r="N4" s="269"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="286"/>
+      <c r="B5" s="296"/>
+      <c r="C5" s="284"/>
+      <c r="D5" s="284"/>
+      <c r="E5" s="284"/>
+      <c r="F5" s="284"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="269"/>
+      <c r="I5" s="284"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="283"/>
+      <c r="L5" s="395"/>
+      <c r="M5" s="401"/>
+      <c r="N5" s="478"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="269"/>
+      <c r="B6" s="269"/>
+      <c r="C6" s="269"/>
+      <c r="D6" s="269"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="269"/>
+      <c r="G6" s="269"/>
+      <c r="H6" s="269"/>
+      <c r="I6" s="269"/>
+      <c r="J6" s="269"/>
+      <c r="K6" s="283"/>
+      <c r="L6" s="460"/>
+      <c r="M6" s="518"/>
+      <c r="N6" s="478"/>
+      <c r="O6" s="50"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
+    </row>
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="286"/>
+      <c r="B7" s="501"/>
+      <c r="C7" s="505" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="503" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="262" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="263" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="493" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="264" t="s">
+        <v>207</v>
+      </c>
+      <c r="I7" s="495" t="s">
+        <v>205</v>
+      </c>
+      <c r="J7" s="273" t="s">
+        <v>206</v>
+      </c>
+      <c r="K7" s="276" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="390" t="s">
+        <v>184</v>
+      </c>
+      <c r="M7" s="520" t="s">
+        <v>204</v>
+      </c>
+      <c r="N7" s="496"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="294"/>
+      <c r="B8" s="502"/>
+      <c r="C8" s="478"/>
+      <c r="D8" s="504"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="367"/>
+      <c r="G8" s="494">
+        <v>99773.25</v>
+      </c>
+      <c r="H8" s="507">
+        <v>46193</v>
+      </c>
+      <c r="I8" s="496"/>
+      <c r="J8" s="286"/>
+      <c r="K8" s="291"/>
+      <c r="L8" s="283"/>
+      <c r="M8" s="519"/>
+      <c r="N8" s="478"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+    </row>
+    <row r="9" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="286"/>
+      <c r="B9" s="499">
+        <v>1</v>
+      </c>
+      <c r="C9" s="500"/>
+      <c r="D9" s="376"/>
+      <c r="E9" s="287"/>
+      <c r="F9" s="466"/>
+      <c r="G9" s="508">
+        <v>66924</v>
+      </c>
+      <c r="H9" s="507">
+        <v>46210</v>
+      </c>
+      <c r="I9" s="496"/>
+      <c r="J9" s="287"/>
+      <c r="K9" s="288"/>
+      <c r="L9" s="283"/>
+      <c r="M9" s="486"/>
+      <c r="N9" s="478"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+    </row>
+    <row r="10" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="286"/>
+      <c r="B10" s="499">
+        <v>2</v>
+      </c>
+      <c r="C10" s="438"/>
+      <c r="D10" s="374"/>
+      <c r="E10" s="289"/>
+      <c r="F10" s="467"/>
+      <c r="G10" s="506">
+        <v>235158.78</v>
+      </c>
+      <c r="H10" s="507">
+        <v>46193</v>
+      </c>
+      <c r="I10" s="496"/>
+      <c r="J10" s="287"/>
+      <c r="K10" s="397"/>
+      <c r="L10" s="465">
+        <v>69853</v>
+      </c>
+      <c r="M10" s="478"/>
+      <c r="N10" s="478"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+    </row>
+    <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="286"/>
+      <c r="B11" s="391">
+        <v>3</v>
+      </c>
+      <c r="C11" s="498"/>
+      <c r="D11" s="375">
+        <v>446458</v>
+      </c>
+      <c r="E11" s="468">
+        <v>500</v>
+      </c>
+      <c r="F11" s="492" t="s">
+        <v>208</v>
+      </c>
+      <c r="G11" s="522">
+        <f>SUM(G8:G10)</f>
+        <v>401856.03</v>
+      </c>
+      <c r="H11" s="374"/>
+      <c r="I11" s="496"/>
+      <c r="J11" s="469">
+        <v>98858</v>
+      </c>
+      <c r="K11" s="471">
+        <v>52966</v>
+      </c>
+      <c r="L11" s="470">
+        <v>13840</v>
+      </c>
+      <c r="M11" s="150">
+        <v>122867</v>
+      </c>
+      <c r="N11" s="478"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+    </row>
+    <row r="12" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="271"/>
+      <c r="B12" s="392">
+        <v>4</v>
+      </c>
+      <c r="C12" s="284"/>
+      <c r="D12" s="379"/>
+      <c r="E12" s="287"/>
+      <c r="F12" s="275"/>
+      <c r="G12" s="523"/>
+      <c r="H12" s="478"/>
+      <c r="I12" s="497"/>
+      <c r="J12" s="478"/>
+      <c r="K12" s="401"/>
+      <c r="L12" s="483"/>
+      <c r="M12" s="514"/>
+      <c r="N12" s="269"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="268"/>
+      <c r="B13" s="393">
+        <v>5</v>
+      </c>
+      <c r="C13" s="396"/>
+      <c r="D13" s="388"/>
+      <c r="E13" s="275"/>
+      <c r="F13" s="382"/>
+      <c r="G13" s="524"/>
+      <c r="H13" s="401"/>
+      <c r="I13" s="480"/>
+      <c r="J13" s="403"/>
+      <c r="K13" s="401"/>
+      <c r="L13" s="457"/>
+      <c r="M13" s="283"/>
+      <c r="N13" s="269"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+    </row>
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="268"/>
+      <c r="B14" s="302"/>
+      <c r="C14" s="389"/>
+      <c r="D14" s="394"/>
+      <c r="E14" s="405"/>
+      <c r="F14" s="406"/>
+      <c r="G14" s="525"/>
+      <c r="H14" s="478"/>
+      <c r="I14" s="509"/>
+      <c r="J14" s="481"/>
+      <c r="K14" s="484"/>
+      <c r="L14" s="458"/>
+      <c r="M14" s="515"/>
+      <c r="N14" s="269"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="268"/>
+      <c r="B15" s="302"/>
+      <c r="C15" s="377"/>
+      <c r="D15" s="322"/>
+      <c r="E15" s="408" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" s="409">
+        <v>200000</v>
+      </c>
+      <c r="G15" s="526"/>
+      <c r="H15" s="482"/>
+      <c r="I15" s="403"/>
+      <c r="J15" s="478"/>
+      <c r="K15" s="485"/>
+      <c r="L15" s="458"/>
+      <c r="M15" s="516"/>
+      <c r="N15" s="269"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="269"/>
+      <c r="B16" s="283"/>
+      <c r="C16" s="378"/>
+      <c r="D16" s="322"/>
+      <c r="E16" s="410"/>
+      <c r="F16" s="411"/>
+      <c r="G16" s="521"/>
+      <c r="H16" s="478"/>
+      <c r="I16" s="510"/>
+      <c r="J16" s="478"/>
+      <c r="K16" s="486"/>
+      <c r="L16" s="458"/>
+      <c r="M16" s="283"/>
+      <c r="N16" s="198"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="269"/>
+      <c r="B17" s="283"/>
+      <c r="C17" s="269"/>
+      <c r="D17" s="322"/>
+      <c r="E17" s="412"/>
+      <c r="F17" s="411"/>
+      <c r="G17" s="477"/>
+      <c r="H17" s="479"/>
+      <c r="I17" s="511"/>
+      <c r="J17" s="479"/>
+      <c r="K17" s="484"/>
+      <c r="L17" s="458"/>
+      <c r="M17" s="461"/>
+      <c r="N17" s="269"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="367"/>
+      <c r="B18" s="369"/>
+      <c r="C18" s="368"/>
+      <c r="D18" s="325"/>
+      <c r="E18" s="414"/>
+      <c r="F18" s="415"/>
+      <c r="G18" s="413"/>
+      <c r="H18" s="402"/>
+      <c r="I18" s="491"/>
+      <c r="J18" s="479"/>
+      <c r="K18" s="487"/>
+      <c r="L18" s="458"/>
+      <c r="M18" s="461"/>
+      <c r="N18" s="269"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="50"/>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="301"/>
+      <c r="B19" s="302"/>
+      <c r="C19" s="355"/>
+      <c r="D19" s="404"/>
+      <c r="E19" s="416"/>
+      <c r="F19" s="417"/>
+      <c r="G19" s="418"/>
+      <c r="H19" s="488"/>
+      <c r="I19" s="512"/>
+      <c r="J19" s="489"/>
+      <c r="K19" s="490"/>
+      <c r="L19" s="458"/>
+      <c r="M19" s="461"/>
+      <c r="N19" s="269"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="300"/>
+      <c r="B20" s="302"/>
+      <c r="C20" s="345"/>
+      <c r="D20" s="357"/>
+      <c r="E20" s="407"/>
+      <c r="F20" s="357"/>
+      <c r="G20" s="332"/>
+      <c r="H20" s="491"/>
+      <c r="I20" s="491"/>
+      <c r="J20" s="479"/>
+      <c r="K20" s="490"/>
+      <c r="L20" s="458"/>
+      <c r="M20" s="283"/>
+      <c r="N20" s="269"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="301"/>
+      <c r="B21" s="297"/>
+      <c r="C21" s="366" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="387" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="270" t="s">
         <v>192</v>
       </c>
-      <c r="E7" s="263" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="264" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="264" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="265" t="s">
+      <c r="F21" s="274" t="s">
+        <v>177</v>
+      </c>
+      <c r="G21" s="264" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="348" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="267" t="s">
+        <v>55</v>
+      </c>
+      <c r="J21" s="292" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="275" t="s">
-        <v>173</v>
-      </c>
-      <c r="J7" s="278" t="s">
-        <v>150</v>
-      </c>
-      <c r="K7" s="405" t="s">
-        <v>186</v>
-      </c>
-      <c r="L7" s="271"/>
-      <c r="M7" s="248"/>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="298"/>
-      <c r="B8" s="292"/>
-      <c r="C8" s="288"/>
-      <c r="D8" s="293"/>
-      <c r="E8" s="289"/>
-      <c r="F8" s="289"/>
-      <c r="G8" s="294"/>
-      <c r="H8" s="289"/>
-      <c r="I8" s="289"/>
-      <c r="J8" s="295"/>
-      <c r="K8" s="286"/>
-      <c r="L8" s="437"/>
-      <c r="M8" s="248"/>
-      <c r="N8" s="51"/>
-    </row>
-    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="289"/>
-      <c r="B9" s="406">
-        <v>1</v>
-      </c>
-      <c r="C9" s="479">
-        <v>107000</v>
-      </c>
-      <c r="D9" s="387"/>
-      <c r="E9" s="290"/>
-      <c r="F9" s="290"/>
-      <c r="G9" s="287"/>
-      <c r="H9" s="290"/>
-      <c r="I9" s="290"/>
-      <c r="J9" s="291"/>
-      <c r="K9" s="286"/>
-      <c r="L9" s="411"/>
-      <c r="M9" s="248"/>
-      <c r="N9" s="51"/>
-    </row>
-    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="289"/>
-      <c r="B10" s="406">
-        <v>2</v>
-      </c>
-      <c r="C10" s="287">
-        <v>107000</v>
-      </c>
-      <c r="D10" s="385"/>
-      <c r="E10" s="293"/>
-      <c r="F10" s="290"/>
-      <c r="G10" s="290"/>
-      <c r="H10" s="290"/>
-      <c r="I10" s="290"/>
-      <c r="J10" s="416"/>
-      <c r="K10" s="417">
-        <v>69853</v>
-      </c>
-      <c r="L10" s="271"/>
-      <c r="M10" s="434"/>
-      <c r="N10" s="51"/>
-    </row>
-    <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="289"/>
-      <c r="B11" s="406">
-        <v>3</v>
-      </c>
-      <c r="C11" s="287">
-        <v>107000</v>
-      </c>
-      <c r="D11" s="386">
-        <v>257883</v>
-      </c>
-      <c r="E11" s="460">
-        <v>500</v>
-      </c>
-      <c r="F11" s="393">
-        <v>440000</v>
-      </c>
-      <c r="G11" s="287"/>
-      <c r="H11" s="293">
-        <v>0</v>
-      </c>
-      <c r="I11" s="393">
-        <v>92416</v>
-      </c>
-      <c r="J11" s="291">
-        <v>55747</v>
-      </c>
-      <c r="K11" s="458">
-        <v>13800</v>
-      </c>
-      <c r="L11" s="271"/>
-      <c r="M11" s="248"/>
-      <c r="N11" s="51"/>
-    </row>
-    <row r="12" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="273"/>
-      <c r="B12" s="407">
-        <v>4</v>
-      </c>
-      <c r="C12" s="287">
-        <v>107000</v>
-      </c>
-      <c r="D12" s="390"/>
-      <c r="E12" s="290"/>
-      <c r="F12" s="455"/>
-      <c r="G12" s="372"/>
-      <c r="H12" s="302"/>
-      <c r="I12" s="394"/>
-      <c r="J12" s="286"/>
-      <c r="K12" s="286"/>
-      <c r="L12" s="271"/>
-      <c r="M12" s="434"/>
-      <c r="N12" s="51"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="270"/>
-      <c r="B13" s="408">
-        <v>5</v>
-      </c>
-      <c r="C13" s="287">
-        <v>107000</v>
-      </c>
-      <c r="D13" s="403"/>
-      <c r="E13" s="277"/>
-      <c r="F13" s="393"/>
-      <c r="G13" s="303"/>
-      <c r="H13" s="326"/>
-      <c r="I13" s="395"/>
-      <c r="J13" s="304"/>
-      <c r="K13" s="286"/>
-      <c r="L13" s="431"/>
-      <c r="M13" s="248"/>
-      <c r="N13" s="51"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="270"/>
-      <c r="B14" s="306"/>
-      <c r="C14" s="404">
-        <f>SUM(C9:C13)</f>
-        <v>535000</v>
-      </c>
-      <c r="D14" s="409"/>
-      <c r="E14" s="439"/>
-      <c r="F14" s="440"/>
-      <c r="G14" s="369"/>
-      <c r="H14" s="326"/>
-      <c r="I14" s="396"/>
-      <c r="J14" s="328"/>
-      <c r="K14" s="382"/>
-      <c r="L14" s="432"/>
-      <c r="M14" s="415"/>
-      <c r="N14" s="51"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="270"/>
-      <c r="B15" s="306"/>
-      <c r="C15" s="388"/>
-      <c r="D15" s="326"/>
-      <c r="E15" s="442" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="443">
-        <v>5000000</v>
-      </c>
-      <c r="G15" s="444" t="s">
-        <v>199</v>
-      </c>
-      <c r="H15" s="375"/>
-      <c r="I15" s="393"/>
-      <c r="J15" s="376"/>
-      <c r="K15" s="423"/>
-      <c r="L15" s="432"/>
-      <c r="M15" s="248"/>
-      <c r="N15" s="51"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="271"/>
-      <c r="B16" s="286"/>
-      <c r="C16" s="389"/>
-      <c r="D16" s="326"/>
-      <c r="E16" s="445"/>
-      <c r="F16" s="446"/>
-      <c r="G16" s="447"/>
-      <c r="H16" s="429"/>
-      <c r="I16" s="411"/>
-      <c r="J16" s="361"/>
-      <c r="K16" s="424"/>
-      <c r="L16" s="432"/>
-      <c r="M16" s="413"/>
-      <c r="N16" s="51"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="271"/>
-      <c r="B17" s="286"/>
-      <c r="C17" s="271"/>
-      <c r="D17" s="326"/>
-      <c r="E17" s="448"/>
-      <c r="F17" s="446"/>
-      <c r="G17" s="449"/>
-      <c r="H17" s="430"/>
-      <c r="I17" s="410"/>
-      <c r="J17" s="397"/>
-      <c r="K17" s="423"/>
-      <c r="L17" s="432"/>
-      <c r="M17" s="435"/>
-      <c r="N17" s="248"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="378"/>
-      <c r="B18" s="380"/>
-      <c r="C18" s="379"/>
-      <c r="D18" s="329"/>
-      <c r="E18" s="450"/>
-      <c r="F18" s="451"/>
-      <c r="G18" s="449"/>
-      <c r="H18" s="374"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="424"/>
-      <c r="L18" s="432"/>
-      <c r="M18" s="371"/>
-      <c r="N18" s="51"/>
-    </row>
-    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="305"/>
-      <c r="B19" s="306"/>
-      <c r="C19" s="360"/>
-      <c r="D19" s="438"/>
-      <c r="E19" s="452"/>
-      <c r="F19" s="453"/>
-      <c r="G19" s="454"/>
-      <c r="H19" s="364"/>
-      <c r="I19" s="363"/>
-      <c r="J19" s="363"/>
-      <c r="K19" s="423"/>
-      <c r="L19" s="432"/>
-      <c r="M19" s="248"/>
-      <c r="N19" s="51"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="304"/>
-      <c r="B20" s="306"/>
-      <c r="C20" s="349"/>
-      <c r="D20" s="363"/>
-      <c r="E20" s="441"/>
-      <c r="F20" s="363"/>
-      <c r="G20" s="336"/>
-      <c r="H20" s="281"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="423"/>
-      <c r="L20" s="432"/>
-      <c r="M20" s="248"/>
-      <c r="N20" s="51"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="305"/>
-      <c r="B21" s="301"/>
-      <c r="C21" s="377" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="402" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="272" t="s">
-        <v>194</v>
-      </c>
-      <c r="F21" s="276" t="s">
-        <v>179</v>
-      </c>
-      <c r="G21" s="266" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="352" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" s="269" t="s">
-        <v>55</v>
-      </c>
-      <c r="J21" s="296" t="s">
-        <v>172</v>
-      </c>
-      <c r="K21" s="425"/>
-      <c r="L21" s="433"/>
-      <c r="M21" s="248"/>
-      <c r="N21" s="51"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="289"/>
-      <c r="B22" s="307"/>
-      <c r="C22" s="308"/>
-      <c r="D22" s="388">
+      <c r="K21" s="462"/>
+      <c r="L21" s="459"/>
+      <c r="M21" s="447">
+        <v>893484.19</v>
+      </c>
+      <c r="N21" s="517"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="286"/>
+      <c r="B22" s="303"/>
+      <c r="C22" s="304"/>
+      <c r="D22" s="377">
         <v>15000</v>
       </c>
-      <c r="E22" s="283"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="372"/>
-      <c r="H22" s="372">
+      <c r="E22" s="280"/>
+      <c r="F22" s="280"/>
+      <c r="G22" s="364"/>
+      <c r="H22" s="364">
         <v>59159</v>
       </c>
-      <c r="I22" s="283"/>
-      <c r="J22" s="283"/>
-      <c r="K22" s="426"/>
-      <c r="L22" s="433"/>
-      <c r="M22" s="248"/>
-      <c r="N22" s="51"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="302"/>
-      <c r="B23" s="307"/>
-      <c r="C23" s="308"/>
-      <c r="D23" s="383"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="283"/>
-      <c r="G23" s="283"/>
-      <c r="H23" s="283"/>
-      <c r="I23" s="283"/>
-      <c r="J23" s="461"/>
-      <c r="K23" s="423"/>
-      <c r="L23" s="433"/>
-      <c r="M23" s="248"/>
-      <c r="N23" s="51"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="302"/>
-      <c r="B24" s="307"/>
-      <c r="C24" s="308"/>
-      <c r="D24" s="308"/>
-      <c r="E24" s="354"/>
-      <c r="F24" s="271"/>
-      <c r="G24" s="271"/>
-      <c r="H24" s="271"/>
-      <c r="I24" s="271"/>
-      <c r="J24" s="271"/>
-      <c r="K24" s="423"/>
-      <c r="L24" s="433"/>
-      <c r="M24" s="248"/>
-      <c r="N24" s="51"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="302"/>
-      <c r="B25" s="309"/>
-      <c r="C25" s="308"/>
-      <c r="D25" s="308"/>
-      <c r="E25" s="354"/>
-      <c r="F25" s="271"/>
-      <c r="G25" s="271"/>
-      <c r="H25" s="271"/>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="423"/>
-      <c r="L25" s="419"/>
-      <c r="M25" s="248"/>
-      <c r="N25" s="51"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="302"/>
-      <c r="B26" s="309"/>
-      <c r="C26" s="308"/>
-      <c r="D26" s="308"/>
-      <c r="E26" s="354"/>
-      <c r="F26" s="271"/>
-      <c r="G26" s="271"/>
-      <c r="H26" s="271"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
-      <c r="K26" s="423"/>
-      <c r="L26" s="420"/>
-      <c r="M26" s="248"/>
-      <c r="N26" s="51"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="369"/>
-      <c r="B27" s="370"/>
-      <c r="C27" s="308"/>
-      <c r="D27" s="283"/>
-      <c r="E27" s="277"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="271"/>
-      <c r="K27" s="423"/>
-      <c r="L27" s="418"/>
-      <c r="M27" s="248"/>
-      <c r="N27" s="51"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="277"/>
-      <c r="B28" s="273"/>
-      <c r="C28" s="398"/>
-      <c r="D28" s="348"/>
-      <c r="E28" s="480"/>
-      <c r="F28" s="271"/>
-      <c r="G28" s="271"/>
-      <c r="H28" s="271"/>
-      <c r="I28" s="271"/>
-      <c r="J28" s="271"/>
-      <c r="K28" s="427"/>
-      <c r="L28" s="414"/>
-      <c r="M28" s="248"/>
-      <c r="N28" s="51"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="399"/>
-      <c r="B29" s="271"/>
-      <c r="C29" s="400"/>
-      <c r="D29" s="401"/>
-      <c r="E29" s="481"/>
-      <c r="F29" s="271"/>
-      <c r="G29" s="271"/>
-      <c r="H29" s="271"/>
-      <c r="I29" s="271"/>
-      <c r="J29" s="271"/>
-      <c r="K29" s="428"/>
-      <c r="L29" s="421"/>
-      <c r="M29" s="248"/>
-      <c r="N29" s="51"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="271"/>
-      <c r="B30" s="271"/>
-      <c r="C30" s="271"/>
-      <c r="D30" s="271"/>
-      <c r="E30" s="286"/>
-      <c r="F30" s="271"/>
-      <c r="G30" s="271"/>
-      <c r="H30" s="271"/>
-      <c r="I30" s="271"/>
-      <c r="J30" s="271"/>
-      <c r="K30" s="422"/>
-      <c r="L30" s="271"/>
-      <c r="M30" s="248"/>
-      <c r="N30" s="51"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="271"/>
-      <c r="B31" s="271"/>
-      <c r="C31" s="271"/>
-      <c r="D31" s="283"/>
-      <c r="E31" s="354" t="s">
-        <v>200</v>
-      </c>
-      <c r="F31" s="401"/>
-      <c r="G31" s="401"/>
-      <c r="H31" s="459"/>
-      <c r="I31" s="271"/>
-      <c r="J31" s="271"/>
-      <c r="K31" s="422"/>
-      <c r="L31" s="271"/>
+      <c r="I22" s="280"/>
+      <c r="J22" s="280"/>
+      <c r="K22" s="463"/>
+      <c r="L22" s="459"/>
+      <c r="M22" s="464">
+        <f>SUM(M17:M21)</f>
+        <v>893484.19</v>
+      </c>
+      <c r="N22" s="444"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="298"/>
+      <c r="B23" s="303"/>
+      <c r="C23" s="304"/>
+      <c r="D23" s="372"/>
+      <c r="E23" s="282"/>
+      <c r="F23" s="280"/>
+      <c r="G23" s="280"/>
+      <c r="H23" s="280"/>
+      <c r="I23" s="280"/>
+      <c r="J23" s="420"/>
+      <c r="K23" s="371"/>
+      <c r="L23" s="459"/>
+      <c r="M23" s="445"/>
+      <c r="N23" s="444"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="298"/>
+      <c r="B24" s="303"/>
+      <c r="C24" s="304"/>
+      <c r="D24" s="304"/>
+      <c r="E24" s="349"/>
+      <c r="F24" s="269"/>
+      <c r="G24" s="269"/>
+      <c r="H24" s="269"/>
+      <c r="I24" s="269"/>
+      <c r="J24" s="269"/>
+      <c r="K24" s="285"/>
+      <c r="L24" s="403"/>
+      <c r="M24" s="444"/>
+      <c r="N24" s="444"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="298"/>
+      <c r="B25" s="305"/>
+      <c r="C25" s="304"/>
+      <c r="D25" s="304"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="269"/>
+      <c r="G25" s="269"/>
+      <c r="H25" s="269"/>
+      <c r="I25" s="269"/>
+      <c r="J25" s="269"/>
+      <c r="K25" s="400"/>
+      <c r="L25" s="367"/>
+      <c r="M25" s="444"/>
+      <c r="N25" s="269"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="298"/>
+      <c r="B26" s="305"/>
+      <c r="C26" s="304"/>
+      <c r="D26" s="304"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="269"/>
+      <c r="G26" s="269"/>
+      <c r="H26" s="269"/>
+      <c r="I26" s="269"/>
+      <c r="J26" s="269"/>
+      <c r="K26" s="400"/>
+      <c r="L26" s="475"/>
+      <c r="M26" s="444"/>
+      <c r="N26" s="269"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="362"/>
+      <c r="B27" s="363"/>
+      <c r="C27" s="304"/>
+      <c r="D27" s="280"/>
+      <c r="E27" s="275"/>
+      <c r="F27" s="269"/>
+      <c r="G27" s="269"/>
+      <c r="H27" s="269"/>
+      <c r="I27" s="269"/>
+      <c r="J27" s="269"/>
+      <c r="K27" s="474"/>
+      <c r="L27" s="367"/>
+      <c r="M27" s="444"/>
+      <c r="N27" s="269"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="275"/>
+      <c r="B28" s="271"/>
+      <c r="C28" s="383"/>
+      <c r="D28" s="344"/>
+      <c r="E28" s="439"/>
+      <c r="F28" s="269"/>
+      <c r="G28" s="269"/>
+      <c r="H28" s="269"/>
+      <c r="I28" s="269"/>
+      <c r="J28" s="269"/>
+      <c r="K28" s="399"/>
+      <c r="L28" s="476"/>
+      <c r="N28" s="269"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="384"/>
+      <c r="B29" s="269"/>
+      <c r="C29" s="385"/>
+      <c r="D29" s="386"/>
+      <c r="E29" s="440"/>
+      <c r="F29" s="269"/>
+      <c r="G29" s="269"/>
+      <c r="H29" s="269"/>
+      <c r="I29" s="269"/>
+      <c r="J29" s="269"/>
+      <c r="K29" s="472"/>
+      <c r="L29" s="473"/>
+      <c r="M29" s="444"/>
+      <c r="N29" s="269"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="269"/>
+      <c r="B30" s="269"/>
+      <c r="C30" s="269"/>
+      <c r="D30" s="269"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="269"/>
+      <c r="G30" s="269"/>
+      <c r="H30" s="269"/>
+      <c r="I30" s="269"/>
+      <c r="J30" s="269"/>
+      <c r="K30" s="398"/>
+      <c r="L30" s="269"/>
+      <c r="M30" s="444"/>
+      <c r="N30" s="269"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="269"/>
+      <c r="B31" s="269"/>
+      <c r="C31" s="269"/>
+      <c r="D31" s="280"/>
+      <c r="E31" s="349" t="s">
+        <v>196</v>
+      </c>
+      <c r="F31" s="386"/>
+      <c r="G31" s="386"/>
+      <c r="H31" s="419"/>
+      <c r="I31" s="269"/>
+      <c r="J31" s="269"/>
+      <c r="K31" s="398"/>
+      <c r="L31" s="269"/>
       <c r="M31" s="248"/>
       <c r="N31" s="51"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="271"/>
-      <c r="B32" s="271"/>
-      <c r="C32" s="271"/>
-      <c r="D32" s="283"/>
-      <c r="E32" s="354"/>
-      <c r="F32" s="401"/>
-      <c r="G32" s="459"/>
-      <c r="H32" s="459"/>
-      <c r="I32" s="271"/>
-      <c r="J32" s="271"/>
-      <c r="K32" s="271"/>
-      <c r="L32" s="271"/>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="269"/>
+      <c r="B32" s="269"/>
+      <c r="C32" s="269"/>
+      <c r="D32" s="280"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="386"/>
+      <c r="G32" s="419"/>
+      <c r="H32" s="419"/>
+      <c r="I32" s="269"/>
+      <c r="J32" s="269"/>
+      <c r="K32" s="269"/>
+      <c r="L32" s="269"/>
       <c r="M32" s="248"/>
       <c r="N32" s="51"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="271"/>
-      <c r="B33" s="271"/>
-      <c r="C33" s="271"/>
-      <c r="D33" s="470"/>
-      <c r="E33" s="471" t="s">
-        <v>201</v>
-      </c>
-      <c r="F33" s="459" t="s">
-        <v>202</v>
-      </c>
-      <c r="G33" s="459" t="s">
-        <v>203</v>
-      </c>
-      <c r="H33" s="459" t="s">
-        <v>204</v>
-      </c>
-      <c r="I33" s="271"/>
-      <c r="J33" s="271"/>
-      <c r="K33" s="271"/>
-      <c r="L33" s="271"/>
+      <c r="A33" s="269"/>
+      <c r="B33" s="269"/>
+      <c r="C33" s="269"/>
+      <c r="D33" s="429"/>
+      <c r="E33" s="430" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" s="419" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" s="419" t="s">
+        <v>199</v>
+      </c>
+      <c r="H33" s="419" t="s">
+        <v>200</v>
+      </c>
+      <c r="I33" s="269"/>
+      <c r="J33" s="269"/>
+      <c r="K33" s="269"/>
+      <c r="L33" s="269"/>
       <c r="M33" s="248"/>
       <c r="N33" s="51"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="271"/>
-      <c r="B34" s="271"/>
-      <c r="C34" s="271"/>
-      <c r="D34" s="461" t="s">
-        <v>205</v>
-      </c>
-      <c r="E34" s="464">
+      <c r="A34" s="269"/>
+      <c r="B34" s="269"/>
+      <c r="C34" s="269"/>
+      <c r="D34" s="420" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="423">
         <v>466976.92</v>
       </c>
-      <c r="F34" s="482">
-        <v>100649</v>
-      </c>
-      <c r="G34" s="459">
+      <c r="F34" s="441">
+        <v>99774</v>
+      </c>
+      <c r="G34" s="419">
         <v>5</v>
       </c>
-      <c r="H34" s="483">
+      <c r="H34" s="442">
         <v>20</v>
       </c>
-      <c r="I34" s="279"/>
-      <c r="J34" s="279"/>
-      <c r="K34" s="271"/>
-      <c r="L34" s="271"/>
+      <c r="I34" s="277"/>
+      <c r="J34" s="277"/>
+      <c r="K34" s="269"/>
+      <c r="L34" s="269"/>
       <c r="M34" s="248"/>
       <c r="N34" s="51"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="271"/>
-      <c r="B35" s="271"/>
-      <c r="C35" s="271"/>
-      <c r="D35" s="461" t="s">
-        <v>205</v>
-      </c>
-      <c r="E35" s="468">
+      <c r="A35" s="269"/>
+      <c r="B35" s="269"/>
+      <c r="C35" s="269"/>
+      <c r="D35" s="420" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="427">
         <v>815680.37</v>
       </c>
-      <c r="F35" s="465">
-        <v>67064.67</v>
-      </c>
-      <c r="G35" s="462">
+      <c r="F35" s="424">
+        <v>66925</v>
+      </c>
+      <c r="G35" s="421">
         <v>31</v>
       </c>
-      <c r="H35" s="462">
+      <c r="H35" s="421">
         <v>7</v>
       </c>
-      <c r="I35" s="279"/>
-      <c r="J35" s="271"/>
-      <c r="K35" s="271"/>
-      <c r="L35" s="271"/>
+      <c r="I35" s="277"/>
+      <c r="J35" s="269"/>
+      <c r="K35" s="269"/>
+      <c r="L35" s="269"/>
       <c r="M35" s="248"/>
       <c r="N35" s="51"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="271"/>
-      <c r="B36" s="271"/>
-      <c r="C36" s="271"/>
-      <c r="D36" s="461" t="s">
-        <v>205</v>
-      </c>
-      <c r="E36" s="469">
+      <c r="A36" s="269"/>
+      <c r="B36" s="269"/>
+      <c r="C36" s="269"/>
+      <c r="D36" s="420" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="428">
         <v>3073505.09</v>
       </c>
-      <c r="F36" s="469">
-        <v>235697.3</v>
-      </c>
-      <c r="G36" s="459">
+      <c r="F36" s="428">
+        <v>235159</v>
+      </c>
+      <c r="G36" s="419">
         <v>25</v>
       </c>
-      <c r="H36" s="459">
+      <c r="H36" s="419">
         <v>20</v>
       </c>
-      <c r="I36" s="279"/>
-      <c r="J36" s="271"/>
-      <c r="K36" s="271"/>
-      <c r="L36" s="271"/>
+      <c r="I36" s="277"/>
+      <c r="J36" s="269"/>
+      <c r="K36" s="269"/>
+      <c r="L36" s="269"/>
       <c r="M36" s="248"/>
       <c r="N36" s="51"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="271"/>
-      <c r="B37" s="271"/>
-      <c r="C37" s="271"/>
-      <c r="D37" s="289" t="s">
-        <v>206</v>
-      </c>
-      <c r="E37" s="466">
+      <c r="A37" s="269"/>
+      <c r="B37" s="269"/>
+      <c r="C37" s="269"/>
+      <c r="D37" s="286" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="425">
         <v>698529.91</v>
       </c>
-      <c r="F37" s="466">
+      <c r="F37" s="425">
         <v>69852.990000000005</v>
       </c>
-      <c r="G37" s="279">
+      <c r="G37" s="277">
         <v>9</v>
       </c>
-      <c r="H37" s="279">
+      <c r="H37" s="277">
         <v>15</v>
       </c>
-      <c r="I37" s="279"/>
-      <c r="J37" s="279"/>
-      <c r="K37" s="271"/>
-      <c r="L37" s="271"/>
+      <c r="I37" s="277"/>
+      <c r="J37" s="277"/>
+      <c r="K37" s="269"/>
+      <c r="L37" s="269"/>
       <c r="M37" s="248"/>
       <c r="N37" s="51"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="270"/>
-      <c r="B38" s="302"/>
-      <c r="C38" s="308"/>
-      <c r="D38" s="289" t="s">
-        <v>206</v>
-      </c>
-      <c r="E38" s="466">
+      <c r="A38" s="268"/>
+      <c r="B38" s="298"/>
+      <c r="C38" s="304"/>
+      <c r="D38" s="286" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" s="425">
         <v>98848.21</v>
       </c>
-      <c r="F38" s="277">
-        <v>13835</v>
-      </c>
-      <c r="G38" s="279">
+      <c r="F38" s="275">
+        <v>13840</v>
+      </c>
+      <c r="G38" s="277">
         <v>7</v>
       </c>
-      <c r="H38" s="279">
+      <c r="H38" s="277">
         <v>15</v>
       </c>
-      <c r="I38" s="463"/>
-      <c r="J38" s="461"/>
-      <c r="K38" s="354"/>
-      <c r="L38" s="496"/>
+      <c r="I38" s="422"/>
+      <c r="J38" s="420"/>
+      <c r="K38" s="349"/>
+      <c r="L38" s="455"/>
       <c r="M38" s="248"/>
       <c r="N38" s="51"/>
     </row>
     <row r="39" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="304"/>
-      <c r="B39" s="302"/>
-      <c r="C39" s="311"/>
-      <c r="D39" s="472" t="s">
-        <v>207</v>
-      </c>
-      <c r="E39" s="478">
+      <c r="A39" s="300"/>
+      <c r="B39" s="298"/>
+      <c r="C39" s="307"/>
+      <c r="D39" s="431" t="s">
+        <v>203</v>
+      </c>
+      <c r="E39" s="437">
         <v>746515</v>
       </c>
-      <c r="F39" s="475">
-        <v>131515</v>
-      </c>
-      <c r="G39" s="279">
+      <c r="F39" s="434">
+        <v>122867</v>
+      </c>
+      <c r="G39" s="277">
         <v>11</v>
       </c>
-      <c r="H39" s="473">
+      <c r="H39" s="432">
         <v>5</v>
       </c>
-      <c r="I39" s="310"/>
-      <c r="J39" s="283"/>
-      <c r="K39" s="354"/>
-      <c r="L39" s="496"/>
+      <c r="I39" s="306"/>
+      <c r="J39" s="280"/>
+      <c r="K39" s="349"/>
+      <c r="L39" s="455"/>
       <c r="M39" s="248"/>
       <c r="N39" s="51"/>
     </row>
     <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="304"/>
-      <c r="B40" s="302"/>
-      <c r="C40" s="308"/>
-      <c r="D40" s="477"/>
-      <c r="E40" s="476">
+      <c r="A40" s="300"/>
+      <c r="B40" s="298"/>
+      <c r="C40" s="304"/>
+      <c r="D40" s="436"/>
+      <c r="E40" s="435">
         <f>SUM(E34:E39)</f>
         <v>5900055.5</v>
       </c>
-      <c r="F40" s="476">
+      <c r="F40" s="435">
         <f>SUM(F34:F39)</f>
-        <v>618613.96</v>
-      </c>
-      <c r="G40" s="474"/>
-      <c r="H40" s="279"/>
-      <c r="I40" s="310"/>
-      <c r="J40" s="283"/>
-      <c r="K40" s="354"/>
-      <c r="L40" s="496"/>
+        <v>608417.99</v>
+      </c>
+      <c r="G40" s="433"/>
+      <c r="H40" s="277"/>
+      <c r="I40" s="306"/>
+      <c r="J40" s="280"/>
+      <c r="K40" s="349"/>
+      <c r="L40" s="455"/>
       <c r="M40" s="248"/>
       <c r="N40" s="51"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="312"/>
-      <c r="B41" s="302"/>
-      <c r="C41" s="308"/>
-      <c r="D41" s="310"/>
-      <c r="E41" s="283"/>
-      <c r="F41" s="471"/>
-      <c r="G41" s="464"/>
-      <c r="H41" s="283"/>
-      <c r="I41" s="310"/>
-      <c r="J41" s="283"/>
-      <c r="K41" s="354"/>
-      <c r="L41" s="496"/>
+      <c r="A41" s="308"/>
+      <c r="B41" s="298"/>
+      <c r="C41" s="304"/>
+      <c r="D41" s="306"/>
+      <c r="E41" s="280"/>
+      <c r="F41" s="430"/>
+      <c r="G41" s="423"/>
+      <c r="H41" s="280"/>
+      <c r="I41" s="306"/>
+      <c r="J41" s="280"/>
+      <c r="K41" s="349"/>
+      <c r="L41" s="455"/>
       <c r="M41" s="248"/>
       <c r="N41" s="51"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="304"/>
-      <c r="B42" s="302"/>
-      <c r="C42" s="308"/>
-      <c r="D42" s="310"/>
-      <c r="E42" s="283"/>
-      <c r="F42" s="461"/>
-      <c r="G42" s="464"/>
-      <c r="H42" s="283"/>
-      <c r="I42" s="283"/>
-      <c r="J42" s="283"/>
-      <c r="K42" s="354"/>
-      <c r="L42" s="496"/>
+      <c r="A42" s="300">
+        <v>387</v>
+      </c>
+      <c r="B42" s="298"/>
+      <c r="C42" s="304"/>
+      <c r="D42" s="306"/>
+      <c r="E42" s="280"/>
+      <c r="F42" s="420"/>
+      <c r="G42" s="423"/>
+      <c r="H42" s="280"/>
+      <c r="I42" s="280"/>
+      <c r="J42" s="280"/>
+      <c r="K42" s="349"/>
+      <c r="L42" s="455"/>
       <c r="M42" s="248"/>
       <c r="N42" s="51"/>
     </row>
     <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="304"/>
-      <c r="B43" s="302"/>
-      <c r="C43" s="308"/>
-      <c r="D43" s="310"/>
-      <c r="E43" s="283"/>
-      <c r="F43" s="461"/>
-      <c r="G43" s="465"/>
-      <c r="H43" s="283"/>
-      <c r="I43" s="283"/>
-      <c r="J43" s="270"/>
-      <c r="K43" s="354"/>
-      <c r="L43" s="496"/>
+      <c r="A43" s="300"/>
+      <c r="B43" s="298"/>
+      <c r="C43" s="304"/>
+      <c r="D43" s="306"/>
+      <c r="E43" s="280"/>
+      <c r="F43" s="420"/>
+      <c r="G43" s="424"/>
+      <c r="H43" s="280"/>
+      <c r="I43" s="280"/>
+      <c r="J43" s="268"/>
+      <c r="K43" s="349"/>
+      <c r="L43" s="455"/>
       <c r="M43" s="248"/>
       <c r="N43" s="51"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="304"/>
-      <c r="B44" s="302"/>
-      <c r="C44" s="308"/>
-      <c r="D44" s="313"/>
-      <c r="E44" s="348"/>
-      <c r="F44" s="462"/>
-      <c r="G44" s="467" t="s">
+      <c r="A44" s="300"/>
+      <c r="B44" s="298"/>
+      <c r="C44" s="304"/>
+      <c r="D44" s="309"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="421"/>
+      <c r="G44" s="426" t="s">
         <v>24</v>
       </c>
-      <c r="H44" s="313"/>
-      <c r="I44" s="313"/>
-      <c r="J44" s="283"/>
-      <c r="K44" s="354"/>
-      <c r="L44" s="496"/>
+      <c r="H44" s="309"/>
+      <c r="I44" s="309"/>
+      <c r="J44" s="280"/>
+      <c r="K44" s="349"/>
+      <c r="L44" s="455"/>
       <c r="M44" s="248"/>
       <c r="N44" s="51"/>
     </row>
     <row r="45" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="304"/>
-      <c r="B45" s="314" t="s">
-        <v>190</v>
-      </c>
-      <c r="C45" s="315"/>
-      <c r="D45" s="337"/>
-      <c r="E45" s="283"/>
-      <c r="F45" s="345" t="s">
-        <v>185</v>
-      </c>
-      <c r="G45" s="320" t="s">
-        <v>178</v>
-      </c>
-      <c r="H45" s="316" t="s">
+      <c r="A45" s="300"/>
+      <c r="B45" s="310" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="311"/>
+      <c r="D45" s="333"/>
+      <c r="E45" s="280"/>
+      <c r="F45" s="341" t="s">
+        <v>183</v>
+      </c>
+      <c r="G45" s="316" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="312" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="317" t="s">
+      <c r="I45" s="313" t="s">
         <v>21</v>
       </c>
-      <c r="J45" s="310"/>
-      <c r="K45" s="354"/>
-      <c r="L45" s="496"/>
+      <c r="J45" s="306"/>
+      <c r="K45" s="349"/>
+      <c r="L45" s="455"/>
       <c r="M45" s="248"/>
       <c r="N45" s="51"/>
     </row>
     <row r="46" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="308"/>
-      <c r="B46" s="318"/>
-      <c r="C46" s="319"/>
-      <c r="D46" s="273"/>
-      <c r="E46" s="283"/>
-      <c r="F46" s="346"/>
-      <c r="G46" s="324"/>
-      <c r="H46" s="321" t="s">
-        <v>178</v>
-      </c>
-      <c r="I46" s="322" t="s">
-        <v>178</v>
-      </c>
-      <c r="J46" s="310"/>
-      <c r="K46" s="354"/>
-      <c r="L46" s="496"/>
+      <c r="A46" s="304"/>
+      <c r="B46" s="314"/>
+      <c r="C46" s="315"/>
+      <c r="D46" s="271"/>
+      <c r="E46" s="280"/>
+      <c r="F46" s="342"/>
+      <c r="G46" s="320"/>
+      <c r="H46" s="317" t="s">
+        <v>176</v>
+      </c>
+      <c r="I46" s="318" t="s">
+        <v>176</v>
+      </c>
+      <c r="J46" s="306"/>
+      <c r="K46" s="349"/>
+      <c r="L46" s="455"/>
       <c r="M46" s="248"/>
       <c r="N46" s="51"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="308"/>
-      <c r="B47" s="323" t="s">
-        <v>174</v>
-      </c>
-      <c r="C47" s="273"/>
-      <c r="D47" s="270"/>
-      <c r="E47" s="283"/>
-      <c r="F47" s="347" t="s">
-        <v>197</v>
-      </c>
-      <c r="G47" s="327"/>
-      <c r="H47" s="325"/>
-      <c r="I47" s="282"/>
-      <c r="J47" s="283"/>
-      <c r="K47" s="354"/>
-      <c r="L47" s="496"/>
+      <c r="A47" s="304"/>
+      <c r="B47" s="319" t="s">
+        <v>172</v>
+      </c>
+      <c r="C47" s="271"/>
+      <c r="D47" s="268"/>
+      <c r="E47" s="280"/>
+      <c r="F47" s="343" t="s">
+        <v>194</v>
+      </c>
+      <c r="G47" s="323"/>
+      <c r="H47" s="321"/>
+      <c r="I47" s="279"/>
+      <c r="J47" s="280"/>
+      <c r="K47" s="349"/>
+      <c r="L47" s="455"/>
       <c r="M47" s="248"/>
       <c r="N47" s="51"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="309"/>
-      <c r="B48" s="323" t="s">
+      <c r="A48" s="305"/>
+      <c r="B48" s="319" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="359"/>
-      <c r="D48" s="270"/>
-      <c r="E48" s="302"/>
-      <c r="F48" s="341" t="s">
-        <v>188</v>
-      </c>
-      <c r="G48" s="327"/>
-      <c r="H48" s="328"/>
-      <c r="I48" s="302"/>
-      <c r="J48" s="302"/>
-      <c r="K48" s="329"/>
-      <c r="L48" s="496"/>
-      <c r="M48" s="284"/>
+      <c r="C48" s="354"/>
+      <c r="D48" s="268"/>
+      <c r="E48" s="298"/>
+      <c r="F48" s="337" t="s">
+        <v>186</v>
+      </c>
+      <c r="G48" s="323"/>
+      <c r="H48" s="324"/>
+      <c r="I48" s="298"/>
+      <c r="J48" s="298"/>
+      <c r="K48" s="325"/>
+      <c r="L48" s="455"/>
+      <c r="M48" s="281"/>
       <c r="N48" s="51"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="309"/>
-      <c r="B49" s="323" t="s">
+      <c r="A49" s="305"/>
+      <c r="B49" s="319" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" s="354"/>
+      <c r="D49" s="268"/>
+      <c r="E49" s="298"/>
+      <c r="F49" s="337" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="323"/>
+      <c r="H49" s="324"/>
+      <c r="I49" s="298"/>
+      <c r="J49" s="298"/>
+      <c r="K49" s="352"/>
+      <c r="L49" s="455"/>
+      <c r="M49" s="281"/>
+      <c r="N49" s="51"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="305"/>
+      <c r="B50" s="319" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="354"/>
+      <c r="D50" s="268"/>
+      <c r="E50" s="298"/>
+      <c r="F50" s="337" t="s">
+        <v>177</v>
+      </c>
+      <c r="G50" s="323"/>
+      <c r="H50" s="324"/>
+      <c r="I50" s="298"/>
+      <c r="J50" s="298"/>
+      <c r="K50" s="352"/>
+      <c r="L50" s="455"/>
+      <c r="M50" s="281"/>
+      <c r="N50" s="51"/>
+    </row>
+    <row r="51" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="305"/>
+      <c r="B51" s="340" t="s">
         <v>175</v>
       </c>
-      <c r="C49" s="359"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="341" t="s">
-        <v>189</v>
-      </c>
-      <c r="G49" s="327"/>
-      <c r="H49" s="328"/>
-      <c r="I49" s="302"/>
-      <c r="J49" s="302"/>
-      <c r="K49" s="357"/>
-      <c r="L49" s="496"/>
-      <c r="M49" s="284"/>
-      <c r="N49" s="51"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="309"/>
-      <c r="B50" s="323" t="s">
+      <c r="C51" s="356"/>
+      <c r="D51" s="300"/>
+      <c r="E51" s="298"/>
+      <c r="F51" s="337" t="s">
+        <v>179</v>
+      </c>
+      <c r="G51" s="327"/>
+      <c r="H51" s="324"/>
+      <c r="I51" s="298"/>
+      <c r="J51" s="298"/>
+      <c r="K51" s="352"/>
+      <c r="L51" s="455"/>
+      <c r="M51" s="281"/>
+      <c r="N51" s="51"/>
+    </row>
+    <row r="52" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="334"/>
+      <c r="B52" s="326" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="360"/>
+      <c r="D52" s="358"/>
+      <c r="E52" s="298"/>
+      <c r="F52" s="337" t="s">
+        <v>180</v>
+      </c>
+      <c r="G52" s="329"/>
+      <c r="H52" s="328"/>
+      <c r="I52" s="298"/>
+      <c r="J52" s="298"/>
+      <c r="K52" s="334"/>
+      <c r="L52" s="455"/>
+      <c r="M52" s="281"/>
+      <c r="N52" s="51"/>
+    </row>
+    <row r="53" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="334"/>
+      <c r="B53" s="315"/>
+      <c r="C53" s="359"/>
+      <c r="D53" s="298"/>
+      <c r="E53" s="298"/>
+      <c r="F53" s="338" t="s">
+        <v>178</v>
+      </c>
+      <c r="G53" s="315"/>
+      <c r="H53" s="330"/>
+      <c r="I53" s="299"/>
+      <c r="J53" s="298"/>
+      <c r="K53" s="352"/>
+      <c r="L53" s="455"/>
+      <c r="M53" s="281"/>
+      <c r="N53" s="51"/>
+    </row>
+    <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="335"/>
+      <c r="B54" s="298"/>
+      <c r="C54" s="298"/>
+      <c r="D54" s="298"/>
+      <c r="E54" s="298"/>
+      <c r="F54" s="299"/>
+      <c r="G54" s="331" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="270"/>
-      <c r="E50" s="302"/>
-      <c r="F50" s="341" t="s">
-        <v>179</v>
-      </c>
-      <c r="G50" s="327"/>
-      <c r="H50" s="328"/>
-      <c r="I50" s="302"/>
-      <c r="J50" s="302"/>
-      <c r="K50" s="357"/>
-      <c r="L50" s="496"/>
-      <c r="M50" s="284"/>
-      <c r="N50" s="51"/>
-    </row>
-    <row r="51" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="309"/>
-      <c r="B51" s="344" t="s">
-        <v>177</v>
-      </c>
-      <c r="C51" s="362"/>
-      <c r="D51" s="304"/>
-      <c r="E51" s="302"/>
-      <c r="F51" s="341" t="s">
-        <v>181</v>
-      </c>
-      <c r="G51" s="331"/>
-      <c r="H51" s="328"/>
-      <c r="I51" s="302"/>
-      <c r="J51" s="302"/>
-      <c r="K51" s="357"/>
-      <c r="L51" s="496"/>
-      <c r="M51" s="284"/>
-      <c r="N51" s="51"/>
-    </row>
-    <row r="52" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="338"/>
-      <c r="B52" s="330" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" s="367"/>
-      <c r="D52" s="365"/>
-      <c r="E52" s="302"/>
-      <c r="F52" s="341" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="333"/>
-      <c r="H52" s="332"/>
-      <c r="I52" s="302"/>
-      <c r="J52" s="302"/>
-      <c r="K52" s="338"/>
-      <c r="L52" s="496"/>
-      <c r="M52" s="284"/>
-      <c r="N52" s="51"/>
-    </row>
-    <row r="53" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="338"/>
-      <c r="B53" s="319"/>
-      <c r="C53" s="366"/>
-      <c r="D53" s="302"/>
-      <c r="E53" s="302"/>
-      <c r="F53" s="342" t="s">
-        <v>180</v>
-      </c>
-      <c r="G53" s="319"/>
-      <c r="H53" s="334"/>
-      <c r="I53" s="303"/>
-      <c r="J53" s="302"/>
-      <c r="K53" s="357"/>
-      <c r="L53" s="496"/>
-      <c r="M53" s="284"/>
-      <c r="N53" s="51"/>
-    </row>
-    <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="339"/>
-      <c r="B54" s="302"/>
-      <c r="C54" s="302"/>
-      <c r="D54" s="302"/>
-      <c r="E54" s="302"/>
-      <c r="F54" s="303"/>
-      <c r="G54" s="335" t="s">
-        <v>178</v>
-      </c>
-      <c r="H54" s="319"/>
-      <c r="I54" s="302"/>
-      <c r="J54" s="302"/>
-      <c r="K54" s="358"/>
-      <c r="L54" s="496"/>
-      <c r="M54" s="284"/>
+      <c r="H54" s="315"/>
+      <c r="I54" s="298"/>
+      <c r="J54" s="298"/>
+      <c r="K54" s="353"/>
+      <c r="L54" s="455"/>
+      <c r="M54" s="281"/>
       <c r="N54" s="51"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="340"/>
-      <c r="B55" s="302"/>
-      <c r="C55" s="302"/>
-      <c r="D55" s="302"/>
-      <c r="E55" s="302"/>
-      <c r="F55" s="343"/>
-      <c r="G55" s="302"/>
-      <c r="H55" s="335" t="s">
-        <v>178</v>
-      </c>
-      <c r="I55" s="270"/>
-      <c r="J55" s="302"/>
-      <c r="K55" s="356"/>
-      <c r="L55" s="496"/>
-      <c r="M55" s="284"/>
+      <c r="A55" s="336"/>
+      <c r="B55" s="298"/>
+      <c r="C55" s="298"/>
+      <c r="D55" s="298"/>
+      <c r="E55" s="298"/>
+      <c r="F55" s="339"/>
+      <c r="G55" s="298"/>
+      <c r="H55" s="331" t="s">
+        <v>176</v>
+      </c>
+      <c r="I55" s="268"/>
+      <c r="J55" s="298"/>
+      <c r="K55" s="351"/>
+      <c r="L55" s="455"/>
+      <c r="M55" s="281"/>
       <c r="N55" s="51"/>
     </row>
     <row r="56" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="340"/>
-      <c r="B56" s="302"/>
-      <c r="C56" s="302"/>
-      <c r="D56" s="302"/>
-      <c r="E56" s="302"/>
-      <c r="F56" s="303"/>
-      <c r="G56" s="271"/>
-      <c r="H56" s="302"/>
-      <c r="I56" s="270"/>
-      <c r="J56" s="302"/>
-      <c r="K56" s="329"/>
-      <c r="L56" s="497"/>
-      <c r="M56" s="284"/>
+      <c r="A56" s="336"/>
+      <c r="B56" s="298"/>
+      <c r="C56" s="298"/>
+      <c r="D56" s="298"/>
+      <c r="E56" s="298"/>
+      <c r="F56" s="299"/>
+      <c r="G56" s="269"/>
+      <c r="H56" s="298"/>
+      <c r="I56" s="268"/>
+      <c r="J56" s="298"/>
+      <c r="K56" s="325"/>
+      <c r="L56" s="456"/>
+      <c r="M56" s="281"/>
       <c r="N56" s="51"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="484"/>
-      <c r="B57" s="271"/>
-      <c r="C57" s="271"/>
-      <c r="D57" s="271"/>
-      <c r="E57" s="271"/>
-      <c r="F57" s="485"/>
-      <c r="G57" s="279"/>
-      <c r="H57" s="271"/>
+      <c r="A57" s="443"/>
+      <c r="B57" s="269"/>
+      <c r="C57" s="269"/>
+      <c r="D57" s="269"/>
+      <c r="E57" s="269"/>
+      <c r="F57" s="444"/>
+      <c r="G57" s="277"/>
+      <c r="H57" s="269"/>
       <c r="I57" s="198"/>
-      <c r="J57" s="271"/>
-      <c r="K57" s="271"/>
-      <c r="L57" s="486"/>
+      <c r="J57" s="269"/>
+      <c r="K57" s="269"/>
+      <c r="L57" s="445"/>
       <c r="M57" s="87"/>
       <c r="N57" s="51"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="484"/>
-      <c r="B58" s="271"/>
-      <c r="C58" s="271"/>
-      <c r="D58" s="271"/>
-      <c r="E58" s="279"/>
-      <c r="F58" s="487"/>
-      <c r="G58" s="279"/>
-      <c r="H58" s="279"/>
+      <c r="A58" s="443"/>
+      <c r="B58" s="269"/>
+      <c r="C58" s="269"/>
+      <c r="D58" s="269"/>
+      <c r="E58" s="277"/>
+      <c r="F58" s="446"/>
+      <c r="G58" s="277"/>
+      <c r="H58" s="277"/>
       <c r="I58" s="198"/>
-      <c r="J58" s="271"/>
-      <c r="K58" s="271"/>
-      <c r="L58" s="271"/>
+      <c r="J58" s="269"/>
+      <c r="K58" s="269"/>
+      <c r="L58" s="269"/>
       <c r="M58" s="87"/>
       <c r="N58" s="51"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="484"/>
-      <c r="B59" s="271"/>
-      <c r="C59" s="271"/>
-      <c r="D59" s="271"/>
-      <c r="E59" s="279"/>
-      <c r="F59" s="279"/>
-      <c r="G59" s="279"/>
-      <c r="H59" s="279"/>
-      <c r="I59" s="289"/>
-      <c r="J59" s="271"/>
-      <c r="K59" s="271"/>
-      <c r="L59" s="271"/>
+      <c r="A59" s="443"/>
+      <c r="B59" s="269"/>
+      <c r="C59" s="269"/>
+      <c r="D59" s="269"/>
+      <c r="E59" s="277"/>
+      <c r="F59" s="277"/>
+      <c r="G59" s="277"/>
+      <c r="H59" s="277"/>
+      <c r="I59" s="286"/>
+      <c r="J59" s="269"/>
+      <c r="K59" s="269"/>
+      <c r="L59" s="269"/>
       <c r="M59" s="87"/>
       <c r="N59" s="51"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="484"/>
-      <c r="B60" s="271"/>
-      <c r="C60" s="271"/>
-      <c r="D60" s="271"/>
-      <c r="E60" s="279"/>
-      <c r="F60" s="279"/>
-      <c r="G60" s="279"/>
-      <c r="H60" s="279"/>
-      <c r="I60" s="294"/>
-      <c r="J60" s="271"/>
-      <c r="K60" s="271"/>
-      <c r="L60" s="271"/>
+      <c r="A60" s="443"/>
+      <c r="B60" s="269"/>
+      <c r="C60" s="269"/>
+      <c r="D60" s="269"/>
+      <c r="E60" s="277"/>
+      <c r="F60" s="277"/>
+      <c r="G60" s="277"/>
+      <c r="H60" s="277"/>
+      <c r="I60" s="290"/>
+      <c r="J60" s="269"/>
+      <c r="K60" s="269"/>
+      <c r="L60" s="269"/>
       <c r="M60" s="87"/>
       <c r="N60" s="51"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="484"/>
-      <c r="B61" s="271"/>
-      <c r="C61" s="271"/>
-      <c r="D61" s="271"/>
-      <c r="E61" s="279"/>
-      <c r="F61" s="279"/>
-      <c r="G61" s="279"/>
-      <c r="H61" s="279"/>
-      <c r="I61" s="294"/>
-      <c r="J61" s="271"/>
-      <c r="K61" s="271"/>
-      <c r="L61" s="271"/>
+      <c r="A61" s="443"/>
+      <c r="B61" s="269"/>
+      <c r="C61" s="269"/>
+      <c r="D61" s="269"/>
+      <c r="E61" s="277"/>
+      <c r="F61" s="277"/>
+      <c r="G61" s="277"/>
+      <c r="H61" s="277"/>
+      <c r="I61" s="290"/>
+      <c r="J61" s="269"/>
+      <c r="K61" s="269"/>
+      <c r="L61" s="269"/>
       <c r="M61" s="87"/>
       <c r="N61" s="51"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="489"/>
-      <c r="B62" s="490"/>
-      <c r="C62" s="271"/>
-      <c r="D62" s="271"/>
-      <c r="E62" s="279"/>
-      <c r="F62" s="279"/>
-      <c r="G62" s="279"/>
-      <c r="H62" s="279"/>
-      <c r="I62" s="289"/>
-      <c r="J62" s="271"/>
-      <c r="K62" s="271"/>
-      <c r="L62" s="271"/>
+      <c r="A62" s="448"/>
+      <c r="B62" s="449"/>
+      <c r="C62" s="269"/>
+      <c r="D62" s="269"/>
+      <c r="E62" s="277"/>
+      <c r="F62" s="277"/>
+      <c r="G62" s="277"/>
+      <c r="H62" s="277"/>
+      <c r="I62" s="286"/>
+      <c r="J62" s="269"/>
+      <c r="K62" s="269"/>
+      <c r="L62" s="269"/>
       <c r="M62" s="87"/>
       <c r="N62" s="51"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="286"/>
-      <c r="B63" s="490"/>
-      <c r="C63" s="271"/>
-      <c r="D63" s="271"/>
-      <c r="E63" s="279"/>
-      <c r="F63" s="279"/>
-      <c r="G63" s="495"/>
-      <c r="H63" s="289"/>
-      <c r="I63" s="279"/>
-      <c r="J63" s="271"/>
-      <c r="K63" s="271"/>
-      <c r="L63" s="271"/>
+      <c r="A63" s="283"/>
+      <c r="B63" s="449"/>
+      <c r="C63" s="269"/>
+      <c r="D63" s="269"/>
+      <c r="E63" s="277"/>
+      <c r="F63" s="277"/>
+      <c r="G63" s="454"/>
+      <c r="H63" s="286"/>
+      <c r="I63" s="277"/>
+      <c r="J63" s="269"/>
+      <c r="K63" s="269"/>
+      <c r="L63" s="269"/>
       <c r="M63" s="87"/>
       <c r="N63" s="51"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="286"/>
-      <c r="B64" s="490"/>
-      <c r="C64" s="271"/>
-      <c r="D64" s="271"/>
-      <c r="E64" s="271"/>
-      <c r="F64" s="495"/>
-      <c r="G64" s="271"/>
-      <c r="H64" s="495"/>
-      <c r="I64" s="495"/>
-      <c r="J64" s="495"/>
-      <c r="K64" s="271"/>
-      <c r="L64" s="271"/>
+      <c r="A64" s="283"/>
+      <c r="B64" s="449"/>
+      <c r="C64" s="269"/>
+      <c r="D64" s="269"/>
+      <c r="E64" s="269"/>
+      <c r="F64" s="454"/>
+      <c r="G64" s="269"/>
+      <c r="H64" s="454"/>
+      <c r="I64" s="454"/>
+      <c r="J64" s="454"/>
+      <c r="K64" s="269"/>
+      <c r="L64" s="269"/>
       <c r="M64" s="87"/>
       <c r="N64" s="51"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="286"/>
-      <c r="B65" s="271"/>
-      <c r="C65" s="271"/>
-      <c r="D65" s="271"/>
-      <c r="E65" s="271"/>
-      <c r="F65" s="271"/>
-      <c r="G65" s="271"/>
+      <c r="A65" s="283"/>
+      <c r="B65" s="269"/>
+      <c r="C65" s="269"/>
+      <c r="D65" s="269"/>
+      <c r="E65" s="269"/>
+      <c r="F65" s="269"/>
+      <c r="G65" s="269"/>
       <c r="H65" s="198"/>
-      <c r="I65" s="271"/>
-      <c r="J65" s="271"/>
-      <c r="K65" s="271"/>
-      <c r="L65" s="271"/>
+      <c r="I65" s="269"/>
+      <c r="J65" s="269"/>
+      <c r="K65" s="269"/>
+      <c r="L65" s="269"/>
       <c r="M65" s="87"/>
       <c r="N65" s="51"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="286"/>
-      <c r="B66" s="271"/>
-      <c r="C66" s="271"/>
-      <c r="D66" s="271"/>
-      <c r="E66" s="271"/>
-      <c r="F66" s="271"/>
-      <c r="G66" s="271"/>
+      <c r="A66" s="283"/>
+      <c r="B66" s="269"/>
+      <c r="C66" s="269"/>
+      <c r="D66" s="269"/>
+      <c r="E66" s="269"/>
+      <c r="F66" s="269"/>
+      <c r="G66" s="269"/>
       <c r="H66" s="198"/>
-      <c r="I66" s="271"/>
-      <c r="J66" s="271"/>
-      <c r="K66" s="271"/>
-      <c r="L66" s="271"/>
+      <c r="I66" s="269"/>
+      <c r="J66" s="269"/>
+      <c r="K66" s="269"/>
+      <c r="L66" s="269"/>
       <c r="M66" s="87"/>
       <c r="N66" s="51"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="286"/>
-      <c r="B67" s="271"/>
-      <c r="C67" s="271"/>
-      <c r="D67" s="271"/>
-      <c r="E67" s="271"/>
-      <c r="F67" s="271"/>
-      <c r="G67" s="271"/>
-      <c r="H67" s="378"/>
-      <c r="I67" s="271"/>
-      <c r="J67" s="271"/>
-      <c r="K67" s="271"/>
-      <c r="L67" s="271"/>
+      <c r="A67" s="283"/>
+      <c r="B67" s="269"/>
+      <c r="C67" s="269"/>
+      <c r="D67" s="269"/>
+      <c r="E67" s="269"/>
+      <c r="F67" s="269"/>
+      <c r="G67" s="269"/>
+      <c r="H67" s="367"/>
+      <c r="I67" s="269"/>
+      <c r="J67" s="269"/>
+      <c r="K67" s="269"/>
+      <c r="L67" s="269"/>
       <c r="M67" s="87"/>
       <c r="N67" s="51"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="271"/>
-      <c r="B68" s="271"/>
-      <c r="C68" s="271"/>
-      <c r="D68" s="271"/>
-      <c r="E68" s="271"/>
-      <c r="F68" s="271"/>
-      <c r="G68" s="271"/>
-      <c r="H68" s="378"/>
-      <c r="I68" s="271"/>
-      <c r="J68" s="271"/>
-      <c r="K68" s="271"/>
-      <c r="L68" s="271"/>
+      <c r="A68" s="269"/>
+      <c r="B68" s="269"/>
+      <c r="C68" s="269"/>
+      <c r="D68" s="269"/>
+      <c r="E68" s="269"/>
+      <c r="F68" s="269"/>
+      <c r="G68" s="269"/>
+      <c r="H68" s="367"/>
+      <c r="I68" s="269"/>
+      <c r="J68" s="269"/>
+      <c r="K68" s="269"/>
+      <c r="L68" s="269"/>
       <c r="M68" s="87"/>
       <c r="N68" s="51"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="271"/>
-      <c r="B69" s="271"/>
-      <c r="C69" s="271"/>
-      <c r="D69" s="271"/>
-      <c r="E69" s="271"/>
-      <c r="F69" s="271"/>
-      <c r="G69" s="271"/>
-      <c r="H69" s="378"/>
-      <c r="I69" s="271"/>
-      <c r="J69" s="271"/>
-      <c r="K69" s="271"/>
-      <c r="L69" s="271"/>
+      <c r="A69" s="269"/>
+      <c r="B69" s="269"/>
+      <c r="C69" s="269"/>
+      <c r="D69" s="269"/>
+      <c r="E69" s="269"/>
+      <c r="F69" s="269"/>
+      <c r="G69" s="269"/>
+      <c r="H69" s="367"/>
+      <c r="I69" s="269"/>
+      <c r="J69" s="269"/>
+      <c r="K69" s="269"/>
+      <c r="L69" s="269"/>
       <c r="M69" s="87"/>
       <c r="N69" s="51"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="271"/>
-      <c r="B70" s="271"/>
-      <c r="C70" s="271"/>
-      <c r="D70" s="271"/>
-      <c r="E70" s="271"/>
-      <c r="F70" s="271"/>
-      <c r="G70" s="271"/>
-      <c r="H70" s="378"/>
-      <c r="I70" s="271"/>
-      <c r="J70" s="378"/>
-      <c r="K70" s="271"/>
-      <c r="L70" s="271"/>
+      <c r="A70" s="269"/>
+      <c r="B70" s="269"/>
+      <c r="C70" s="269"/>
+      <c r="D70" s="269"/>
+      <c r="E70" s="269"/>
+      <c r="F70" s="269"/>
+      <c r="G70" s="269"/>
+      <c r="H70" s="367"/>
+      <c r="I70" s="269"/>
+      <c r="J70" s="367"/>
+      <c r="K70" s="269"/>
+      <c r="L70" s="269"/>
       <c r="M70" s="87"/>
       <c r="N70" s="51"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="271"/>
-      <c r="B71" s="271"/>
-      <c r="C71" s="271"/>
-      <c r="D71" s="271"/>
-      <c r="E71" s="271"/>
-      <c r="F71" s="271"/>
-      <c r="G71" s="271"/>
-      <c r="H71" s="378"/>
-      <c r="I71" s="271"/>
-      <c r="J71" s="271"/>
-      <c r="K71" s="271"/>
-      <c r="L71" s="271"/>
+      <c r="A71" s="269"/>
+      <c r="B71" s="269"/>
+      <c r="C71" s="269"/>
+      <c r="D71" s="269"/>
+      <c r="E71" s="269"/>
+      <c r="F71" s="269"/>
+      <c r="G71" s="269"/>
+      <c r="H71" s="367"/>
+      <c r="I71" s="269"/>
+      <c r="J71" s="269"/>
+      <c r="K71" s="269"/>
+      <c r="L71" s="269"/>
       <c r="M71" s="87"/>
       <c r="N71" s="51"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="271"/>
-      <c r="B72" s="271"/>
-      <c r="C72" s="271"/>
-      <c r="D72" s="271"/>
-      <c r="E72" s="271"/>
-      <c r="F72" s="271"/>
-      <c r="G72" s="271"/>
-      <c r="H72" s="378"/>
-      <c r="I72" s="491"/>
-      <c r="J72" s="271"/>
-      <c r="K72" s="271"/>
-      <c r="L72" s="271"/>
+      <c r="A72" s="269"/>
+      <c r="B72" s="269"/>
+      <c r="C72" s="269"/>
+      <c r="D72" s="269"/>
+      <c r="E72" s="269"/>
+      <c r="F72" s="269"/>
+      <c r="G72" s="269"/>
+      <c r="H72" s="367"/>
+      <c r="I72" s="450"/>
+      <c r="J72" s="269"/>
+      <c r="K72" s="269"/>
+      <c r="L72" s="269"/>
       <c r="M72" s="87"/>
       <c r="N72" s="51"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="271"/>
-      <c r="B73" s="271"/>
-      <c r="C73" s="271"/>
-      <c r="D73" s="271"/>
-      <c r="E73" s="271"/>
-      <c r="F73" s="271"/>
-      <c r="G73" s="271"/>
+      <c r="A73" s="269"/>
+      <c r="B73" s="269"/>
+      <c r="C73" s="269"/>
+      <c r="D73" s="269"/>
+      <c r="E73" s="269"/>
+      <c r="F73" s="269"/>
+      <c r="G73" s="269"/>
       <c r="H73" s="198"/>
-      <c r="I73" s="491"/>
-      <c r="J73" s="271"/>
-      <c r="K73" s="271"/>
-      <c r="L73" s="271"/>
+      <c r="I73" s="450"/>
+      <c r="J73" s="269"/>
+      <c r="K73" s="269"/>
+      <c r="L73" s="269"/>
       <c r="M73" s="87"/>
       <c r="N73" s="51"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="271"/>
-      <c r="B74" s="271"/>
-      <c r="C74" s="271"/>
-      <c r="D74" s="271"/>
-      <c r="E74" s="271"/>
-      <c r="F74" s="271"/>
-      <c r="G74" s="271"/>
+      <c r="A74" s="269"/>
+      <c r="B74" s="269"/>
+      <c r="C74" s="269"/>
+      <c r="D74" s="269"/>
+      <c r="E74" s="269"/>
+      <c r="F74" s="269"/>
+      <c r="G74" s="269"/>
       <c r="H74" s="198"/>
-      <c r="I74" s="491"/>
-      <c r="J74" s="271"/>
-      <c r="K74" s="271"/>
-      <c r="L74" s="271"/>
+      <c r="I74" s="450"/>
+      <c r="J74" s="269"/>
+      <c r="K74" s="269"/>
+      <c r="L74" s="269"/>
       <c r="M74" s="87"/>
       <c r="N74" s="51"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="271"/>
-      <c r="B75" s="271"/>
-      <c r="C75" s="271"/>
-      <c r="D75" s="271"/>
-      <c r="E75" s="271"/>
-      <c r="F75" s="271"/>
-      <c r="G75" s="271"/>
-      <c r="H75" s="378"/>
-      <c r="I75" s="491"/>
-      <c r="J75" s="271"/>
-      <c r="K75" s="271"/>
-      <c r="L75" s="271"/>
+      <c r="A75" s="269"/>
+      <c r="B75" s="269"/>
+      <c r="C75" s="269"/>
+      <c r="D75" s="269"/>
+      <c r="E75" s="269"/>
+      <c r="F75" s="269"/>
+      <c r="G75" s="269"/>
+      <c r="H75" s="367"/>
+      <c r="I75" s="450"/>
+      <c r="J75" s="269"/>
+      <c r="K75" s="269"/>
+      <c r="L75" s="269"/>
       <c r="M75" s="87"/>
       <c r="N75" s="51"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="271"/>
-      <c r="B76" s="271"/>
-      <c r="C76" s="271"/>
-      <c r="D76" s="271"/>
-      <c r="E76" s="271"/>
-      <c r="F76" s="488"/>
-      <c r="G76" s="492"/>
-      <c r="H76" s="493"/>
-      <c r="I76" s="491"/>
-      <c r="J76" s="271"/>
-      <c r="K76" s="271"/>
-      <c r="L76" s="271"/>
+      <c r="A76" s="269"/>
+      <c r="B76" s="269"/>
+      <c r="C76" s="269"/>
+      <c r="D76" s="269"/>
+      <c r="E76" s="269"/>
+      <c r="F76" s="447"/>
+      <c r="G76" s="451"/>
+      <c r="H76" s="452"/>
+      <c r="I76" s="450"/>
+      <c r="J76" s="269"/>
+      <c r="K76" s="269"/>
+      <c r="L76" s="269"/>
       <c r="M76" s="87"/>
       <c r="N76" s="51"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="271"/>
-      <c r="B77" s="271"/>
-      <c r="C77" s="271"/>
-      <c r="D77" s="271"/>
-      <c r="E77" s="286"/>
-      <c r="F77" s="271"/>
-      <c r="G77" s="491"/>
-      <c r="H77" s="378"/>
-      <c r="I77" s="485"/>
-      <c r="J77" s="271"/>
-      <c r="K77" s="271"/>
-      <c r="L77" s="271"/>
+      <c r="A77" s="269"/>
+      <c r="B77" s="269"/>
+      <c r="C77" s="269"/>
+      <c r="D77" s="269"/>
+      <c r="E77" s="283"/>
+      <c r="F77" s="269"/>
+      <c r="G77" s="450"/>
+      <c r="H77" s="367"/>
+      <c r="I77" s="444"/>
+      <c r="J77" s="269"/>
+      <c r="K77" s="269"/>
+      <c r="L77" s="269"/>
       <c r="M77" s="87"/>
       <c r="N77" s="51"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="271"/>
-      <c r="B78" s="271"/>
-      <c r="C78" s="271"/>
+      <c r="A78" s="269"/>
+      <c r="B78" s="269"/>
+      <c r="C78" s="269"/>
       <c r="D78" s="198"/>
-      <c r="E78" s="271"/>
-      <c r="F78" s="486"/>
-      <c r="G78" s="271"/>
-      <c r="H78" s="494"/>
-      <c r="I78" s="495"/>
-      <c r="J78" s="271"/>
-      <c r="K78" s="271"/>
-      <c r="L78" s="271"/>
+      <c r="E78" s="269"/>
+      <c r="F78" s="445"/>
+      <c r="G78" s="269"/>
+      <c r="H78" s="453"/>
+      <c r="I78" s="454"/>
+      <c r="J78" s="269"/>
+      <c r="K78" s="269"/>
+      <c r="L78" s="269"/>
       <c r="M78" s="87"/>
       <c r="N78" s="51"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="271"/>
-      <c r="B79" s="271"/>
-      <c r="C79" s="271"/>
+      <c r="A79" s="269"/>
+      <c r="B79" s="269"/>
+      <c r="C79" s="269"/>
       <c r="D79" s="198"/>
-      <c r="E79" s="271"/>
-      <c r="F79" s="271"/>
-      <c r="G79" s="271"/>
-      <c r="H79" s="495"/>
-      <c r="I79" s="271"/>
-      <c r="J79" s="271"/>
-      <c r="K79" s="271"/>
-      <c r="L79" s="271"/>
+      <c r="E79" s="269"/>
+      <c r="F79" s="269"/>
+      <c r="G79" s="269"/>
+      <c r="H79" s="454"/>
+      <c r="I79" s="269"/>
+      <c r="J79" s="269"/>
+      <c r="K79" s="269"/>
+      <c r="L79" s="269"/>
       <c r="M79" s="87"/>
       <c r="N79" s="51"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="271"/>
-      <c r="B80" s="271"/>
-      <c r="C80" s="271"/>
+      <c r="A80" s="269"/>
+      <c r="B80" s="269"/>
+      <c r="C80" s="269"/>
       <c r="D80" s="198"/>
-      <c r="E80" s="271"/>
-      <c r="F80" s="271"/>
-      <c r="G80" s="271"/>
-      <c r="H80" s="495"/>
-      <c r="I80" s="271"/>
-      <c r="J80" s="271"/>
-      <c r="K80" s="271"/>
-      <c r="L80" s="271"/>
+      <c r="E80" s="269"/>
+      <c r="F80" s="269"/>
+      <c r="G80" s="269"/>
+      <c r="H80" s="454"/>
+      <c r="I80" s="269"/>
+      <c r="J80" s="269"/>
+      <c r="K80" s="269"/>
+      <c r="L80" s="269"/>
       <c r="M80" s="87"/>
       <c r="N80" s="51"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="271"/>
-      <c r="B81" s="271"/>
-      <c r="C81" s="271"/>
+      <c r="A81" s="269"/>
+      <c r="B81" s="269"/>
+      <c r="C81" s="269"/>
       <c r="D81" s="198"/>
-      <c r="E81" s="271"/>
-      <c r="F81" s="271"/>
-      <c r="G81" s="271"/>
-      <c r="H81" s="495"/>
-      <c r="I81" s="271"/>
-      <c r="J81" s="271"/>
-      <c r="K81" s="271"/>
-      <c r="L81" s="271"/>
+      <c r="E81" s="269"/>
+      <c r="F81" s="269"/>
+      <c r="G81" s="269"/>
+      <c r="H81" s="454"/>
+      <c r="I81" s="269"/>
+      <c r="J81" s="269"/>
+      <c r="K81" s="269"/>
+      <c r="L81" s="269"/>
       <c r="M81" s="87"/>
       <c r="N81" s="51"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="271"/>
-      <c r="B82" s="271"/>
-      <c r="C82" s="271"/>
-      <c r="D82" s="271"/>
-      <c r="E82" s="271"/>
-      <c r="F82" s="271"/>
-      <c r="G82" s="271"/>
-      <c r="H82" s="495"/>
-      <c r="I82" s="271"/>
-      <c r="J82" s="271"/>
-      <c r="K82" s="271"/>
-      <c r="L82" s="271"/>
+      <c r="A82" s="269"/>
+      <c r="B82" s="269"/>
+      <c r="C82" s="269"/>
+      <c r="D82" s="269"/>
+      <c r="E82" s="269"/>
+      <c r="F82" s="269"/>
+      <c r="G82" s="269"/>
+      <c r="H82" s="454"/>
+      <c r="I82" s="269"/>
+      <c r="J82" s="269"/>
+      <c r="K82" s="269"/>
+      <c r="L82" s="269"/>
       <c r="M82" s="87"/>
       <c r="N82" s="51"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="271"/>
-      <c r="B83" s="271"/>
-      <c r="C83" s="271"/>
-      <c r="D83" s="271"/>
-      <c r="E83" s="271"/>
-      <c r="F83" s="271"/>
-      <c r="G83" s="271"/>
-      <c r="H83" s="495"/>
-      <c r="I83" s="271"/>
-      <c r="J83" s="271"/>
-      <c r="K83" s="271"/>
-      <c r="L83" s="271"/>
+      <c r="A83" s="269"/>
+      <c r="B83" s="269"/>
+      <c r="C83" s="269"/>
+      <c r="D83" s="269"/>
+      <c r="E83" s="269"/>
+      <c r="F83" s="269"/>
+      <c r="G83" s="269"/>
+      <c r="H83" s="454"/>
+      <c r="I83" s="269"/>
+      <c r="J83" s="269"/>
+      <c r="K83" s="269"/>
+      <c r="L83" s="269"/>
       <c r="M83" s="87"/>
       <c r="N83" s="51"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="271"/>
-      <c r="B84" s="271"/>
-      <c r="C84" s="271"/>
-      <c r="D84" s="271"/>
-      <c r="E84" s="271"/>
-      <c r="F84" s="271"/>
-      <c r="G84" s="271"/>
-      <c r="H84" s="495"/>
-      <c r="I84" s="271"/>
-      <c r="J84" s="271"/>
-      <c r="K84" s="271"/>
-      <c r="L84" s="271"/>
+      <c r="A84" s="269"/>
+      <c r="B84" s="269"/>
+      <c r="C84" s="269"/>
+      <c r="D84" s="269"/>
+      <c r="E84" s="269"/>
+      <c r="F84" s="269"/>
+      <c r="G84" s="269"/>
+      <c r="H84" s="454"/>
+      <c r="I84" s="269"/>
+      <c r="J84" s="269"/>
+      <c r="K84" s="269"/>
+      <c r="L84" s="269"/>
       <c r="M84" s="87"/>
       <c r="N84" s="51"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="271"/>
-      <c r="B85" s="271"/>
-      <c r="C85" s="271"/>
-      <c r="D85" s="271"/>
-      <c r="E85" s="271"/>
-      <c r="F85" s="271"/>
-      <c r="G85" s="271"/>
-      <c r="H85" s="495"/>
-      <c r="I85" s="271"/>
-      <c r="J85" s="271"/>
-      <c r="K85" s="271"/>
-      <c r="L85" s="271"/>
+      <c r="A85" s="269"/>
+      <c r="B85" s="269"/>
+      <c r="C85" s="269"/>
+      <c r="D85" s="269"/>
+      <c r="E85" s="269"/>
+      <c r="F85" s="269"/>
+      <c r="G85" s="269"/>
+      <c r="H85" s="454"/>
+      <c r="I85" s="269"/>
+      <c r="J85" s="269"/>
+      <c r="K85" s="269"/>
+      <c r="L85" s="269"/>
       <c r="M85" s="87"/>
       <c r="N85" s="51"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="271"/>
-      <c r="B86" s="271"/>
-      <c r="C86" s="271"/>
-      <c r="D86" s="271"/>
-      <c r="E86" s="271"/>
-      <c r="F86" s="271"/>
-      <c r="G86" s="271"/>
-      <c r="H86" s="495"/>
-      <c r="I86" s="271"/>
-      <c r="J86" s="271"/>
-      <c r="K86" s="271"/>
-      <c r="L86" s="271"/>
+      <c r="A86" s="269"/>
+      <c r="B86" s="269"/>
+      <c r="C86" s="269"/>
+      <c r="D86" s="269"/>
+      <c r="E86" s="269"/>
+      <c r="F86" s="269"/>
+      <c r="G86" s="269"/>
+      <c r="H86" s="454"/>
+      <c r="I86" s="269"/>
+      <c r="J86" s="269"/>
+      <c r="K86" s="269"/>
+      <c r="L86" s="269"/>
       <c r="M86" s="87"/>
       <c r="N86" s="51"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="271"/>
-      <c r="B87" s="271"/>
-      <c r="C87" s="271"/>
-      <c r="D87" s="271"/>
-      <c r="E87" s="271"/>
-      <c r="F87" s="271"/>
-      <c r="G87" s="271"/>
-      <c r="H87" s="495"/>
-      <c r="I87" s="271"/>
-      <c r="J87" s="271"/>
-      <c r="K87" s="271"/>
-      <c r="L87" s="271"/>
+      <c r="A87" s="269"/>
+      <c r="B87" s="269"/>
+      <c r="C87" s="269"/>
+      <c r="D87" s="269"/>
+      <c r="E87" s="269"/>
+      <c r="F87" s="269"/>
+      <c r="G87" s="269"/>
+      <c r="H87" s="454"/>
+      <c r="I87" s="269"/>
+      <c r="J87" s="269"/>
+      <c r="K87" s="269"/>
+      <c r="L87" s="269"/>
       <c r="M87" s="87"/>
       <c r="N87" s="51"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="271"/>
-      <c r="B88" s="271"/>
-      <c r="C88" s="271"/>
-      <c r="D88" s="271"/>
-      <c r="E88" s="271"/>
-      <c r="F88" s="271"/>
-      <c r="G88" s="271"/>
-      <c r="H88" s="271"/>
-      <c r="I88" s="271"/>
-      <c r="J88" s="271"/>
-      <c r="K88" s="271"/>
-      <c r="L88" s="271"/>
+      <c r="A88" s="269"/>
+      <c r="B88" s="269"/>
+      <c r="C88" s="269"/>
+      <c r="D88" s="269"/>
+      <c r="E88" s="269"/>
+      <c r="F88" s="269"/>
+      <c r="G88" s="269"/>
+      <c r="H88" s="269"/>
+      <c r="I88" s="269"/>
+      <c r="J88" s="269"/>
+      <c r="K88" s="269"/>
+      <c r="L88" s="269"/>
       <c r="M88" s="51"/>
       <c r="N88" s="51"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="271"/>
-      <c r="B89" s="271"/>
-      <c r="C89" s="271"/>
-      <c r="D89" s="271"/>
-      <c r="E89" s="271"/>
-      <c r="F89" s="271"/>
-      <c r="G89" s="271"/>
-      <c r="H89" s="271"/>
-      <c r="I89" s="271"/>
-      <c r="J89" s="271"/>
-      <c r="K89" s="271"/>
-      <c r="L89" s="271"/>
+      <c r="A89" s="269"/>
+      <c r="B89" s="269"/>
+      <c r="C89" s="269"/>
+      <c r="D89" s="269"/>
+      <c r="E89" s="269"/>
+      <c r="F89" s="269"/>
+      <c r="G89" s="269"/>
+      <c r="H89" s="269"/>
+      <c r="I89" s="269"/>
+      <c r="J89" s="269"/>
+      <c r="K89" s="269"/>
+      <c r="L89" s="269"/>
       <c r="M89" s="51"/>
       <c r="N89" s="51"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="271"/>
-      <c r="B90" s="271"/>
-      <c r="C90" s="271"/>
-      <c r="D90" s="271"/>
-      <c r="E90" s="271"/>
-      <c r="F90" s="271"/>
-      <c r="G90" s="271"/>
-      <c r="H90" s="271"/>
-      <c r="I90" s="271"/>
-      <c r="J90" s="271"/>
-      <c r="K90" s="271"/>
-      <c r="L90" s="271"/>
+      <c r="A90" s="269"/>
+      <c r="B90" s="269"/>
+      <c r="C90" s="269"/>
+      <c r="D90" s="269"/>
+      <c r="E90" s="269"/>
+      <c r="F90" s="269"/>
+      <c r="G90" s="269"/>
+      <c r="H90" s="269"/>
+      <c r="I90" s="269"/>
+      <c r="J90" s="269"/>
+      <c r="K90" s="269"/>
+      <c r="L90" s="269"/>
       <c r="M90" s="51"/>
       <c r="N90" s="51"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="271"/>
-      <c r="B91" s="271"/>
-      <c r="C91" s="271"/>
-      <c r="D91" s="271"/>
-      <c r="E91" s="271"/>
-      <c r="F91" s="271"/>
-      <c r="G91" s="271"/>
-      <c r="H91" s="271"/>
-      <c r="I91" s="271"/>
-      <c r="J91" s="271"/>
-      <c r="K91" s="271"/>
-      <c r="L91" s="271"/>
+      <c r="A91" s="269"/>
+      <c r="B91" s="269"/>
+      <c r="C91" s="269"/>
+      <c r="D91" s="269"/>
+      <c r="E91" s="269"/>
+      <c r="F91" s="269"/>
+      <c r="G91" s="269"/>
+      <c r="H91" s="269"/>
+      <c r="I91" s="269"/>
+      <c r="J91" s="269"/>
+      <c r="K91" s="269"/>
+      <c r="L91" s="269"/>
       <c r="M91" s="51"/>
       <c r="N91" s="51"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="271"/>
-      <c r="B92" s="271"/>
-      <c r="C92" s="271"/>
-      <c r="D92" s="271"/>
-      <c r="E92" s="271"/>
-      <c r="F92" s="271"/>
-      <c r="G92" s="271"/>
-      <c r="H92" s="271"/>
-      <c r="I92" s="271"/>
-      <c r="J92" s="271"/>
-      <c r="K92" s="271"/>
-      <c r="L92" s="271"/>
+      <c r="A92" s="269"/>
+      <c r="B92" s="269"/>
+      <c r="C92" s="269"/>
+      <c r="D92" s="269"/>
+      <c r="E92" s="269"/>
+      <c r="F92" s="269"/>
+      <c r="G92" s="269"/>
+      <c r="H92" s="269"/>
+      <c r="I92" s="269"/>
+      <c r="J92" s="269"/>
+      <c r="K92" s="269"/>
+      <c r="L92" s="269"/>
       <c r="M92" s="51"/>
       <c r="N92" s="51"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="271"/>
-      <c r="B93" s="271"/>
-      <c r="C93" s="271"/>
-      <c r="D93" s="271"/>
-      <c r="E93" s="271"/>
-      <c r="F93" s="271"/>
-      <c r="G93" s="271"/>
-      <c r="H93" s="271"/>
-      <c r="I93" s="271"/>
-      <c r="J93" s="271"/>
-      <c r="K93" s="271"/>
-      <c r="L93" s="271"/>
+      <c r="A93" s="269"/>
+      <c r="B93" s="269"/>
+      <c r="C93" s="269"/>
+      <c r="D93" s="269"/>
+      <c r="E93" s="269"/>
+      <c r="F93" s="269"/>
+      <c r="G93" s="269"/>
+      <c r="H93" s="269"/>
+      <c r="I93" s="269"/>
+      <c r="J93" s="269"/>
+      <c r="K93" s="269"/>
+      <c r="L93" s="269"/>
       <c r="M93" s="51"/>
       <c r="N93" s="51"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="271"/>
-      <c r="B94" s="271"/>
-      <c r="C94" s="271"/>
-      <c r="D94" s="271"/>
-      <c r="E94" s="271"/>
-      <c r="F94" s="271"/>
-      <c r="G94" s="271"/>
-      <c r="H94" s="271"/>
-      <c r="I94" s="271"/>
-      <c r="J94" s="271"/>
-      <c r="K94" s="271"/>
-      <c r="L94" s="271"/>
+      <c r="A94" s="269"/>
+      <c r="B94" s="269"/>
+      <c r="C94" s="269"/>
+      <c r="D94" s="269"/>
+      <c r="E94" s="269"/>
+      <c r="F94" s="269"/>
+      <c r="G94" s="269"/>
+      <c r="H94" s="269"/>
+      <c r="I94" s="269"/>
+      <c r="J94" s="269"/>
+      <c r="K94" s="269"/>
+      <c r="L94" s="269"/>
       <c r="M94" s="51"/>
       <c r="N94" s="51"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="271"/>
-      <c r="B95" s="271"/>
-      <c r="C95" s="271"/>
-      <c r="D95" s="271"/>
-      <c r="E95" s="271"/>
-      <c r="F95" s="271"/>
-      <c r="G95" s="271"/>
-      <c r="H95" s="271"/>
-      <c r="I95" s="271"/>
-      <c r="J95" s="271"/>
-      <c r="K95" s="271"/>
-      <c r="L95" s="271"/>
+      <c r="A95" s="269"/>
+      <c r="B95" s="269"/>
+      <c r="C95" s="269"/>
+      <c r="D95" s="269"/>
+      <c r="E95" s="269"/>
+      <c r="F95" s="269"/>
+      <c r="G95" s="269"/>
+      <c r="H95" s="269"/>
+      <c r="I95" s="269"/>
+      <c r="J95" s="269"/>
+      <c r="K95" s="269"/>
+      <c r="L95" s="269"/>
       <c r="M95" s="51"/>
       <c r="N95" s="51"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="271"/>
-      <c r="B96" s="271"/>
-      <c r="C96" s="271"/>
-      <c r="D96" s="271"/>
-      <c r="E96" s="271"/>
-      <c r="F96" s="271"/>
-      <c r="G96" s="271"/>
-      <c r="H96" s="271"/>
-      <c r="I96" s="271"/>
-      <c r="J96" s="271"/>
-      <c r="K96" s="271"/>
-      <c r="L96" s="271"/>
+      <c r="A96" s="269"/>
+      <c r="B96" s="269"/>
+      <c r="C96" s="269"/>
+      <c r="D96" s="269"/>
+      <c r="E96" s="269"/>
+      <c r="F96" s="269"/>
+      <c r="G96" s="269"/>
+      <c r="H96" s="269"/>
+      <c r="I96" s="269"/>
+      <c r="J96" s="269"/>
+      <c r="K96" s="269"/>
+      <c r="L96" s="269"/>
       <c r="M96" s="51"/>
       <c r="N96" s="51"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="271"/>
-      <c r="B97" s="271"/>
-      <c r="C97" s="271"/>
-      <c r="D97" s="271"/>
-      <c r="E97" s="271"/>
-      <c r="F97" s="271"/>
-      <c r="G97" s="271"/>
-      <c r="H97" s="271"/>
-      <c r="I97" s="271"/>
-      <c r="J97" s="271"/>
-      <c r="K97" s="271"/>
-      <c r="L97" s="271"/>
+      <c r="A97" s="269"/>
+      <c r="B97" s="269"/>
+      <c r="C97" s="269"/>
+      <c r="D97" s="269"/>
+      <c r="E97" s="269"/>
+      <c r="F97" s="269"/>
+      <c r="G97" s="269"/>
+      <c r="H97" s="269"/>
+      <c r="I97" s="269"/>
+      <c r="J97" s="269"/>
+      <c r="K97" s="269"/>
+      <c r="L97" s="269"/>
       <c r="M97" s="51"/>
       <c r="N97" s="51"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="271"/>
-      <c r="B98" s="271"/>
-      <c r="C98" s="271"/>
-      <c r="D98" s="271"/>
-      <c r="E98" s="271"/>
-      <c r="F98" s="271"/>
-      <c r="G98" s="271"/>
-      <c r="H98" s="271"/>
-      <c r="I98" s="271"/>
-      <c r="J98" s="271"/>
-      <c r="K98" s="271"/>
-      <c r="L98" s="271"/>
+      <c r="A98" s="269"/>
+      <c r="B98" s="269"/>
+      <c r="C98" s="269"/>
+      <c r="D98" s="269"/>
+      <c r="E98" s="269"/>
+      <c r="F98" s="269"/>
+      <c r="G98" s="269"/>
+      <c r="H98" s="269"/>
+      <c r="I98" s="269"/>
+      <c r="J98" s="269"/>
+      <c r="K98" s="269"/>
+      <c r="L98" s="269"/>
       <c r="M98" s="51"/>
       <c r="N98" s="51"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="271"/>
-      <c r="B99" s="271"/>
-      <c r="C99" s="271"/>
-      <c r="D99" s="271"/>
-      <c r="E99" s="271"/>
-      <c r="F99" s="271"/>
-      <c r="G99" s="271"/>
-      <c r="H99" s="271"/>
-      <c r="I99" s="271"/>
-      <c r="J99" s="271"/>
-      <c r="K99" s="271"/>
-      <c r="L99" s="271"/>
+      <c r="A99" s="269"/>
+      <c r="B99" s="269"/>
+      <c r="C99" s="269"/>
+      <c r="D99" s="269"/>
+      <c r="E99" s="269"/>
+      <c r="F99" s="269"/>
+      <c r="G99" s="269"/>
+      <c r="H99" s="269"/>
+      <c r="I99" s="269"/>
+      <c r="J99" s="269"/>
+      <c r="K99" s="269"/>
+      <c r="L99" s="269"/>
       <c r="M99" s="51"/>
       <c r="N99" s="51"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="271"/>
-      <c r="B100" s="271"/>
-      <c r="C100" s="271"/>
-      <c r="D100" s="271"/>
-      <c r="E100" s="271"/>
-      <c r="F100" s="271"/>
-      <c r="G100" s="271"/>
-      <c r="H100" s="271"/>
-      <c r="I100" s="271"/>
-      <c r="J100" s="271"/>
-      <c r="K100" s="271"/>
-      <c r="L100" s="271"/>
+      <c r="A100" s="269"/>
+      <c r="B100" s="269"/>
+      <c r="C100" s="269"/>
+      <c r="D100" s="269"/>
+      <c r="E100" s="269"/>
+      <c r="F100" s="269"/>
+      <c r="G100" s="269"/>
+      <c r="H100" s="269"/>
+      <c r="I100" s="269"/>
+      <c r="J100" s="269"/>
+      <c r="K100" s="269"/>
+      <c r="L100" s="269"/>
       <c r="M100" s="51"/>
       <c r="N100" s="51"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" s="271"/>
-      <c r="B101" s="271"/>
-      <c r="C101" s="271"/>
-      <c r="D101" s="271"/>
-      <c r="E101" s="271"/>
-      <c r="F101" s="271"/>
-      <c r="G101" s="271"/>
-      <c r="H101" s="271"/>
-      <c r="I101" s="271"/>
-      <c r="J101" s="271"/>
-      <c r="K101" s="271"/>
-      <c r="L101" s="271"/>
+      <c r="A101" s="269"/>
+      <c r="B101" s="269"/>
+      <c r="C101" s="269"/>
+      <c r="D101" s="269"/>
+      <c r="E101" s="269"/>
+      <c r="F101" s="269"/>
+      <c r="G101" s="269"/>
+      <c r="H101" s="269"/>
+      <c r="I101" s="269"/>
+      <c r="J101" s="269"/>
+      <c r="K101" s="269"/>
+      <c r="L101" s="269"/>
       <c r="M101" s="51"/>
       <c r="N101" s="51"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" s="271"/>
-      <c r="B102" s="271"/>
-      <c r="C102" s="271"/>
-      <c r="D102" s="271"/>
-      <c r="E102" s="271"/>
-      <c r="F102" s="271"/>
-      <c r="G102" s="271"/>
-      <c r="H102" s="271"/>
-      <c r="I102" s="271"/>
-      <c r="J102" s="271"/>
-      <c r="K102" s="271"/>
-      <c r="L102" s="271"/>
+      <c r="A102" s="269"/>
+      <c r="B102" s="269"/>
+      <c r="C102" s="269"/>
+      <c r="D102" s="269"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="269"/>
+      <c r="G102" s="269"/>
+      <c r="H102" s="269"/>
+      <c r="I102" s="269"/>
+      <c r="J102" s="269"/>
+      <c r="K102" s="269"/>
+      <c r="L102" s="269"/>
       <c r="M102" s="51"/>
       <c r="N102" s="51"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="271"/>
-      <c r="B103" s="271"/>
-      <c r="C103" s="271"/>
-      <c r="D103" s="271"/>
-      <c r="E103" s="271"/>
-      <c r="F103" s="271"/>
-      <c r="G103" s="271"/>
-      <c r="H103" s="271"/>
-      <c r="I103" s="271"/>
-      <c r="J103" s="271"/>
-      <c r="K103" s="271"/>
-      <c r="L103" s="271"/>
+      <c r="A103" s="269"/>
+      <c r="B103" s="269"/>
+      <c r="C103" s="269"/>
+      <c r="D103" s="269"/>
+      <c r="E103" s="269"/>
+      <c r="F103" s="269"/>
+      <c r="G103" s="269"/>
+      <c r="H103" s="269"/>
+      <c r="I103" s="269"/>
+      <c r="J103" s="269"/>
+      <c r="K103" s="269"/>
+      <c r="L103" s="269"/>
       <c r="M103" s="51"/>
       <c r="N103" s="51"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="271"/>
-      <c r="B104" s="271"/>
-      <c r="C104" s="271"/>
-      <c r="D104" s="271"/>
-      <c r="E104" s="271"/>
-      <c r="F104" s="271"/>
-      <c r="G104" s="271"/>
-      <c r="H104" s="271"/>
-      <c r="I104" s="271"/>
-      <c r="J104" s="271"/>
-      <c r="K104" s="271"/>
-      <c r="L104" s="271"/>
+      <c r="A104" s="269"/>
+      <c r="B104" s="269"/>
+      <c r="C104" s="269"/>
+      <c r="D104" s="269"/>
+      <c r="E104" s="269"/>
+      <c r="F104" s="269"/>
+      <c r="G104" s="269"/>
+      <c r="H104" s="269"/>
+      <c r="I104" s="269"/>
+      <c r="J104" s="269"/>
+      <c r="K104" s="269"/>
+      <c r="L104" s="269"/>
       <c r="M104" s="51"/>
       <c r="N104" s="51"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="302"/>
+      <c r="A105" s="298"/>
       <c r="B105" s="51"/>
       <c r="C105" s="51"/>
       <c r="D105" s="51"/>
@@ -6166,7 +6309,7 @@
       <c r="N105" s="51"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="302"/>
+      <c r="A106" s="298"/>
       <c r="B106" s="51"/>
       <c r="C106" s="51"/>
       <c r="D106" s="51"/>
@@ -6182,7 +6325,7 @@
       <c r="N106" s="51"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="302"/>
+      <c r="A107" s="298"/>
       <c r="B107" s="51"/>
       <c r="C107" s="51"/>
       <c r="D107" s="51"/>
@@ -6198,7 +6341,7 @@
       <c r="N107" s="51"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="302"/>
+      <c r="A108" s="298"/>
       <c r="B108" s="51"/>
       <c r="C108" s="51"/>
       <c r="D108" s="51"/>
@@ -6214,7 +6357,7 @@
       <c r="N108" s="51"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" s="302"/>
+      <c r="A109" s="298"/>
       <c r="B109" s="51"/>
       <c r="C109" s="51"/>
       <c r="D109" s="51"/>
@@ -6230,7 +6373,7 @@
       <c r="N109" s="51"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="302"/>
+      <c r="A110" s="298"/>
       <c r="B110" s="51"/>
       <c r="C110" s="51"/>
       <c r="D110" s="51"/>
@@ -6246,7 +6389,7 @@
       <c r="N110" s="51"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="302"/>
+      <c r="A111" s="298"/>
       <c r="B111" s="51"/>
       <c r="C111" s="51"/>
       <c r="D111" s="51"/>
@@ -6262,7 +6405,7 @@
       <c r="N111" s="51"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" s="302"/>
+      <c r="A112" s="298"/>
       <c r="B112" s="51"/>
       <c r="C112" s="51"/>
       <c r="D112" s="51"/>
@@ -6278,7 +6421,7 @@
       <c r="N112" s="51"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="302"/>
+      <c r="A113" s="298"/>
       <c r="B113" s="51"/>
       <c r="C113" s="51"/>
       <c r="D113" s="51"/>
@@ -6294,13 +6437,13 @@
       <c r="N113" s="51"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="302"/>
+      <c r="A114" s="298"/>
       <c r="B114" s="51"/>
       <c r="C114" s="51"/>
       <c r="D114" s="51"/>
       <c r="E114" s="51"/>
       <c r="F114" s="51"/>
-      <c r="G114" s="302"/>
+      <c r="G114" s="298"/>
       <c r="H114" s="51"/>
       <c r="I114" s="51"/>
       <c r="J114" s="51"/>
@@ -6310,179 +6453,179 @@
       <c r="N114" s="51"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="302"/>
-      <c r="B115" s="302"/>
-      <c r="C115" s="302"/>
-      <c r="D115" s="302"/>
-      <c r="E115" s="302"/>
-      <c r="F115" s="302"/>
-      <c r="G115" s="302"/>
-      <c r="H115" s="302"/>
-      <c r="I115" s="302"/>
-      <c r="J115" s="302"/>
-      <c r="K115" s="302"/>
-      <c r="L115" s="302"/>
-      <c r="M115" s="302"/>
+      <c r="A115" s="298"/>
+      <c r="B115" s="298"/>
+      <c r="C115" s="298"/>
+      <c r="D115" s="298"/>
+      <c r="E115" s="298"/>
+      <c r="F115" s="298"/>
+      <c r="G115" s="298"/>
+      <c r="H115" s="298"/>
+      <c r="I115" s="298"/>
+      <c r="J115" s="298"/>
+      <c r="K115" s="298"/>
+      <c r="L115" s="298"/>
+      <c r="M115" s="298"/>
       <c r="N115" s="51"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="302"/>
-      <c r="B116" s="302"/>
-      <c r="C116" s="302"/>
-      <c r="D116" s="302"/>
-      <c r="E116" s="302"/>
-      <c r="F116" s="302"/>
-      <c r="G116" s="302"/>
-      <c r="H116" s="302"/>
-      <c r="I116" s="302"/>
-      <c r="J116" s="302"/>
-      <c r="K116" s="302"/>
-      <c r="L116" s="302"/>
-      <c r="M116" s="302"/>
+      <c r="A116" s="298"/>
+      <c r="B116" s="298"/>
+      <c r="C116" s="298"/>
+      <c r="D116" s="298"/>
+      <c r="E116" s="298"/>
+      <c r="F116" s="298"/>
+      <c r="G116" s="298"/>
+      <c r="H116" s="298"/>
+      <c r="I116" s="298"/>
+      <c r="J116" s="298"/>
+      <c r="K116" s="298"/>
+      <c r="L116" s="298"/>
+      <c r="M116" s="298"/>
       <c r="N116" s="51"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="302"/>
-      <c r="B117" s="302"/>
-      <c r="C117" s="302"/>
-      <c r="D117" s="302"/>
-      <c r="E117" s="302"/>
-      <c r="F117" s="302"/>
-      <c r="G117" s="302"/>
-      <c r="H117" s="302"/>
-      <c r="I117" s="302"/>
-      <c r="J117" s="302"/>
-      <c r="K117" s="302"/>
-      <c r="L117" s="302"/>
-      <c r="M117" s="302"/>
+      <c r="A117" s="298"/>
+      <c r="B117" s="298"/>
+      <c r="C117" s="298"/>
+      <c r="D117" s="298"/>
+      <c r="E117" s="298"/>
+      <c r="F117" s="298"/>
+      <c r="G117" s="298"/>
+      <c r="H117" s="298"/>
+      <c r="I117" s="298"/>
+      <c r="J117" s="298"/>
+      <c r="K117" s="298"/>
+      <c r="L117" s="298"/>
+      <c r="M117" s="298"/>
       <c r="N117" s="51"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="302"/>
-      <c r="B118" s="302"/>
-      <c r="C118" s="302"/>
-      <c r="D118" s="302"/>
-      <c r="E118" s="302"/>
-      <c r="F118" s="302"/>
-      <c r="G118" s="302"/>
-      <c r="H118" s="302"/>
-      <c r="I118" s="302"/>
-      <c r="J118" s="302"/>
-      <c r="K118" s="302"/>
-      <c r="L118" s="302"/>
-      <c r="M118" s="302"/>
+      <c r="A118" s="298"/>
+      <c r="B118" s="298"/>
+      <c r="C118" s="298"/>
+      <c r="D118" s="298"/>
+      <c r="E118" s="298"/>
+      <c r="F118" s="298"/>
+      <c r="G118" s="298"/>
+      <c r="H118" s="298"/>
+      <c r="I118" s="298"/>
+      <c r="J118" s="298"/>
+      <c r="K118" s="298"/>
+      <c r="L118" s="298"/>
+      <c r="M118" s="298"/>
       <c r="N118" s="51"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="302"/>
-      <c r="B119" s="302"/>
-      <c r="C119" s="302"/>
-      <c r="D119" s="302"/>
-      <c r="E119" s="302"/>
-      <c r="F119" s="302"/>
-      <c r="G119" s="302"/>
-      <c r="H119" s="302"/>
-      <c r="I119" s="302"/>
-      <c r="J119" s="302"/>
-      <c r="K119" s="302"/>
-      <c r="L119" s="302"/>
-      <c r="M119" s="302"/>
+      <c r="A119" s="298"/>
+      <c r="B119" s="298"/>
+      <c r="C119" s="298"/>
+      <c r="D119" s="298"/>
+      <c r="E119" s="298"/>
+      <c r="F119" s="298"/>
+      <c r="G119" s="298"/>
+      <c r="H119" s="298"/>
+      <c r="I119" s="298"/>
+      <c r="J119" s="298"/>
+      <c r="K119" s="298"/>
+      <c r="L119" s="298"/>
+      <c r="M119" s="298"/>
       <c r="N119" s="51"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="302"/>
-      <c r="B120" s="302"/>
-      <c r="C120" s="302"/>
-      <c r="D120" s="302"/>
-      <c r="E120" s="302"/>
-      <c r="F120" s="302"/>
-      <c r="G120" s="302"/>
-      <c r="H120" s="302"/>
-      <c r="I120" s="302"/>
-      <c r="J120" s="302"/>
-      <c r="K120" s="302"/>
-      <c r="L120" s="302"/>
-      <c r="M120" s="302"/>
+      <c r="A120" s="298"/>
+      <c r="B120" s="298"/>
+      <c r="C120" s="298"/>
+      <c r="D120" s="298"/>
+      <c r="E120" s="298"/>
+      <c r="F120" s="298"/>
+      <c r="G120" s="298"/>
+      <c r="H120" s="298"/>
+      <c r="I120" s="298"/>
+      <c r="J120" s="298"/>
+      <c r="K120" s="298"/>
+      <c r="L120" s="298"/>
+      <c r="M120" s="298"/>
       <c r="N120" s="51"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="302"/>
-      <c r="B121" s="302"/>
-      <c r="C121" s="302"/>
-      <c r="D121" s="302"/>
-      <c r="E121" s="302"/>
-      <c r="F121" s="302"/>
-      <c r="G121" s="302"/>
-      <c r="H121" s="302"/>
-      <c r="I121" s="302"/>
-      <c r="J121" s="302"/>
-      <c r="K121" s="302"/>
-      <c r="L121" s="302"/>
-      <c r="M121" s="302"/>
+      <c r="A121" s="298"/>
+      <c r="B121" s="298"/>
+      <c r="C121" s="298"/>
+      <c r="D121" s="298"/>
+      <c r="E121" s="298"/>
+      <c r="F121" s="298"/>
+      <c r="G121" s="298"/>
+      <c r="H121" s="298"/>
+      <c r="I121" s="298"/>
+      <c r="J121" s="298"/>
+      <c r="K121" s="298"/>
+      <c r="L121" s="298"/>
+      <c r="M121" s="298"/>
       <c r="N121" s="51"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A122" s="302"/>
-      <c r="B122" s="302"/>
-      <c r="C122" s="302"/>
-      <c r="D122" s="302"/>
-      <c r="E122" s="302"/>
-      <c r="F122" s="302"/>
-      <c r="G122" s="302"/>
-      <c r="H122" s="302"/>
-      <c r="I122" s="302"/>
-      <c r="J122" s="302"/>
-      <c r="K122" s="302"/>
-      <c r="L122" s="302"/>
-      <c r="M122" s="302"/>
+      <c r="A122" s="298"/>
+      <c r="B122" s="298"/>
+      <c r="C122" s="298"/>
+      <c r="D122" s="298"/>
+      <c r="E122" s="298"/>
+      <c r="F122" s="298"/>
+      <c r="G122" s="298"/>
+      <c r="H122" s="298"/>
+      <c r="I122" s="298"/>
+      <c r="J122" s="298"/>
+      <c r="K122" s="298"/>
+      <c r="L122" s="298"/>
+      <c r="M122" s="298"/>
       <c r="N122" s="51"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A123" s="302"/>
-      <c r="B123" s="302"/>
-      <c r="C123" s="302"/>
-      <c r="D123" s="302"/>
-      <c r="E123" s="302"/>
-      <c r="F123" s="302"/>
-      <c r="G123" s="302"/>
-      <c r="H123" s="302"/>
-      <c r="I123" s="302"/>
-      <c r="J123" s="302"/>
-      <c r="K123" s="302"/>
-      <c r="L123" s="302"/>
-      <c r="M123" s="302"/>
+      <c r="A123" s="298"/>
+      <c r="B123" s="298"/>
+      <c r="C123" s="298"/>
+      <c r="D123" s="298"/>
+      <c r="E123" s="298"/>
+      <c r="F123" s="298"/>
+      <c r="G123" s="298"/>
+      <c r="H123" s="298"/>
+      <c r="I123" s="298"/>
+      <c r="J123" s="298"/>
+      <c r="K123" s="298"/>
+      <c r="L123" s="298"/>
+      <c r="M123" s="298"/>
       <c r="N123" s="51"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A124" s="302"/>
-      <c r="B124" s="302"/>
-      <c r="C124" s="302"/>
-      <c r="D124" s="302"/>
-      <c r="E124" s="302"/>
-      <c r="F124" s="302"/>
-      <c r="G124" s="302"/>
-      <c r="H124" s="302"/>
-      <c r="I124" s="302"/>
-      <c r="J124" s="302"/>
-      <c r="K124" s="302"/>
-      <c r="L124" s="302"/>
-      <c r="M124" s="302"/>
+      <c r="A124" s="298"/>
+      <c r="B124" s="298"/>
+      <c r="C124" s="298"/>
+      <c r="D124" s="298"/>
+      <c r="E124" s="298"/>
+      <c r="F124" s="298"/>
+      <c r="G124" s="298"/>
+      <c r="H124" s="298"/>
+      <c r="I124" s="298"/>
+      <c r="J124" s="298"/>
+      <c r="K124" s="298"/>
+      <c r="L124" s="298"/>
+      <c r="M124" s="298"/>
       <c r="N124" s="51"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A125" s="302"/>
-      <c r="B125" s="302"/>
-      <c r="C125" s="302"/>
-      <c r="D125" s="302"/>
-      <c r="E125" s="302"/>
-      <c r="F125" s="302"/>
+      <c r="A125" s="298"/>
+      <c r="B125" s="298"/>
+      <c r="C125" s="298"/>
+      <c r="D125" s="298"/>
+      <c r="E125" s="298"/>
+      <c r="F125" s="298"/>
       <c r="G125" s="50"/>
-      <c r="H125" s="302"/>
-      <c r="I125" s="302"/>
-      <c r="J125" s="302"/>
-      <c r="K125" s="302"/>
-      <c r="L125" s="302"/>
-      <c r="M125" s="302"/>
+      <c r="H125" s="298"/>
+      <c r="I125" s="298"/>
+      <c r="J125" s="298"/>
+      <c r="K125" s="298"/>
+      <c r="L125" s="298"/>
+      <c r="M125" s="298"/>
       <c r="N125" s="51"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
@@ -11657,7 +11800,7 @@
       <c r="I13" s="196" t="s">
         <v>118</v>
       </c>
-      <c r="J13" s="279" t="s">
+      <c r="J13" s="277" t="s">
         <v>152</v>
       </c>
       <c r="K13" s="51"/>
@@ -11683,7 +11826,7 @@
         <v>101</v>
       </c>
       <c r="G14" s="185" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H14" s="185" t="s">
         <v>105</v>
@@ -11691,7 +11834,7 @@
       <c r="I14" s="185" t="s">
         <v>132</v>
       </c>
-      <c r="J14" s="280" t="s">
+      <c r="J14" s="278" t="s">
         <v>162</v>
       </c>
       <c r="K14" s="51"/>

--- a/Gastos_2026.xlsx
+++ b/Gastos_2026.xlsx
@@ -256,7 +256,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="207">
   <si>
     <t>Servicios</t>
   </si>
@@ -843,9 +843,6 @@
     <t>Serv e Impuestos</t>
   </si>
   <si>
-    <t>CHAMPION</t>
-  </si>
-  <si>
     <t>Prerstamos</t>
   </si>
   <si>
@@ -880,16 +877,13 @@
   </si>
   <si>
     <t>Vto Prestamos</t>
-  </si>
-  <si>
-    <t>Mantenimiento</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="62" x14ac:knownFonts="1">
+  <fonts count="63" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1357,6 +1351,15 @@
       <b/>
       <sz val="11"/>
       <color theme="8" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2244,7 +2247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="527">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2703,16 +2706,10 @@
     <xf numFmtId="0" fontId="17" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3030,7 +3027,6 @@
     <xf numFmtId="0" fontId="10" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3040,14 +3036,8 @@
     <xf numFmtId="0" fontId="59" fillId="35" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="35" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="57" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3064,7 +3054,6 @@
     <xf numFmtId="0" fontId="17" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="17" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3113,9 +3102,6 @@
     <xf numFmtId="16" fontId="9" fillId="35" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="43" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3148,6 +3134,12 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="62" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4324,11 +4316,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="291" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="295"/>
-      <c r="C1" s="361" t="s">
+      <c r="B1" s="293"/>
+      <c r="C1" s="359" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="265" t="s">
@@ -4344,17 +4336,17 @@
         <v>55</v>
       </c>
       <c r="H1" s="272"/>
-      <c r="I1" s="346" t="s">
+      <c r="I1" s="344" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="347" t="s">
+      <c r="J1" s="345" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="373" t="s">
+      <c r="K1" s="371" t="s">
         <v>193</v>
       </c>
-      <c r="L1" s="350"/>
-      <c r="M1" s="448"/>
+      <c r="L1" s="348"/>
+      <c r="M1" s="446"/>
       <c r="N1" s="269"/>
       <c r="O1" s="50"/>
       <c r="P1" s="50"/>
@@ -4362,18 +4354,18 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="286"/>
-      <c r="B2" s="296"/>
-      <c r="C2" s="371"/>
-      <c r="D2" s="367"/>
+      <c r="B2" s="294"/>
+      <c r="C2" s="369"/>
+      <c r="D2" s="365"/>
       <c r="E2" s="284"/>
-      <c r="F2" s="372"/>
+      <c r="F2" s="370"/>
       <c r="G2" s="198"/>
       <c r="H2" s="269"/>
       <c r="I2" s="268"/>
-      <c r="J2" s="365"/>
-      <c r="K2" s="325"/>
-      <c r="L2" s="380"/>
-      <c r="M2" s="513"/>
+      <c r="J2" s="363"/>
+      <c r="K2" s="323"/>
+      <c r="L2" s="378"/>
+      <c r="M2" s="506"/>
       <c r="N2" s="269"/>
       <c r="O2" s="50"/>
       <c r="P2" s="50"/>
@@ -4381,7 +4373,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="286"/>
-      <c r="B3" s="296"/>
+      <c r="B3" s="294"/>
       <c r="C3" s="284"/>
       <c r="D3" s="198"/>
       <c r="E3" s="198"/>
@@ -4390,16 +4382,16 @@
       <c r="H3" s="269"/>
       <c r="I3" s="198"/>
       <c r="J3" s="283"/>
-      <c r="K3" s="325"/>
-      <c r="L3" s="381"/>
-      <c r="M3" s="448"/>
+      <c r="K3" s="323"/>
+      <c r="L3" s="379"/>
+      <c r="M3" s="446"/>
       <c r="N3" s="269"/>
       <c r="O3" s="50"/>
       <c r="P3" s="50"/>
       <c r="Q3" s="50"/>
     </row>
     <row r="4" spans="1:17" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="370" t="s">
+      <c r="A4" s="368" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="269"/>
@@ -4420,10 +4412,10 @@
       <c r="I4" s="284">
         <v>12165</v>
       </c>
-      <c r="J4" s="461"/>
-      <c r="K4" s="325"/>
-      <c r="L4" s="380"/>
-      <c r="M4" s="448"/>
+      <c r="J4" s="459"/>
+      <c r="K4" s="323"/>
+      <c r="L4" s="378"/>
+      <c r="M4" s="446"/>
       <c r="N4" s="269"/>
       <c r="O4" s="50"/>
       <c r="P4" s="50"/>
@@ -4431,7 +4423,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="286"/>
-      <c r="B5" s="296"/>
+      <c r="B5" s="294"/>
       <c r="C5" s="284"/>
       <c r="D5" s="284"/>
       <c r="E5" s="284"/>
@@ -4441,9 +4433,9 @@
       <c r="I5" s="284"/>
       <c r="J5" s="269"/>
       <c r="K5" s="283"/>
-      <c r="L5" s="395"/>
-      <c r="M5" s="401"/>
-      <c r="N5" s="478"/>
+      <c r="L5" s="393"/>
+      <c r="M5" s="399"/>
+      <c r="N5" s="473"/>
       <c r="O5" s="50"/>
       <c r="P5" s="50"/>
       <c r="Q5" s="50"/>
@@ -4460,20 +4452,20 @@
       <c r="I6" s="269"/>
       <c r="J6" s="269"/>
       <c r="K6" s="283"/>
-      <c r="L6" s="460"/>
-      <c r="M6" s="518"/>
-      <c r="N6" s="478"/>
+      <c r="L6" s="458"/>
+      <c r="M6" s="511"/>
+      <c r="N6" s="473"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="50"/>
     </row>
     <row r="7" spans="1:17" s="1" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="286"/>
-      <c r="B7" s="501"/>
-      <c r="C7" s="505" t="s">
+      <c r="B7" s="495"/>
+      <c r="C7" s="499" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="503" t="s">
+      <c r="D7" s="497" t="s">
         <v>190</v>
       </c>
       <c r="E7" s="262" t="s">
@@ -4482,225 +4474,229 @@
       <c r="F7" s="263" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="493" t="s">
+      <c r="G7" s="487" t="s">
         <v>32</v>
       </c>
       <c r="H7" s="264" t="s">
-        <v>207</v>
-      </c>
-      <c r="I7" s="495" t="s">
+        <v>206</v>
+      </c>
+      <c r="I7" s="489" t="s">
+        <v>204</v>
+      </c>
+      <c r="J7" s="273" t="s">
         <v>205</v>
-      </c>
-      <c r="J7" s="273" t="s">
-        <v>206</v>
       </c>
       <c r="K7" s="276" t="s">
         <v>150</v>
       </c>
-      <c r="L7" s="390" t="s">
+      <c r="L7" s="388" t="s">
         <v>184</v>
       </c>
-      <c r="M7" s="520" t="s">
-        <v>204</v>
-      </c>
-      <c r="N7" s="496"/>
+      <c r="M7" s="513" t="s">
+        <v>203</v>
+      </c>
+      <c r="N7" s="490"/>
       <c r="O7" s="50"/>
       <c r="P7" s="50"/>
       <c r="Q7" s="50"/>
     </row>
     <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="294"/>
-      <c r="B8" s="502"/>
-      <c r="C8" s="478"/>
-      <c r="D8" s="504"/>
+      <c r="A8" s="292"/>
+      <c r="B8" s="496"/>
+      <c r="C8" s="473"/>
+      <c r="D8" s="498"/>
       <c r="E8" s="286"/>
-      <c r="F8" s="367"/>
-      <c r="G8" s="494">
+      <c r="F8" s="365"/>
+      <c r="G8" s="488">
         <v>99773.25</v>
       </c>
-      <c r="H8" s="507">
+      <c r="H8" s="501">
         <v>46193</v>
       </c>
-      <c r="I8" s="496"/>
+      <c r="I8" s="490"/>
       <c r="J8" s="286"/>
-      <c r="K8" s="291"/>
-      <c r="L8" s="283"/>
-      <c r="M8" s="519"/>
-      <c r="N8" s="478"/>
+      <c r="K8" s="286"/>
+      <c r="L8" s="446"/>
+      <c r="M8" s="512"/>
+      <c r="N8" s="473"/>
       <c r="O8" s="50"/>
       <c r="P8" s="50"/>
       <c r="Q8" s="50"/>
     </row>
     <row r="9" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="286"/>
-      <c r="B9" s="499">
+      <c r="B9" s="493">
         <v>1</v>
       </c>
-      <c r="C9" s="500"/>
-      <c r="D9" s="376"/>
+      <c r="C9" s="494"/>
+      <c r="D9" s="374"/>
       <c r="E9" s="287"/>
-      <c r="F9" s="466"/>
-      <c r="G9" s="508">
+      <c r="F9" s="463"/>
+      <c r="G9" s="520">
         <v>66924</v>
       </c>
-      <c r="H9" s="507">
+      <c r="H9" s="501">
         <v>46210</v>
       </c>
-      <c r="I9" s="496"/>
-      <c r="J9" s="287"/>
-      <c r="K9" s="288"/>
-      <c r="L9" s="283"/>
-      <c r="M9" s="486"/>
-      <c r="N9" s="478"/>
+      <c r="I9" s="490"/>
+      <c r="J9" s="521"/>
+      <c r="K9" s="287"/>
+      <c r="L9" s="446"/>
+      <c r="M9" s="480"/>
+      <c r="N9" s="473"/>
       <c r="O9" s="50"/>
       <c r="P9" s="50"/>
       <c r="Q9" s="50"/>
     </row>
     <row r="10" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="286"/>
-      <c r="B10" s="499">
+      <c r="B10" s="493">
         <v>2</v>
       </c>
-      <c r="C10" s="438"/>
-      <c r="D10" s="374"/>
-      <c r="E10" s="289"/>
-      <c r="F10" s="467"/>
-      <c r="G10" s="506">
+      <c r="C10" s="436"/>
+      <c r="D10" s="372">
+        <v>623788.28</v>
+      </c>
+      <c r="E10" s="288"/>
+      <c r="F10" s="464"/>
+      <c r="G10" s="500">
         <v>235158.78</v>
       </c>
-      <c r="H10" s="507">
+      <c r="H10" s="501">
         <v>46193</v>
       </c>
-      <c r="I10" s="496"/>
-      <c r="J10" s="287"/>
-      <c r="K10" s="397"/>
-      <c r="L10" s="465">
+      <c r="I10" s="490"/>
+      <c r="J10" s="287">
+        <v>121269.37</v>
+      </c>
+      <c r="K10" s="473"/>
+      <c r="L10" s="522">
         <v>69853</v>
       </c>
-      <c r="M10" s="478"/>
-      <c r="N10" s="478"/>
+      <c r="M10" s="473"/>
+      <c r="N10" s="473"/>
       <c r="O10" s="50"/>
       <c r="P10" s="50"/>
       <c r="Q10" s="50"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="286"/>
-      <c r="B11" s="391">
+      <c r="B11" s="389">
         <v>3</v>
       </c>
-      <c r="C11" s="498"/>
-      <c r="D11" s="375">
-        <v>446458</v>
-      </c>
-      <c r="E11" s="468">
+      <c r="C11" s="492"/>
+      <c r="D11" s="373"/>
+      <c r="E11" s="465">
         <v>500</v>
       </c>
-      <c r="F11" s="492" t="s">
-        <v>208</v>
-      </c>
-      <c r="G11" s="522">
+      <c r="F11" s="486">
+        <v>83000</v>
+      </c>
+      <c r="G11" s="515">
         <f>SUM(G8:G10)</f>
         <v>401856.03</v>
       </c>
-      <c r="H11" s="374"/>
-      <c r="I11" s="496"/>
-      <c r="J11" s="469">
-        <v>98858</v>
-      </c>
-      <c r="K11" s="471">
+      <c r="H11" s="372"/>
+      <c r="I11" s="490"/>
+      <c r="J11" s="380">
+        <v>25178</v>
+      </c>
+      <c r="K11" s="287">
         <v>52966</v>
       </c>
-      <c r="L11" s="470">
+      <c r="L11" s="466">
         <v>13840</v>
       </c>
       <c r="M11" s="150">
         <v>122867</v>
       </c>
-      <c r="N11" s="478"/>
+      <c r="N11" s="473"/>
       <c r="O11" s="50"/>
       <c r="P11" s="50"/>
       <c r="Q11" s="50"/>
     </row>
     <row r="12" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="271"/>
-      <c r="B12" s="392">
+      <c r="B12" s="390">
         <v>4</v>
       </c>
       <c r="C12" s="284"/>
-      <c r="D12" s="379"/>
+      <c r="D12" s="377"/>
       <c r="E12" s="287"/>
       <c r="F12" s="275"/>
-      <c r="G12" s="523"/>
-      <c r="H12" s="478"/>
-      <c r="I12" s="497"/>
-      <c r="J12" s="478"/>
-      <c r="K12" s="401"/>
-      <c r="L12" s="483"/>
-      <c r="M12" s="514"/>
-      <c r="N12" s="269"/>
+      <c r="G12" s="516"/>
+      <c r="H12" s="473"/>
+      <c r="I12" s="491"/>
+      <c r="J12" s="473"/>
+      <c r="K12" s="473"/>
+      <c r="L12" s="523"/>
+      <c r="M12" s="507"/>
+      <c r="N12" s="395"/>
       <c r="O12" s="50"/>
       <c r="P12" s="50"/>
       <c r="Q12" s="50"/>
     </row>
     <row r="13" spans="1:17" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="268"/>
-      <c r="B13" s="393">
+      <c r="B13" s="391">
         <v>5</v>
       </c>
-      <c r="C13" s="396"/>
-      <c r="D13" s="388"/>
+      <c r="C13" s="394"/>
+      <c r="D13" s="386"/>
       <c r="E13" s="275"/>
-      <c r="F13" s="382"/>
-      <c r="G13" s="524"/>
-      <c r="H13" s="401"/>
-      <c r="I13" s="480"/>
-      <c r="J13" s="403"/>
-      <c r="K13" s="401"/>
-      <c r="L13" s="457"/>
+      <c r="F13" s="380"/>
+      <c r="G13" s="517"/>
+      <c r="H13" s="399"/>
+      <c r="I13" s="475"/>
+      <c r="J13" s="401"/>
+      <c r="K13" s="399"/>
+      <c r="L13" s="455"/>
       <c r="M13" s="283"/>
-      <c r="N13" s="269"/>
+      <c r="N13" s="476">
+        <v>328599</v>
+      </c>
       <c r="O13" s="50"/>
       <c r="P13" s="50"/>
       <c r="Q13" s="50"/>
     </row>
     <row r="14" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="268"/>
-      <c r="B14" s="302"/>
-      <c r="C14" s="389"/>
-      <c r="D14" s="394"/>
-      <c r="E14" s="405"/>
-      <c r="F14" s="406"/>
-      <c r="G14" s="525"/>
-      <c r="H14" s="478"/>
-      <c r="I14" s="509"/>
-      <c r="J14" s="481"/>
-      <c r="K14" s="484"/>
-      <c r="L14" s="458"/>
-      <c r="M14" s="515"/>
-      <c r="N14" s="269"/>
+      <c r="B14" s="300"/>
+      <c r="C14" s="387"/>
+      <c r="D14" s="392"/>
+      <c r="E14" s="403"/>
+      <c r="F14" s="404"/>
+      <c r="G14" s="518"/>
+      <c r="H14" s="473"/>
+      <c r="I14" s="502"/>
+      <c r="J14" s="476"/>
+      <c r="K14" s="478"/>
+      <c r="L14" s="456"/>
+      <c r="M14" s="508"/>
+      <c r="N14" s="473">
+        <v>2952000</v>
+      </c>
       <c r="O14" s="50"/>
       <c r="P14" s="50"/>
       <c r="Q14" s="50"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="268"/>
-      <c r="B15" s="302"/>
-      <c r="C15" s="377"/>
-      <c r="D15" s="322"/>
-      <c r="E15" s="408" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="409">
-        <v>200000</v>
-      </c>
-      <c r="G15" s="526"/>
-      <c r="H15" s="482"/>
-      <c r="I15" s="403"/>
-      <c r="J15" s="478"/>
-      <c r="K15" s="485"/>
-      <c r="L15" s="458"/>
-      <c r="M15" s="516"/>
-      <c r="N15" s="269"/>
+      <c r="B15" s="300"/>
+      <c r="C15" s="375"/>
+      <c r="D15" s="320"/>
+      <c r="E15" s="406"/>
+      <c r="F15" s="407"/>
+      <c r="G15" s="519"/>
+      <c r="H15" s="477"/>
+      <c r="I15" s="401"/>
+      <c r="J15" s="473"/>
+      <c r="K15" s="479"/>
+      <c r="L15" s="456"/>
+      <c r="M15" s="509"/>
+      <c r="N15" s="473">
+        <v>807021</v>
+      </c>
       <c r="O15" s="50"/>
       <c r="P15" s="50"/>
       <c r="Q15" s="50"/>
@@ -4708,18 +4704,21 @@
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="269"/>
       <c r="B16" s="283"/>
-      <c r="C16" s="378"/>
-      <c r="D16" s="322"/>
-      <c r="E16" s="410"/>
-      <c r="F16" s="411"/>
-      <c r="G16" s="521"/>
-      <c r="H16" s="478"/>
-      <c r="I16" s="510"/>
-      <c r="J16" s="478"/>
-      <c r="K16" s="486"/>
-      <c r="L16" s="458"/>
+      <c r="C16" s="376"/>
+      <c r="D16" s="320"/>
+      <c r="E16" s="408"/>
+      <c r="F16" s="409"/>
+      <c r="G16" s="514"/>
+      <c r="H16" s="473"/>
+      <c r="I16" s="503"/>
+      <c r="J16" s="473"/>
+      <c r="K16" s="480"/>
+      <c r="L16" s="456"/>
       <c r="M16" s="283"/>
-      <c r="N16" s="198"/>
+      <c r="N16" s="395">
+        <f>SUM(N13:N15)</f>
+        <v>4087620</v>
+      </c>
       <c r="O16" s="50"/>
       <c r="P16" s="50"/>
       <c r="Q16" s="50"/>
@@ -4728,85 +4727,92 @@
       <c r="A17" s="269"/>
       <c r="B17" s="283"/>
       <c r="C17" s="269"/>
-      <c r="D17" s="322"/>
-      <c r="E17" s="412"/>
-      <c r="F17" s="411"/>
-      <c r="G17" s="477"/>
-      <c r="H17" s="479"/>
-      <c r="I17" s="511"/>
-      <c r="J17" s="479"/>
-      <c r="K17" s="484"/>
-      <c r="L17" s="458"/>
-      <c r="M17" s="461"/>
+      <c r="D17" s="320"/>
+      <c r="E17" s="410"/>
+      <c r="F17" s="409"/>
+      <c r="G17" s="472"/>
+      <c r="H17" s="474"/>
+      <c r="I17" s="504"/>
+      <c r="J17" s="474"/>
+      <c r="K17" s="478"/>
+      <c r="L17" s="456"/>
+      <c r="M17" s="459"/>
       <c r="N17" s="269"/>
       <c r="O17" s="50"/>
       <c r="P17" s="50"/>
       <c r="Q17" s="50"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="367"/>
-      <c r="B18" s="369"/>
-      <c r="C18" s="368"/>
-      <c r="D18" s="325"/>
-      <c r="E18" s="414"/>
-      <c r="F18" s="415"/>
-      <c r="G18" s="413"/>
-      <c r="H18" s="402"/>
-      <c r="I18" s="491"/>
-      <c r="J18" s="479"/>
-      <c r="K18" s="487"/>
-      <c r="L18" s="458"/>
-      <c r="M18" s="461"/>
-      <c r="N18" s="269"/>
+      <c r="A18" s="365"/>
+      <c r="B18" s="367"/>
+      <c r="C18" s="366"/>
+      <c r="D18" s="323"/>
+      <c r="E18" s="412"/>
+      <c r="F18" s="413"/>
+      <c r="G18" s="411"/>
+      <c r="H18" s="400"/>
+      <c r="I18" s="485"/>
+      <c r="J18" s="474"/>
+      <c r="K18" s="481"/>
+      <c r="L18" s="456"/>
+      <c r="M18" s="459"/>
+      <c r="N18" s="269">
+        <v>66924</v>
+      </c>
       <c r="O18" s="50"/>
       <c r="P18" s="50"/>
       <c r="Q18" s="50"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="301"/>
-      <c r="B19" s="302"/>
-      <c r="C19" s="355"/>
-      <c r="D19" s="404"/>
-      <c r="E19" s="416"/>
-      <c r="F19" s="417"/>
-      <c r="G19" s="418"/>
-      <c r="H19" s="488"/>
-      <c r="I19" s="512"/>
-      <c r="J19" s="489"/>
-      <c r="K19" s="490"/>
-      <c r="L19" s="458"/>
-      <c r="M19" s="461"/>
-      <c r="N19" s="269"/>
+      <c r="A19" s="299"/>
+      <c r="B19" s="300"/>
+      <c r="C19" s="353"/>
+      <c r="D19" s="402"/>
+      <c r="E19" s="414"/>
+      <c r="F19" s="415"/>
+      <c r="G19" s="416"/>
+      <c r="H19" s="482"/>
+      <c r="I19" s="505"/>
+      <c r="J19" s="483"/>
+      <c r="K19" s="484"/>
+      <c r="L19" s="456"/>
+      <c r="M19" s="459"/>
+      <c r="N19" s="269">
+        <v>234393</v>
+      </c>
       <c r="O19" s="50"/>
       <c r="P19" s="50"/>
       <c r="Q19" s="50"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="300"/>
-      <c r="B20" s="302"/>
-      <c r="C20" s="345"/>
-      <c r="D20" s="357"/>
-      <c r="E20" s="407"/>
-      <c r="F20" s="357"/>
-      <c r="G20" s="332"/>
-      <c r="H20" s="491"/>
-      <c r="I20" s="491"/>
-      <c r="J20" s="479"/>
-      <c r="K20" s="490"/>
-      <c r="L20" s="458"/>
+      <c r="A20" s="298"/>
+      <c r="B20" s="300"/>
+      <c r="C20" s="343"/>
+      <c r="D20" s="355"/>
+      <c r="E20" s="405"/>
+      <c r="F20" s="355"/>
+      <c r="G20" s="330"/>
+      <c r="H20" s="485"/>
+      <c r="I20" s="485"/>
+      <c r="J20" s="474"/>
+      <c r="K20" s="484"/>
+      <c r="L20" s="456"/>
       <c r="M20" s="283"/>
-      <c r="N20" s="269"/>
+      <c r="N20" s="269">
+        <f>SUM(N18:N19)</f>
+        <v>301317</v>
+      </c>
       <c r="O20" s="50"/>
       <c r="P20" s="50"/>
       <c r="Q20" s="50"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="301"/>
-      <c r="B21" s="297"/>
-      <c r="C21" s="366" t="s">
+      <c r="A21" s="299"/>
+      <c r="B21" s="295"/>
+      <c r="C21" s="364" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="387" t="s">
+      <c r="D21" s="385" t="s">
         <v>54</v>
       </c>
       <c r="E21" s="270" t="s">
@@ -4818,113 +4824,108 @@
       <c r="G21" s="264" t="s">
         <v>58</v>
       </c>
-      <c r="H21" s="348" t="s">
+      <c r="H21" s="346" t="s">
         <v>80</v>
       </c>
       <c r="I21" s="267" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="292" t="s">
+      <c r="J21" s="290" t="s">
         <v>171</v>
       </c>
-      <c r="K21" s="462"/>
-      <c r="L21" s="459"/>
-      <c r="M21" s="447">
-        <v>893484.19</v>
-      </c>
-      <c r="N21" s="517"/>
+      <c r="K21" s="460"/>
+      <c r="L21" s="457"/>
+      <c r="M21" s="445"/>
+      <c r="N21" s="510"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="286"/>
-      <c r="B22" s="303"/>
-      <c r="C22" s="304"/>
-      <c r="D22" s="377">
+      <c r="B22" s="301"/>
+      <c r="C22" s="302"/>
+      <c r="D22" s="375">
         <v>15000</v>
       </c>
       <c r="E22" s="280"/>
       <c r="F22" s="280"/>
-      <c r="G22" s="364"/>
-      <c r="H22" s="364">
+      <c r="G22" s="362"/>
+      <c r="H22" s="362">
         <v>59159</v>
       </c>
       <c r="I22" s="280"/>
       <c r="J22" s="280"/>
-      <c r="K22" s="463"/>
-      <c r="L22" s="459"/>
-      <c r="M22" s="464">
-        <f>SUM(M17:M21)</f>
-        <v>893484.19</v>
-      </c>
-      <c r="N22" s="444"/>
+      <c r="K22" s="461"/>
+      <c r="L22" s="457"/>
+      <c r="M22" s="462"/>
+      <c r="N22" s="442"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="298"/>
-      <c r="B23" s="303"/>
-      <c r="C23" s="304"/>
-      <c r="D23" s="372"/>
+      <c r="A23" s="296"/>
+      <c r="B23" s="301"/>
+      <c r="C23" s="302"/>
+      <c r="D23" s="370"/>
       <c r="E23" s="282"/>
       <c r="F23" s="280"/>
       <c r="G23" s="280"/>
       <c r="H23" s="280"/>
       <c r="I23" s="280"/>
-      <c r="J23" s="420"/>
-      <c r="K23" s="371"/>
-      <c r="L23" s="459"/>
-      <c r="M23" s="445"/>
-      <c r="N23" s="444"/>
+      <c r="J23" s="418"/>
+      <c r="K23" s="369"/>
+      <c r="L23" s="457"/>
+      <c r="M23" s="443"/>
+      <c r="N23" s="442"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="298"/>
-      <c r="B24" s="303"/>
-      <c r="C24" s="304"/>
-      <c r="D24" s="304"/>
-      <c r="E24" s="349"/>
+      <c r="A24" s="296"/>
+      <c r="B24" s="301"/>
+      <c r="C24" s="302"/>
+      <c r="D24" s="302"/>
+      <c r="E24" s="347"/>
       <c r="F24" s="269"/>
       <c r="G24" s="269"/>
       <c r="H24" s="269"/>
       <c r="I24" s="269"/>
       <c r="J24" s="269"/>
       <c r="K24" s="285"/>
-      <c r="L24" s="403"/>
-      <c r="M24" s="444"/>
-      <c r="N24" s="444"/>
+      <c r="L24" s="401"/>
+      <c r="M24" s="442"/>
+      <c r="N24" s="442"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="298"/>
-      <c r="B25" s="305"/>
-      <c r="C25" s="304"/>
-      <c r="D25" s="304"/>
-      <c r="E25" s="349"/>
+      <c r="A25" s="296"/>
+      <c r="B25" s="303"/>
+      <c r="C25" s="302"/>
+      <c r="D25" s="302"/>
+      <c r="E25" s="347"/>
       <c r="F25" s="269"/>
       <c r="G25" s="269"/>
       <c r="H25" s="269"/>
       <c r="I25" s="269"/>
       <c r="J25" s="269"/>
-      <c r="K25" s="400"/>
-      <c r="L25" s="367"/>
-      <c r="M25" s="444"/>
+      <c r="K25" s="398"/>
+      <c r="L25" s="365"/>
+      <c r="M25" s="442"/>
       <c r="N25" s="269"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="298"/>
-      <c r="B26" s="305"/>
-      <c r="C26" s="304"/>
-      <c r="D26" s="304"/>
-      <c r="E26" s="349"/>
+      <c r="A26" s="296"/>
+      <c r="B26" s="303"/>
+      <c r="C26" s="302"/>
+      <c r="D26" s="302"/>
+      <c r="E26" s="347"/>
       <c r="F26" s="269"/>
       <c r="G26" s="269"/>
       <c r="H26" s="269"/>
       <c r="I26" s="269"/>
       <c r="J26" s="269"/>
-      <c r="K26" s="400"/>
-      <c r="L26" s="475"/>
-      <c r="M26" s="444"/>
+      <c r="K26" s="398"/>
+      <c r="L26" s="470"/>
+      <c r="M26" s="442"/>
       <c r="N26" s="269"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="362"/>
-      <c r="B27" s="363"/>
-      <c r="C27" s="304"/>
+      <c r="A27" s="360"/>
+      <c r="B27" s="361"/>
+      <c r="C27" s="302"/>
       <c r="D27" s="280"/>
       <c r="E27" s="275"/>
       <c r="F27" s="269"/>
@@ -4932,40 +4933,40 @@
       <c r="H27" s="269"/>
       <c r="I27" s="269"/>
       <c r="J27" s="269"/>
-      <c r="K27" s="474"/>
-      <c r="L27" s="367"/>
-      <c r="M27" s="444"/>
+      <c r="K27" s="469"/>
+      <c r="L27" s="365"/>
+      <c r="M27" s="442"/>
       <c r="N27" s="269"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="275"/>
       <c r="B28" s="271"/>
-      <c r="C28" s="383"/>
-      <c r="D28" s="344"/>
-      <c r="E28" s="439"/>
+      <c r="C28" s="381"/>
+      <c r="D28" s="342"/>
+      <c r="E28" s="437"/>
       <c r="F28" s="269"/>
       <c r="G28" s="269"/>
       <c r="H28" s="269"/>
       <c r="I28" s="269"/>
       <c r="J28" s="269"/>
-      <c r="K28" s="399"/>
-      <c r="L28" s="476"/>
+      <c r="K28" s="397"/>
+      <c r="L28" s="471"/>
       <c r="N28" s="269"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="384"/>
+      <c r="A29" s="382"/>
       <c r="B29" s="269"/>
-      <c r="C29" s="385"/>
-      <c r="D29" s="386"/>
-      <c r="E29" s="440"/>
+      <c r="C29" s="383"/>
+      <c r="D29" s="384"/>
+      <c r="E29" s="438"/>
       <c r="F29" s="269"/>
       <c r="G29" s="269"/>
       <c r="H29" s="269"/>
       <c r="I29" s="269"/>
       <c r="J29" s="269"/>
-      <c r="K29" s="472"/>
-      <c r="L29" s="473"/>
-      <c r="M29" s="444"/>
+      <c r="K29" s="467"/>
+      <c r="L29" s="468"/>
+      <c r="M29" s="442"/>
       <c r="N29" s="269"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -4979,9 +4980,9 @@
       <c r="H30" s="269"/>
       <c r="I30" s="269"/>
       <c r="J30" s="269"/>
-      <c r="K30" s="398"/>
+      <c r="K30" s="396"/>
       <c r="L30" s="269"/>
-      <c r="M30" s="444"/>
+      <c r="M30" s="442"/>
       <c r="N30" s="269"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -4989,15 +4990,15 @@
       <c r="B31" s="269"/>
       <c r="C31" s="269"/>
       <c r="D31" s="280"/>
-      <c r="E31" s="349" t="s">
-        <v>196</v>
-      </c>
-      <c r="F31" s="386"/>
-      <c r="G31" s="386"/>
-      <c r="H31" s="419"/>
+      <c r="E31" s="347" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="384"/>
+      <c r="G31" s="384"/>
+      <c r="H31" s="417"/>
       <c r="I31" s="269"/>
       <c r="J31" s="269"/>
-      <c r="K31" s="398"/>
+      <c r="K31" s="396"/>
       <c r="L31" s="269"/>
       <c r="M31" s="248"/>
       <c r="N31" s="51"/>
@@ -5007,10 +5008,10 @@
       <c r="B32" s="269"/>
       <c r="C32" s="269"/>
       <c r="D32" s="280"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="386"/>
-      <c r="G32" s="419"/>
-      <c r="H32" s="419"/>
+      <c r="E32" s="347"/>
+      <c r="F32" s="384"/>
+      <c r="G32" s="417"/>
+      <c r="H32" s="417"/>
       <c r="I32" s="269"/>
       <c r="J32" s="269"/>
       <c r="K32" s="269"/>
@@ -5022,18 +5023,18 @@
       <c r="A33" s="269"/>
       <c r="B33" s="269"/>
       <c r="C33" s="269"/>
-      <c r="D33" s="429"/>
-      <c r="E33" s="430" t="s">
+      <c r="D33" s="427"/>
+      <c r="E33" s="428" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33" s="417" t="s">
         <v>197</v>
       </c>
-      <c r="F33" s="419" t="s">
+      <c r="G33" s="417" t="s">
         <v>198</v>
       </c>
-      <c r="G33" s="419" t="s">
+      <c r="H33" s="417" t="s">
         <v>199</v>
-      </c>
-      <c r="H33" s="419" t="s">
-        <v>200</v>
       </c>
       <c r="I33" s="269"/>
       <c r="J33" s="269"/>
@@ -5046,19 +5047,19 @@
       <c r="A34" s="269"/>
       <c r="B34" s="269"/>
       <c r="C34" s="269"/>
-      <c r="D34" s="420" t="s">
-        <v>201</v>
-      </c>
-      <c r="E34" s="423">
+      <c r="D34" s="418" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34" s="421">
         <v>466976.92</v>
       </c>
-      <c r="F34" s="441">
+      <c r="F34" s="439">
         <v>99774</v>
       </c>
-      <c r="G34" s="419">
+      <c r="G34" s="417">
         <v>5</v>
       </c>
-      <c r="H34" s="442">
+      <c r="H34" s="440">
         <v>20</v>
       </c>
       <c r="I34" s="277"/>
@@ -5072,19 +5073,19 @@
       <c r="A35" s="269"/>
       <c r="B35" s="269"/>
       <c r="C35" s="269"/>
-      <c r="D35" s="420" t="s">
-        <v>201</v>
-      </c>
-      <c r="E35" s="427">
+      <c r="D35" s="418" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="425">
         <v>815680.37</v>
       </c>
-      <c r="F35" s="424">
+      <c r="F35" s="422">
         <v>66925</v>
       </c>
-      <c r="G35" s="421">
+      <c r="G35" s="419">
         <v>31</v>
       </c>
-      <c r="H35" s="421">
+      <c r="H35" s="419">
         <v>7</v>
       </c>
       <c r="I35" s="277"/>
@@ -5098,19 +5099,19 @@
       <c r="A36" s="269"/>
       <c r="B36" s="269"/>
       <c r="C36" s="269"/>
-      <c r="D36" s="420" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="428">
+      <c r="D36" s="418" t="s">
+        <v>200</v>
+      </c>
+      <c r="E36" s="426">
         <v>3073505.09</v>
       </c>
-      <c r="F36" s="428">
+      <c r="F36" s="426">
         <v>235159</v>
       </c>
-      <c r="G36" s="419">
+      <c r="G36" s="417">
         <v>25</v>
       </c>
-      <c r="H36" s="419">
+      <c r="H36" s="417">
         <v>20</v>
       </c>
       <c r="I36" s="277"/>
@@ -5125,12 +5126,12 @@
       <c r="B37" s="269"/>
       <c r="C37" s="269"/>
       <c r="D37" s="286" t="s">
-        <v>202</v>
-      </c>
-      <c r="E37" s="425">
+        <v>201</v>
+      </c>
+      <c r="E37" s="423">
         <v>698529.91</v>
       </c>
-      <c r="F37" s="425">
+      <c r="F37" s="423">
         <v>69852.990000000005</v>
       </c>
       <c r="G37" s="277">
@@ -5148,12 +5149,12 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="268"/>
-      <c r="B38" s="298"/>
-      <c r="C38" s="304"/>
+      <c r="B38" s="296"/>
+      <c r="C38" s="302"/>
       <c r="D38" s="286" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" s="425">
+        <v>201</v>
+      </c>
+      <c r="E38" s="423">
         <v>98848.21</v>
       </c>
       <c r="F38" s="275">
@@ -5165,388 +5166,388 @@
       <c r="H38" s="277">
         <v>15</v>
       </c>
-      <c r="I38" s="422"/>
-      <c r="J38" s="420"/>
-      <c r="K38" s="349"/>
-      <c r="L38" s="455"/>
+      <c r="I38" s="420"/>
+      <c r="J38" s="418"/>
+      <c r="K38" s="347"/>
+      <c r="L38" s="453"/>
       <c r="M38" s="248"/>
       <c r="N38" s="51"/>
     </row>
     <row r="39" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="300"/>
-      <c r="B39" s="298"/>
-      <c r="C39" s="307"/>
-      <c r="D39" s="431" t="s">
-        <v>203</v>
-      </c>
-      <c r="E39" s="437">
+      <c r="A39" s="298"/>
+      <c r="B39" s="296"/>
+      <c r="C39" s="305"/>
+      <c r="D39" s="429" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" s="435">
         <v>746515</v>
       </c>
-      <c r="F39" s="434">
+      <c r="F39" s="432">
         <v>122867</v>
       </c>
       <c r="G39" s="277">
         <v>11</v>
       </c>
-      <c r="H39" s="432">
+      <c r="H39" s="430">
         <v>5</v>
       </c>
-      <c r="I39" s="306"/>
+      <c r="I39" s="304"/>
       <c r="J39" s="280"/>
-      <c r="K39" s="349"/>
-      <c r="L39" s="455"/>
+      <c r="K39" s="347"/>
+      <c r="L39" s="453"/>
       <c r="M39" s="248"/>
       <c r="N39" s="51"/>
     </row>
     <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="300"/>
-      <c r="B40" s="298"/>
-      <c r="C40" s="304"/>
-      <c r="D40" s="436"/>
-      <c r="E40" s="435">
+      <c r="A40" s="298"/>
+      <c r="B40" s="296"/>
+      <c r="C40" s="302"/>
+      <c r="D40" s="434"/>
+      <c r="E40" s="433">
         <f>SUM(E34:E39)</f>
         <v>5900055.5</v>
       </c>
-      <c r="F40" s="435">
+      <c r="F40" s="433">
         <f>SUM(F34:F39)</f>
         <v>608417.99</v>
       </c>
-      <c r="G40" s="433"/>
+      <c r="G40" s="431"/>
       <c r="H40" s="277"/>
-      <c r="I40" s="306"/>
+      <c r="I40" s="304"/>
       <c r="J40" s="280"/>
-      <c r="K40" s="349"/>
-      <c r="L40" s="455"/>
+      <c r="K40" s="347"/>
+      <c r="L40" s="453"/>
       <c r="M40" s="248"/>
       <c r="N40" s="51"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="308"/>
-      <c r="B41" s="298"/>
-      <c r="C41" s="304"/>
-      <c r="D41" s="306"/>
+      <c r="A41" s="306"/>
+      <c r="B41" s="296"/>
+      <c r="C41" s="302"/>
+      <c r="D41" s="304"/>
       <c r="E41" s="280"/>
-      <c r="F41" s="430"/>
-      <c r="G41" s="423"/>
+      <c r="F41" s="428"/>
+      <c r="G41" s="421"/>
       <c r="H41" s="280"/>
-      <c r="I41" s="306"/>
+      <c r="I41" s="304"/>
       <c r="J41" s="280"/>
-      <c r="K41" s="349"/>
-      <c r="L41" s="455"/>
+      <c r="K41" s="347"/>
+      <c r="L41" s="453"/>
       <c r="M41" s="248"/>
       <c r="N41" s="51"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="300">
+      <c r="A42" s="298">
         <v>387</v>
       </c>
-      <c r="B42" s="298"/>
-      <c r="C42" s="304"/>
-      <c r="D42" s="306"/>
+      <c r="B42" s="296"/>
+      <c r="C42" s="302"/>
+      <c r="D42" s="304"/>
       <c r="E42" s="280"/>
-      <c r="F42" s="420"/>
-      <c r="G42" s="423"/>
+      <c r="F42" s="418"/>
+      <c r="G42" s="421"/>
       <c r="H42" s="280"/>
       <c r="I42" s="280"/>
       <c r="J42" s="280"/>
-      <c r="K42" s="349"/>
-      <c r="L42" s="455"/>
+      <c r="K42" s="347"/>
+      <c r="L42" s="453"/>
       <c r="M42" s="248"/>
       <c r="N42" s="51"/>
     </row>
     <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="300"/>
-      <c r="B43" s="298"/>
-      <c r="C43" s="304"/>
-      <c r="D43" s="306"/>
+      <c r="A43" s="298"/>
+      <c r="B43" s="296"/>
+      <c r="C43" s="302"/>
+      <c r="D43" s="304"/>
       <c r="E43" s="280"/>
-      <c r="F43" s="420"/>
-      <c r="G43" s="424"/>
+      <c r="F43" s="418"/>
+      <c r="G43" s="422"/>
       <c r="H43" s="280"/>
       <c r="I43" s="280"/>
       <c r="J43" s="268"/>
-      <c r="K43" s="349"/>
-      <c r="L43" s="455"/>
+      <c r="K43" s="347"/>
+      <c r="L43" s="453"/>
       <c r="M43" s="248"/>
       <c r="N43" s="51"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="300"/>
-      <c r="B44" s="298"/>
-      <c r="C44" s="304"/>
-      <c r="D44" s="309"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="421"/>
-      <c r="G44" s="426" t="s">
+      <c r="A44" s="298"/>
+      <c r="B44" s="296"/>
+      <c r="C44" s="302"/>
+      <c r="D44" s="307"/>
+      <c r="E44" s="342"/>
+      <c r="F44" s="419"/>
+      <c r="G44" s="424" t="s">
         <v>24</v>
       </c>
-      <c r="H44" s="309"/>
-      <c r="I44" s="309"/>
+      <c r="H44" s="307"/>
+      <c r="I44" s="307"/>
       <c r="J44" s="280"/>
-      <c r="K44" s="349"/>
-      <c r="L44" s="455"/>
+      <c r="K44" s="347"/>
+      <c r="L44" s="453"/>
       <c r="M44" s="248"/>
       <c r="N44" s="51"/>
     </row>
     <row r="45" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="300"/>
-      <c r="B45" s="310" t="s">
+      <c r="A45" s="298"/>
+      <c r="B45" s="308" t="s">
         <v>188</v>
       </c>
-      <c r="C45" s="311"/>
-      <c r="D45" s="333"/>
+      <c r="C45" s="309"/>
+      <c r="D45" s="331"/>
       <c r="E45" s="280"/>
-      <c r="F45" s="341" t="s">
+      <c r="F45" s="339" t="s">
         <v>183</v>
       </c>
-      <c r="G45" s="316" t="s">
+      <c r="G45" s="314" t="s">
         <v>176</v>
       </c>
-      <c r="H45" s="312" t="s">
+      <c r="H45" s="310" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="313" t="s">
+      <c r="I45" s="311" t="s">
         <v>21</v>
       </c>
-      <c r="J45" s="306"/>
-      <c r="K45" s="349"/>
-      <c r="L45" s="455"/>
+      <c r="J45" s="304"/>
+      <c r="K45" s="347"/>
+      <c r="L45" s="453"/>
       <c r="M45" s="248"/>
       <c r="N45" s="51"/>
     </row>
     <row r="46" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="304"/>
-      <c r="B46" s="314"/>
-      <c r="C46" s="315"/>
+      <c r="A46" s="302"/>
+      <c r="B46" s="312"/>
+      <c r="C46" s="313"/>
       <c r="D46" s="271"/>
       <c r="E46" s="280"/>
-      <c r="F46" s="342"/>
-      <c r="G46" s="320"/>
-      <c r="H46" s="317" t="s">
+      <c r="F46" s="340"/>
+      <c r="G46" s="318"/>
+      <c r="H46" s="315" t="s">
         <v>176</v>
       </c>
-      <c r="I46" s="318" t="s">
+      <c r="I46" s="316" t="s">
         <v>176</v>
       </c>
-      <c r="J46" s="306"/>
-      <c r="K46" s="349"/>
-      <c r="L46" s="455"/>
+      <c r="J46" s="304"/>
+      <c r="K46" s="347"/>
+      <c r="L46" s="453"/>
       <c r="M46" s="248"/>
       <c r="N46" s="51"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="304"/>
-      <c r="B47" s="319" t="s">
+      <c r="A47" s="302"/>
+      <c r="B47" s="317" t="s">
         <v>172</v>
       </c>
       <c r="C47" s="271"/>
       <c r="D47" s="268"/>
       <c r="E47" s="280"/>
-      <c r="F47" s="343" t="s">
+      <c r="F47" s="341" t="s">
         <v>194</v>
       </c>
-      <c r="G47" s="323"/>
-      <c r="H47" s="321"/>
+      <c r="G47" s="321"/>
+      <c r="H47" s="319"/>
       <c r="I47" s="279"/>
       <c r="J47" s="280"/>
-      <c r="K47" s="349"/>
-      <c r="L47" s="455"/>
+      <c r="K47" s="347"/>
+      <c r="L47" s="453"/>
       <c r="M47" s="248"/>
       <c r="N47" s="51"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="305"/>
-      <c r="B48" s="319" t="s">
+      <c r="A48" s="303"/>
+      <c r="B48" s="317" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="354"/>
+      <c r="C48" s="352"/>
       <c r="D48" s="268"/>
-      <c r="E48" s="298"/>
-      <c r="F48" s="337" t="s">
+      <c r="E48" s="296"/>
+      <c r="F48" s="335" t="s">
         <v>186</v>
       </c>
-      <c r="G48" s="323"/>
-      <c r="H48" s="324"/>
-      <c r="I48" s="298"/>
-      <c r="J48" s="298"/>
-      <c r="K48" s="325"/>
-      <c r="L48" s="455"/>
+      <c r="G48" s="321"/>
+      <c r="H48" s="322"/>
+      <c r="I48" s="296"/>
+      <c r="J48" s="296"/>
+      <c r="K48" s="323"/>
+      <c r="L48" s="453"/>
       <c r="M48" s="281"/>
       <c r="N48" s="51"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="305"/>
-      <c r="B49" s="319" t="s">
+      <c r="A49" s="303"/>
+      <c r="B49" s="317" t="s">
         <v>173</v>
       </c>
-      <c r="C49" s="354"/>
+      <c r="C49" s="352"/>
       <c r="D49" s="268"/>
-      <c r="E49" s="298"/>
-      <c r="F49" s="337" t="s">
+      <c r="E49" s="296"/>
+      <c r="F49" s="335" t="s">
         <v>187</v>
       </c>
-      <c r="G49" s="323"/>
-      <c r="H49" s="324"/>
-      <c r="I49" s="298"/>
-      <c r="J49" s="298"/>
-      <c r="K49" s="352"/>
-      <c r="L49" s="455"/>
+      <c r="G49" s="321"/>
+      <c r="H49" s="322"/>
+      <c r="I49" s="296"/>
+      <c r="J49" s="296"/>
+      <c r="K49" s="350"/>
+      <c r="L49" s="453"/>
       <c r="M49" s="281"/>
       <c r="N49" s="51"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="305"/>
-      <c r="B50" s="319" t="s">
+      <c r="A50" s="303"/>
+      <c r="B50" s="317" t="s">
         <v>174</v>
       </c>
-      <c r="C50" s="354"/>
+      <c r="C50" s="352"/>
       <c r="D50" s="268"/>
-      <c r="E50" s="298"/>
-      <c r="F50" s="337" t="s">
+      <c r="E50" s="296"/>
+      <c r="F50" s="335" t="s">
         <v>177</v>
       </c>
-      <c r="G50" s="323"/>
-      <c r="H50" s="324"/>
-      <c r="I50" s="298"/>
-      <c r="J50" s="298"/>
-      <c r="K50" s="352"/>
-      <c r="L50" s="455"/>
+      <c r="G50" s="321"/>
+      <c r="H50" s="322"/>
+      <c r="I50" s="296"/>
+      <c r="J50" s="296"/>
+      <c r="K50" s="350"/>
+      <c r="L50" s="453"/>
       <c r="M50" s="281"/>
       <c r="N50" s="51"/>
     </row>
     <row r="51" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="305"/>
-      <c r="B51" s="340" t="s">
+      <c r="A51" s="303"/>
+      <c r="B51" s="338" t="s">
         <v>175</v>
       </c>
-      <c r="C51" s="356"/>
-      <c r="D51" s="300"/>
-      <c r="E51" s="298"/>
-      <c r="F51" s="337" t="s">
+      <c r="C51" s="354"/>
+      <c r="D51" s="298"/>
+      <c r="E51" s="296"/>
+      <c r="F51" s="335" t="s">
         <v>179</v>
       </c>
-      <c r="G51" s="327"/>
-      <c r="H51" s="324"/>
-      <c r="I51" s="298"/>
-      <c r="J51" s="298"/>
-      <c r="K51" s="352"/>
-      <c r="L51" s="455"/>
+      <c r="G51" s="325"/>
+      <c r="H51" s="322"/>
+      <c r="I51" s="296"/>
+      <c r="J51" s="296"/>
+      <c r="K51" s="350"/>
+      <c r="L51" s="453"/>
       <c r="M51" s="281"/>
       <c r="N51" s="51"/>
     </row>
     <row r="52" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="334"/>
-      <c r="B52" s="326" t="s">
+      <c r="A52" s="332"/>
+      <c r="B52" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="360"/>
-      <c r="D52" s="358"/>
-      <c r="E52" s="298"/>
-      <c r="F52" s="337" t="s">
+      <c r="C52" s="358"/>
+      <c r="D52" s="356"/>
+      <c r="E52" s="296"/>
+      <c r="F52" s="335" t="s">
         <v>180</v>
       </c>
-      <c r="G52" s="329"/>
-      <c r="H52" s="328"/>
-      <c r="I52" s="298"/>
-      <c r="J52" s="298"/>
-      <c r="K52" s="334"/>
-      <c r="L52" s="455"/>
+      <c r="G52" s="327"/>
+      <c r="H52" s="326"/>
+      <c r="I52" s="296"/>
+      <c r="J52" s="296"/>
+      <c r="K52" s="332"/>
+      <c r="L52" s="453"/>
       <c r="M52" s="281"/>
       <c r="N52" s="51"/>
     </row>
     <row r="53" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="334"/>
-      <c r="B53" s="315"/>
-      <c r="C53" s="359"/>
-      <c r="D53" s="298"/>
-      <c r="E53" s="298"/>
-      <c r="F53" s="338" t="s">
+      <c r="A53" s="332"/>
+      <c r="B53" s="313"/>
+      <c r="C53" s="357"/>
+      <c r="D53" s="296"/>
+      <c r="E53" s="296"/>
+      <c r="F53" s="336" t="s">
         <v>178</v>
       </c>
-      <c r="G53" s="315"/>
-      <c r="H53" s="330"/>
-      <c r="I53" s="299"/>
-      <c r="J53" s="298"/>
-      <c r="K53" s="352"/>
-      <c r="L53" s="455"/>
+      <c r="G53" s="313"/>
+      <c r="H53" s="328"/>
+      <c r="I53" s="297"/>
+      <c r="J53" s="296"/>
+      <c r="K53" s="350"/>
+      <c r="L53" s="453"/>
       <c r="M53" s="281"/>
       <c r="N53" s="51"/>
     </row>
     <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="335"/>
-      <c r="B54" s="298"/>
-      <c r="C54" s="298"/>
-      <c r="D54" s="298"/>
-      <c r="E54" s="298"/>
-      <c r="F54" s="299"/>
-      <c r="G54" s="331" t="s">
+      <c r="A54" s="333"/>
+      <c r="B54" s="296"/>
+      <c r="C54" s="296"/>
+      <c r="D54" s="296"/>
+      <c r="E54" s="296"/>
+      <c r="F54" s="297"/>
+      <c r="G54" s="329" t="s">
         <v>176</v>
       </c>
-      <c r="H54" s="315"/>
-      <c r="I54" s="298"/>
-      <c r="J54" s="298"/>
-      <c r="K54" s="353"/>
-      <c r="L54" s="455"/>
+      <c r="H54" s="313"/>
+      <c r="I54" s="296"/>
+      <c r="J54" s="296"/>
+      <c r="K54" s="351"/>
+      <c r="L54" s="453"/>
       <c r="M54" s="281"/>
       <c r="N54" s="51"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="336"/>
-      <c r="B55" s="298"/>
-      <c r="C55" s="298"/>
-      <c r="D55" s="298"/>
-      <c r="E55" s="298"/>
-      <c r="F55" s="339"/>
-      <c r="G55" s="298"/>
-      <c r="H55" s="331" t="s">
+      <c r="A55" s="334"/>
+      <c r="B55" s="296"/>
+      <c r="C55" s="296"/>
+      <c r="D55" s="296"/>
+      <c r="E55" s="296"/>
+      <c r="F55" s="337"/>
+      <c r="G55" s="296"/>
+      <c r="H55" s="329" t="s">
         <v>176</v>
       </c>
       <c r="I55" s="268"/>
-      <c r="J55" s="298"/>
-      <c r="K55" s="351"/>
-      <c r="L55" s="455"/>
+      <c r="J55" s="296"/>
+      <c r="K55" s="349"/>
+      <c r="L55" s="453"/>
       <c r="M55" s="281"/>
       <c r="N55" s="51"/>
     </row>
     <row r="56" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="336"/>
-      <c r="B56" s="298"/>
-      <c r="C56" s="298"/>
-      <c r="D56" s="298"/>
-      <c r="E56" s="298"/>
-      <c r="F56" s="299"/>
+      <c r="A56" s="334"/>
+      <c r="B56" s="296"/>
+      <c r="C56" s="296"/>
+      <c r="D56" s="296"/>
+      <c r="E56" s="296"/>
+      <c r="F56" s="297"/>
       <c r="G56" s="269"/>
-      <c r="H56" s="298"/>
+      <c r="H56" s="296"/>
       <c r="I56" s="268"/>
-      <c r="J56" s="298"/>
-      <c r="K56" s="325"/>
-      <c r="L56" s="456"/>
+      <c r="J56" s="296"/>
+      <c r="K56" s="323"/>
+      <c r="L56" s="454"/>
       <c r="M56" s="281"/>
       <c r="N56" s="51"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="443"/>
+      <c r="A57" s="441"/>
       <c r="B57" s="269"/>
       <c r="C57" s="269"/>
       <c r="D57" s="269"/>
       <c r="E57" s="269"/>
-      <c r="F57" s="444"/>
+      <c r="F57" s="442"/>
       <c r="G57" s="277"/>
       <c r="H57" s="269"/>
       <c r="I57" s="198"/>
       <c r="J57" s="269"/>
       <c r="K57" s="269"/>
-      <c r="L57" s="445"/>
+      <c r="L57" s="443"/>
       <c r="M57" s="87"/>
       <c r="N57" s="51"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="443"/>
+      <c r="A58" s="441"/>
       <c r="B58" s="269"/>
       <c r="C58" s="269"/>
       <c r="D58" s="269"/>
       <c r="E58" s="277"/>
-      <c r="F58" s="446"/>
+      <c r="F58" s="444"/>
       <c r="G58" s="277"/>
       <c r="H58" s="277"/>
       <c r="I58" s="198"/>
@@ -5557,7 +5558,7 @@
       <c r="N58" s="51"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="443"/>
+      <c r="A59" s="441"/>
       <c r="B59" s="269"/>
       <c r="C59" s="269"/>
       <c r="D59" s="269"/>
@@ -5573,7 +5574,7 @@
       <c r="N59" s="51"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="443"/>
+      <c r="A60" s="441"/>
       <c r="B60" s="269"/>
       <c r="C60" s="269"/>
       <c r="D60" s="269"/>
@@ -5581,7 +5582,7 @@
       <c r="F60" s="277"/>
       <c r="G60" s="277"/>
       <c r="H60" s="277"/>
-      <c r="I60" s="290"/>
+      <c r="I60" s="289"/>
       <c r="J60" s="269"/>
       <c r="K60" s="269"/>
       <c r="L60" s="269"/>
@@ -5589,7 +5590,7 @@
       <c r="N60" s="51"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="443"/>
+      <c r="A61" s="441"/>
       <c r="B61" s="269"/>
       <c r="C61" s="269"/>
       <c r="D61" s="269"/>
@@ -5597,7 +5598,7 @@
       <c r="F61" s="277"/>
       <c r="G61" s="277"/>
       <c r="H61" s="277"/>
-      <c r="I61" s="290"/>
+      <c r="I61" s="289"/>
       <c r="J61" s="269"/>
       <c r="K61" s="269"/>
       <c r="L61" s="269"/>
@@ -5605,8 +5606,8 @@
       <c r="N61" s="51"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="448"/>
-      <c r="B62" s="449"/>
+      <c r="A62" s="446"/>
+      <c r="B62" s="447"/>
       <c r="C62" s="269"/>
       <c r="D62" s="269"/>
       <c r="E62" s="277"/>
@@ -5622,12 +5623,12 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="283"/>
-      <c r="B63" s="449"/>
+      <c r="B63" s="447"/>
       <c r="C63" s="269"/>
       <c r="D63" s="269"/>
       <c r="E63" s="277"/>
       <c r="F63" s="277"/>
-      <c r="G63" s="454"/>
+      <c r="G63" s="452"/>
       <c r="H63" s="286"/>
       <c r="I63" s="277"/>
       <c r="J63" s="269"/>
@@ -5638,15 +5639,15 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="283"/>
-      <c r="B64" s="449"/>
+      <c r="B64" s="447"/>
       <c r="C64" s="269"/>
       <c r="D64" s="269"/>
       <c r="E64" s="269"/>
-      <c r="F64" s="454"/>
+      <c r="F64" s="452"/>
       <c r="G64" s="269"/>
-      <c r="H64" s="454"/>
-      <c r="I64" s="454"/>
-      <c r="J64" s="454"/>
+      <c r="H64" s="452"/>
+      <c r="I64" s="452"/>
+      <c r="J64" s="452"/>
       <c r="K64" s="269"/>
       <c r="L64" s="269"/>
       <c r="M64" s="87"/>
@@ -5692,7 +5693,7 @@
       <c r="E67" s="269"/>
       <c r="F67" s="269"/>
       <c r="G67" s="269"/>
-      <c r="H67" s="367"/>
+      <c r="H67" s="365"/>
       <c r="I67" s="269"/>
       <c r="J67" s="269"/>
       <c r="K67" s="269"/>
@@ -5708,7 +5709,7 @@
       <c r="E68" s="269"/>
       <c r="F68" s="269"/>
       <c r="G68" s="269"/>
-      <c r="H68" s="367"/>
+      <c r="H68" s="365"/>
       <c r="I68" s="269"/>
       <c r="J68" s="269"/>
       <c r="K68" s="269"/>
@@ -5724,7 +5725,7 @@
       <c r="E69" s="269"/>
       <c r="F69" s="269"/>
       <c r="G69" s="269"/>
-      <c r="H69" s="367"/>
+      <c r="H69" s="365"/>
       <c r="I69" s="269"/>
       <c r="J69" s="269"/>
       <c r="K69" s="269"/>
@@ -5740,9 +5741,9 @@
       <c r="E70" s="269"/>
       <c r="F70" s="269"/>
       <c r="G70" s="269"/>
-      <c r="H70" s="367"/>
+      <c r="H70" s="365"/>
       <c r="I70" s="269"/>
-      <c r="J70" s="367"/>
+      <c r="J70" s="365"/>
       <c r="K70" s="269"/>
       <c r="L70" s="269"/>
       <c r="M70" s="87"/>
@@ -5756,7 +5757,7 @@
       <c r="E71" s="269"/>
       <c r="F71" s="269"/>
       <c r="G71" s="269"/>
-      <c r="H71" s="367"/>
+      <c r="H71" s="365"/>
       <c r="I71" s="269"/>
       <c r="J71" s="269"/>
       <c r="K71" s="269"/>
@@ -5772,8 +5773,8 @@
       <c r="E72" s="269"/>
       <c r="F72" s="269"/>
       <c r="G72" s="269"/>
-      <c r="H72" s="367"/>
-      <c r="I72" s="450"/>
+      <c r="H72" s="365"/>
+      <c r="I72" s="448"/>
       <c r="J72" s="269"/>
       <c r="K72" s="269"/>
       <c r="L72" s="269"/>
@@ -5789,7 +5790,7 @@
       <c r="F73" s="269"/>
       <c r="G73" s="269"/>
       <c r="H73" s="198"/>
-      <c r="I73" s="450"/>
+      <c r="I73" s="448"/>
       <c r="J73" s="269"/>
       <c r="K73" s="269"/>
       <c r="L73" s="269"/>
@@ -5805,7 +5806,7 @@
       <c r="F74" s="269"/>
       <c r="G74" s="269"/>
       <c r="H74" s="198"/>
-      <c r="I74" s="450"/>
+      <c r="I74" s="448"/>
       <c r="J74" s="269"/>
       <c r="K74" s="269"/>
       <c r="L74" s="269"/>
@@ -5820,8 +5821,8 @@
       <c r="E75" s="269"/>
       <c r="F75" s="269"/>
       <c r="G75" s="269"/>
-      <c r="H75" s="367"/>
-      <c r="I75" s="450"/>
+      <c r="H75" s="365"/>
+      <c r="I75" s="448"/>
       <c r="J75" s="269"/>
       <c r="K75" s="269"/>
       <c r="L75" s="269"/>
@@ -5834,10 +5835,10 @@
       <c r="C76" s="269"/>
       <c r="D76" s="269"/>
       <c r="E76" s="269"/>
-      <c r="F76" s="447"/>
-      <c r="G76" s="451"/>
-      <c r="H76" s="452"/>
-      <c r="I76" s="450"/>
+      <c r="F76" s="445"/>
+      <c r="G76" s="449"/>
+      <c r="H76" s="450"/>
+      <c r="I76" s="448"/>
       <c r="J76" s="269"/>
       <c r="K76" s="269"/>
       <c r="L76" s="269"/>
@@ -5851,9 +5852,9 @@
       <c r="D77" s="269"/>
       <c r="E77" s="283"/>
       <c r="F77" s="269"/>
-      <c r="G77" s="450"/>
-      <c r="H77" s="367"/>
-      <c r="I77" s="444"/>
+      <c r="G77" s="448"/>
+      <c r="H77" s="365"/>
+      <c r="I77" s="442"/>
       <c r="J77" s="269"/>
       <c r="K77" s="269"/>
       <c r="L77" s="269"/>
@@ -5866,10 +5867,10 @@
       <c r="C78" s="269"/>
       <c r="D78" s="198"/>
       <c r="E78" s="269"/>
-      <c r="F78" s="445"/>
+      <c r="F78" s="443"/>
       <c r="G78" s="269"/>
-      <c r="H78" s="453"/>
-      <c r="I78" s="454"/>
+      <c r="H78" s="451"/>
+      <c r="I78" s="452"/>
       <c r="J78" s="269"/>
       <c r="K78" s="269"/>
       <c r="L78" s="269"/>
@@ -5884,7 +5885,7 @@
       <c r="E79" s="269"/>
       <c r="F79" s="269"/>
       <c r="G79" s="269"/>
-      <c r="H79" s="454"/>
+      <c r="H79" s="452"/>
       <c r="I79" s="269"/>
       <c r="J79" s="269"/>
       <c r="K79" s="269"/>
@@ -5900,7 +5901,7 @@
       <c r="E80" s="269"/>
       <c r="F80" s="269"/>
       <c r="G80" s="269"/>
-      <c r="H80" s="454"/>
+      <c r="H80" s="452"/>
       <c r="I80" s="269"/>
       <c r="J80" s="269"/>
       <c r="K80" s="269"/>
@@ -5916,7 +5917,7 @@
       <c r="E81" s="269"/>
       <c r="F81" s="269"/>
       <c r="G81" s="269"/>
-      <c r="H81" s="454"/>
+      <c r="H81" s="452"/>
       <c r="I81" s="269"/>
       <c r="J81" s="269"/>
       <c r="K81" s="269"/>
@@ -5932,7 +5933,7 @@
       <c r="E82" s="269"/>
       <c r="F82" s="269"/>
       <c r="G82" s="269"/>
-      <c r="H82" s="454"/>
+      <c r="H82" s="452"/>
       <c r="I82" s="269"/>
       <c r="J82" s="269"/>
       <c r="K82" s="269"/>
@@ -5948,7 +5949,7 @@
       <c r="E83" s="269"/>
       <c r="F83" s="269"/>
       <c r="G83" s="269"/>
-      <c r="H83" s="454"/>
+      <c r="H83" s="452"/>
       <c r="I83" s="269"/>
       <c r="J83" s="269"/>
       <c r="K83" s="269"/>
@@ -5964,7 +5965,7 @@
       <c r="E84" s="269"/>
       <c r="F84" s="269"/>
       <c r="G84" s="269"/>
-      <c r="H84" s="454"/>
+      <c r="H84" s="452"/>
       <c r="I84" s="269"/>
       <c r="J84" s="269"/>
       <c r="K84" s="269"/>
@@ -5980,7 +5981,7 @@
       <c r="E85" s="269"/>
       <c r="F85" s="269"/>
       <c r="G85" s="269"/>
-      <c r="H85" s="454"/>
+      <c r="H85" s="452"/>
       <c r="I85" s="269"/>
       <c r="J85" s="269"/>
       <c r="K85" s="269"/>
@@ -5996,7 +5997,7 @@
       <c r="E86" s="269"/>
       <c r="F86" s="269"/>
       <c r="G86" s="269"/>
-      <c r="H86" s="454"/>
+      <c r="H86" s="452"/>
       <c r="I86" s="269"/>
       <c r="J86" s="269"/>
       <c r="K86" s="269"/>
@@ -6012,7 +6013,7 @@
       <c r="E87" s="269"/>
       <c r="F87" s="269"/>
       <c r="G87" s="269"/>
-      <c r="H87" s="454"/>
+      <c r="H87" s="452"/>
       <c r="I87" s="269"/>
       <c r="J87" s="269"/>
       <c r="K87" s="269"/>
@@ -6293,7 +6294,7 @@
       <c r="N104" s="51"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="298"/>
+      <c r="A105" s="296"/>
       <c r="B105" s="51"/>
       <c r="C105" s="51"/>
       <c r="D105" s="51"/>
@@ -6309,7 +6310,7 @@
       <c r="N105" s="51"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="298"/>
+      <c r="A106" s="296"/>
       <c r="B106" s="51"/>
       <c r="C106" s="51"/>
       <c r="D106" s="51"/>
@@ -6325,7 +6326,7 @@
       <c r="N106" s="51"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="298"/>
+      <c r="A107" s="296"/>
       <c r="B107" s="51"/>
       <c r="C107" s="51"/>
       <c r="D107" s="51"/>
@@ -6341,7 +6342,7 @@
       <c r="N107" s="51"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="298"/>
+      <c r="A108" s="296"/>
       <c r="B108" s="51"/>
       <c r="C108" s="51"/>
       <c r="D108" s="51"/>
@@ -6357,7 +6358,7 @@
       <c r="N108" s="51"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" s="298"/>
+      <c r="A109" s="296"/>
       <c r="B109" s="51"/>
       <c r="C109" s="51"/>
       <c r="D109" s="51"/>
@@ -6373,7 +6374,7 @@
       <c r="N109" s="51"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="298"/>
+      <c r="A110" s="296"/>
       <c r="B110" s="51"/>
       <c r="C110" s="51"/>
       <c r="D110" s="51"/>
@@ -6389,7 +6390,7 @@
       <c r="N110" s="51"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="298"/>
+      <c r="A111" s="296"/>
       <c r="B111" s="51"/>
       <c r="C111" s="51"/>
       <c r="D111" s="51"/>
@@ -6405,7 +6406,7 @@
       <c r="N111" s="51"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" s="298"/>
+      <c r="A112" s="296"/>
       <c r="B112" s="51"/>
       <c r="C112" s="51"/>
       <c r="D112" s="51"/>
@@ -6421,7 +6422,7 @@
       <c r="N112" s="51"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="298"/>
+      <c r="A113" s="296"/>
       <c r="B113" s="51"/>
       <c r="C113" s="51"/>
       <c r="D113" s="51"/>
@@ -6437,13 +6438,13 @@
       <c r="N113" s="51"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="298"/>
+      <c r="A114" s="296"/>
       <c r="B114" s="51"/>
       <c r="C114" s="51"/>
       <c r="D114" s="51"/>
       <c r="E114" s="51"/>
       <c r="F114" s="51"/>
-      <c r="G114" s="298"/>
+      <c r="G114" s="296"/>
       <c r="H114" s="51"/>
       <c r="I114" s="51"/>
       <c r="J114" s="51"/>
@@ -6453,179 +6454,179 @@
       <c r="N114" s="51"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A115" s="298"/>
-      <c r="B115" s="298"/>
-      <c r="C115" s="298"/>
-      <c r="D115" s="298"/>
-      <c r="E115" s="298"/>
-      <c r="F115" s="298"/>
-      <c r="G115" s="298"/>
-      <c r="H115" s="298"/>
-      <c r="I115" s="298"/>
-      <c r="J115" s="298"/>
-      <c r="K115" s="298"/>
-      <c r="L115" s="298"/>
-      <c r="M115" s="298"/>
+      <c r="A115" s="296"/>
+      <c r="B115" s="296"/>
+      <c r="C115" s="296"/>
+      <c r="D115" s="296"/>
+      <c r="E115" s="296"/>
+      <c r="F115" s="296"/>
+      <c r="G115" s="296"/>
+      <c r="H115" s="296"/>
+      <c r="I115" s="296"/>
+      <c r="J115" s="296"/>
+      <c r="K115" s="296"/>
+      <c r="L115" s="296"/>
+      <c r="M115" s="296"/>
       <c r="N115" s="51"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="298"/>
-      <c r="B116" s="298"/>
-      <c r="C116" s="298"/>
-      <c r="D116" s="298"/>
-      <c r="E116" s="298"/>
-      <c r="F116" s="298"/>
-      <c r="G116" s="298"/>
-      <c r="H116" s="298"/>
-      <c r="I116" s="298"/>
-      <c r="J116" s="298"/>
-      <c r="K116" s="298"/>
-      <c r="L116" s="298"/>
-      <c r="M116" s="298"/>
+      <c r="A116" s="296"/>
+      <c r="B116" s="296"/>
+      <c r="C116" s="296"/>
+      <c r="D116" s="296"/>
+      <c r="E116" s="296"/>
+      <c r="F116" s="296"/>
+      <c r="G116" s="296"/>
+      <c r="H116" s="296"/>
+      <c r="I116" s="296"/>
+      <c r="J116" s="296"/>
+      <c r="K116" s="296"/>
+      <c r="L116" s="296"/>
+      <c r="M116" s="296"/>
       <c r="N116" s="51"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="298"/>
-      <c r="B117" s="298"/>
-      <c r="C117" s="298"/>
-      <c r="D117" s="298"/>
-      <c r="E117" s="298"/>
-      <c r="F117" s="298"/>
-      <c r="G117" s="298"/>
-      <c r="H117" s="298"/>
-      <c r="I117" s="298"/>
-      <c r="J117" s="298"/>
-      <c r="K117" s="298"/>
-      <c r="L117" s="298"/>
-      <c r="M117" s="298"/>
+      <c r="A117" s="296"/>
+      <c r="B117" s="296"/>
+      <c r="C117" s="296"/>
+      <c r="D117" s="296"/>
+      <c r="E117" s="296"/>
+      <c r="F117" s="296"/>
+      <c r="G117" s="296"/>
+      <c r="H117" s="296"/>
+      <c r="I117" s="296"/>
+      <c r="J117" s="296"/>
+      <c r="K117" s="296"/>
+      <c r="L117" s="296"/>
+      <c r="M117" s="296"/>
       <c r="N117" s="51"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="298"/>
-      <c r="B118" s="298"/>
-      <c r="C118" s="298"/>
-      <c r="D118" s="298"/>
-      <c r="E118" s="298"/>
-      <c r="F118" s="298"/>
-      <c r="G118" s="298"/>
-      <c r="H118" s="298"/>
-      <c r="I118" s="298"/>
-      <c r="J118" s="298"/>
-      <c r="K118" s="298"/>
-      <c r="L118" s="298"/>
-      <c r="M118" s="298"/>
+      <c r="A118" s="296"/>
+      <c r="B118" s="296"/>
+      <c r="C118" s="296"/>
+      <c r="D118" s="296"/>
+      <c r="E118" s="296"/>
+      <c r="F118" s="296"/>
+      <c r="G118" s="296"/>
+      <c r="H118" s="296"/>
+      <c r="I118" s="296"/>
+      <c r="J118" s="296"/>
+      <c r="K118" s="296"/>
+      <c r="L118" s="296"/>
+      <c r="M118" s="296"/>
       <c r="N118" s="51"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="298"/>
-      <c r="B119" s="298"/>
-      <c r="C119" s="298"/>
-      <c r="D119" s="298"/>
-      <c r="E119" s="298"/>
-      <c r="F119" s="298"/>
-      <c r="G119" s="298"/>
-      <c r="H119" s="298"/>
-      <c r="I119" s="298"/>
-      <c r="J119" s="298"/>
-      <c r="K119" s="298"/>
-      <c r="L119" s="298"/>
-      <c r="M119" s="298"/>
+      <c r="A119" s="296"/>
+      <c r="B119" s="296"/>
+      <c r="C119" s="296"/>
+      <c r="D119" s="296"/>
+      <c r="E119" s="296"/>
+      <c r="F119" s="296"/>
+      <c r="G119" s="296"/>
+      <c r="H119" s="296"/>
+      <c r="I119" s="296"/>
+      <c r="J119" s="296"/>
+      <c r="K119" s="296"/>
+      <c r="L119" s="296"/>
+      <c r="M119" s="296"/>
       <c r="N119" s="51"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="298"/>
-      <c r="B120" s="298"/>
-      <c r="C120" s="298"/>
-      <c r="D120" s="298"/>
-      <c r="E120" s="298"/>
-      <c r="F120" s="298"/>
-      <c r="G120" s="298"/>
-      <c r="H120" s="298"/>
-      <c r="I120" s="298"/>
-      <c r="J120" s="298"/>
-      <c r="K120" s="298"/>
-      <c r="L120" s="298"/>
-      <c r="M120" s="298"/>
+      <c r="A120" s="296"/>
+      <c r="B120" s="296"/>
+      <c r="C120" s="296"/>
+      <c r="D120" s="296"/>
+      <c r="E120" s="296"/>
+      <c r="F120" s="296"/>
+      <c r="G120" s="296"/>
+      <c r="H120" s="296"/>
+      <c r="I120" s="296"/>
+      <c r="J120" s="296"/>
+      <c r="K120" s="296"/>
+      <c r="L120" s="296"/>
+      <c r="M120" s="296"/>
       <c r="N120" s="51"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="298"/>
-      <c r="B121" s="298"/>
-      <c r="C121" s="298"/>
-      <c r="D121" s="298"/>
-      <c r="E121" s="298"/>
-      <c r="F121" s="298"/>
-      <c r="G121" s="298"/>
-      <c r="H121" s="298"/>
-      <c r="I121" s="298"/>
-      <c r="J121" s="298"/>
-      <c r="K121" s="298"/>
-      <c r="L121" s="298"/>
-      <c r="M121" s="298"/>
+      <c r="A121" s="296"/>
+      <c r="B121" s="296"/>
+      <c r="C121" s="296"/>
+      <c r="D121" s="296"/>
+      <c r="E121" s="296"/>
+      <c r="F121" s="296"/>
+      <c r="G121" s="296"/>
+      <c r="H121" s="296"/>
+      <c r="I121" s="296"/>
+      <c r="J121" s="296"/>
+      <c r="K121" s="296"/>
+      <c r="L121" s="296"/>
+      <c r="M121" s="296"/>
       <c r="N121" s="51"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A122" s="298"/>
-      <c r="B122" s="298"/>
-      <c r="C122" s="298"/>
-      <c r="D122" s="298"/>
-      <c r="E122" s="298"/>
-      <c r="F122" s="298"/>
-      <c r="G122" s="298"/>
-      <c r="H122" s="298"/>
-      <c r="I122" s="298"/>
-      <c r="J122" s="298"/>
-      <c r="K122" s="298"/>
-      <c r="L122" s="298"/>
-      <c r="M122" s="298"/>
+      <c r="A122" s="296"/>
+      <c r="B122" s="296"/>
+      <c r="C122" s="296"/>
+      <c r="D122" s="296"/>
+      <c r="E122" s="296"/>
+      <c r="F122" s="296"/>
+      <c r="G122" s="296"/>
+      <c r="H122" s="296"/>
+      <c r="I122" s="296"/>
+      <c r="J122" s="296"/>
+      <c r="K122" s="296"/>
+      <c r="L122" s="296"/>
+      <c r="M122" s="296"/>
       <c r="N122" s="51"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A123" s="298"/>
-      <c r="B123" s="298"/>
-      <c r="C123" s="298"/>
-      <c r="D123" s="298"/>
-      <c r="E123" s="298"/>
-      <c r="F123" s="298"/>
-      <c r="G123" s="298"/>
-      <c r="H123" s="298"/>
-      <c r="I123" s="298"/>
-      <c r="J123" s="298"/>
-      <c r="K123" s="298"/>
-      <c r="L123" s="298"/>
-      <c r="M123" s="298"/>
+      <c r="A123" s="296"/>
+      <c r="B123" s="296"/>
+      <c r="C123" s="296"/>
+      <c r="D123" s="296"/>
+      <c r="E123" s="296"/>
+      <c r="F123" s="296"/>
+      <c r="G123" s="296"/>
+      <c r="H123" s="296"/>
+      <c r="I123" s="296"/>
+      <c r="J123" s="296"/>
+      <c r="K123" s="296"/>
+      <c r="L123" s="296"/>
+      <c r="M123" s="296"/>
       <c r="N123" s="51"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A124" s="298"/>
-      <c r="B124" s="298"/>
-      <c r="C124" s="298"/>
-      <c r="D124" s="298"/>
-      <c r="E124" s="298"/>
-      <c r="F124" s="298"/>
-      <c r="G124" s="298"/>
-      <c r="H124" s="298"/>
-      <c r="I124" s="298"/>
-      <c r="J124" s="298"/>
-      <c r="K124" s="298"/>
-      <c r="L124" s="298"/>
-      <c r="M124" s="298"/>
+      <c r="A124" s="296"/>
+      <c r="B124" s="296"/>
+      <c r="C124" s="296"/>
+      <c r="D124" s="296"/>
+      <c r="E124" s="296"/>
+      <c r="F124" s="296"/>
+      <c r="G124" s="296"/>
+      <c r="H124" s="296"/>
+      <c r="I124" s="296"/>
+      <c r="J124" s="296"/>
+      <c r="K124" s="296"/>
+      <c r="L124" s="296"/>
+      <c r="M124" s="296"/>
       <c r="N124" s="51"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A125" s="298"/>
-      <c r="B125" s="298"/>
-      <c r="C125" s="298"/>
-      <c r="D125" s="298"/>
-      <c r="E125" s="298"/>
-      <c r="F125" s="298"/>
+      <c r="A125" s="296"/>
+      <c r="B125" s="296"/>
+      <c r="C125" s="296"/>
+      <c r="D125" s="296"/>
+      <c r="E125" s="296"/>
+      <c r="F125" s="296"/>
       <c r="G125" s="50"/>
-      <c r="H125" s="298"/>
-      <c r="I125" s="298"/>
-      <c r="J125" s="298"/>
-      <c r="K125" s="298"/>
-      <c r="L125" s="298"/>
-      <c r="M125" s="298"/>
+      <c r="H125" s="296"/>
+      <c r="I125" s="296"/>
+      <c r="J125" s="296"/>
+      <c r="K125" s="296"/>
+      <c r="L125" s="296"/>
+      <c r="M125" s="296"/>
       <c r="N125" s="51"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
